--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -1006,10 +1006,10 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="F3" t="n">
-        <v>64.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 68.9; priority 64.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 68.8; priority 64.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>28.94</v>
+        <v>29.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.02</v>
+        <v>40.18</v>
       </c>
       <c r="AA3" t="n">
         <v>21.32</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>17.69</v>
+        <v>17.71</v>
       </c>
       <c r="AH3" t="n">
         <v>51.3</v>
@@ -1130,25 +1130,25 @@
         <v>45.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AM3" t="n">
-        <v>26.88</v>
+        <v>27.03</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.88</v>
+        <v>17.92</v>
       </c>
       <c r="AO3" t="n">
         <v>0.84</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.1688</v>
+        <v>16.1692</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.4672</v>
+        <v>14.4673</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
@@ -1161,7 +1161,7 @@
         <v>50.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="AW3" t="n">
         <v>756</v>
@@ -1173,10 +1173,10 @@
         <v>18.17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.41</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>22.28</v>
+        <v>22.41</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
       <c r="Z9" t="n">
-        <v>-15.26</v>
+        <v>-15.25</v>
       </c>
       <c r="AA9" t="n">
         <v>33.93</v>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>26.875</v>
+        <v>26.88</v>
       </c>
       <c r="AH9" t="n">
         <v>22.4</v>
@@ -2442,13 +2442,13 @@
         <v>15.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="AL9" t="n">
-        <v>11.51</v>
+        <v>11.54</v>
       </c>
       <c r="AM9" t="n">
-        <v>-7.46</v>
+        <v>-7.44</v>
       </c>
       <c r="AN9" t="n">
         <v>-1.98</v>
@@ -2457,7 +2457,7 @@
         <v>-0.06</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.2645</v>
+        <v>24.2646</v>
       </c>
       <c r="AQ9" t="n">
         <v>26.9667</v>
@@ -2473,7 +2473,7 @@
         <v>20.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="AW9" t="n">
         <v>757</v>
@@ -2485,10 +2485,10 @@
         <v>30.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.76</v>
+        <v>10.78</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="F10" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 62.0; priority 19.8; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 62.1; priority 20.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 18.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 18.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.3%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.2%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1527.80 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1526.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>1109.5466</v>
       </c>
       <c r="T10" t="n">
-        <v>1527.8</v>
+        <v>1526.2</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>33.42</v>
+        <v>33.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>127.61</v>
+        <v>127.37</v>
       </c>
       <c r="AA10" t="n">
         <v>38.1</v>
@@ -2624,10 +2624,10 @@
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.99</v>
+        <v>58.93</v>
       </c>
       <c r="AD10" t="n">
-        <v>36.85</v>
+        <v>36.81</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1527.8</v>
+        <v>1526.2</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>17.02</v>
+        <v>16.9</v>
       </c>
       <c r="AM10" t="n">
-        <v>61.12</v>
+        <v>60.95</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.55</v>
+        <v>32.51</v>
       </c>
       <c r="AO10" t="n">
         <v>0.85</v>
       </c>
       <c r="AP10" t="n">
-        <v>1291.6841</v>
+        <v>1291.6521</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1052.314</v>
+        <v>1052.306</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2671,7 +2671,7 @@
         <v>18.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>25.6</v>
+        <v>26.1</v>
       </c>
       <c r="AW10" t="n">
         <v>765</v>
@@ -2680,13 +2680,13 @@
         <v>1249</v>
       </c>
       <c r="AY10" t="n">
-        <v>1527.8</v>
+        <v>1526.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.28</v>
+        <v>18.16</v>
       </c>
       <c r="BA10" t="n">
-        <v>45.18</v>
+        <v>45.03</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>588841156608</v>
+        <v>588224397312</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="BM10" t="n">
         <v>18.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>25.6</v>
+        <v>26.1</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -3403,7 +3403,7 @@
         <v>76.40000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 76.4; priority 76.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.4; priority 76.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>10.53</v>
+        <v>10.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.3</v>
+        <v>24.23</v>
       </c>
       <c r="AA14" t="n">
         <v>12.86</v>
@@ -3512,50 +3512,50 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>161.82</v>
+        <v>161.72</v>
       </c>
       <c r="AH14" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="AJ14" t="n">
         <v>67.7</v>
       </c>
       <c r="AK14" t="n">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AM14" t="n">
-        <v>12.17</v>
+        <v>12.1</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.23</v>
+        <v>17.21</v>
       </c>
       <c r="AO14" t="n">
         <v>1.34</v>
       </c>
       <c r="AP14" t="n">
-        <v>155.4296</v>
+        <v>155.4276</v>
       </c>
       <c r="AQ14" t="n">
-        <v>146.7653</v>
+        <v>146.7648</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="AU14" t="n">
         <v>67.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AW14" t="n">
         <v>759</v>
@@ -3567,10 +3567,10 @@
         <v>164.88</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.26</v>
+        <v>10.19</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.31</v>
+        <v>22.29</v>
       </c>
       <c r="AA15" t="n">
         <v>13.13</v>
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>122.52</v>
+        <v>122.5</v>
       </c>
       <c r="AH15" t="n">
         <v>71.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="AJ15" t="n">
         <v>66.90000000000001</v>
@@ -3733,10 +3733,10 @@
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AM15" t="n">
-        <v>10.34</v>
+        <v>10.32</v>
       </c>
       <c r="AN15" t="n">
         <v>17.12</v>
@@ -3745,17 +3745,17 @@
         <v>1.3</v>
       </c>
       <c r="AP15" t="n">
-        <v>117.9804</v>
+        <v>117.98</v>
       </c>
       <c r="AQ15" t="n">
-        <v>112.2004</v>
+        <v>112.2003</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="AU15" t="n">
         <v>66.90000000000001</v>
@@ -3773,10 +3773,10 @@
         <v>124.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.5%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>11.21</v>
+        <v>11.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.57</v>
+        <v>23.52</v>
       </c>
       <c r="AA17" t="n">
         <v>14.09</v>
@@ -4130,50 +4130,50 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>692.16</v>
+        <v>691.88</v>
       </c>
       <c r="AH17" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="AI17" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="AJ17" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AM17" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.37</v>
+        <v>18.36</v>
       </c>
       <c r="AO17" t="n">
         <v>1.3</v>
       </c>
       <c r="AP17" t="n">
-        <v>662.6624</v>
+        <v>662.6568</v>
       </c>
       <c r="AQ17" t="n">
-        <v>629.9932</v>
+        <v>629.9918</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="AU17" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AW17" t="n">
         <v>759</v>
@@ -4185,10 +4185,10 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.869999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 5.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.2%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 360.75 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 360.85 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>360.75</v>
+        <v>360.85</v>
       </c>
       <c r="T22" t="n">
         <v>424.57</v>
@@ -5188,16 +5188,16 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-14.83</v>
+        <v>-14.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>27.63</v>
+        <v>27.66</v>
       </c>
       <c r="AA22" t="n">
         <v>17.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>-17.33</v>
+        <v>-17.31</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>360.75</v>
+        <v>360.85</v>
       </c>
       <c r="AH22" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="AJ22" t="n">
         <v>64.8</v>
@@ -5227,29 +5227,29 @@
         <v>67.40000000000001</v>
       </c>
       <c r="AL22" t="n">
-        <v>-6.67</v>
+        <v>-6.65</v>
       </c>
       <c r="AM22" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.96</v>
+        <v>26.97</v>
       </c>
       <c r="AO22" t="n">
         <v>1.52</v>
       </c>
       <c r="AP22" t="n">
-        <v>380.8004</v>
+        <v>380.8024</v>
       </c>
       <c r="AQ22" t="n">
-        <v>362.171</v>
+        <v>362.1715</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="AU22" t="n">
         <v>64.8</v>
@@ -5261,16 +5261,16 @@
         <v>756</v>
       </c>
       <c r="AX22" t="n">
-        <v>360.75</v>
+        <v>360.85</v>
       </c>
       <c r="AY22" t="n">
         <v>386.38</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-5.27</v>
+        <v>-5.24</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0.39</v>
+        <v>-0.36</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -766,24 +766,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>66.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>66.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +793,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 66.8; priority 66.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 69.6; priority 68.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,22 +808,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 199.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -837,156 +833,136 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>199.34</v>
+        <v>12.936</v>
       </c>
       <c r="T2" t="n">
-        <v>274.99</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Amazon.com, Inc.</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>18.17</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>14.86</v>
+        <v>27.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.95</v>
+        <v>38.29</v>
       </c>
       <c r="AA2" t="n">
-        <v>30.99</v>
+        <v>21.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>-30.88</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>24.86</v>
-      </c>
+        <v>-29.37</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Robotica e automazione</t>
+        </is>
+      </c>
       <c r="AG2" t="n">
-        <v>245.22</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+        <v>17.472</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>66.40000000000001</v>
+      </c>
       <c r="AL2" t="n">
-        <v>-9.57</v>
+        <v>-0.31</v>
       </c>
       <c r="AM2" t="n">
-        <v>7.03</v>
+        <v>25.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.9</v>
+        <v>17.39</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="AP2" t="n">
-        <v>251.9112</v>
+        <v>16.1644</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.2354</v>
+        <v>14.4661</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT2" t="n">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="AU2" t="n">
-        <v>38.1</v>
+        <v>50.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>75.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AX2" t="n">
-        <v>245.22</v>
+        <v>16.544</v>
       </c>
       <c r="AY2" t="n">
-        <v>274</v>
+        <v>18.17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-2.66</v>
+        <v>8.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>Internet Retail</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>2637858340864</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>53.3</v>
-      </c>
+        <v>20.78</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>75.8</v>
-      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>USA / Consumer &amp; Cloud</t>
-        </is>
-      </c>
+      <c r="BP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -996,20 +972,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>68.8</v>
+        <v>66.3</v>
       </c>
       <c r="F3" t="n">
-        <v>64.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1003,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 68.8; priority 64.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 66.3; priority 65.9; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1038,22 +1018,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.2%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 199.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1063,136 +1043,156 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>12.936</v>
+        <v>199.34</v>
       </c>
       <c r="T3" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>274.99</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>29.08</v>
+        <v>14.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.18</v>
+        <v>14.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.32</v>
+        <v>30.97</v>
       </c>
       <c r="AB3" t="n">
-        <v>-29.37</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+        <v>-30.88</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>24.82</v>
+      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Robotica e automazione</t>
-        </is>
-      </c>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>60.6</v>
-      </c>
+        <v>244.772</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>1.05</v>
+        <v>-10.23</v>
       </c>
       <c r="AM3" t="n">
-        <v>27.03</v>
+        <v>6.64</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.92</v>
+        <v>25.79</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.1692</v>
+        <v>252.8198</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.4673</v>
+        <v>232.3495</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT3" t="n">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>50.9</v>
+        <v>38.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>60.6</v>
+        <v>75</v>
       </c>
       <c r="AW3" t="n">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="AX3" t="n">
-        <v>16.544</v>
+        <v>244.772</v>
       </c>
       <c r="AY3" t="n">
-        <v>18.17</v>
+        <v>274</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.529999999999999</v>
+        <v>-3.18</v>
       </c>
       <c r="BA3" t="n">
-        <v>22.41</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+        <v>5.35</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Internet Retail</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>2633039347712</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>53.3</v>
+      </c>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+      <c r="BJ3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>75</v>
+      </c>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>USA / Consumer &amp; Cloud</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65.5</v>
+        <v>63.8</v>
       </c>
       <c r="F4" t="n">
-        <v>61.6</v>
+        <v>59.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 65.5; priority 61.6; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 63.8; priority 59.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 65.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>0.79</v>
+        <v>0.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>-11.26</v>
+        <v>-12.86</v>
       </c>
       <c r="AA4" t="n">
         <v>23.97</v>
@@ -1312,57 +1312,57 @@
         <v>-33.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>24.51</v>
+        <v>24.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>21.29</v>
+        <v>21.02</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>411.74</v>
+        <v>406.635</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-1.93</v>
+        <v>-1.83</v>
       </c>
       <c r="AM4" t="n">
-        <v>-13.99</v>
+        <v>-15.46</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.91</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AP4" t="n">
-        <v>408.6026</v>
+        <v>409.6153</v>
       </c>
       <c r="AQ4" t="n">
-        <v>453.9891</v>
+        <v>453.517</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AT4" t="n">
-        <v>39.9</v>
+        <v>38.1</v>
       </c>
       <c r="AU4" t="n">
         <v>44.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>78.2</v>
+        <v>74.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX4" t="n">
         <v>404.3343</v>
@@ -1371,10 +1371,10 @@
         <v>460.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.77</v>
+        <v>-0.73</v>
       </c>
       <c r="BA4" t="n">
-        <v>-9.31</v>
+        <v>-10.34</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>3058583732224</v>
+        <v>3020624494592</v>
       </c>
       <c r="BE4" t="n">
         <v>39.34</v>
@@ -1408,16 +1408,16 @@
         <v>100</v>
       </c>
       <c r="BK4" t="n">
-        <v>39.9</v>
+        <v>38.1</v>
       </c>
       <c r="BL4" t="n">
-        <v>69.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="BM4" t="n">
         <v>44.1</v>
       </c>
       <c r="BN4" t="n">
-        <v>78.2</v>
+        <v>74.2</v>
       </c>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
@@ -1444,10 +1444,10 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>64.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 64.3; priority 58.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 64.1; priority 58.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>20.41</v>
+        <v>17.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>66.43000000000001</v>
+        <v>61.96</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.17</v>
+        <v>23.22</v>
       </c>
       <c r="AB5" t="n">
         <v>-44.26</v>
@@ -1556,37 +1556,37 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>10.572</v>
+        <v>10.288</v>
       </c>
       <c r="AH5" t="n">
-        <v>31.2</v>
+        <v>30.4</v>
       </c>
       <c r="AI5" t="n">
         <v>100</v>
       </c>
       <c r="AJ5" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="AK5" t="n">
         <v>82.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.19</v>
+        <v>-3.84</v>
       </c>
       <c r="AM5" t="n">
-        <v>29.13</v>
+        <v>25.66</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.1817</v>
+        <v>10.176</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.756500000000001</v>
+        <v>8.755100000000001</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
@@ -1596,7 +1596,7 @@
         <v>100</v>
       </c>
       <c r="AU5" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="AV5" t="n">
         <v>82.8</v>
@@ -1611,10 +1611,10 @@
         <v>11.61</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.83</v>
+        <v>1.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>20.73</v>
+        <v>17.51</v>
       </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="F6" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 59.4; priority 39.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 59.5; priority 40.2; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 5.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-9.5</v>
+        <v>-9.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>-14.23</v>
+        <v>-14.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.3</v>
+        <v>36.28</v>
       </c>
       <c r="AB6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.28</v>
+        <v>21.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.19</v>
+        <v>16.4</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1762,29 +1762,29 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>585.39</v>
+        <v>593.12</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-5.09</v>
+        <v>-2.71</v>
       </c>
       <c r="AM6" t="n">
-        <v>-11.36</v>
+        <v>-11.78</v>
       </c>
       <c r="AN6" t="n">
-        <v>30.82</v>
+        <v>31.35</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AP6" t="n">
-        <v>620.2773999999999</v>
+        <v>621.6254</v>
       </c>
       <c r="AQ6" t="n">
-        <v>660.9453</v>
+        <v>660.2241</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
@@ -1797,10 +1797,10 @@
         <v>29.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>66.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX6" t="n">
         <v>585.39</v>
@@ -1809,10 +1809,10 @@
         <v>635.29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-5.62</v>
+        <v>-4.59</v>
       </c>
       <c r="BA6" t="n">
-        <v>-11.43</v>
+        <v>-10.16</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1485967589376</v>
+        <v>1505462714368</v>
       </c>
       <c r="BE6" t="n">
         <v>32.84</v>
@@ -1849,13 +1849,13 @@
         <v>26.3</v>
       </c>
       <c r="BL6" t="n">
-        <v>80.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="BM6" t="n">
         <v>29.1</v>
       </c>
       <c r="BN6" t="n">
-        <v>66.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41.3</v>
+        <v>39.5</v>
       </c>
       <c r="F7" t="n">
-        <v>34.9</v>
+        <v>33</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 41.3; priority 34.9; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 39.5; priority 33.0; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 41.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.3%.</t>
+          <t>TSLA: scenario base High Risk, score 39.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1970,22 +1970,22 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>2.58</v>
+        <v>-0.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>43.64</v>
+        <v>35.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>57.95</v>
+        <v>57.93</v>
       </c>
       <c r="AB7" t="n">
         <v>-53.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>371.77</v>
+        <v>362.82</v>
       </c>
       <c r="AD7" t="n">
-        <v>163.28</v>
+        <v>159.35</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1994,36 +1994,36 @@
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>408.95</v>
+        <v>399.105</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-6.83</v>
       </c>
       <c r="AM7" t="n">
-        <v>-10.03</v>
+        <v>-12.28</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.86</v>
+        <v>17.86</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AP7" t="n">
-        <v>396.0254</v>
+        <v>396.7709</v>
       </c>
       <c r="AQ7" t="n">
-        <v>414.5671</v>
+        <v>414.9621</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
         <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>58.5</v>
+        <v>51.4</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>78.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX7" t="n">
         <v>391</v>
@@ -2041,10 +2041,10 @@
         <v>445.27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.26</v>
+        <v>0.59</v>
       </c>
       <c r="BA7" t="n">
-        <v>-1.35</v>
+        <v>-3.82</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1535903268864</v>
+        <v>1498928119808</v>
       </c>
       <c r="BE7" t="n">
         <v>3.95</v>
@@ -2076,7 +2076,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>58.5</v>
+        <v>51.4</v>
       </c>
       <c r="BL7" t="n">
         <v>0</v>
@@ -2112,10 +2112,10 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>61.9</v>
+        <v>63.3</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>32.6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 61.9; priority 25.0; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 63.3; priority 32.6; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo 17.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 14.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 61.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.0%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.5%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>51.67</v>
+        <v>48.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>138.77</v>
+        <v>134.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>34.92</v>
+        <v>34.91</v>
       </c>
       <c r="AB8" t="n">
         <v>-35.74</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>598.16</v>
+        <v>590.2506</v>
       </c>
       <c r="AH8" t="n">
-        <v>58.7</v>
+        <v>58.2</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
@@ -2236,25 +2236,25 @@
         <v>24.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>30.8</v>
+        <v>40.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>10.75</v>
+        <v>4.19</v>
       </c>
       <c r="AM8" t="n">
-        <v>65.94</v>
+        <v>62.47</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.94</v>
+        <v>60.12</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AP8" t="n">
-        <v>511.287</v>
+        <v>515.607</v>
       </c>
       <c r="AQ8" t="n">
-        <v>397.8009</v>
+        <v>399.3193</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
@@ -2267,10 +2267,10 @@
         <v>29.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>30.8</v>
+        <v>40.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX8" t="n">
         <v>543.96</v>
@@ -2279,10 +2279,10 @@
         <v>637.9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.99</v>
+        <v>14.48</v>
       </c>
       <c r="BA8" t="n">
-        <v>50.37</v>
+        <v>47.81</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="F9" t="n">
-        <v>21.9</v>
+        <v>25.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 37.7; priority 21.9; trend: Recovery; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 37.8; priority 25.1; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 10.8% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 37.7, trend Recovery. Entry zone: Extended - wait pullback. Distanza da MA50: 10.8%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 37.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>7.69</v>
+        <v>6.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>-15.25</v>
+        <v>-16.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>33.93</v>
+        <v>33.95</v>
       </c>
       <c r="AB9" t="n">
         <v>-48.6</v>
@@ -2430,50 +2430,50 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>26.88</v>
+        <v>26.56</v>
       </c>
       <c r="AH9" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>52.5</v>
+        <v>49.8</v>
       </c>
       <c r="AJ9" t="n">
         <v>15.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>51.1</v>
+        <v>56.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>11.54</v>
+        <v>10.21</v>
       </c>
       <c r="AM9" t="n">
-        <v>-7.44</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1.98</v>
+        <v>-2.37</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.2646</v>
+        <v>24.2582</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26.9667</v>
+        <v>26.9651</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
         <v>55</v>
       </c>
       <c r="AT9" t="n">
-        <v>52.5</v>
+        <v>49.8</v>
       </c>
       <c r="AU9" t="n">
         <v>20.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>51.1</v>
+        <v>56.3</v>
       </c>
       <c r="AW9" t="n">
         <v>757</v>
@@ -2485,10 +2485,10 @@
         <v>30.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.78</v>
+        <v>9.49</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.32</v>
+        <v>-1.5</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62.1</v>
+        <v>61.6</v>
       </c>
       <c r="F10" t="n">
-        <v>20.2</v>
+        <v>17</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 62.1; priority 20.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 61.6; priority 17.0; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 18.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 19.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 18.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 61.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.2%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1526.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1539.80 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>1109.5466</v>
       </c>
       <c r="T10" t="n">
-        <v>1526.2</v>
+        <v>1539.8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>33.28</v>
+        <v>34.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>127.37</v>
+        <v>129.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.1</v>
+        <v>38.11</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.93</v>
+        <v>59.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>36.81</v>
+        <v>37.14</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1526.2</v>
+        <v>1539.8</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>16.9</v>
+        <v>17.94</v>
       </c>
       <c r="AM10" t="n">
-        <v>60.95</v>
+        <v>62.39</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.51</v>
+        <v>32.89</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AP10" t="n">
-        <v>1291.6521</v>
+        <v>1291.9241</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1052.306</v>
+        <v>1052.374</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2668,10 +2668,10 @@
         <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>26.1</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>765</v>
@@ -2680,13 +2680,13 @@
         <v>1249</v>
       </c>
       <c r="AY10" t="n">
-        <v>1526.2</v>
+        <v>1539.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.16</v>
+        <v>19.19</v>
       </c>
       <c r="BA10" t="n">
-        <v>45.03</v>
+        <v>46.32</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>588224397312</v>
+        <v>593466163200</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="BM10" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>26.1</v>
+        <v>22</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2756,10 +2756,10 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>79.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>79.7</v>
+        <v>80.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 79.4; priority 79.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 79.0; priority 80.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.3%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>16.2</v>
+        <v>14.47</v>
       </c>
       <c r="Z11" t="n">
-        <v>43</v>
+        <v>40.87</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.01</v>
+        <v>15.98</v>
       </c>
       <c r="AB11" t="n">
         <v>-19.17</v>
@@ -2868,50 +2868,50 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>47.305</v>
+        <v>46.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>69</v>
+        <v>68.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>98.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AJ11" t="n">
         <v>65.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>77.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2</v>
+        <v>-1.29</v>
       </c>
       <c r="AM11" t="n">
-        <v>24.96</v>
+        <v>23.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.61</v>
+        <v>18.02</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AP11" t="n">
-        <v>44.9277</v>
+        <v>44.9136</v>
       </c>
       <c r="AQ11" t="n">
-        <v>40.3702</v>
+        <v>40.3666</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
         <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>98.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AU11" t="n">
         <v>65.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>77.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AW11" t="n">
         <v>756</v>
@@ -2923,10 +2923,10 @@
         <v>49.485</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.29</v>
+        <v>3.75</v>
       </c>
       <c r="BA11" t="n">
-        <v>17.18</v>
+        <v>15.44</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2947,69 +2947,73 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3. Interessanti ma da attendere</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>79.2</v>
+        <v>80.2</v>
       </c>
       <c r="F12" t="n">
-        <v>65.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🟠 Attendi pullback</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Non inseguire il prezzo: imposta alert su pullback o tenuta supporto. Supporto 60D: 54.81.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 79.2; priority 65.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Normal risk</t>
+          <t>score 80.2; priority 77.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3019,7 +3023,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -3028,83 +3032,71 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>54.81</v>
+        <v>273.3367</v>
       </c>
       <c r="T12" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>28.08</v>
+        <v>18.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>62.01</v>
+        <v>110.08</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.61</v>
+        <v>29.71</v>
       </c>
       <c r="AB12" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>25.13</v>
+      </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>Value globale</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
-        <v>70.93000000000001</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>51.8</v>
-      </c>
+        <v>363.385</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>6.97</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AM12" t="n">
-        <v>38.43</v>
+        <v>13.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.9</v>
+        <v>44.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>63.482</v>
+        <v>357.7259</v>
       </c>
       <c r="AQ12" t="n">
-        <v>54.8732</v>
+        <v>305.2903</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
@@ -3114,41 +3106,75 @@
         <v>100</v>
       </c>
       <c r="AU12" t="n">
-        <v>69.40000000000001</v>
+        <v>40.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>51.8</v>
+        <v>82.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="AX12" t="n">
-        <v>65.27</v>
+        <v>358.7757</v>
       </c>
       <c r="AY12" t="n">
-        <v>72.27</v>
+        <v>402.3797</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.73</v>
+        <v>1.58</v>
       </c>
       <c r="BA12" t="n">
-        <v>29.26</v>
-      </c>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
+        <v>19.03</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>4431456239616</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3158,24 +3184,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>80.2</v>
+        <v>75.8</v>
       </c>
       <c r="F13" t="n">
-        <v>77.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3184,22 +3206,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 80.2; priority 77.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 75.8; priority 76.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3209,17 +3231,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.1%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3229,7 +3251,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3238,149 +3260,127 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>273.3367</v>
+        <v>140.98</v>
       </c>
       <c r="T13" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+        <v>164.88</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>18.66</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>116.86</v>
+        <v>23.31</v>
       </c>
       <c r="AA13" t="n">
-        <v>29.73</v>
+        <v>12.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>27.69</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>25.12</v>
-      </c>
+        <v>-21.07</v>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Azionario globale</t>
+        </is>
+      </c>
       <c r="AG13" t="n">
-        <v>363.31</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+        <v>160.52</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL13" t="n">
-        <v>-8.66</v>
+        <v>1.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>14.61</v>
+        <v>11.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.56</v>
+        <v>16.92</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AP13" t="n">
-        <v>355.9417</v>
+        <v>155.4036</v>
       </c>
       <c r="AQ13" t="n">
-        <v>304.4693</v>
+        <v>146.7588</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>100</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>40.5</v>
+        <v>67.7</v>
       </c>
       <c r="AV13" t="n">
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="AX13" t="n">
-        <v>358.7757</v>
+        <v>158.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>402.3797</v>
+        <v>164.88</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.07</v>
+        <v>3.29</v>
       </c>
       <c r="BA13" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>4430541881344</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>82.8</v>
-      </c>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3390,20 +3390,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>76.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>76.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 76.4; priority 76.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.9; priority 75.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.2%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3466,15 +3466,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>140.98</v>
+        <v>107.5</v>
       </c>
       <c r="T14" t="n">
-        <v>164.88</v>
+        <v>124.27</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3488,16 +3488,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>10.46</v>
+        <v>9.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.23</v>
+        <v>21.51</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.86</v>
+        <v>13.14</v>
       </c>
       <c r="AB14" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3508,69 +3508,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>161.72</v>
+        <v>121.72</v>
       </c>
       <c r="AH14" t="n">
-        <v>72.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AJ14" t="n">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK14" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AM14" t="n">
-        <v>12.1</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.21</v>
+        <v>16.87</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AP14" t="n">
-        <v>155.4276</v>
+        <v>117.9644</v>
       </c>
       <c r="AQ14" t="n">
-        <v>146.7648</v>
+        <v>112.1964</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AU14" t="n">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="AX14" t="n">
-        <v>158.2</v>
+        <v>120.3</v>
       </c>
       <c r="AY14" t="n">
-        <v>164.88</v>
+        <v>124.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.05</v>
+        <v>3.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.19</v>
+        <v>8.49</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3596,21 +3596,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="F15" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="F15" t="n">
-        <v>76</v>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>🟡 Metti alert / monitora</t>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 75.4; priority 76.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.7; priority 75.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3643,17 +3643,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3672,15 +3672,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>107.5</v>
+        <v>597.92</v>
       </c>
       <c r="T15" t="n">
-        <v>124.27</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>9.85</v>
+        <v>10.53</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.29</v>
+        <v>22.81</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.13</v>
+        <v>14.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>-21.63</v>
+        <v>-23.32</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3714,69 +3714,69 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>122.5</v>
+        <v>687.92</v>
       </c>
       <c r="AH15" t="n">
-        <v>71.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>75.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK15" t="n">
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="AM15" t="n">
-        <v>10.32</v>
+        <v>9.42</v>
       </c>
       <c r="AN15" t="n">
-        <v>17.12</v>
+        <v>18.13</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AP15" t="n">
-        <v>117.98</v>
+        <v>662.5776</v>
       </c>
       <c r="AQ15" t="n">
-        <v>112.2003</v>
+        <v>629.972</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>75.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV15" t="n">
         <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="AX15" t="n">
-        <v>120.3</v>
+        <v>680.66</v>
       </c>
       <c r="AY15" t="n">
-        <v>124.27</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="F16" t="n">
-        <v>75.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 74.5; priority 75.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.3; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.8</v>
+        <v>15.47</v>
       </c>
       <c r="AA16" t="n">
         <v>12.85</v>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>62.85</v>
+        <v>62.67</v>
       </c>
       <c r="AH16" t="n">
         <v>70.09999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>69.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>71.5</v>
@@ -3939,29 +3939,29 @@
         <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>10.5</v>
+        <v>10.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.81</v>
+        <v>13.7</v>
       </c>
       <c r="AO16" t="n">
         <v>1.07</v>
       </c>
       <c r="AP16" t="n">
-        <v>61.3448</v>
+        <v>61.3412</v>
       </c>
       <c r="AQ16" t="n">
-        <v>58.5815</v>
+        <v>58.5806</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>69.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>71.5</v>
@@ -3979,10 +3979,10 @@
         <v>63.94</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.29</v>
+        <v>6.98</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4008,20 +4008,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>74.8</v>
+        <v>72.5</v>
       </c>
       <c r="F17" t="n">
-        <v>75.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 74.8; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 72.5; priority 74.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4055,17 +4055,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4084,38 +4084,38 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>597.92</v>
+        <v>66.58</v>
       </c>
       <c r="T17" t="n">
-        <v>703.9400000000001</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>11.16</v>
+        <v>7.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.52</v>
+        <v>17.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>14.09</v>
+        <v>12.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>-23.32</v>
+        <v>-20.6</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
@@ -4126,69 +4126,69 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>691.88</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AH17" t="n">
-        <v>70.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>77.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>81.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AM17" t="n">
-        <v>10.05</v>
+        <v>9.42</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.36</v>
+        <v>14.94</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AP17" t="n">
-        <v>662.6568</v>
+        <v>71.9044</v>
       </c>
       <c r="AQ17" t="n">
-        <v>629.9918</v>
+        <v>68.7041</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>77.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>81.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="AX17" t="n">
-        <v>680.66</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>703.9400000000001</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.41</v>
+        <v>3.05</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.82</v>
+        <v>7.85</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4214,20 +4214,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>72.8</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>74.3</v>
+        <v>72.2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4236,42 +4240,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 72.8; priority 74.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.0; priority 72.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 73.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4290,127 +4294,149 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>66.58</v>
+        <v>246.403</v>
       </c>
       <c r="T18" t="n">
-        <v>74.95999999999999</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>7.49</v>
+        <v>12.55</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.12</v>
+        <v>44.39</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.86</v>
+        <v>25.94</v>
       </c>
       <c r="AB18" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>30.52</v>
+      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Quality globale</t>
-        </is>
-      </c>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>74.33</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>82.8</v>
-      </c>
+        <v>293.285</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>2.65</v>
+        <v>0.08</v>
       </c>
       <c r="AM18" t="n">
-        <v>9.76</v>
+        <v>5.4</v>
       </c>
       <c r="AN18" t="n">
-        <v>15.06</v>
+        <v>18.11</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.17</v>
+        <v>0.7</v>
       </c>
       <c r="AP18" t="n">
-        <v>71.90900000000001</v>
+        <v>282.9571</v>
       </c>
       <c r="AQ18" t="n">
-        <v>68.70529999999999</v>
+        <v>265.4899</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>70.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>68.09999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="AV18" t="n">
         <v>82.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="AX18" t="n">
-        <v>72.59999999999999</v>
+        <v>293.285</v>
       </c>
       <c r="AY18" t="n">
-        <v>74.95999999999999</v>
+        <v>315.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
-      <c r="BM18" t="inlineStr"/>
-      <c r="BN18" t="inlineStr"/>
+        <v>10.47</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>4307581140992</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4420,24 +4446,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>73.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>70.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4446,12 +4468,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 10.0% sopra MA50: evitare inseguimento.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 73.4; priority 70.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 80.0; priority 70.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4461,27 +4483,27 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 10.0% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.0%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4491,7 +4513,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -4500,149 +4522,127 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>246.403</v>
+        <v>54.81</v>
       </c>
       <c r="T19" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+        <v>72.27</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>16.14</v>
+        <v>26.04</v>
       </c>
       <c r="Z19" t="n">
-        <v>50.89</v>
+        <v>59.43</v>
       </c>
       <c r="AA19" t="n">
-        <v>25.91</v>
+        <v>13.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>-33.36</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>36.51</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>31.38</v>
-      </c>
+        <v>-17.8</v>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Value globale</t>
+        </is>
+      </c>
       <c r="AG19" t="n">
-        <v>301.54</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
+        <v>69.8</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>58.8</v>
+      </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>5.26</v>
       </c>
       <c r="AM19" t="n">
-        <v>7.62</v>
+        <v>36.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>19.25</v>
+        <v>25.23</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.74</v>
+        <v>1.85</v>
       </c>
       <c r="AP19" t="n">
-        <v>282.0628</v>
+        <v>63.4594</v>
       </c>
       <c r="AQ19" t="n">
-        <v>265.1448</v>
+        <v>54.8676</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>89.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AU19" t="n">
-        <v>42.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>71.09999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AX19" t="n">
-        <v>292.68</v>
+        <v>65.27</v>
       </c>
       <c r="AY19" t="n">
-        <v>315.2</v>
+        <v>72.27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.91</v>
+        <v>9.99</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.73</v>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>4428825362432</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>41</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>71.09999999999999</v>
-      </c>
+        <v>27.22</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4662,10 +4662,10 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="F20" t="n">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 68.2; priority 70.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 68.3; priority 70.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -4750,13 +4750,13 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>-1.95</v>
+        <v>-1.77</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.28</v>
+        <v>0.47</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB20" t="n">
         <v>-12.85</v>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>63.74</v>
+        <v>63.86</v>
       </c>
       <c r="AH20" t="n">
         <v>61.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
       <c r="AJ20" t="n">
         <v>78.3</v>
@@ -4789,29 +4789,29 @@
         <v>82.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.57</v>
+        <v>6.64</v>
       </c>
       <c r="AO20" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.3206</v>
+        <v>63.323</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.1004</v>
+        <v>63.101</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
       <c r="AU20" t="n">
         <v>78.3</v>
@@ -4829,10 +4829,10 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>74.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>58.1</v>
+        <v>56.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 74.8; priority 58.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 73.6; priority 56.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 73.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>14.37</v>
+        <v>11.59</v>
       </c>
       <c r="Z21" t="n">
-        <v>49.25</v>
+        <v>45.52</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.98</v>
+        <v>46.96</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>31.95</v>
+        <v>31.54</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.45</v>
+        <v>16.24</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,36 +4980,36 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>208.64</v>
+        <v>205.94</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-1.24</v>
+        <v>-4.19</v>
       </c>
       <c r="AM21" t="n">
-        <v>13.91</v>
+        <v>13.04</v>
       </c>
       <c r="AN21" t="n">
-        <v>76.01000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AP21" t="n">
-        <v>203.972</v>
+        <v>204.7443</v>
       </c>
       <c r="AQ21" t="n">
-        <v>188.512</v>
+        <v>188.668</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
         <v>85</v>
       </c>
       <c r="AT21" t="n">
-        <v>90.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AU21" t="n">
         <v>14.1</v>
@@ -5018,7 +5018,7 @@
         <v>82.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX21" t="n">
         <v>205.1</v>
@@ -5027,10 +5027,10 @@
         <v>235.4656</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.29</v>
+        <v>0.57</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.68</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>5053469425664</v>
+        <v>4988072886272</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5064,10 +5064,10 @@
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>90.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="BL21" t="n">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="BM21" t="n">
         <v>14.1</v>
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>55.6</v>
+        <v>54.5</v>
       </c>
       <c r="F22" t="n">
-        <v>57.4</v>
+        <v>56.1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 55.6; priority 57.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 54.5; priority 56.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 5.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.2%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.1%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 360.85 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 357.35 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>360.85</v>
+        <v>357.35</v>
       </c>
       <c r="T22" t="n">
         <v>424.57</v>
@@ -5184,20 +5184,20 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-14.8</v>
+        <v>-15.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>27.66</v>
+        <v>26.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>-17.31</v>
+        <v>-18.11</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,65 +5212,65 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>360.85</v>
+        <v>357.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>70.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="AI22" t="n">
-        <v>38.6</v>
+        <v>36.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>64.8</v>
+        <v>64.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>67.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="AL22" t="n">
-        <v>-6.65</v>
+        <v>-7.55</v>
       </c>
       <c r="AM22" t="n">
-        <v>4.01</v>
+        <v>3</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.97</v>
+        <v>26.56</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AP22" t="n">
-        <v>380.8024</v>
+        <v>380.7324</v>
       </c>
       <c r="AQ22" t="n">
-        <v>362.1715</v>
+        <v>362.154</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>38.6</v>
+        <v>36.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>64.8</v>
+        <v>64.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>67.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="AW22" t="n">
         <v>756</v>
       </c>
       <c r="AX22" t="n">
-        <v>360.85</v>
+        <v>357.35</v>
       </c>
       <c r="AY22" t="n">
         <v>386.38</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-5.24</v>
+        <v>-6.14</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0.36</v>
+        <v>-1.33</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -776,10 +776,10 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>68.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 69.6; priority 68.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 69.4; priority 67.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.5%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>27.35</v>
+        <v>27.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.29</v>
+        <v>38.8</v>
       </c>
       <c r="AA2" t="n">
         <v>21.33</v>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>17.472</v>
+        <v>17.536</v>
       </c>
       <c r="AH2" t="n">
         <v>50.9</v>
@@ -900,25 +900,25 @@
         <v>45.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>66.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.31</v>
+        <v>0.06</v>
       </c>
       <c r="AM2" t="n">
-        <v>25.32</v>
+        <v>25.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.39</v>
+        <v>17.54</v>
       </c>
       <c r="AO2" t="n">
         <v>0.82</v>
       </c>
       <c r="AP2" t="n">
-        <v>16.1644</v>
+        <v>16.1657</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.4661</v>
+        <v>14.4664</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
@@ -931,7 +931,7 @@
         <v>50.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>66.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AW2" t="n">
         <v>756</v>
@@ -943,10 +943,10 @@
         <v>18.17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.09</v>
+        <v>8.48</v>
       </c>
       <c r="BA2" t="n">
-        <v>20.78</v>
+        <v>21.22</v>
       </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.3</v>
+        <v>65.7</v>
       </c>
       <c r="F3" t="n">
-        <v>65.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 66.3; priority 65.9; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 65.7; priority 65.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.0%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1070,22 +1070,22 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>14.2</v>
+        <v>13.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.61</v>
+        <v>13.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>30.97</v>
+        <v>30.98</v>
       </c>
       <c r="AB3" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>31.58</v>
+        <v>31.31</v>
       </c>
       <c r="AD3" t="n">
-        <v>24.82</v>
+        <v>24.6</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1094,57 +1094,57 @@
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>244.772</v>
+        <v>242.64</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-10.23</v>
+        <v>-11.02</v>
       </c>
       <c r="AM3" t="n">
-        <v>6.64</v>
+        <v>5.71</v>
       </c>
       <c r="AN3" t="n">
-        <v>25.79</v>
+        <v>25.42</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AP3" t="n">
-        <v>252.8198</v>
+        <v>252.7772</v>
       </c>
       <c r="AQ3" t="n">
-        <v>232.3495</v>
+        <v>232.3388</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
         <v>65</v>
       </c>
       <c r="AT3" t="n">
-        <v>77.5</v>
+        <v>75.3</v>
       </c>
       <c r="AU3" t="n">
         <v>38.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>75</v>
+        <v>73.7</v>
       </c>
       <c r="AW3" t="n">
         <v>752</v>
       </c>
       <c r="AX3" t="n">
-        <v>244.772</v>
+        <v>242.64</v>
       </c>
       <c r="AY3" t="n">
         <v>274</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-3.18</v>
+        <v>-4.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.35</v>
+        <v>4.43</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2633039347712</v>
+        <v>2609943674880</v>
       </c>
       <c r="BE3" t="n">
         <v>12.22</v>
@@ -1176,16 +1176,16 @@
         <v>78.2</v>
       </c>
       <c r="BK3" t="n">
-        <v>77.5</v>
+        <v>75.3</v>
       </c>
       <c r="BL3" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="BM3" t="n">
         <v>38.1</v>
       </c>
       <c r="BN3" t="n">
-        <v>75</v>
+        <v>73.7</v>
       </c>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr">
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>63.8</v>
+        <v>63.4</v>
       </c>
       <c r="F4" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 63.8; priority 59.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 63.4; priority 58.9; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.7%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1300,22 +1300,22 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>0.43</v>
+        <v>-0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>-12.86</v>
+        <v>-13.52</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.97</v>
+        <v>23.98</v>
       </c>
       <c r="AB4" t="n">
         <v>-33.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>24.2</v>
+        <v>24.02</v>
       </c>
       <c r="AD4" t="n">
-        <v>21.02</v>
+        <v>20.86</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1324,57 +1324,57 @@
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>406.635</v>
+        <v>403.54</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-1.83</v>
+        <v>-2.58</v>
       </c>
       <c r="AM4" t="n">
-        <v>-15.46</v>
+        <v>-16.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.449999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AP4" t="n">
-        <v>409.6153</v>
+        <v>409.5534</v>
       </c>
       <c r="AQ4" t="n">
-        <v>453.517</v>
+        <v>453.5015</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
         <v>35</v>
       </c>
       <c r="AT4" t="n">
-        <v>38.1</v>
+        <v>36.5</v>
       </c>
       <c r="AU4" t="n">
         <v>44.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>74.2</v>
+        <v>73</v>
       </c>
       <c r="AW4" t="n">
         <v>752</v>
       </c>
       <c r="AX4" t="n">
-        <v>404.3343</v>
+        <v>403.54</v>
       </c>
       <c r="AY4" t="n">
         <v>460.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.73</v>
+        <v>-1.47</v>
       </c>
       <c r="BA4" t="n">
-        <v>-10.34</v>
+        <v>-11.02</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>3020624494592</v>
+        <v>2997522006016</v>
       </c>
       <c r="BE4" t="n">
         <v>39.34</v>
@@ -1408,16 +1408,16 @@
         <v>100</v>
       </c>
       <c r="BK4" t="n">
-        <v>38.1</v>
+        <v>36.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="BM4" t="n">
         <v>44.1</v>
       </c>
       <c r="BN4" t="n">
-        <v>74.2</v>
+        <v>73</v>
       </c>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>17.17</v>
+        <v>17.54</v>
       </c>
       <c r="Z5" t="n">
-        <v>61.96</v>
+        <v>62.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.22</v>
+        <v>23.21</v>
       </c>
       <c r="AB5" t="n">
         <v>-44.26</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>10.288</v>
+        <v>10.32</v>
       </c>
       <c r="AH5" t="n">
         <v>30.4</v>
@@ -1571,22 +1571,22 @@
         <v>82.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.84</v>
+        <v>-3.54</v>
       </c>
       <c r="AM5" t="n">
-        <v>25.66</v>
+        <v>26.05</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AO5" t="n">
         <v>0.1</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.176</v>
+        <v>10.1767</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.755100000000001</v>
+        <v>8.7553</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
@@ -1611,10 +1611,10 @@
         <v>11.61</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="BA5" t="n">
-        <v>17.51</v>
+        <v>17.87</v>
       </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
@@ -1640,24 +1640,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>59.5</v>
+        <v>64.5</v>
       </c>
       <c r="F6" t="n">
-        <v>40.2</v>
+        <v>39.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,12 +1667,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 59.5; priority 40.2; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 64.5; priority 39.6; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1686,22 +1682,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 12.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 64.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1716,153 +1712,131 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>525.72</v>
+        <v>362.53</v>
       </c>
       <c r="T6" t="n">
-        <v>688.55</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+        <v>637.9</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-9.24</v>
+        <v>45.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>-14.73</v>
+        <v>129.51</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.28</v>
+        <v>34.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>21.56</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>16.4</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG6" t="n">
-        <v>593.12</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+        <v>578.25</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>49.9</v>
+      </c>
       <c r="AL6" t="n">
-        <v>-2.71</v>
+        <v>2.07</v>
       </c>
       <c r="AM6" t="n">
-        <v>-11.78</v>
+        <v>59.17</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.35</v>
+        <v>59.02</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.86</v>
+        <v>1.69</v>
       </c>
       <c r="AP6" t="n">
-        <v>621.6254</v>
+        <v>515.367</v>
       </c>
       <c r="AQ6" t="n">
-        <v>660.2241</v>
+        <v>399.2593</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT6" t="n">
-        <v>26.3</v>
+        <v>100</v>
       </c>
       <c r="AU6" t="n">
-        <v>29.1</v>
+        <v>29.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>68.40000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="AW6" t="n">
         <v>752</v>
       </c>
       <c r="AX6" t="n">
-        <v>585.39</v>
+        <v>543.96</v>
       </c>
       <c r="AY6" t="n">
-        <v>635.29</v>
+        <v>637.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-4.59</v>
+        <v>12.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>-10.16</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>1505462714368</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>68.40000000000001</v>
-      </c>
+        <v>44.83</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1872,12 +1846,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1886,10 +1860,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39.5</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>39.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1903,12 +1877,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 39.5; priority 33.0; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 59.0; priority 39.4; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1918,22 +1892,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 39.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1943,23 +1917,23 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>343.25</v>
+        <v>525.72</v>
       </c>
       <c r="T7" t="n">
-        <v>445.27</v>
+        <v>688.55</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1970,22 +1944,22 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>-0.03</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.23</v>
+        <v>-15.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>57.93</v>
+        <v>36.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>-53.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>362.82</v>
+        <v>21.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>159.35</v>
+        <v>16.27</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1994,103 +1968,105 @@
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>399.105</v>
+        <v>588.42</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>-6.83</v>
+        <v>-3.48</v>
       </c>
       <c r="AM7" t="n">
-        <v>-12.28</v>
+        <v>-12.48</v>
       </c>
       <c r="AN7" t="n">
-        <v>17.86</v>
+        <v>31</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.31</v>
+        <v>0.85</v>
       </c>
       <c r="AP7" t="n">
-        <v>396.7709</v>
+        <v>621.5314</v>
       </c>
       <c r="AQ7" t="n">
-        <v>414.9621</v>
+        <v>660.2005</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AT7" t="n">
-        <v>51.4</v>
+        <v>24.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>29.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>78.2</v>
+        <v>67.3</v>
       </c>
       <c r="AW7" t="n">
         <v>752</v>
       </c>
       <c r="AX7" t="n">
-        <v>391</v>
+        <v>585.39</v>
       </c>
       <c r="AY7" t="n">
-        <v>445.27</v>
+        <v>635.29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.59</v>
+        <v>-5.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>-3.82</v>
+        <v>-10.87</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1498928119808</v>
+        <v>1493659025408</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.95</v>
+        <v>32.84</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>32.93</v>
       </c>
       <c r="BG7" t="n">
-        <v>15.8</v>
+        <v>33.1</v>
       </c>
       <c r="BH7" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="BI7" t="inlineStr"/>
+        <v>35.61</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>36</v>
+      </c>
       <c r="BJ7" t="n">
-        <v>64.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="BK7" t="n">
-        <v>51.4</v>
+        <v>24.7</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>29.1</v>
       </c>
       <c r="BN7" t="n">
-        <v>78.2</v>
+        <v>67.3</v>
       </c>
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
@@ -2102,20 +2078,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E8" t="n">
-        <v>63.3</v>
+        <v>37.4</v>
       </c>
       <c r="F8" t="n">
-        <v>32.6</v>
+        <v>30.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2129,12 +2109,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 63.3; priority 32.6; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 37.4; priority 30.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2144,22 +2124,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo 14.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.5%.</t>
+          <t>TSLA: scenario base High Risk, score 37.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.6%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2169,136 +2149,156 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>362.53</v>
+        <v>343.25</v>
       </c>
       <c r="T8" t="n">
-        <v>637.9</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>48.55</v>
+        <v>-1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>134.28</v>
+        <v>33.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>34.91</v>
+        <v>57.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>157.39</v>
+      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>590.2506</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>40.8</v>
-      </c>
+        <v>394.16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>4.19</v>
+        <v>-7.98</v>
       </c>
       <c r="AM8" t="n">
-        <v>62.47</v>
+        <v>-13.37</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.12</v>
+        <v>17.37</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.72</v>
+        <v>0.3</v>
       </c>
       <c r="AP8" t="n">
-        <v>515.607</v>
+        <v>396.672</v>
       </c>
       <c r="AQ8" t="n">
-        <v>399.3193</v>
+        <v>414.9374</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT8" t="n">
-        <v>100</v>
+        <v>48.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>29.5</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>40.8</v>
+        <v>74.3</v>
       </c>
       <c r="AW8" t="n">
         <v>752</v>
       </c>
       <c r="AX8" t="n">
-        <v>543.96</v>
+        <v>391</v>
       </c>
       <c r="AY8" t="n">
-        <v>637.9</v>
+        <v>445.27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.48</v>
+        <v>-0.62</v>
       </c>
       <c r="BA8" t="n">
-        <v>47.81</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>1480543830016</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
+      <c r="BJ8" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>74.3</v>
+      </c>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>6.41</v>
+        <v>6.43</v>
       </c>
       <c r="Z9" t="n">
-        <v>-16.25</v>
+        <v>-16.24</v>
       </c>
       <c r="AA9" t="n">
         <v>33.95</v>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>26.56</v>
+        <v>26.565</v>
       </c>
       <c r="AH9" t="n">
         <v>22.2</v>
@@ -2442,22 +2442,22 @@
         <v>15.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>10.21</v>
+        <v>10.23</v>
       </c>
       <c r="AM9" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.52</v>
       </c>
       <c r="AN9" t="n">
-        <v>-2.37</v>
+        <v>-2.36</v>
       </c>
       <c r="AO9" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.2582</v>
+        <v>24.2583</v>
       </c>
       <c r="AQ9" t="n">
         <v>26.9651</v>
@@ -2473,7 +2473,7 @@
         <v>20.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="AW9" t="n">
         <v>757</v>
@@ -2485,10 +2485,10 @@
         <v>30.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.49</v>
+        <v>9.51</v>
       </c>
       <c r="BA9" t="n">
-        <v>-1.5</v>
+        <v>-1.48</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>61.6</v>
+        <v>61.4</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>15.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 61.6; priority 17.0; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 61.4; priority 15.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 19.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 19.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 61.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 61.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.6%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1539.80 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1544.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>1109.5466</v>
       </c>
       <c r="T10" t="n">
-        <v>1539.8</v>
+        <v>1544.6</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>34.47</v>
+        <v>34.89</v>
       </c>
       <c r="Z10" t="n">
-        <v>129.4</v>
+        <v>130.11</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.11</v>
+        <v>38.12</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>59.45</v>
+        <v>59.64</v>
       </c>
       <c r="AD10" t="n">
-        <v>37.14</v>
+        <v>37.26</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1539.8</v>
+        <v>1544.6</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>17.94</v>
+        <v>18.31</v>
       </c>
       <c r="AM10" t="n">
-        <v>62.39</v>
+        <v>62.89</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.89</v>
+        <v>33.03</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AP10" t="n">
-        <v>1291.9241</v>
+        <v>1292.0201</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1052.374</v>
+        <v>1052.398</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2671,7 +2671,7 @@
         <v>18.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>20.6</v>
       </c>
       <c r="AW10" t="n">
         <v>765</v>
@@ -2680,13 +2680,13 @@
         <v>1249</v>
       </c>
       <c r="AY10" t="n">
-        <v>1539.8</v>
+        <v>1544.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19.19</v>
+        <v>19.55</v>
       </c>
       <c r="BA10" t="n">
-        <v>46.32</v>
+        <v>46.77</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>593466163200</v>
+        <v>595316113408</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="BM10" t="n">
         <v>18.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>22</v>
+        <v>20.6</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="F12" t="n">
         <v>77.90000000000001</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 80.2; priority 77.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 80.3; priority 77.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>18.42</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>110.08</v>
+        <v>108.44</v>
       </c>
       <c r="AA12" t="n">
         <v>29.71</v>
@@ -3062,10 +3062,10 @@
         <v>-29.81</v>
       </c>
       <c r="AC12" t="n">
-        <v>27.7</v>
+        <v>27.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>25.13</v>
+        <v>24.93</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -3074,29 +3074,29 @@
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
-        <v>363.385</v>
+        <v>360.55</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>-9.279999999999999</v>
+        <v>-9.99</v>
       </c>
       <c r="AM12" t="n">
-        <v>13.33</v>
+        <v>12.45</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.5</v>
+        <v>44.12</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>357.7259</v>
+        <v>357.6692</v>
       </c>
       <c r="AQ12" t="n">
-        <v>305.2903</v>
+        <v>305.2761</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
@@ -3121,10 +3121,10 @@
         <v>402.3797</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.58</v>
+        <v>0.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>19.03</v>
+        <v>18.1</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>4431456239616</v>
+        <v>4396578766848</v>
       </c>
       <c r="BE12" t="n">
         <v>37.92</v>
@@ -3161,7 +3161,7 @@
         <v>100</v>
       </c>
       <c r="BL12" t="n">
-        <v>60.1</v>
+        <v>60.7</v>
       </c>
       <c r="BM12" t="n">
         <v>40.5</v>
@@ -3194,10 +3194,10 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 75.8; priority 76.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.9; priority 76.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.31</v>
+        <v>23.41</v>
       </c>
       <c r="AA13" t="n">
         <v>12.87</v>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>160.52</v>
+        <v>160.66</v>
       </c>
       <c r="AH13" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="AJ13" t="n">
         <v>67.7</v>
@@ -3321,29 +3321,29 @@
         <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AM13" t="n">
-        <v>11.27</v>
+        <v>11.37</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.92</v>
+        <v>16.96</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>155.4036</v>
+        <v>155.4064</v>
       </c>
       <c r="AQ13" t="n">
-        <v>146.7588</v>
+        <v>146.7595</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="AU13" t="n">
         <v>67.7</v>
@@ -3361,10 +3361,10 @@
         <v>164.88</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3403,7 +3403,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 74.9; priority 75.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.9; priority 75.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>9.15</v>
+        <v>9.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.51</v>
+        <v>21.56</v>
       </c>
       <c r="AA14" t="n">
         <v>13.14</v>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>121.72</v>
+        <v>121.77</v>
       </c>
       <c r="AH14" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>66.90000000000001</v>
@@ -3527,29 +3527,29 @@
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AM14" t="n">
-        <v>9.619999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="AN14" t="n">
-        <v>16.87</v>
+        <v>16.88</v>
       </c>
       <c r="AO14" t="n">
         <v>1.28</v>
       </c>
       <c r="AP14" t="n">
-        <v>117.9644</v>
+        <v>117.9654</v>
       </c>
       <c r="AQ14" t="n">
-        <v>112.1964</v>
+        <v>112.1966</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AU14" t="n">
         <v>66.90000000000001</v>
@@ -3567,10 +3567,10 @@
         <v>124.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>74.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 74.7; priority 75.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.6; priority 75.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>10.53</v>
+        <v>10.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.81</v>
+        <v>22.76</v>
       </c>
       <c r="AA15" t="n">
         <v>14.1</v>
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>687.92</v>
+        <v>687.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="AJ15" t="n">
         <v>64.40000000000001</v>
@@ -3733,29 +3733,29 @@
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AM15" t="n">
-        <v>9.42</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.13</v>
+        <v>18.11</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AP15" t="n">
-        <v>662.5776</v>
+        <v>662.5712</v>
       </c>
       <c r="AQ15" t="n">
-        <v>629.972</v>
+        <v>629.9704</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="AU15" t="n">
         <v>64.40000000000001</v>
@@ -3773,10 +3773,10 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="F16" t="n">
         <v>75.2</v>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 74.3; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.2; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>6.5</v>
+        <v>6.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.47</v>
+        <v>15.38</v>
       </c>
       <c r="AA16" t="n">
         <v>12.85</v>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>62.67</v>
+        <v>62.62</v>
       </c>
       <c r="AH16" t="n">
-        <v>70.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AI16" t="n">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AJ16" t="n">
         <v>71.5</v>
@@ -3939,29 +3939,29 @@
         <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AM16" t="n">
-        <v>10.18</v>
+        <v>10.09</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.7</v>
+        <v>13.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AP16" t="n">
-        <v>61.3412</v>
+        <v>61.3402</v>
       </c>
       <c r="AQ16" t="n">
-        <v>58.5806</v>
+        <v>58.5804</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AU16" t="n">
         <v>71.5</v>
@@ -3979,10 +3979,10 @@
         <v>63.94</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.98</v>
+        <v>6.9</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="F17" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 72.5; priority 74.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 72.7; priority 74.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.2%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>7.16</v>
+        <v>7.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.75</v>
+        <v>17.97</v>
       </c>
       <c r="AA17" t="n">
         <v>12.87</v>
@@ -4130,13 +4130,13 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>74.09999999999999</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="AH17" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="AI17" t="n">
-        <v>70.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AJ17" t="n">
         <v>68.09999999999999</v>
@@ -4145,29 +4145,29 @@
         <v>82.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="AM17" t="n">
-        <v>9.42</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.94</v>
+        <v>15.01</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AP17" t="n">
-        <v>71.9044</v>
+        <v>71.9072</v>
       </c>
       <c r="AQ17" t="n">
-        <v>68.7041</v>
+        <v>68.70480000000001</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>70.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AU17" t="n">
         <v>68.09999999999999</v>
@@ -4185,10 +4185,10 @@
         <v>74.95999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.85</v>
+        <v>8.06</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>72.7</v>
       </c>
       <c r="F18" t="n">
-        <v>72.2</v>
+        <v>71.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 73.0; priority 72.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 72.7; priority 71.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 73.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4312,22 +4312,22 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>12.55</v>
+        <v>11.88</v>
       </c>
       <c r="Z18" t="n">
-        <v>44.39</v>
+        <v>43.54</v>
       </c>
       <c r="AA18" t="n">
-        <v>25.94</v>
+        <v>25.96</v>
       </c>
       <c r="AB18" t="n">
         <v>-33.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>35.51</v>
+        <v>35.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>30.52</v>
+        <v>30.34</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -4336,36 +4336,36 @@
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>293.285</v>
+        <v>291.56</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.08</v>
+        <v>-0.51</v>
       </c>
       <c r="AM18" t="n">
-        <v>5.4</v>
+        <v>4.78</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.11</v>
+        <v>17.88</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP18" t="n">
-        <v>282.9571</v>
+        <v>282.9226</v>
       </c>
       <c r="AQ18" t="n">
-        <v>265.4899</v>
+        <v>265.4813</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>81.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>42.2</v>
@@ -4377,16 +4377,16 @@
         <v>752</v>
       </c>
       <c r="AX18" t="n">
-        <v>293.285</v>
+        <v>291.56</v>
       </c>
       <c r="AY18" t="n">
         <v>315.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.47</v>
+        <v>9.82</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>4307581140992</v>
+        <v>4282539048960</v>
       </c>
       <c r="BE18" t="n">
         <v>27.15</v>
@@ -4420,10 +4420,10 @@
         <v>100</v>
       </c>
       <c r="BK18" t="n">
-        <v>81.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BL18" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="BM18" t="n">
         <v>42.2</v>
@@ -4446,20 +4446,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>68.3</v>
       </c>
       <c r="F19" t="n">
-        <v>70.7</v>
+        <v>70.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,17 +4468,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 10.0% sopra MA50: evitare inseguimento.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 65.28. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 80.0; priority 70.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 68.3; priority 70.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo 10.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.0%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -4522,20 +4522,20 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>54.81</v>
+        <v>62.06</v>
       </c>
       <c r="T19" t="n">
-        <v>72.27</v>
+        <v>65.28</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -4544,89 +4544,89 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>26.04</v>
+        <v>-1.85</v>
       </c>
       <c r="Z19" t="n">
-        <v>59.43</v>
+        <v>0.39</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.62</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>-17.8</v>
+        <v>-12.85</v>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>69.8</v>
+        <v>63.81</v>
       </c>
       <c r="AH19" t="n">
-        <v>78.2</v>
+        <v>61.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>48.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>69.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>58.8</v>
+        <v>82.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.26</v>
+        <v>2.82</v>
       </c>
       <c r="AM19" t="n">
-        <v>36.22</v>
+        <v>1.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>25.23</v>
+        <v>6.61</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP19" t="n">
-        <v>63.4594</v>
+        <v>63.322</v>
       </c>
       <c r="AQ19" t="n">
-        <v>54.8676</v>
+        <v>63.1007</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>100</v>
+        <v>48.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>69.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="AV19" t="n">
-        <v>58.8</v>
+        <v>82.8</v>
       </c>
       <c r="AW19" t="n">
         <v>756</v>
       </c>
       <c r="AX19" t="n">
-        <v>65.27</v>
+        <v>62.34</v>
       </c>
       <c r="AY19" t="n">
-        <v>72.27</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9.99</v>
+        <v>0.77</v>
       </c>
       <c r="BA19" t="n">
-        <v>27.22</v>
+        <v>1.12</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>68.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>70.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 65.28. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 10.1% sopra MA50: evitare inseguimento.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 68.3; priority 70.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 79.9; priority 70.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.8%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4728,20 +4728,20 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>62.06</v>
+        <v>54.81</v>
       </c>
       <c r="T20" t="n">
-        <v>65.28</v>
+        <v>72.27</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4750,89 +4750,89 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>-1.77</v>
+        <v>26.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.47</v>
+        <v>59.57</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.550000000000001</v>
+        <v>13.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>-12.85</v>
+        <v>-17.8</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>63.86</v>
+        <v>69.86</v>
       </c>
       <c r="AH20" t="n">
-        <v>61.3</v>
+        <v>78.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>48.7</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>78.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AK20" t="n">
-        <v>82.8</v>
+        <v>58.4</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.9</v>
+        <v>5.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.7</v>
+        <v>36.34</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.64</v>
+        <v>25.26</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.323</v>
+        <v>63.4606</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.101</v>
+        <v>54.8679</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>48.7</v>
+        <v>100</v>
       </c>
       <c r="AU20" t="n">
-        <v>78.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>82.8</v>
+        <v>58.4</v>
       </c>
       <c r="AW20" t="n">
         <v>756</v>
       </c>
       <c r="AX20" t="n">
-        <v>62.34</v>
+        <v>65.27</v>
       </c>
       <c r="AY20" t="n">
-        <v>64.68000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.85</v>
+        <v>10.08</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.2</v>
+        <v>27.32</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F21" t="n">
-        <v>56.7</v>
+        <v>54.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 73.6; priority 56.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 71.5; priority 54.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 73.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.6%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>11.59</v>
+        <v>10.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>45.52</v>
+        <v>43.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.96</v>
+        <v>46.98</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>31.54</v>
+        <v>31.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.24</v>
+        <v>16.04</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,57 +4980,57 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>205.94</v>
+        <v>203.42</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-4.19</v>
+        <v>-5.36</v>
       </c>
       <c r="AM21" t="n">
-        <v>13.04</v>
+        <v>11.65</v>
       </c>
       <c r="AN21" t="n">
-        <v>75.11</v>
+        <v>74.39</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AP21" t="n">
-        <v>204.7443</v>
+        <v>204.6939</v>
       </c>
       <c r="AQ21" t="n">
-        <v>188.668</v>
+        <v>188.6554</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>85.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="AU21" t="n">
         <v>14.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>82.8</v>
+        <v>78.8</v>
       </c>
       <c r="AW21" t="n">
         <v>752</v>
       </c>
       <c r="AX21" t="n">
-        <v>205.1</v>
+        <v>203.42</v>
       </c>
       <c r="AY21" t="n">
         <v>235.4656</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.57</v>
+        <v>-0.62</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.140000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4988072886272</v>
+        <v>4926793580544</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5064,16 +5064,16 @@
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>85.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="BL21" t="n">
-        <v>68.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="BM21" t="n">
         <v>14.1</v>
       </c>
       <c r="BN21" t="n">
-        <v>82.8</v>
+        <v>78.8</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 6.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.1%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 357.35 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 357.13 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>357.35</v>
+        <v>357.13</v>
       </c>
       <c r="T22" t="n">
         <v>424.57</v>
@@ -5188,16 +5188,16 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-15.63</v>
+        <v>-15.68</v>
       </c>
       <c r="Z22" t="n">
-        <v>26.42</v>
+        <v>26.35</v>
       </c>
       <c r="AA22" t="n">
         <v>17.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>-18.11</v>
+        <v>-18.16</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,47 +5212,47 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>357.35</v>
+        <v>357.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AK22" t="n">
         <v>66</v>
       </c>
       <c r="AL22" t="n">
-        <v>-7.55</v>
+        <v>-7.61</v>
       </c>
       <c r="AM22" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.56</v>
+        <v>26.54</v>
       </c>
       <c r="AO22" t="n">
         <v>1.49</v>
       </c>
       <c r="AP22" t="n">
-        <v>380.7324</v>
+        <v>380.728</v>
       </c>
       <c r="AQ22" t="n">
-        <v>362.154</v>
+        <v>362.1529</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AV22" t="n">
         <v>66</v>
@@ -5261,16 +5261,16 @@
         <v>756</v>
       </c>
       <c r="AX22" t="n">
-        <v>357.35</v>
+        <v>357.13</v>
       </c>
       <c r="AY22" t="n">
         <v>386.38</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-6.14</v>
+        <v>-6.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>-1.33</v>
+        <v>-1.39</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -766,20 +766,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>69.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>67.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -793,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 69.4; priority 67.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 66.1; priority 65.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -808,22 +812,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 8.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.5%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 199.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -833,136 +837,156 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>12.936</v>
+        <v>199.34</v>
       </c>
       <c r="T2" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>274.99</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>27.81</v>
+        <v>13.93</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.8</v>
+        <v>14.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.33</v>
+        <v>30.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>-29.37</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+        <v>-30.88</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>24.77</v>
+      </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Robotica e automazione</t>
-        </is>
-      </c>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>17.536</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>64.8</v>
-      </c>
+        <v>244.19</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.06</v>
+        <v>-10.45</v>
       </c>
       <c r="AM2" t="n">
-        <v>25.78</v>
+        <v>6.39</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.54</v>
+        <v>24.67</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
-        <v>16.1657</v>
+        <v>252.8082</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.4664</v>
+        <v>232.3466</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>100</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>50.9</v>
+        <v>38.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>64.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="AX2" t="n">
-        <v>16.544</v>
+        <v>244.19</v>
       </c>
       <c r="AY2" t="n">
-        <v>18.17</v>
+        <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.48</v>
+        <v>-3.41</v>
       </c>
       <c r="BA2" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+        <v>5.1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Internet Retail</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>2626778562560</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>53.3</v>
+      </c>
       <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
+      <c r="BJ2" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>74.59999999999999</v>
+      </c>
       <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>USA / Consumer &amp; Cloud</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -972,24 +996,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>65.7</v>
+        <v>68.8</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>64.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1003,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 65.7; priority 65.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 68.8; priority 64.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1018,22 +1038,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 4.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.0%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 199.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1043,156 +1063,136 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>199.34</v>
+        <v>12.936</v>
       </c>
       <c r="T3" t="n">
-        <v>274.99</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Amazon.com, Inc.</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>18.17</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>13.21</v>
+        <v>24.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.61</v>
+        <v>40.12</v>
       </c>
       <c r="AA3" t="n">
-        <v>30.98</v>
+        <v>21.34</v>
       </c>
       <c r="AB3" t="n">
-        <v>-30.88</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>31.31</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24.6</v>
-      </c>
+        <v>-29.37</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Robotica e automazione</t>
+        </is>
+      </c>
       <c r="AG3" t="n">
-        <v>242.64</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+        <v>17.616</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>60.6</v>
+      </c>
       <c r="AL3" t="n">
-        <v>-11.02</v>
+        <v>1.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.71</v>
+        <v>27.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>25.42</v>
+        <v>17.74</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>252.7772</v>
+        <v>16.083</v>
       </c>
       <c r="AQ3" t="n">
-        <v>232.3388</v>
+        <v>14.4439</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT3" t="n">
-        <v>75.3</v>
+        <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>38.1</v>
+        <v>50.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>73.7</v>
+        <v>60.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="AX3" t="n">
-        <v>242.64</v>
+        <v>16.544</v>
       </c>
       <c r="AY3" t="n">
-        <v>274</v>
+        <v>18.17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-4.01</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>Internet Retail</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>2609943674880</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>53.3</v>
-      </c>
+        <v>21.96</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>73.7</v>
-      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>USA / Consumer &amp; Cloud</t>
-        </is>
-      </c>
+      <c r="BP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>63.4</v>
+        <v>63.3</v>
       </c>
       <c r="F4" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 63.4; priority 58.9; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 63.3; priority 58.8; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1300,19 +1300,19 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>-13.52</v>
+        <v>-13.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.98</v>
+        <v>23.99</v>
       </c>
       <c r="AB4" t="n">
         <v>-33.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>24.02</v>
+        <v>24.01</v>
       </c>
       <c r="AD4" t="n">
         <v>20.86</v>
@@ -1324,36 +1324,36 @@
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>403.54</v>
+        <v>403.41</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-2.58</v>
+        <v>-2.61</v>
       </c>
       <c r="AM4" t="n">
-        <v>-16.11</v>
+        <v>-16.13</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.17</v>
+        <v>7.61</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="AP4" t="n">
-        <v>409.5534</v>
+        <v>409.5508</v>
       </c>
       <c r="AQ4" t="n">
-        <v>453.5015</v>
+        <v>453.5009</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
         <v>35</v>
       </c>
       <c r="AT4" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="AU4" t="n">
         <v>44.1</v>
@@ -1362,19 +1362,19 @@
         <v>73</v>
       </c>
       <c r="AW4" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AX4" t="n">
-        <v>403.54</v>
+        <v>403.41</v>
       </c>
       <c r="AY4" t="n">
         <v>460.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1.47</v>
+        <v>-1.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>-11.02</v>
+        <v>-11.05</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>2997522006016</v>
+        <v>2996704903168</v>
       </c>
       <c r="BE4" t="n">
         <v>39.34</v>
@@ -1408,7 +1408,7 @@
         <v>100</v>
       </c>
       <c r="BK4" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="BL4" t="n">
         <v>70.5</v>
@@ -1444,10 +1444,10 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="F5" t="n">
-        <v>58.1</v>
+        <v>57.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 64.1; priority 58.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 64.2; priority 57.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>17.54</v>
+        <v>20.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>62.46</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.21</v>
+        <v>23.18</v>
       </c>
       <c r="AB5" t="n">
         <v>-44.26</v>
@@ -1556,37 +1556,37 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>10.32</v>
+        <v>10.584</v>
       </c>
       <c r="AH5" t="n">
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="AI5" t="n">
         <v>100</v>
       </c>
       <c r="AJ5" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>82.8</v>
+        <v>81.7</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.54</v>
+        <v>3.48</v>
       </c>
       <c r="AM5" t="n">
-        <v>26.05</v>
+        <v>29.65</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.1767</v>
+        <v>10.1519</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.7553</v>
+        <v>8.738899999999999</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
@@ -1596,13 +1596,13 @@
         <v>100</v>
       </c>
       <c r="AU5" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>82.8</v>
+        <v>81.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AX5" t="n">
         <v>10.2879</v>
@@ -1611,10 +1611,10 @@
         <v>11.61</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.41</v>
+        <v>4.26</v>
       </c>
       <c r="BA5" t="n">
-        <v>17.87</v>
+        <v>21.11</v>
       </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
@@ -1640,20 +1640,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>64.5</v>
+        <v>58.7</v>
       </c>
       <c r="F6" t="n">
-        <v>39.6</v>
+        <v>38.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1667,12 +1671,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 64.5; priority 39.6; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 58.7; priority 38.9; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1682,22 +1686,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 12.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 5.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 64.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 58.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.9%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1712,131 +1716,153 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>362.53</v>
+        <v>525.72</v>
       </c>
       <c r="T6" t="n">
-        <v>637.9</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>688.55</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>45.53</v>
+        <v>-10.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>129.51</v>
+        <v>-15.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>34.96</v>
+        <v>36.28</v>
       </c>
       <c r="AB6" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+        <v>-34.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>16.17</v>
+      </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>578.25</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>49.9</v>
-      </c>
+        <v>584.59</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>2.07</v>
+        <v>-4.11</v>
       </c>
       <c r="AM6" t="n">
-        <v>59.17</v>
+        <v>-13.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>59.02</v>
+        <v>29.76</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.69</v>
+        <v>0.82</v>
       </c>
       <c r="AP6" t="n">
-        <v>515.367</v>
+        <v>621.4548</v>
       </c>
       <c r="AQ6" t="n">
-        <v>399.2593</v>
+        <v>660.1814000000001</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>751</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>584.59</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>635.29</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-5.93</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>1483936890880</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>100</v>
       </c>
-      <c r="AU6" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>752</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>543.96</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>637.9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>66.40000000000001</v>
+      </c>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>USA / Social &amp; AI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1846,24 +1872,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>63.1</v>
       </c>
       <c r="F7" t="n">
-        <v>39.4</v>
+        <v>32.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1877,12 +1899,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 59.0; priority 39.4; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 63.1; priority 32.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1892,22 +1914,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
+          <t>prezzo 14.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.3%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.6%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1922,153 +1944,131 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>525.72</v>
+        <v>362.53</v>
       </c>
       <c r="T7" t="n">
-        <v>688.55</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+        <v>637.9</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>-9.960000000000001</v>
+        <v>48.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>-15.4</v>
+        <v>134.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>36.28</v>
+        <v>34.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>16.27</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG7" t="n">
-        <v>588.42</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+        <v>591.01</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>40.3</v>
+      </c>
       <c r="AL7" t="n">
-        <v>-3.48</v>
+        <v>4.32</v>
       </c>
       <c r="AM7" t="n">
-        <v>-12.48</v>
+        <v>62.68</v>
       </c>
       <c r="AN7" t="n">
-        <v>31</v>
+        <v>58.73</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.85</v>
+        <v>1.68</v>
       </c>
       <c r="AP7" t="n">
-        <v>621.5314</v>
+        <v>515.6222</v>
       </c>
       <c r="AQ7" t="n">
-        <v>660.2005</v>
+        <v>399.3231</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.7</v>
+        <v>100</v>
       </c>
       <c r="AU7" t="n">
-        <v>29.1</v>
+        <v>29.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>67.3</v>
+        <v>40.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AX7" t="n">
-        <v>585.39</v>
+        <v>543.96</v>
       </c>
       <c r="AY7" t="n">
-        <v>635.29</v>
+        <v>637.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-5.33</v>
+        <v>14.62</v>
       </c>
       <c r="BA7" t="n">
-        <v>-10.87</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>1493659025408</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>67.3</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>37.4</v>
+        <v>37.9</v>
       </c>
       <c r="F8" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 37.4; priority 30.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 37.9; priority 31.4; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 37.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.6%.</t>
+          <t>TSLA: scenario base High Risk, score 37.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.0%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2176,22 +2176,22 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>-1.27</v>
+        <v>-0.64</v>
       </c>
       <c r="Z8" t="n">
-        <v>33.55</v>
+        <v>34.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>57.96</v>
+        <v>57.97</v>
       </c>
       <c r="AB8" t="n">
         <v>-53.77</v>
       </c>
       <c r="AC8" t="n">
-        <v>358.37</v>
+        <v>360.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>157.39</v>
+        <v>157.88</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -2200,45 +2200,45 @@
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>394.16</v>
+        <v>396.68</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>-7.98</v>
+        <v>-7.39</v>
       </c>
       <c r="AM8" t="n">
-        <v>-13.37</v>
+        <v>-12.82</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.37</v>
+        <v>16.78</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AP8" t="n">
-        <v>396.672</v>
+        <v>396.7224</v>
       </c>
       <c r="AQ8" t="n">
-        <v>414.9374</v>
+        <v>414.95</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
         <v>35</v>
       </c>
       <c r="AT8" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AX8" t="n">
         <v>391</v>
@@ -2247,10 +2247,10 @@
         <v>445.27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.62</v>
+        <v>-0.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>-5</v>
+        <v>-4.4</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1480543830016</v>
+        <v>1489820450816</v>
       </c>
       <c r="BE8" t="n">
         <v>3.95</v>
@@ -2282,7 +2282,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="BL8" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="inlineStr">
@@ -2318,10 +2318,10 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>37.8</v>
+        <v>42.8</v>
       </c>
       <c r="F9" t="n">
-        <v>25.1</v>
+        <v>21.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 37.8; priority 25.1; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 42.8; priority 21.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 12.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 37.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 42.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.1%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>6.43</v>
+        <v>8.69</v>
       </c>
       <c r="Z9" t="n">
-        <v>-16.24</v>
+        <v>-14.87</v>
       </c>
       <c r="AA9" t="n">
         <v>33.95</v>
@@ -2430,53 +2430,53 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>26.565</v>
+        <v>27.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>49.8</v>
+        <v>55.2</v>
       </c>
       <c r="AJ9" t="n">
         <v>15.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>56.2</v>
+        <v>50.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>10.23</v>
+        <v>11.03</v>
       </c>
       <c r="AM9" t="n">
-        <v>-8.52</v>
+        <v>-5.37</v>
       </c>
       <c r="AN9" t="n">
-        <v>-2.36</v>
+        <v>-1.67</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.2583</v>
+        <v>24.1953</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26.9651</v>
+        <v>26.9741</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AT9" t="n">
-        <v>49.8</v>
+        <v>55.2</v>
       </c>
       <c r="AU9" t="n">
         <v>20.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>56.2</v>
+        <v>50.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AX9" t="n">
         <v>23.01</v>
@@ -2485,10 +2485,10 @@
         <v>30.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.51</v>
+        <v>12.13</v>
       </c>
       <c r="BA9" t="n">
-        <v>-1.48</v>
+        <v>0.58</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>61.4</v>
+        <v>62.3</v>
       </c>
       <c r="F10" t="n">
-        <v>15.9</v>
+        <v>20.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 61.4; priority 15.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 62.3; priority 20.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 19.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 17.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 61.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.9%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1544.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1514.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>1109.5466</v>
       </c>
       <c r="T10" t="n">
-        <v>1544.6</v>
+        <v>1514.6</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>34.89</v>
+        <v>32.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>130.11</v>
+        <v>121.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.12</v>
+        <v>38.13</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>59.64</v>
+        <v>58.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>37.26</v>
+        <v>36.38</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1544.6</v>
+        <v>1514.6</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>18.31</v>
+        <v>14.79</v>
       </c>
       <c r="AM10" t="n">
-        <v>62.89</v>
+        <v>58.78</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.03</v>
+        <v>32.22</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="AP10" t="n">
-        <v>1292.0201</v>
+        <v>1284.3927</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1052.398</v>
+        <v>1047.8913</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2671,22 +2671,22 @@
         <v>18.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>20.6</v>
+        <v>27.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AX10" t="n">
         <v>1249</v>
       </c>
       <c r="AY10" t="n">
-        <v>1544.6</v>
+        <v>1514.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19.55</v>
+        <v>17.92</v>
       </c>
       <c r="BA10" t="n">
-        <v>46.77</v>
+        <v>44.54</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>595316113408</v>
+        <v>581364023296</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>11.1</v>
+        <v>12.3</v>
       </c>
       <c r="BM10" t="n">
         <v>18.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>20.6</v>
+        <v>27.1</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2756,10 +2756,10 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>78.7</v>
       </c>
       <c r="F11" t="n">
-        <v>80.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 79.0; priority 80.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.7; priority 79.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>14.47</v>
+        <v>13.84</v>
       </c>
       <c r="Z11" t="n">
-        <v>40.87</v>
+        <v>41.41</v>
       </c>
       <c r="AA11" t="n">
-        <v>15.98</v>
+        <v>15.99</v>
       </c>
       <c r="AB11" t="n">
         <v>-19.17</v>
@@ -2868,13 +2868,13 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>46.6</v>
+        <v>46.46</v>
       </c>
       <c r="AH11" t="n">
-        <v>68.5</v>
+        <v>68.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.3</v>
+        <v>93.2</v>
       </c>
       <c r="AJ11" t="n">
         <v>65.5</v>
@@ -2883,29 +2883,29 @@
         <v>82.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.29</v>
+        <v>-1.25</v>
       </c>
       <c r="AM11" t="n">
-        <v>23.1</v>
+        <v>22.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.02</v>
+        <v>17.92</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AP11" t="n">
-        <v>44.9136</v>
+        <v>44.7763</v>
       </c>
       <c r="AQ11" t="n">
-        <v>40.3666</v>
+        <v>40.3085</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
         <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>94.3</v>
+        <v>93.2</v>
       </c>
       <c r="AU11" t="n">
         <v>65.5</v>
@@ -2914,7 +2914,7 @@
         <v>82.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AX11" t="n">
         <v>44.985</v>
@@ -2923,10 +2923,10 @@
         <v>49.485</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="BA11" t="n">
-        <v>15.44</v>
+        <v>15.26</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2947,73 +2947,69 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>3. Interessanti ma da attendere</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>80.3</v>
+        <v>79.2</v>
       </c>
       <c r="F12" t="n">
-        <v>77.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟠 Attendi pullback</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Non inseguire il prezzo: imposta alert su pullback o tenuta supporto. Supporto 60D: 54.81.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 80.3; priority 77.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 79.2; priority 66.0; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 11.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.6%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3023,7 +3019,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -3032,71 +3028,83 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>273.3367</v>
+        <v>54.81</v>
       </c>
       <c r="T12" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+        <v>72.27</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>24.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>108.44</v>
+        <v>61.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>29.71</v>
+        <v>13.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>27.48</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>24.93</v>
-      </c>
+        <v>-17.8</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Value globale</t>
+        </is>
+      </c>
       <c r="AG12" t="n">
-        <v>360.55</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
+        <v>70.48</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>52.5</v>
+      </c>
       <c r="AL12" t="n">
-        <v>-9.99</v>
+        <v>8.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>12.45</v>
+        <v>37.87</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.12</v>
+        <v>25.67</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="AP12" t="n">
-        <v>357.6692</v>
+        <v>63.1764</v>
       </c>
       <c r="AQ12" t="n">
-        <v>305.2761</v>
+        <v>54.7527</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
@@ -3106,75 +3114,41 @@
         <v>100</v>
       </c>
       <c r="AU12" t="n">
-        <v>40.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>82.8</v>
+        <v>52.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="AX12" t="n">
-        <v>358.7757</v>
+        <v>65.25</v>
       </c>
       <c r="AY12" t="n">
-        <v>402.3797</v>
+        <v>72.27</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.8</v>
+        <v>11.56</v>
       </c>
       <c r="BA12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>4396578766848</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>82.8</v>
-      </c>
+        <v>28.72</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
       <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3184,20 +3158,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E13" t="n">
-        <v>75.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="F13" t="n">
-        <v>76.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3206,22 +3184,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 75.9; priority 76.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.2; priority 77.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3231,17 +3209,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.8%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3251,7 +3229,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3260,127 +3238,149 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>140.98</v>
+        <v>273.3367</v>
       </c>
       <c r="T13" t="n">
-        <v>164.88</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>9.74</v>
+        <v>18.71</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.41</v>
+        <v>110.58</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.87</v>
+        <v>29.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>25.18</v>
+      </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>Azionario globale</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="n">
-        <v>160.66</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>82.8</v>
-      </c>
+        <v>364.26</v>
+      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>1.29</v>
+        <v>-9.06</v>
       </c>
       <c r="AM13" t="n">
-        <v>11.37</v>
+        <v>13.6</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.96</v>
+        <v>44.13</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AP13" t="n">
-        <v>155.4064</v>
+        <v>357.7434</v>
       </c>
       <c r="AQ13" t="n">
-        <v>146.7595</v>
+        <v>305.2947</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>76.3</v>
+        <v>100</v>
       </c>
       <c r="AU13" t="n">
-        <v>67.7</v>
+        <v>40.5</v>
       </c>
       <c r="AV13" t="n">
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="AX13" t="n">
-        <v>158.2</v>
+        <v>358.7757</v>
       </c>
       <c r="AY13" t="n">
-        <v>164.88</v>
+        <v>402.3797</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.38</v>
+        <v>1.82</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
+        <v>19.31</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>4442127073280</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3390,20 +3390,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>74.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="F14" t="n">
-        <v>75.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 74.9; priority 75.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.8; priority 76.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.2%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3466,15 +3466,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>107.5</v>
+        <v>140.98</v>
       </c>
       <c r="T14" t="n">
-        <v>124.27</v>
+        <v>164.88</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3488,16 +3488,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>9.19</v>
+        <v>8.91</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.56</v>
+        <v>24.58</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.14</v>
+        <v>12.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3508,69 +3508,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>121.77</v>
+        <v>161.56</v>
       </c>
       <c r="AH14" t="n">
-        <v>71.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>74.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>66.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="AK14" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AM14" t="n">
-        <v>9.66</v>
+        <v>11.96</v>
       </c>
       <c r="AN14" t="n">
-        <v>16.88</v>
+        <v>17.2</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AP14" t="n">
-        <v>117.9654</v>
+        <v>155.0524</v>
       </c>
       <c r="AQ14" t="n">
-        <v>112.1966</v>
+        <v>146.6353</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>74.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>66.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="AW14" t="n">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AX14" t="n">
-        <v>120.3</v>
+        <v>156.96</v>
       </c>
       <c r="AY14" t="n">
-        <v>124.27</v>
+        <v>164.88</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.529999999999999</v>
+        <v>10.18</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3596,20 +3596,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>74.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="F15" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 74.6; priority 75.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.8; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3643,17 +3643,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3672,15 +3672,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>597.92</v>
+        <v>107.5</v>
       </c>
       <c r="T15" t="n">
-        <v>703.9400000000001</v>
+        <v>124.27</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>10.48</v>
+        <v>8.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.76</v>
+        <v>22.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>14.1</v>
+        <v>13.14</v>
       </c>
       <c r="AB15" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3714,69 +3714,69 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>687.6</v>
+        <v>122.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>70.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>76</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>64.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK15" t="n">
-        <v>82.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.56</v>
+        <v>2.64</v>
       </c>
       <c r="AM15" t="n">
-        <v>9.369999999999999</v>
+        <v>10.51</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.11</v>
+        <v>17.19</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AP15" t="n">
-        <v>662.5712</v>
+        <v>117.7098</v>
       </c>
       <c r="AQ15" t="n">
-        <v>629.9704</v>
+        <v>112.1115</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>76</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>64.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>82.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="AX15" t="n">
-        <v>680.66</v>
+        <v>119.18</v>
       </c>
       <c r="AY15" t="n">
-        <v>703.9400000000001</v>
+        <v>124.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.78</v>
+        <v>4.21</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.15</v>
+        <v>9.42</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>74.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>75.2</v>
+        <v>74.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 74.2; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.9; priority 74.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3896,14 +3896,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>6.41</v>
+        <v>5.56</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.38</v>
+        <v>15.11</v>
       </c>
       <c r="AA16" t="n">
         <v>12.85</v>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>62.62</v>
+        <v>62.55</v>
       </c>
       <c r="AH16" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="AI16" t="n">
-        <v>68.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>71.5</v>
@@ -3939,29 +3939,29 @@
         <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AM16" t="n">
-        <v>10.09</v>
+        <v>10.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.67</v>
+        <v>13.64</v>
       </c>
       <c r="AO16" t="n">
         <v>1.06</v>
       </c>
       <c r="AP16" t="n">
-        <v>61.3402</v>
+        <v>61.2392</v>
       </c>
       <c r="AQ16" t="n">
-        <v>58.5804</v>
+        <v>58.5426</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>68.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>71.5</v>
@@ -3970,19 +3970,19 @@
         <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AX16" t="n">
-        <v>60.81</v>
+        <v>60.74</v>
       </c>
       <c r="AY16" t="n">
         <v>63.94</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>72.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>74.2</v>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 72.7; priority 74.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.1; priority 74.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4050,22 +4050,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.2%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.9%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4084,20 +4084,20 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>66.58</v>
+        <v>597.92</v>
       </c>
       <c r="T17" t="n">
-        <v>74.95999999999999</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -4106,16 +4106,16 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>7.36</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.97</v>
+        <v>24.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.87</v>
+        <v>14.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>-20.6</v>
+        <v>-23.32</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
@@ -4126,69 +4126,69 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>74.23999999999999</v>
+        <v>693.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>65</v>
+        <v>70.7</v>
       </c>
       <c r="AI17" t="n">
-        <v>70.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>68.09999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>82.8</v>
+        <v>79.2</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="AM17" t="n">
-        <v>9.630000000000001</v>
+        <v>10.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>15.01</v>
+        <v>18.46</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AP17" t="n">
-        <v>71.9072</v>
+        <v>660.9632</v>
       </c>
       <c r="AQ17" t="n">
-        <v>68.70480000000001</v>
+        <v>629.4737</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>70.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>68.09999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>82.8</v>
+        <v>79.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AX17" t="n">
-        <v>72.59999999999999</v>
+        <v>673.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>74.95999999999999</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.24</v>
+        <v>4.89</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.06</v>
+        <v>10.13</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4214,24 +4214,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="F18" t="n">
-        <v>71.8</v>
+        <v>73.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4240,42 +4236,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 72.7; priority 71.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 72.3; priority 73.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.0%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4294,149 +4290,127 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>246.403</v>
+        <v>66.58</v>
       </c>
       <c r="T18" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+        <v>74.95999999999999</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>11.88</v>
+        <v>5.92</v>
       </c>
       <c r="Z18" t="n">
-        <v>43.54</v>
+        <v>18.32</v>
       </c>
       <c r="AA18" t="n">
-        <v>25.96</v>
+        <v>12.87</v>
       </c>
       <c r="AB18" t="n">
-        <v>-33.36</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>30.34</v>
-      </c>
+        <v>-20.6</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Quality globale</t>
+        </is>
+      </c>
       <c r="AG18" t="n">
-        <v>291.56</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+        <v>74.45999999999999</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL18" t="n">
-        <v>-0.51</v>
+        <v>2.82</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.78</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AN18" t="n">
-        <v>17.88</v>
+        <v>15.15</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="AP18" t="n">
-        <v>282.9226</v>
+        <v>71.77119999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>265.4813</v>
+        <v>68.6544</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>80.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>42.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV18" t="n">
         <v>82.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="AX18" t="n">
-        <v>291.56</v>
+        <v>72.11</v>
       </c>
       <c r="AY18" t="n">
-        <v>315.2</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>4282539048960</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>82.8</v>
-      </c>
+        <v>8.460000000000001</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
       <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4446,20 +4420,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>68.3</v>
+        <v>72.5</v>
       </c>
       <c r="F19" t="n">
-        <v>70.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,42 +4446,42 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 65.28. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 68.3; priority 70.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 72.5; priority 71.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.8%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4522,127 +4500,149 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>62.06</v>
+        <v>246.403</v>
       </c>
       <c r="T19" t="n">
-        <v>65.28</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>-1.85</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.39</v>
+        <v>43.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.550000000000001</v>
+        <v>25.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>30.23</v>
+      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>Min volatility</t>
-        </is>
-      </c>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
-        <v>63.81</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>82.8</v>
-      </c>
+        <v>290.55</v>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>2.82</v>
+        <v>-0.85</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.62</v>
+        <v>4.42</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.61</v>
+        <v>17.16</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="AP19" t="n">
-        <v>63.322</v>
+        <v>282.9024</v>
       </c>
       <c r="AQ19" t="n">
-        <v>63.1007</v>
+        <v>265.4762</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>48.5</v>
+        <v>79.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>78.3</v>
+        <v>42.1</v>
       </c>
       <c r="AV19" t="n">
         <v>82.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="AX19" t="n">
-        <v>62.34</v>
+        <v>290.55</v>
       </c>
       <c r="AY19" t="n">
-        <v>64.68000000000001</v>
+        <v>315.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.77</v>
+        <v>2.7</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="inlineStr"/>
-      <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="inlineStr"/>
+        <v>9.44</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>4267410980864</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>79.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="F20" t="n">
         <v>70.40000000000001</v>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 10.1% sopra MA50: evitare inseguimento.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 65.28. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 79.9; priority 70.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 68.3; priority 70.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4728,20 +4728,20 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>54.81</v>
+        <v>62.06</v>
       </c>
       <c r="T20" t="n">
-        <v>72.27</v>
+        <v>65.28</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4750,89 +4750,89 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>26.15</v>
+        <v>-1.83</v>
       </c>
       <c r="Z20" t="n">
-        <v>59.57</v>
+        <v>0.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.62</v>
+        <v>9.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>-17.8</v>
+        <v>-12.85</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>69.86</v>
+        <v>63.99</v>
       </c>
       <c r="AH20" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>78.2</v>
       </c>
-      <c r="AI20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>69.40000000000001</v>
-      </c>
       <c r="AK20" t="n">
-        <v>58.4</v>
+        <v>82.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.35</v>
+        <v>2.76</v>
       </c>
       <c r="AM20" t="n">
-        <v>36.34</v>
+        <v>1.31</v>
       </c>
       <c r="AN20" t="n">
-        <v>25.26</v>
+        <v>6.72</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.85</v>
+        <v>0.7</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.4606</v>
+        <v>63.3138</v>
       </c>
       <c r="AQ20" t="n">
-        <v>54.8679</v>
+        <v>63.0971</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="AU20" t="n">
-        <v>69.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>58.4</v>
+        <v>82.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AX20" t="n">
-        <v>65.27</v>
+        <v>62.34</v>
       </c>
       <c r="AY20" t="n">
-        <v>72.27</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10.08</v>
+        <v>1.07</v>
       </c>
       <c r="BA20" t="n">
-        <v>27.32</v>
+        <v>1.42</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>71.5</v>
+        <v>74.2</v>
       </c>
       <c r="F21" t="n">
-        <v>54.3</v>
+        <v>57.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 71.5; priority 54.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 74.2; priority 57.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.7%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>10.23</v>
+        <v>12.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>43.74</v>
+        <v>47.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.98</v>
+        <v>46.97</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>31.15</v>
+        <v>31.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.04</v>
+        <v>16.42</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,57 +4980,57 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>203.42</v>
+        <v>208.19</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-5.36</v>
+        <v>-3.14</v>
       </c>
       <c r="AM21" t="n">
-        <v>11.65</v>
+        <v>14.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>74.39</v>
+        <v>74.81</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AP21" t="n">
-        <v>204.6939</v>
+        <v>204.7893</v>
       </c>
       <c r="AQ21" t="n">
-        <v>188.6554</v>
+        <v>188.6792</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT21" t="n">
-        <v>82.2</v>
+        <v>88.3</v>
       </c>
       <c r="AU21" t="n">
         <v>14.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AX21" t="n">
-        <v>203.42</v>
+        <v>205.1</v>
       </c>
       <c r="AY21" t="n">
         <v>235.4656</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.62</v>
+        <v>1.66</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.83</v>
+        <v>10.34</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4926793580544</v>
+        <v>5042570002432</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5064,16 +5064,16 @@
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>82.2</v>
+        <v>88.3</v>
       </c>
       <c r="BL21" t="n">
-        <v>69.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="BM21" t="n">
         <v>14.1</v>
       </c>
       <c r="BN21" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54.5</v>
+        <v>55.7</v>
       </c>
       <c r="F22" t="n">
-        <v>56.1</v>
+        <v>57.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 54.5; priority 56.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 55.7; priority 57.5; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,22 +5132,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 6.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.1%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 424.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 428.69 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 357.13 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 361.39 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>357.13</v>
+        <v>361.39</v>
       </c>
       <c r="T22" t="n">
-        <v>424.57</v>
+        <v>428.69</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -5184,20 +5184,20 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-15.68</v>
+        <v>-14.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>26.35</v>
+        <v>27.05</v>
       </c>
       <c r="AA22" t="n">
         <v>17.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>-18.16</v>
+        <v>-17.19</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,65 +5212,65 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>357.13</v>
+        <v>361.39</v>
       </c>
       <c r="AH22" t="n">
-        <v>69.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>36.4</v>
+        <v>38.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>64.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AK22" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AL22" t="n">
-        <v>-7.61</v>
+        <v>-6.18</v>
       </c>
       <c r="AM22" t="n">
-        <v>2.93</v>
+        <v>3.11</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.54</v>
+        <v>27.08</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AP22" t="n">
-        <v>380.728</v>
+        <v>380.915</v>
       </c>
       <c r="AQ22" t="n">
-        <v>362.1529</v>
+        <v>361.74</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>36.4</v>
+        <v>38.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>64.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AV22" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AX22" t="n">
-        <v>357.13</v>
+        <v>361.39</v>
       </c>
       <c r="AY22" t="n">
         <v>386.38</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-6.2</v>
+        <v>-5.13</v>
       </c>
       <c r="BA22" t="n">
-        <v>-1.39</v>
+        <v>-0.1</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>66.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="F2" t="n">
-        <v>65.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 66.1; priority 65.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 64.8; priority 63.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 6.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 64.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.1%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>13.93</v>
+        <v>11.92</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.34</v>
+        <v>9.69</v>
       </c>
       <c r="AA2" t="n">
-        <v>30.96</v>
+        <v>30.98</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>31.51</v>
+        <v>30.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.77</v>
+        <v>24.14</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,57 +888,57 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>244.19</v>
+        <v>238</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-10.45</v>
+        <v>-11.52</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.39</v>
+        <v>4.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.67</v>
+        <v>23.57</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="AP2" t="n">
-        <v>252.8082</v>
+        <v>253.5492</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.3466</v>
+        <v>232.3924</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>76.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="AU2" t="n">
         <v>38.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>74.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX2" t="n">
-        <v>244.19</v>
+        <v>238</v>
       </c>
       <c r="AY2" t="n">
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-3.41</v>
+        <v>-6.13</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.1</v>
+        <v>2.41</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2626778562560</v>
+        <v>2560192151552</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>76.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="BL2" t="n">
-        <v>56.2</v>
+        <v>57.9</v>
       </c>
       <c r="BM2" t="n">
         <v>38.1</v>
       </c>
       <c r="BN2" t="n">
-        <v>74.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -996,20 +996,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>68.8</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>64.2</v>
+        <v>58</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 68.8; priority 64.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 64.0; priority 58.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1033,27 +1033,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 9.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.5%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.1%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1072,15 +1072,15 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>12.936</v>
+        <v>8.7643</v>
       </c>
       <c r="T3" t="n">
-        <v>18.17</v>
+        <v>11.61</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1094,61 +1094,61 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>24.71</v>
+        <v>15.96</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.12</v>
+        <v>60.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.34</v>
+        <v>23.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>-29.37</v>
+        <v>-44.26</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>17.616</v>
+        <v>10.182</v>
       </c>
       <c r="AH3" t="n">
-        <v>51.1</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
         <v>100</v>
       </c>
       <c r="AJ3" t="n">
-        <v>45.9</v>
+        <v>31.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>60.6</v>
+        <v>82.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.8</v>
+        <v>-4.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>27.26</v>
+        <v>24.37</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.74</v>
+        <v>1.75</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.83</v>
+        <v>0.08</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.083</v>
+        <v>10.1739</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.4439</v>
+        <v>8.7546</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
@@ -1158,25 +1158,25 @@
         <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>50.9</v>
+        <v>36.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>60.6</v>
+        <v>82.8</v>
       </c>
       <c r="AW3" t="n">
         <v>755</v>
       </c>
       <c r="AX3" t="n">
-        <v>16.544</v>
+        <v>10.182</v>
       </c>
       <c r="AY3" t="n">
-        <v>18.17</v>
+        <v>11.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.529999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>21.96</v>
+        <v>16.3</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>63.3</v>
+        <v>62.3</v>
       </c>
       <c r="F4" t="n">
-        <v>58.8</v>
+        <v>57.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 63.3; priority 58.8; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 62.3; priority 57.2; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.5%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.2%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>-0.36</v>
+        <v>-1.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>-13.55</v>
+        <v>-15.28</v>
       </c>
       <c r="AA4" t="n">
         <v>23.99</v>
@@ -1312,10 +1312,10 @@
         <v>-33.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>24.01</v>
+        <v>23.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.86</v>
+        <v>20.49</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1324,57 +1324,57 @@
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>403.41</v>
+        <v>397.36</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-2.61</v>
+        <v>-3.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>-16.13</v>
+        <v>-18.71</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.61</v>
+        <v>7.06</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="AP4" t="n">
-        <v>409.5508</v>
+        <v>410.3343</v>
       </c>
       <c r="AQ4" t="n">
-        <v>453.5009</v>
+        <v>452.9675</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
         <v>35</v>
       </c>
       <c r="AT4" t="n">
-        <v>36.4</v>
+        <v>32.6</v>
       </c>
       <c r="AU4" t="n">
         <v>44.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>73</v>
+        <v>70.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX4" t="n">
-        <v>403.41</v>
+        <v>397.36</v>
       </c>
       <c r="AY4" t="n">
         <v>460.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1.5</v>
+        <v>-3.16</v>
       </c>
       <c r="BA4" t="n">
-        <v>-11.05</v>
+        <v>-12.28</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>2996704903168</v>
+        <v>2951762673664</v>
       </c>
       <c r="BE4" t="n">
         <v>39.34</v>
@@ -1402,22 +1402,22 @@
         <v>30.27</v>
       </c>
       <c r="BI4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BJ4" t="n">
         <v>100</v>
       </c>
       <c r="BK4" t="n">
-        <v>36.4</v>
+        <v>32.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>70.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="BM4" t="n">
         <v>44.1</v>
       </c>
       <c r="BN4" t="n">
-        <v>73</v>
+        <v>70.5</v>
       </c>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
@@ -1434,20 +1434,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>64.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>57.8</v>
+        <v>52</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1461,7 +1465,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 64.2; priority 57.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 69.9; priority 52.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1481,17 +1485,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 69.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1501,136 +1505,158 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>8.7643</v>
+        <v>164.9777</v>
       </c>
       <c r="T5" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>235.4656</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>20.32</v>
+        <v>7.86</v>
       </c>
       <c r="Z5" t="n">
-        <v>66.09999999999999</v>
+        <v>40.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.18</v>
+        <v>47</v>
       </c>
       <c r="AB5" t="n">
-        <v>-44.26</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+        <v>-36.88</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15.75</v>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Energia pulita</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>10.584</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>81.7</v>
-      </c>
+        <v>200.42</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>3.48</v>
+        <v>-8.56</v>
       </c>
       <c r="AM5" t="n">
-        <v>29.65</v>
+        <v>8.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.3</v>
+        <v>72.47</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.14</v>
+        <v>1.54</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.1519</v>
+        <v>205.4982</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.738899999999999</v>
+        <v>188.7925</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>76</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>752</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>200.42</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>235.4656</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>4854372630528</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>100</v>
       </c>
-      <c r="AU5" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>755</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10.2879</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>21.11</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+      <c r="BK5" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>76</v>
+      </c>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>USA / Semiconductors</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1640,24 +1666,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>58.7</v>
+        <v>65.7</v>
       </c>
       <c r="F6" t="n">
-        <v>38.9</v>
+        <v>46.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,12 +1693,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 58.7; priority 38.9; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 65.7; priority 46.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1686,22 +1708,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 5.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.8% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 58.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.9%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 65.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.8%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1716,153 +1738,131 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>525.72</v>
+        <v>362.53</v>
       </c>
       <c r="T6" t="n">
-        <v>688.55</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+        <v>637.9</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-10.55</v>
+        <v>42.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>-15.95</v>
+        <v>122.87</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.28</v>
+        <v>34.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>16.17</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG6" t="n">
-        <v>584.59</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+        <v>570.91</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>59.4</v>
+      </c>
       <c r="AL6" t="n">
-        <v>-4.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>-13.05</v>
+        <v>55.39</v>
       </c>
       <c r="AN6" t="n">
-        <v>29.76</v>
+        <v>56.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.82</v>
+        <v>1.63</v>
       </c>
       <c r="AP6" t="n">
-        <v>621.4548</v>
+        <v>519.7898</v>
       </c>
       <c r="AQ6" t="n">
-        <v>660.1814000000001</v>
+        <v>400.714</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT6" t="n">
-        <v>23.4</v>
+        <v>100</v>
       </c>
       <c r="AU6" t="n">
-        <v>29.1</v>
+        <v>29.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>66.40000000000001</v>
+        <v>59.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX6" t="n">
-        <v>584.59</v>
+        <v>543.96</v>
       </c>
       <c r="AY6" t="n">
-        <v>635.29</v>
+        <v>637.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-5.93</v>
+        <v>9.83</v>
       </c>
       <c r="BA6" t="n">
-        <v>-11.45</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>1483936890880</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>66.40000000000001</v>
-      </c>
+        <v>42.47</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1872,20 +1872,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>63.1</v>
+        <v>57.5</v>
       </c>
       <c r="F7" t="n">
-        <v>32.2</v>
+        <v>36.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1899,12 +1903,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 63.1; priority 32.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 57.5; priority 36.9; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1914,22 +1918,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo 14.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 8.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 57.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.2%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1944,131 +1948,153 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>362.53</v>
+        <v>525.72</v>
       </c>
       <c r="T7" t="n">
-        <v>637.9</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>688.55</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>48.75</v>
+        <v>-12.73</v>
       </c>
       <c r="Z7" t="n">
-        <v>134.58</v>
+        <v>-17.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>34.89</v>
+        <v>36.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+        <v>-34.15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15.79</v>
+      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>591.01</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>40.3</v>
-      </c>
+        <v>570.98</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>4.32</v>
+        <v>-4.66</v>
       </c>
       <c r="AM7" t="n">
-        <v>62.68</v>
+        <v>-14.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.73</v>
+        <v>28.7</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.68</v>
+        <v>0.79</v>
       </c>
       <c r="AP7" t="n">
-        <v>515.6222</v>
+        <v>622.1468</v>
       </c>
       <c r="AQ7" t="n">
-        <v>399.3231</v>
+        <v>659.2712</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>752</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>570.98</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>635.29</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-13.39</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1449388933120</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>36</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>100</v>
       </c>
-      <c r="AU7" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>751</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>543.96</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>637.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
+      <c r="BK7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>62.9</v>
+      </c>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>USA / Social &amp; AI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2078,24 +2104,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="F8" t="n">
-        <v>31.4</v>
+        <v>28.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2109,12 +2131,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 37.9; priority 31.4; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 37.8; priority 28.5; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2124,22 +2146,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 37.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.0%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 37.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2154,151 +2176,131 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>343.25</v>
+        <v>20.205</v>
       </c>
       <c r="T8" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+        <v>30.11</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>-0.64</v>
+        <v>5.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>34.4</v>
+        <v>-17.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>57.97</v>
+        <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>360.62</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>157.88</v>
-      </c>
+        <v>-48.6</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
       <c r="AG8" t="n">
-        <v>396.68</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+        <v>26.22</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>61.8</v>
+      </c>
       <c r="AL8" t="n">
-        <v>-7.39</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>-12.82</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>16.78</v>
+        <v>-3.14</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.29</v>
+        <v>-0.09</v>
       </c>
       <c r="AP8" t="n">
-        <v>396.7224</v>
+        <v>24.2514</v>
       </c>
       <c r="AQ8" t="n">
-        <v>414.95</v>
+        <v>26.9634</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>75.2</v>
+        <v>61.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AX8" t="n">
-        <v>391</v>
+        <v>23.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>445.27</v>
+        <v>30.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.01</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>1489820450816</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>18.74</v>
-      </c>
+        <v>-2.76</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>75.2</v>
-      </c>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>USA / EV</t>
-        </is>
-      </c>
+      <c r="BP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2308,20 +2310,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E9" t="n">
-        <v>42.8</v>
+        <v>34.5</v>
       </c>
       <c r="F9" t="n">
-        <v>21.9</v>
+        <v>26.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2335,12 +2341,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 42.8; priority 21.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 34.5; priority 26.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2350,22 +2356,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 12.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 42.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.1%.</t>
+          <t>TSLA: scenario base High Risk, score 34.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.9%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2380,131 +2386,151 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>20.205</v>
+        <v>343.25</v>
       </c>
       <c r="T9" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>8.69</v>
+        <v>-6.43</v>
       </c>
       <c r="Z9" t="n">
-        <v>-14.87</v>
+        <v>23.66</v>
       </c>
       <c r="AA9" t="n">
-        <v>33.95</v>
+        <v>57.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>-48.6</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>356.63</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>152.64</v>
+      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>27.13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>50.2</v>
-      </c>
+        <v>381.59</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>11.03</v>
+        <v>-14.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>-5.37</v>
+        <v>-13.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1.67</v>
+        <v>15.25</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.05</v>
+        <v>0.26</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.1953</v>
+        <v>397.2486</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26.9741</v>
+        <v>415.1579</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT9" t="n">
-        <v>55.2</v>
+        <v>39</v>
       </c>
       <c r="AU9" t="n">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>50.2</v>
+        <v>69.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="AX9" t="n">
-        <v>23.01</v>
+        <v>381.59</v>
       </c>
       <c r="AY9" t="n">
-        <v>30.11</v>
+        <v>445.27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.13</v>
+        <v>-3.94</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+        <v>-8.09</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>1433146621952</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
+      <c r="BJ9" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>39</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>69.3</v>
+      </c>
       <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2528,10 +2554,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62.3</v>
+        <v>62.8</v>
       </c>
       <c r="F10" t="n">
-        <v>20.9</v>
+        <v>24.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 62.3; priority 20.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 62.8; priority 24.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,12 +2586,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 17.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 16.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.9%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.8%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2612,10 +2638,10 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>32.34</v>
+        <v>31.73</v>
       </c>
       <c r="Z10" t="n">
-        <v>121.2</v>
+        <v>124.72</v>
       </c>
       <c r="AA10" t="n">
         <v>38.13</v>
@@ -2624,10 +2650,10 @@
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>58.24</v>
+        <v>58.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>36.38</v>
+        <v>36.33</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2662,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1514.6</v>
+        <v>1508.4</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>14.79</v>
+        <v>15.53</v>
       </c>
       <c r="AM10" t="n">
-        <v>58.78</v>
+        <v>59.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.22</v>
+        <v>31.72</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="AP10" t="n">
-        <v>1284.3927</v>
+        <v>1291.2961</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1047.8913</v>
+        <v>1052.217</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2671,7 +2697,7 @@
         <v>18.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>27.1</v>
+        <v>31.5</v>
       </c>
       <c r="AW10" t="n">
         <v>764</v>
@@ -2683,10 +2709,10 @@
         <v>1514.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.92</v>
+        <v>16.81</v>
       </c>
       <c r="BA10" t="n">
-        <v>44.54</v>
+        <v>43.35</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2725,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>581364023296</v>
+        <v>580901470208</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2714,7 +2740,7 @@
         <v>12.99</v>
       </c>
       <c r="BI10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BJ10" t="n">
         <v>100</v>
@@ -2723,13 +2749,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="BM10" t="n">
         <v>18.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>27.1</v>
+        <v>31.5</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2756,10 +2782,10 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>79.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2773,7 +2799,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 78.7; priority 79.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.1; priority 79.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2793,7 +2819,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2844,13 +2870,13 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>13.84</v>
+        <v>13.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>41.41</v>
+        <v>39.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>15.99</v>
+        <v>16</v>
       </c>
       <c r="AB11" t="n">
         <v>-19.17</v>
@@ -2868,13 +2894,13 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>46.46</v>
+        <v>46.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>68.3</v>
+        <v>68</v>
       </c>
       <c r="AI11" t="n">
-        <v>93.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>65.5</v>
@@ -2883,29 +2909,29 @@
         <v>82.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.25</v>
+        <v>-2.35</v>
       </c>
       <c r="AM11" t="n">
-        <v>22.36</v>
+        <v>21.78</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.92</v>
+        <v>17.62</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AP11" t="n">
-        <v>44.7763</v>
+        <v>44.9036</v>
       </c>
       <c r="AQ11" t="n">
-        <v>40.3085</v>
+        <v>40.3641</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
         <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>93.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>65.5</v>
@@ -2923,10 +2949,10 @@
         <v>49.485</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.76</v>
+        <v>2.66</v>
       </c>
       <c r="BA11" t="n">
-        <v>15.26</v>
+        <v>14.21</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2947,69 +2973,73 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3. Interessanti ma da attendere</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>76.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🟠 Attendi pullback</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Non inseguire il prezzo: imposta alert su pullback o tenuta supporto. Supporto 60D: 54.81.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 79.2; priority 66.0; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Normal risk</t>
+          <t>score 79.0; priority 76.2; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>prezzo 11.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.6%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 79.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3019,136 +3049,158 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>54.81</v>
+        <v>273.3367</v>
       </c>
       <c r="T12" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>24.52</v>
+        <v>15.51</v>
       </c>
       <c r="Z12" t="n">
-        <v>61.12</v>
+        <v>102.96</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.62</v>
+        <v>29.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>24.64</v>
+      </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>Value globale</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
-        <v>70.48</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>52.5</v>
-      </c>
+        <v>356.38</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>8.5</v>
+        <v>-8.25</v>
       </c>
       <c r="AM12" t="n">
-        <v>37.87</v>
+        <v>13.75</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.67</v>
+        <v>43.01</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="AP12" t="n">
-        <v>63.1764</v>
+        <v>359.4043</v>
       </c>
       <c r="AQ12" t="n">
-        <v>54.7527</v>
+        <v>306.049</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT12" t="n">
         <v>100</v>
       </c>
       <c r="AU12" t="n">
-        <v>69.40000000000001</v>
+        <v>40.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>52.5</v>
+        <v>78.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="AX12" t="n">
-        <v>65.25</v>
+        <v>356.38</v>
       </c>
       <c r="AY12" t="n">
-        <v>72.27</v>
+        <v>402.3797</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.56</v>
+        <v>-0.84</v>
       </c>
       <c r="BA12" t="n">
-        <v>28.72</v>
-      </c>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
+        <v>16.45</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>4346030850048</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>78.5</v>
+      </c>
       <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3158,24 +3210,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>80.2</v>
+        <v>75.3</v>
       </c>
       <c r="F13" t="n">
-        <v>77.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3184,22 +3232,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 80.2; priority 77.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 75.3; priority 75.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3209,17 +3257,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.8%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3229,7 +3277,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3238,149 +3286,127 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>273.3367</v>
+        <v>140.98</v>
       </c>
       <c r="T13" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+        <v>164.88</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>18.71</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>110.58</v>
+        <v>22.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>29.72</v>
+        <v>12.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>27.76</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>25.18</v>
-      </c>
+        <v>-21.07</v>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Azionario globale</t>
+        </is>
+      </c>
       <c r="AG13" t="n">
-        <v>364.26</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+        <v>159.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL13" t="n">
-        <v>-9.06</v>
+        <v>0.55</v>
       </c>
       <c r="AM13" t="n">
-        <v>13.6</v>
+        <v>10.56</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.13</v>
+        <v>16.62</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AP13" t="n">
-        <v>357.7434</v>
+        <v>155.3832</v>
       </c>
       <c r="AQ13" t="n">
-        <v>305.2947</v>
+        <v>146.7537</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>100</v>
+        <v>74.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>40.5</v>
+        <v>67.7</v>
       </c>
       <c r="AV13" t="n">
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="AX13" t="n">
-        <v>358.7757</v>
+        <v>158.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>402.3797</v>
+        <v>164.88</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="BA13" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>4442127073280</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>60</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>82.8</v>
-      </c>
+        <v>8.69</v>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3390,20 +3416,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>75.8</v>
+        <v>74.3</v>
       </c>
       <c r="F14" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3412,12 +3438,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 75.8; priority 76.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.3; priority 75.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,17 +3463,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3466,15 +3492,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>140.98</v>
+        <v>107.5</v>
       </c>
       <c r="T14" t="n">
-        <v>164.88</v>
+        <v>124.27</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3488,16 +3514,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>8.91</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.58</v>
+        <v>20.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.87</v>
+        <v>13.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3508,69 +3534,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>161.56</v>
+        <v>120.88</v>
       </c>
       <c r="AH14" t="n">
-        <v>72.8</v>
+        <v>70.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>75.8</v>
+        <v>72.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK14" t="n">
-        <v>82</v>
+        <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.16</v>
+        <v>0.78</v>
       </c>
       <c r="AM14" t="n">
-        <v>11.96</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.2</v>
+        <v>16.52</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AP14" t="n">
-        <v>155.0524</v>
+        <v>117.9476</v>
       </c>
       <c r="AQ14" t="n">
-        <v>146.6353</v>
+        <v>112.1922</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>75.8</v>
+        <v>72.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>82</v>
+        <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AX14" t="n">
-        <v>156.96</v>
+        <v>120.3</v>
       </c>
       <c r="AY14" t="n">
-        <v>164.88</v>
+        <v>124.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.2</v>
+        <v>2.49</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.18</v>
+        <v>7.74</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3596,21 +3622,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
+        <v>74</v>
+      </c>
+      <c r="F15" t="n">
         <v>74.8</v>
       </c>
-      <c r="F15" t="n">
-        <v>75.2</v>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>🟡 Metti alert / monitora</t>
@@ -3618,12 +3644,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 74.8; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.0; priority 74.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3643,17 +3669,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3672,15 +3698,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>107.5</v>
+        <v>597.92</v>
       </c>
       <c r="T15" t="n">
-        <v>124.27</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3690,20 +3716,20 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>8.32</v>
+        <v>9.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.61</v>
+        <v>21.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.14</v>
+        <v>14.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>-21.63</v>
+        <v>-23.32</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3714,69 +3740,69 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>122.67</v>
+        <v>682.52</v>
       </c>
       <c r="AH15" t="n">
-        <v>71.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>73.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK15" t="n">
-        <v>81.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AM15" t="n">
-        <v>10.51</v>
+        <v>8.56</v>
       </c>
       <c r="AN15" t="n">
-        <v>17.19</v>
+        <v>17.74</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AP15" t="n">
-        <v>117.7098</v>
+        <v>662.4696</v>
       </c>
       <c r="AQ15" t="n">
-        <v>112.1115</v>
+        <v>629.9450000000001</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>73.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>81.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="AX15" t="n">
-        <v>119.18</v>
+        <v>680.66</v>
       </c>
       <c r="AY15" t="n">
-        <v>124.27</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.21</v>
+        <v>3.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.42</v>
+        <v>8.35</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3812,10 +3838,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>73.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="F16" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3829,7 +3855,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 73.9; priority 74.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.7; priority 74.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,7 +3875,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3900,13 +3926,13 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>5.56</v>
+        <v>5.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.11</v>
+        <v>14.64</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.85</v>
+        <v>12.86</v>
       </c>
       <c r="AB16" t="n">
         <v>-16.33</v>
@@ -3924,13 +3950,13 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>62.55</v>
+        <v>62.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>69.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>67.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="AJ16" t="n">
         <v>71.5</v>
@@ -3939,29 +3965,29 @@
         <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.04</v>
+        <v>1.37</v>
       </c>
       <c r="AM16" t="n">
-        <v>10.14</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.64</v>
+        <v>13.41</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AP16" t="n">
-        <v>61.2392</v>
+        <v>61.3322</v>
       </c>
       <c r="AQ16" t="n">
-        <v>58.5426</v>
+        <v>58.5784</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>67.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="AU16" t="n">
         <v>71.5</v>
@@ -3973,16 +3999,16 @@
         <v>759</v>
       </c>
       <c r="AX16" t="n">
-        <v>60.74</v>
+        <v>60.81</v>
       </c>
       <c r="AY16" t="n">
         <v>63.94</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.85</v>
+        <v>6.22</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4008,20 +4034,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>74.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="F17" t="n">
-        <v>74.2</v>
+        <v>74</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4030,17 +4056,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 8.9% sopra MA50: evitare inseguimento.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 74.1; priority 74.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.5; priority 74.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4050,22 +4076,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.9%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4075,7 +4101,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4084,20 +4110,20 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>597.92</v>
+        <v>54.81</v>
       </c>
       <c r="T17" t="n">
-        <v>703.9400000000001</v>
+        <v>72.27</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -4106,89 +4132,89 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>9.630000000000001</v>
+        <v>24.76</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>57.81</v>
       </c>
       <c r="AA17" t="n">
-        <v>14.1</v>
+        <v>13.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>-23.32</v>
+        <v>-17.8</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>693.26</v>
+        <v>69.09</v>
       </c>
       <c r="AH17" t="n">
-        <v>70.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AI17" t="n">
-        <v>75.7</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>64.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>79.2</v>
+        <v>63.2</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.74</v>
+        <v>4.19</v>
       </c>
       <c r="AM17" t="n">
-        <v>10.25</v>
+        <v>34.84</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.46</v>
+        <v>24.71</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="AP17" t="n">
-        <v>660.9632</v>
+        <v>63.4452</v>
       </c>
       <c r="AQ17" t="n">
-        <v>629.4737</v>
+        <v>54.864</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>75.7</v>
+        <v>100</v>
       </c>
       <c r="AU17" t="n">
-        <v>64.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>79.2</v>
+        <v>63.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AX17" t="n">
-        <v>673.5</v>
+        <v>65.27</v>
       </c>
       <c r="AY17" t="n">
-        <v>703.9400000000001</v>
+        <v>72.27</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.89</v>
+        <v>8.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.13</v>
+        <v>25.93</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4224,7 +4250,7 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="F18" t="n">
         <v>73.8</v>
@@ -4236,12 +4262,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 72.3; priority 73.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 72.2; priority 73.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4256,12 +4282,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4312,13 +4338,13 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>5.92</v>
+        <v>6.72</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.32</v>
+        <v>17.27</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="AB18" t="n">
         <v>-20.6</v>
@@ -4336,13 +4362,13 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>74.45999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>65.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AI18" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AJ18" t="n">
         <v>68.09999999999999</v>
@@ -4351,29 +4377,29 @@
         <v>82.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="AM18" t="n">
-        <v>9.890000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="AN18" t="n">
-        <v>15.15</v>
+        <v>14.75</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AP18" t="n">
-        <v>71.77119999999999</v>
+        <v>71.8984</v>
       </c>
       <c r="AQ18" t="n">
-        <v>68.6544</v>
+        <v>68.7026</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AU18" t="n">
         <v>68.09999999999999</v>
@@ -4385,16 +4411,16 @@
         <v>755</v>
       </c>
       <c r="AX18" t="n">
-        <v>72.11</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>74.95999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.460000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
@@ -4420,24 +4446,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>72.5</v>
+        <v>70.3</v>
       </c>
       <c r="F19" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4446,17 +4468,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 18.17. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 72.5; priority 71.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 70.3; priority 72.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4471,17 +4493,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.7%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.7%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4500,149 +4522,127 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>246.403</v>
+        <v>12.936</v>
       </c>
       <c r="T19" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+        <v>18.17</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>11.5</v>
+        <v>25.61</v>
       </c>
       <c r="Z19" t="n">
-        <v>43.05</v>
+        <v>36.41</v>
       </c>
       <c r="AA19" t="n">
-        <v>25.98</v>
+        <v>21.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>-33.36</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>30.23</v>
-      </c>
+        <v>-29.37</v>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Robotica e automazione</t>
+        </is>
+      </c>
       <c r="AG19" t="n">
-        <v>290.55</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
+        <v>17.234</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>72.2</v>
+      </c>
       <c r="AL19" t="n">
-        <v>-0.85</v>
+        <v>-1.67</v>
       </c>
       <c r="AM19" t="n">
-        <v>4.42</v>
+        <v>23.61</v>
       </c>
       <c r="AN19" t="n">
-        <v>17.16</v>
+        <v>16.46</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="AP19" t="n">
-        <v>282.9024</v>
+        <v>16.1597</v>
       </c>
       <c r="AQ19" t="n">
-        <v>265.4762</v>
+        <v>14.4649</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="AU19" t="n">
-        <v>42.1</v>
+        <v>50.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>82.8</v>
+        <v>72.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AX19" t="n">
-        <v>290.55</v>
+        <v>16.544</v>
       </c>
       <c r="AY19" t="n">
-        <v>315.2</v>
+        <v>18.17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.7</v>
+        <v>6.65</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>4267410980864</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>82.8</v>
-      </c>
+        <v>19.14</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4652,20 +4652,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>68.3</v>
+        <v>72.8</v>
       </c>
       <c r="F20" t="n">
-        <v>70.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,42 +4678,42 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 65.28. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 68.3; priority 70.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 72.8; priority 72.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.1%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4728,198 +4732,216 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>62.06</v>
+        <v>246.403</v>
       </c>
       <c r="T20" t="n">
-        <v>65.28</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>-1.83</v>
+        <v>11.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.14</v>
+        <v>45.31</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.56</v>
+        <v>25.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>30.39</v>
+      </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>Min volatility</t>
-        </is>
-      </c>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>82.8</v>
-      </c>
+        <v>291.58</v>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>2.76</v>
+        <v>-0.38</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.31</v>
+        <v>5.12</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.72</v>
+        <v>17.27</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.3138</v>
+        <v>283.8059</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.0971</v>
+        <v>265.7985</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>48.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AU20" t="n">
-        <v>78.2</v>
+        <v>42.2</v>
       </c>
       <c r="AV20" t="n">
         <v>82.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="AX20" t="n">
-        <v>62.34</v>
+        <v>290.55</v>
       </c>
       <c r="AY20" t="n">
-        <v>64.68000000000001</v>
+        <v>315.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.07</v>
+        <v>2.74</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="inlineStr"/>
-      <c r="BF20" t="inlineStr"/>
-      <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
-      <c r="BI20" t="inlineStr"/>
-      <c r="BJ20" t="inlineStr"/>
-      <c r="BK20" t="inlineStr"/>
-      <c r="BL20" t="inlineStr"/>
-      <c r="BM20" t="inlineStr"/>
-      <c r="BN20" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>4282539048960</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>37</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO20" t="inlineStr"/>
-      <c r="BP20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2. Rischio da controllare</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>74.2</v>
+        <v>68.2</v>
       </c>
       <c r="F21" t="n">
-        <v>57.5</v>
+        <v>70.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🟥 Solo size piccola</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tieni in osservazione senza azione immediata; rivaluta dopo aggiornamento dati o news rilevanti.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 65.28. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 74.2; priority 57.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 68.2; priority 70.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 74.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.7%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.6%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4938,149 +4960,127 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>164.9777</v>
+        <v>62.06</v>
       </c>
       <c r="T21" t="n">
-        <v>235.4656</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+        <v>65.28</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>12.81</v>
+        <v>-2</v>
       </c>
       <c r="Z21" t="n">
-        <v>47.11</v>
+        <v>0.24</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.97</v>
+        <v>9.56</v>
       </c>
       <c r="AB21" t="n">
-        <v>-36.88</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>16.42</v>
-      </c>
+        <v>-12.85</v>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr"/>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Min volatility</t>
+        </is>
+      </c>
       <c r="AG21" t="n">
-        <v>208.19</v>
-      </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+        <v>63.71</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL21" t="n">
-        <v>-3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AM21" t="n">
-        <v>14.27</v>
+        <v>1.47</v>
       </c>
       <c r="AN21" t="n">
-        <v>74.81</v>
+        <v>6.61</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP21" t="n">
-        <v>204.7893</v>
+        <v>63.32</v>
       </c>
       <c r="AQ21" t="n">
-        <v>188.6792</v>
+        <v>63.1002</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
         <v>85</v>
       </c>
       <c r="AT21" t="n">
-        <v>88.3</v>
+        <v>48.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>14.1</v>
+        <v>78.2</v>
       </c>
       <c r="AV21" t="n">
         <v>82.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AX21" t="n">
-        <v>205.1</v>
+        <v>62.34</v>
       </c>
       <c r="AY21" t="n">
-        <v>235.4656</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.66</v>
+        <v>0.62</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="BD21" t="n">
-        <v>5042570002432</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>114.29</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>48</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>82.8</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
       <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>USA / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>55.7</v>
+        <v>54.1</v>
       </c>
       <c r="F22" t="n">
-        <v>57.5</v>
+        <v>55.6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 55.7; priority 57.5; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 54.1; priority 55.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,22 +5132,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 5.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.1%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 428.69 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 424.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 361.39 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 355.79 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>361.39</v>
+        <v>355.79</v>
       </c>
       <c r="T22" t="n">
-        <v>428.69</v>
+        <v>424.57</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -5184,20 +5184,20 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-14.19</v>
+        <v>-16</v>
       </c>
       <c r="Z22" t="n">
-        <v>27.05</v>
+        <v>25.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>17.79</v>
+        <v>17.81</v>
       </c>
       <c r="AB22" t="n">
-        <v>-17.19</v>
+        <v>-18.47</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,65 +5212,65 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>361.39</v>
+        <v>355.79</v>
       </c>
       <c r="AH22" t="n">
-        <v>70.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="AK22" t="n">
-        <v>67.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AL22" t="n">
-        <v>-6.18</v>
+        <v>-7.96</v>
       </c>
       <c r="AM22" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="AN22" t="n">
-        <v>27.08</v>
+        <v>26.54</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AP22" t="n">
-        <v>380.915</v>
+        <v>380.7012</v>
       </c>
       <c r="AQ22" t="n">
-        <v>361.74</v>
+        <v>362.1462</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>67.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AW22" t="n">
         <v>755</v>
       </c>
       <c r="AX22" t="n">
-        <v>361.39</v>
+        <v>355.79</v>
       </c>
       <c r="AY22" t="n">
         <v>386.38</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-5.13</v>
+        <v>-6.54</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0.1</v>
+        <v>-1.76</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>64.8</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>63.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 64.8; priority 63.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 66.0; priority 65.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 6.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 64.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.1%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>11.92</v>
+        <v>15.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.69</v>
+        <v>10.98</v>
       </c>
       <c r="AA2" t="n">
-        <v>30.98</v>
+        <v>30.97</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>30.83</v>
+        <v>32.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.14</v>
+        <v>24.49</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,45 +888,45 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>238</v>
+        <v>241.51</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-11.52</v>
+        <v>-9.15</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.9</v>
+        <v>5.96</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.57</v>
+        <v>24.14</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AP2" t="n">
-        <v>253.5492</v>
+        <v>254.214</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.3924</v>
+        <v>232.4602</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>72</v>
+        <v>77.7</v>
       </c>
       <c r="AU2" t="n">
         <v>38.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>70.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX2" t="n">
         <v>238</v>
@@ -935,10 +935,10 @@
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-6.13</v>
+        <v>-5</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.41</v>
+        <v>3.89</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2560192151552</v>
+        <v>2597949538304</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>72</v>
+        <v>77.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>57.9</v>
+        <v>55.9</v>
       </c>
       <c r="BM2" t="n">
         <v>38.1</v>
       </c>
       <c r="BN2" t="n">
-        <v>70.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -996,20 +996,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>61.6</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>55.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,37 +1027,37 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 64.0; priority 58.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 61.6; priority 55.8; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.1%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1068,131 +1072,153 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>8.7643</v>
+        <v>355.9989</v>
       </c>
       <c r="T3" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>460.52</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>15.96</v>
+        <v>-2.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>60.29</v>
+        <v>-16.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.28</v>
+        <v>23.99</v>
       </c>
       <c r="AB3" t="n">
-        <v>-44.26</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+        <v>-33.91</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>20.18</v>
+      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Energia pulita</t>
-        </is>
-      </c>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>10.182</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>82.8</v>
-      </c>
+        <v>390.34</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-4.83</v>
+        <v>-4.07</v>
       </c>
       <c r="AM3" t="n">
-        <v>24.37</v>
+        <v>-20.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.75</v>
+        <v>6.41</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.1739</v>
+        <v>410.7537</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.7546</v>
+        <v>452.4137</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>753</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>390.34</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>460.52</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-13.72</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>2899615154176</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>92</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>100</v>
       </c>
-      <c r="AU3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>755</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10.182</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+      <c r="BK3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>67.8</v>
+      </c>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1202,24 +1228,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>62.3</v>
+        <v>57.3</v>
       </c>
       <c r="F4" t="n">
-        <v>57.2</v>
+        <v>51.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1233,17 +1255,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 62.3; priority 57.2; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 57.3; priority 51.7; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1253,17 +1275,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.2%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 57.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1278,153 +1300,131 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>355.9989</v>
+        <v>8.7643</v>
       </c>
       <c r="T4" t="n">
-        <v>460.52</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>11.61</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>-1.64</v>
+        <v>9.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>-15.28</v>
+        <v>54.52</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.99</v>
+        <v>23.32</v>
       </c>
       <c r="AB4" t="n">
-        <v>-33.91</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>20.49</v>
-      </c>
+        <v>-44.26</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Energia pulita</t>
+        </is>
+      </c>
       <c r="AG4" t="n">
-        <v>397.36</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+        <v>9.914999999999999</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>75.7</v>
+      </c>
       <c r="AL4" t="n">
-        <v>-3.5</v>
+        <v>-4.35</v>
       </c>
       <c r="AM4" t="n">
-        <v>-18.71</v>
+        <v>22.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.06</v>
+        <v>0.85</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.29</v>
+        <v>0.04</v>
       </c>
       <c r="AP4" t="n">
-        <v>410.3343</v>
+        <v>10.1931</v>
       </c>
       <c r="AQ4" t="n">
-        <v>452.9675</v>
+        <v>8.769</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>32.6</v>
+        <v>90.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>44.1</v>
+        <v>36.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>70.5</v>
+        <v>75.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="AX4" t="n">
-        <v>397.36</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>460.52</v>
+        <v>11.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-3.16</v>
+        <v>-2.73</v>
       </c>
       <c r="BA4" t="n">
-        <v>-12.28</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>Software - Infrastructure</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>2951762673664</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>90</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>70.5</v>
-      </c>
+        <v>13.07</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>69.90000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>37.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 69.9; priority 52.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 58.2; priority 37.5; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1480,22 +1480,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 69.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 58.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.6%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1505,23 +1505,23 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>164.9777</v>
+        <v>525.72</v>
       </c>
       <c r="T5" t="n">
-        <v>235.4656</v>
+        <v>688.55</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1532,22 +1532,22 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>7.86</v>
+        <v>-10.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.71</v>
+        <v>-18.82</v>
       </c>
       <c r="AA5" t="n">
-        <v>47</v>
+        <v>36.26</v>
       </c>
       <c r="AB5" t="n">
-        <v>-36.88</v>
+        <v>-34.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.65</v>
+        <v>20.66</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.75</v>
+        <v>15.72</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1556,105 +1556,105 @@
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>200.42</v>
+        <v>568.4299999999999</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-8.56</v>
+        <v>-5.73</v>
       </c>
       <c r="AM5" t="n">
-        <v>8.15</v>
+        <v>-13.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>72.47</v>
+        <v>28.46</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.54</v>
+        <v>0.78</v>
       </c>
       <c r="AP5" t="n">
-        <v>205.4982</v>
+        <v>622.0728</v>
       </c>
       <c r="AQ5" t="n">
-        <v>188.7925</v>
+        <v>658.3557</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AT5" t="n">
-        <v>76.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>14.1</v>
+        <v>29.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>76</v>
+        <v>62.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX5" t="n">
-        <v>200.42</v>
+        <v>568.4299999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>235.4656</v>
+        <v>635.29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-2.47</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.16</v>
+        <v>-13.66</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>4854372630528</v>
+        <v>1442915942400</v>
       </c>
       <c r="BE5" t="n">
-        <v>62.97</v>
+        <v>32.84</v>
       </c>
       <c r="BF5" t="n">
-        <v>114.29</v>
+        <v>32.93</v>
       </c>
       <c r="BG5" t="n">
-        <v>85.2</v>
+        <v>33.1</v>
       </c>
       <c r="BH5" t="n">
-        <v>6.55</v>
+        <v>35.61</v>
       </c>
       <c r="BI5" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="BJ5" t="n">
         <v>100</v>
       </c>
       <c r="BK5" t="n">
-        <v>76.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="BL5" t="n">
-        <v>70.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="BM5" t="n">
-        <v>14.1</v>
+        <v>29.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>76</v>
+        <v>62.3</v>
       </c>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>USA / Semiconductors</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
@@ -1666,20 +1666,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>65.7</v>
+        <v>39.4</v>
       </c>
       <c r="F6" t="n">
-        <v>46.7</v>
+        <v>32.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1693,7 +1697,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 65.7; priority 46.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 39.4; priority 32.9; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1708,22 +1712,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 9.8% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 65.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.8%.</t>
+          <t>TSLA: scenario base High Risk, score 39.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1733,136 +1737,156 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>362.53</v>
+        <v>343.25</v>
       </c>
       <c r="T6" t="n">
-        <v>637.9</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>42.36</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>122.87</v>
+        <v>22.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>34.93</v>
+        <v>57.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>359.59</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>159.54</v>
+      </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>570.91</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>59.4</v>
-      </c>
+        <v>399.15</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-7.91</v>
       </c>
       <c r="AM6" t="n">
-        <v>55.39</v>
+        <v>-10.34</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.8</v>
+        <v>16.98</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.63</v>
+        <v>0.29</v>
       </c>
       <c r="AP6" t="n">
-        <v>519.7898</v>
+        <v>397.7966</v>
       </c>
       <c r="AQ6" t="n">
-        <v>400.714</v>
+        <v>415.4206</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AT6" t="n">
-        <v>100</v>
+        <v>50.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>29.5</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>59.4</v>
+        <v>78.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX6" t="n">
-        <v>543.96</v>
+        <v>381.59</v>
       </c>
       <c r="AY6" t="n">
-        <v>637.9</v>
+        <v>443.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.83</v>
+        <v>0.34</v>
       </c>
       <c r="BA6" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+        <v>-3.92</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>1499097071616</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>78.2</v>
+      </c>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1872,24 +1896,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>57.5</v>
+        <v>62.2</v>
       </c>
       <c r="F7" t="n">
-        <v>36.9</v>
+        <v>27.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1903,12 +1923,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 57.5; priority 36.9; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 62.2; priority 27.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1918,22 +1938,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo 8.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 16.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 57.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.2%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 62.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.2%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1948,153 +1968,131 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>525.72</v>
+        <v>362.53</v>
       </c>
       <c r="T7" t="n">
-        <v>688.55</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+        <v>637.9</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>-12.73</v>
+        <v>57.02</v>
       </c>
       <c r="Z7" t="n">
-        <v>-17.48</v>
+        <v>133.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>36.28</v>
+        <v>35.11</v>
       </c>
       <c r="AB7" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15.79</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG7" t="n">
-        <v>570.98</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+        <v>609.45</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>33.8</v>
+      </c>
       <c r="AL7" t="n">
-        <v>-4.66</v>
+        <v>8.59</v>
       </c>
       <c r="AM7" t="n">
-        <v>-14.23</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.7</v>
+        <v>60.17</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.79</v>
+        <v>1.71</v>
       </c>
       <c r="AP7" t="n">
-        <v>622.1468</v>
+        <v>524.3108</v>
       </c>
       <c r="AQ7" t="n">
-        <v>659.2712</v>
+        <v>402.2962</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT7" t="n">
-        <v>19.3</v>
+        <v>100</v>
       </c>
       <c r="AU7" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>62.9</v>
+        <v>33.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX7" t="n">
-        <v>570.98</v>
+        <v>543.96</v>
       </c>
       <c r="AY7" t="n">
-        <v>635.29</v>
+        <v>637.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-8.220000000000001</v>
+        <v>16.24</v>
       </c>
       <c r="BA7" t="n">
-        <v>-13.39</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>1449388933120</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>62.9</v>
-      </c>
+        <v>51.49</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2114,10 +2112,10 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>37.8</v>
+        <v>38.5</v>
       </c>
       <c r="F8" t="n">
-        <v>28.5</v>
+        <v>27.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2131,7 +2129,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 37.8; priority 28.5; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 38.5; priority 27.1; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2146,12 +2144,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.0% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 37.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 38.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2202,13 +2200,13 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>5.05</v>
+        <v>7.98</v>
       </c>
       <c r="Z8" t="n">
-        <v>-17.33</v>
+        <v>-16.09</v>
       </c>
       <c r="AA8" t="n">
-        <v>34</v>
+        <v>33.98</v>
       </c>
       <c r="AB8" t="n">
         <v>-48.6</v>
@@ -2226,65 +2224,65 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>26.22</v>
+        <v>26.52</v>
       </c>
       <c r="AH8" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>46.9</v>
+        <v>51.8</v>
       </c>
       <c r="AJ8" t="n">
         <v>15.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>61.8</v>
+        <v>58.3</v>
       </c>
       <c r="AL8" t="n">
-        <v>8.800000000000001</v>
+        <v>11.29</v>
       </c>
       <c r="AM8" t="n">
-        <v>-9.710000000000001</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>-3.14</v>
+        <v>-2.77</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AP8" t="n">
-        <v>24.2514</v>
+        <v>24.3314</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.9634</v>
+        <v>26.9534</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
         <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>46.9</v>
+        <v>51.8</v>
       </c>
       <c r="AU8" t="n">
         <v>20.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>61.8</v>
+        <v>58.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX8" t="n">
-        <v>23.01</v>
+        <v>23.625</v>
       </c>
       <c r="AY8" t="n">
         <v>30.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.119999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="BA8" t="n">
-        <v>-2.76</v>
+        <v>-1.61</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2310,12 +2308,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2324,10 +2322,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34.5</v>
+        <v>62.6</v>
       </c>
       <c r="F9" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2341,12 +2339,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 34.5; priority 26.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 62.6; priority 26.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2356,22 +2354,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 16.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 34.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.9%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 62.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.1%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1514.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2381,23 +2379,23 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>343.25</v>
+        <v>1109.5466</v>
       </c>
       <c r="T9" t="n">
-        <v>445.27</v>
+        <v>1514.6</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -2408,22 +2406,22 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>-6.43</v>
+        <v>25.88</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.66</v>
+        <v>128.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>57.98</v>
+        <v>38.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-53.77</v>
+        <v>-44.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>356.63</v>
+        <v>60.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>152.64</v>
+        <v>37.99</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2432,176 +2430,174 @@
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>381.59</v>
+        <v>1507.2</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>-14.25</v>
+        <v>19.07</v>
       </c>
       <c r="AM9" t="n">
-        <v>-13.19</v>
+        <v>57.03</v>
       </c>
       <c r="AN9" t="n">
-        <v>15.25</v>
+        <v>31.64</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.26</v>
+        <v>0.83</v>
       </c>
       <c r="AP9" t="n">
-        <v>397.2486</v>
+        <v>1298.5627</v>
       </c>
       <c r="AQ9" t="n">
-        <v>415.1579</v>
+        <v>1056.5172</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT9" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>69.3</v>
+        <v>34.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="AX9" t="n">
-        <v>381.59</v>
+        <v>1249</v>
       </c>
       <c r="AY9" t="n">
-        <v>445.27</v>
+        <v>1514.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-3.94</v>
+        <v>16.07</v>
       </c>
       <c r="BA9" t="n">
-        <v>-8.09</v>
+        <v>42.66</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1433146621952</v>
+        <v>607418253312</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.95</v>
+        <v>29.71</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>52.24</v>
       </c>
       <c r="BG9" t="n">
-        <v>15.8</v>
+        <v>13.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="BI9" t="inlineStr"/>
+        <v>12.99</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>72</v>
+      </c>
       <c r="BJ9" t="n">
-        <v>64.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="BK9" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>69.3</v>
+        <v>34.5</v>
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. Rischio da controllare</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>62.8</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>24.2</v>
+        <v>78.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🟥 Riduci rischio / non aumentare</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Non aumentare esposizione: controlla peso in portafoglio, stop mentale e correlazione con posizioni simili.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 62.8; priority 24.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 77.0; priority 78.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 16.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.8%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1514.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2611,7 +2607,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2620,191 +2616,169 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>1109.5466</v>
+        <v>39.31</v>
       </c>
       <c r="T10" t="n">
-        <v>1514.6</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+        <v>49.485</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>31.73</v>
+        <v>10.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>124.72</v>
+        <v>38.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.13</v>
+        <v>15.99</v>
       </c>
       <c r="AB10" t="n">
-        <v>-44.77</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>36.33</v>
-      </c>
+        <v>-19.17</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Mercati emergenti</t>
+        </is>
+      </c>
       <c r="AG10" t="n">
-        <v>1508.4</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+        <v>45.945</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL10" t="n">
-        <v>15.53</v>
+        <v>0.89</v>
       </c>
       <c r="AM10" t="n">
-        <v>59.08</v>
+        <v>21.82</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.72</v>
+        <v>17.46</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="AP10" t="n">
-        <v>1291.2961</v>
+        <v>45.0355</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1052.217</v>
+        <v>40.42</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
         <v>85</v>
       </c>
       <c r="AT10" t="n">
-        <v>100</v>
+        <v>87.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>18.4</v>
+        <v>65.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>31.5</v>
+        <v>82.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="AX10" t="n">
-        <v>1249</v>
+        <v>44.985</v>
       </c>
       <c r="AY10" t="n">
-        <v>1514.6</v>
+        <v>49.485</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.81</v>
+        <v>2.02</v>
       </c>
       <c r="BA10" t="n">
-        <v>43.35</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>580901470208</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>52.24</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>72</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>31.5</v>
-      </c>
+        <v>13.67</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>Europe / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>78.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>79.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 8.1% sopra MA50: evitare inseguimento.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 78.1; priority 79.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.9; priority 76.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2814,22 +2788,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2848,20 +2822,20 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>39.31</v>
+        <v>54.81</v>
       </c>
       <c r="T11" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2870,16 +2844,16 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>13.24</v>
+        <v>21.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>39.36</v>
+        <v>56.02</v>
       </c>
       <c r="AA11" t="n">
-        <v>16</v>
+        <v>13.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>-19.17</v>
+        <v>-17.8</v>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
@@ -2890,69 +2864,69 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>46.1</v>
+        <v>68.89</v>
       </c>
       <c r="AH11" t="n">
-        <v>68</v>
+        <v>77.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>82.8</v>
+        <v>66.3</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2.35</v>
+        <v>5.58</v>
       </c>
       <c r="AM11" t="n">
-        <v>21.78</v>
+        <v>34.16</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.62</v>
+        <v>24.56</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>44.9036</v>
+        <v>63.7216</v>
       </c>
       <c r="AQ11" t="n">
-        <v>40.3641</v>
+        <v>54.9753</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
         <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>65.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>82.8</v>
+        <v>66.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX11" t="n">
-        <v>44.985</v>
+        <v>65.27</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.66</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.21</v>
+        <v>25.31</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -3076,22 +3050,22 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>15.51</v>
+        <v>17.93</v>
       </c>
       <c r="Z12" t="n">
-        <v>102.96</v>
+        <v>100.89</v>
       </c>
       <c r="AA12" t="n">
-        <v>29.73</v>
+        <v>29.71</v>
       </c>
       <c r="AB12" t="n">
         <v>-29.81</v>
       </c>
       <c r="AC12" t="n">
-        <v>27.18</v>
+        <v>27.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>24.64</v>
+        <v>24.71</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -3100,29 +3074,29 @@
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
-        <v>356.38</v>
+        <v>357.77</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>-8.25</v>
+        <v>-7.58</v>
       </c>
       <c r="AM12" t="n">
-        <v>13.75</v>
+        <v>12.98</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.01</v>
+        <v>43.12</v>
       </c>
       <c r="AO12" t="n">
         <v>1.45</v>
       </c>
       <c r="AP12" t="n">
-        <v>359.4043</v>
+        <v>360.8119</v>
       </c>
       <c r="AQ12" t="n">
-        <v>306.049</v>
+        <v>306.7984</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
@@ -3138,19 +3112,19 @@
         <v>78.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX12" t="n">
         <v>356.38</v>
       </c>
       <c r="AY12" t="n">
-        <v>402.3797</v>
+        <v>400.8306</v>
       </c>
       <c r="AZ12" t="n">
         <v>-0.84</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.45</v>
+        <v>16.61</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -3163,7 +3137,7 @@
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>4346030850048</v>
+        <v>4362981605376</v>
       </c>
       <c r="BE12" t="n">
         <v>37.92</v>
@@ -3178,7 +3152,7 @@
         <v>20.03</v>
       </c>
       <c r="BI12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BJ12" t="n">
         <v>100</v>
@@ -3187,7 +3161,7 @@
         <v>100</v>
       </c>
       <c r="BL12" t="n">
-        <v>61.4</v>
+        <v>61.2</v>
       </c>
       <c r="BM12" t="n">
         <v>40.5</v>
@@ -3220,10 +3194,10 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>75.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>75.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3237,7 +3211,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 75.3; priority 75.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.6; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3257,7 +3231,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3308,10 +3282,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>8.949999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>22.52</v>
+        <v>22.23</v>
       </c>
       <c r="AA13" t="n">
         <v>12.89</v>
@@ -3332,13 +3306,13 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>159.5</v>
+        <v>159.24</v>
       </c>
       <c r="AH13" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AI13" t="n">
         <v>71.90000000000001</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>74.5</v>
       </c>
       <c r="AJ13" t="n">
         <v>67.7</v>
@@ -3347,29 +3321,29 @@
         <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.55</v>
+        <v>1.45</v>
       </c>
       <c r="AM13" t="n">
-        <v>10.56</v>
+        <v>10.45</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.62</v>
+        <v>16.53</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AP13" t="n">
-        <v>155.3832</v>
+        <v>155.7484</v>
       </c>
       <c r="AQ13" t="n">
-        <v>146.7537</v>
+        <v>146.8745</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>74.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AU13" t="n">
         <v>67.7</v>
@@ -3378,7 +3352,7 @@
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AX13" t="n">
         <v>158.2</v>
@@ -3387,10 +3361,10 @@
         <v>164.88</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.69</v>
+        <v>8.42</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3426,10 +3400,10 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>74.3</v>
+        <v>73.7</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3443,7 +3417,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 74.3; priority 75.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.7; priority 74.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3463,7 +3437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.5%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -3510,17 +3484,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>8.390000000000001</v>
+        <v>6.83</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.67</v>
+        <v>20.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="AB14" t="n">
         <v>-21.63</v>
@@ -3538,13 +3512,13 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>120.88</v>
+        <v>120.73</v>
       </c>
       <c r="AH14" t="n">
         <v>70.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>72.2</v>
+        <v>69.8</v>
       </c>
       <c r="AJ14" t="n">
         <v>66.90000000000001</v>
@@ -3553,29 +3527,29 @@
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.78</v>
+        <v>1.3</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.859999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="AN14" t="n">
-        <v>16.52</v>
+        <v>16.45</v>
       </c>
       <c r="AO14" t="n">
         <v>1.25</v>
       </c>
       <c r="AP14" t="n">
-        <v>117.9476</v>
+        <v>118.2122</v>
       </c>
       <c r="AQ14" t="n">
-        <v>112.1922</v>
+        <v>112.2751</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>72.2</v>
+        <v>69.8</v>
       </c>
       <c r="AU14" t="n">
         <v>66.90000000000001</v>
@@ -3584,7 +3558,7 @@
         <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX14" t="n">
         <v>120.3</v>
@@ -3593,10 +3567,10 @@
         <v>124.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.74</v>
+        <v>7.53</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3632,10 +3606,10 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>73.5</v>
       </c>
       <c r="F15" t="n">
-        <v>74.8</v>
+        <v>74.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3649,7 +3623,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 74.0; priority 74.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.5; priority 74.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3669,7 +3643,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3720,13 +3694,13 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>9.66</v>
+        <v>8.41</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.85</v>
+        <v>21.66</v>
       </c>
       <c r="AA15" t="n">
-        <v>14.13</v>
+        <v>14.12</v>
       </c>
       <c r="AB15" t="n">
         <v>-23.32</v>
@@ -3744,13 +3718,13 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>682.52</v>
+        <v>681.7</v>
       </c>
       <c r="AH15" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>74.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="AJ15" t="n">
         <v>64.40000000000001</v>
@@ -3759,29 +3733,29 @@
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="AM15" t="n">
-        <v>8.56</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AN15" t="n">
-        <v>17.74</v>
+        <v>17.67</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AP15" t="n">
-        <v>662.4696</v>
+        <v>664.1452</v>
       </c>
       <c r="AQ15" t="n">
-        <v>629.9450000000001</v>
+        <v>630.4322</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>74.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="AU15" t="n">
         <v>64.40000000000001</v>
@@ -3790,19 +3764,19 @@
         <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AX15" t="n">
-        <v>680.66</v>
+        <v>680.9400000000001</v>
       </c>
       <c r="AY15" t="n">
         <v>703.9400000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.03</v>
+        <v>2.64</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.35</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3828,20 +3802,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>73.7</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>74.7</v>
+        <v>74</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3850,12 +3824,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 18.17. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 73.7; priority 74.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 71.0; priority 74.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3865,7 +3839,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -3875,17 +3849,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.4%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3904,38 +3878,38 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>56.7</v>
+        <v>12.936</v>
       </c>
       <c r="T16" t="n">
-        <v>63.94</v>
+        <v>18.17</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>5.73</v>
+        <v>20.67</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.64</v>
+        <v>34.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.86</v>
+        <v>21.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>-16.33</v>
+        <v>-29.37</v>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
@@ -3946,69 +3920,69 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>62.22</v>
+        <v>17.092</v>
       </c>
       <c r="AH16" t="n">
-        <v>69.59999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>67.3</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="n">
-        <v>71.5</v>
+        <v>45.9</v>
       </c>
       <c r="AK16" t="n">
-        <v>82.8</v>
+        <v>77.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AM16" t="n">
-        <v>9.390000000000001</v>
+        <v>21.76</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.41</v>
+        <v>16.12</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AP16" t="n">
-        <v>61.3322</v>
+        <v>16.2409</v>
       </c>
       <c r="AQ16" t="n">
-        <v>58.5784</v>
+        <v>14.4862</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>67.3</v>
+        <v>100</v>
       </c>
       <c r="AU16" t="n">
-        <v>71.5</v>
+        <v>50.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>82.8</v>
+        <v>77.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="AX16" t="n">
-        <v>60.81</v>
+        <v>16.544</v>
       </c>
       <c r="AY16" t="n">
-        <v>63.94</v>
+        <v>18.17</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.45</v>
+        <v>5.24</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.22</v>
+        <v>17.99</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4034,20 +4008,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>80.5</v>
+        <v>72.8</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>73.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4056,17 +4030,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 8.9% sopra MA50: evitare inseguimento.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 80.5; priority 74.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 72.8; priority 73.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4076,22 +4050,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo 8.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.9%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.2%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4101,7 +4075,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4110,20 +4084,20 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>54.81</v>
+        <v>56.7</v>
       </c>
       <c r="T17" t="n">
-        <v>72.27</v>
+        <v>63.94</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -4132,89 +4106,89 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>24.76</v>
+        <v>3.59</v>
       </c>
       <c r="Z17" t="n">
-        <v>57.81</v>
+        <v>14.49</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.67</v>
+        <v>12.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>-17.8</v>
+        <v>-16.33</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>69.09</v>
+        <v>62.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>77.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AI17" t="n">
-        <v>100</v>
+        <v>63.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>69.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>63.2</v>
+        <v>82.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.19</v>
+        <v>2.34</v>
       </c>
       <c r="AM17" t="n">
-        <v>34.84</v>
+        <v>8.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>24.71</v>
+        <v>13.35</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="AP17" t="n">
-        <v>63.4452</v>
+        <v>61.4344</v>
       </c>
       <c r="AQ17" t="n">
-        <v>54.864</v>
+        <v>58.6138</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>100</v>
+        <v>63.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>69.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>63.2</v>
+        <v>82.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="AX17" t="n">
-        <v>65.27</v>
+        <v>60.81</v>
       </c>
       <c r="AY17" t="n">
-        <v>72.27</v>
+        <v>63.94</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8.9</v>
+        <v>1.18</v>
       </c>
       <c r="BA17" t="n">
-        <v>25.93</v>
+        <v>6.05</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4240,20 +4214,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>72.2</v>
+        <v>74.3</v>
       </c>
       <c r="F18" t="n">
-        <v>73.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4262,22 +4240,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 72.2; priority 73.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.3; priority 73.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -4287,17 +4265,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4316,127 +4294,149 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>66.58</v>
+        <v>246.403</v>
       </c>
       <c r="T18" t="n">
-        <v>74.95999999999999</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>6.72</v>
+        <v>15.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>17.27</v>
+        <v>46.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.88</v>
+        <v>25.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>30.81</v>
+      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Quality globale</t>
-        </is>
-      </c>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>82.8</v>
-      </c>
+        <v>295.63</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>1.92</v>
+        <v>0.28</v>
       </c>
       <c r="AM18" t="n">
-        <v>8.98</v>
+        <v>6.85</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.75</v>
+        <v>17.79</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP18" t="n">
-        <v>71.8984</v>
+        <v>284.6474</v>
       </c>
       <c r="AQ18" t="n">
-        <v>68.7026</v>
+        <v>266.1441</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>69.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>68.09999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="AV18" t="n">
         <v>82.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AX18" t="n">
-        <v>72.59999999999999</v>
+        <v>290.55</v>
       </c>
       <c r="AY18" t="n">
-        <v>74.95999999999999</v>
+        <v>315.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.64</v>
+        <v>3.86</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
-      <c r="BM18" t="inlineStr"/>
-      <c r="BN18" t="inlineStr"/>
+        <v>11.08</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>4342023192576</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>37</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4446,20 +4446,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>70.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>72.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 18.17. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 70.3; priority 72.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
+          <t>score 71.9; priority 73.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4522,38 +4522,38 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>12.936</v>
+        <v>66.58</v>
       </c>
       <c r="T19" t="n">
-        <v>18.17</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>25.61</v>
+        <v>5.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>36.41</v>
+        <v>17.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.37</v>
+        <v>12.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>-29.37</v>
+        <v>-20.6</v>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
@@ -4564,69 +4564,69 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>17.234</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AH19" t="n">
-        <v>50</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>67.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>45.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK19" t="n">
-        <v>72.2</v>
+        <v>82.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AM19" t="n">
-        <v>23.61</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AN19" t="n">
-        <v>16.46</v>
+        <v>14.84</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AP19" t="n">
-        <v>16.1597</v>
+        <v>72.047</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.4649</v>
+        <v>68.7529</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>100</v>
+        <v>67.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>50.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>72.2</v>
+        <v>82.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX19" t="n">
-        <v>16.544</v>
+        <v>72.94</v>
       </c>
       <c r="AY19" t="n">
-        <v>18.17</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.65</v>
+        <v>2.72</v>
       </c>
       <c r="BA19" t="n">
-        <v>19.14</v>
+        <v>7.65</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4652,24 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>72.8</v>
+        <v>68.8</v>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4678,42 +4674,42 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 65.25. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 72.8; priority 72.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 68.8; priority 70.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.7%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.3%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 65.25 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4732,216 +4728,198 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>246.403</v>
+        <v>62.06</v>
       </c>
       <c r="T20" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+        <v>65.25</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>11.9</v>
+        <v>-1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>45.31</v>
+        <v>0.47</v>
       </c>
       <c r="AA20" t="n">
-        <v>25.97</v>
+        <v>9.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>-33.36</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>35.34</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>30.39</v>
-      </c>
+        <v>-12.85</v>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Min volatility</t>
+        </is>
+      </c>
       <c r="AG20" t="n">
-        <v>291.58</v>
-      </c>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
+        <v>64.18000000000001</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL20" t="n">
-        <v>-0.38</v>
+        <v>2.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.12</v>
+        <v>2.57</v>
       </c>
       <c r="AN20" t="n">
-        <v>17.27</v>
+        <v>6.86</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AP20" t="n">
-        <v>283.8059</v>
+        <v>63.3432</v>
       </c>
       <c r="AQ20" t="n">
-        <v>265.7985</v>
+        <v>63.1035</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>81.09999999999999</v>
+        <v>49.9</v>
       </c>
       <c r="AU20" t="n">
-        <v>42.2</v>
+        <v>78.2</v>
       </c>
       <c r="AV20" t="n">
         <v>82.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="AX20" t="n">
-        <v>290.55</v>
+        <v>63.28</v>
       </c>
       <c r="AY20" t="n">
-        <v>315.2</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.74</v>
+        <v>1.32</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
-        </is>
-      </c>
-      <c r="BD20" t="n">
-        <v>4282539048960</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>37</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>82.8</v>
-      </c>
+        <v>1.71</v>
+      </c>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
       <c r="BO20" t="inlineStr"/>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>2. Rischio da controllare</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>68.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>70.3</v>
+        <v>54.8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟥 Solo size piccola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 65.28. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Tieni in osservazione senza azione immediata; rivaluta dopo aggiornamento dati o news rilevanti.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 68.2; priority 70.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 71.9; priority 54.8; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.6%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.28 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4956,131 +4934,153 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>62.06</v>
+        <v>164.9777</v>
       </c>
       <c r="T21" t="n">
-        <v>65.28</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
+        <v>235.4656</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.24</v>
+        <v>42.51</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.56</v>
+        <v>46.98</v>
       </c>
       <c r="AB21" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
+        <v>-36.88</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>16.1</v>
+      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>Min volatility</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>63.71</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>82.8</v>
-      </c>
+        <v>204.87</v>
+      </c>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>2.66</v>
+        <v>-7.1</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.47</v>
+        <v>10.89</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.61</v>
+        <v>73.62</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="AP21" t="n">
-        <v>63.32</v>
+        <v>206.1116</v>
       </c>
       <c r="AQ21" t="n">
-        <v>63.1002</v>
+        <v>188.919</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>48.1</v>
+        <v>84</v>
       </c>
       <c r="AU21" t="n">
-        <v>78.2</v>
+        <v>14.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>82.8</v>
+        <v>78.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AX21" t="n">
-        <v>62.34</v>
+        <v>200.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>64.68000000000001</v>
+        <v>235.4656</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.62</v>
+        <v>-0.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
-      <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr"/>
-      <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="inlineStr"/>
-      <c r="BL21" t="inlineStr"/>
-      <c r="BM21" t="inlineStr"/>
-      <c r="BN21" t="inlineStr"/>
+        <v>8.44</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>4962156281856</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>84</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>78.8</v>
+      </c>
       <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>USA / Semiconductors</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54.1</v>
+        <v>49.8</v>
       </c>
       <c r="F22" t="n">
-        <v>55.6</v>
+        <v>50.8</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 54.1; priority 55.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 49.8; priority 50.8; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,22 +5132,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 49.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.6%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 424.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 417.50 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 355.79 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 343.71 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>355.79</v>
+        <v>343.71</v>
       </c>
       <c r="T22" t="n">
-        <v>424.57</v>
+        <v>417.5</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -5188,16 +5188,16 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-16</v>
+        <v>-20.47</v>
       </c>
       <c r="Z22" t="n">
-        <v>25.87</v>
+        <v>21.99</v>
       </c>
       <c r="AA22" t="n">
-        <v>17.81</v>
+        <v>17.91</v>
       </c>
       <c r="AB22" t="n">
-        <v>-18.47</v>
+        <v>-21.24</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,65 +5212,65 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>355.79</v>
+        <v>343.71</v>
       </c>
       <c r="AH22" t="n">
-        <v>69.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>35.6</v>
+        <v>26</v>
       </c>
       <c r="AJ22" t="n">
-        <v>63.9</v>
+        <v>61.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>65.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="AL22" t="n">
-        <v>-7.96</v>
+        <v>-10.14</v>
       </c>
       <c r="AM22" t="n">
-        <v>2.55</v>
+        <v>-1.43</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.54</v>
+        <v>25.05</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>380.7012</v>
+        <v>380.0256</v>
       </c>
       <c r="AQ22" t="n">
-        <v>362.1462</v>
+        <v>362.4847</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>35.6</v>
+        <v>26</v>
       </c>
       <c r="AU22" t="n">
-        <v>63.9</v>
+        <v>61.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>65.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="AW22" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX22" t="n">
-        <v>355.79</v>
+        <v>343.71</v>
       </c>
       <c r="AY22" t="n">
         <v>386.38</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-6.54</v>
+        <v>-9.56</v>
       </c>
       <c r="BA22" t="n">
-        <v>-1.76</v>
+        <v>-5.18</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="F2" t="n">
-        <v>65.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 66.0; priority 65.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 65.5; priority 64.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>15.26</v>
+        <v>14.87</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.98</v>
+        <v>11.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>30.97</v>
+        <v>30.98</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>32.12</v>
+        <v>31.26</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.49</v>
+        <v>24.19</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,42 +888,42 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>241.51</v>
+        <v>238.55</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-9.15</v>
+        <v>-11.69</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.96</v>
+        <v>2.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.14</v>
+        <v>23.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="AP2" t="n">
-        <v>254.214</v>
+        <v>254.7736</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.4602</v>
+        <v>232.5094</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>77.7</v>
+        <v>75.5</v>
       </c>
       <c r="AU2" t="n">
         <v>38.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>72.3</v>
+        <v>70.2</v>
       </c>
       <c r="AW2" t="n">
         <v>753</v>
@@ -935,10 +935,10 @@
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-5</v>
+        <v>-6.37</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.89</v>
+        <v>2.6</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2597949538304</v>
+        <v>2566108479488</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>77.7</v>
+        <v>75.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>55.9</v>
+        <v>57.3</v>
       </c>
       <c r="BM2" t="n">
         <v>38.1</v>
       </c>
       <c r="BN2" t="n">
-        <v>72.3</v>
+        <v>70.2</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>61.6</v>
+        <v>62.4</v>
       </c>
       <c r="F3" t="n">
-        <v>55.8</v>
+        <v>56.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 61.6; priority 55.8; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 62.4; priority 56.7; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.0%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.0%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>-2.66</v>
+        <v>-1</v>
       </c>
       <c r="Z3" t="n">
-        <v>-16.45</v>
+        <v>-16.66</v>
       </c>
       <c r="AA3" t="n">
         <v>23.99</v>
@@ -1106,10 +1106,10 @@
         <v>-33.91</v>
       </c>
       <c r="AC3" t="n">
-        <v>23.22</v>
+        <v>23.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>20.18</v>
+        <v>20.2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1118,36 +1118,36 @@
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>390.34</v>
+        <v>390.74</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-4.07</v>
+        <v>-3.36</v>
       </c>
       <c r="AM3" t="n">
-        <v>-20.31</v>
+        <v>-17.99</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.41</v>
+        <v>6.19</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AP3" t="n">
-        <v>410.7537</v>
+        <v>411.1971</v>
       </c>
       <c r="AQ3" t="n">
-        <v>452.4137</v>
+        <v>451.873</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
         <v>35</v>
       </c>
       <c r="AT3" t="n">
-        <v>30</v>
+        <v>33.6</v>
       </c>
       <c r="AU3" t="n">
         <v>44.1</v>
@@ -1165,10 +1165,10 @@
         <v>460.52</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-4.97</v>
+        <v>-4.98</v>
       </c>
       <c r="BA3" t="n">
-        <v>-13.72</v>
+        <v>-13.53</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2899615154176</v>
+        <v>2902586556416</v>
       </c>
       <c r="BE3" t="n">
         <v>39.34</v>
@@ -1196,16 +1196,16 @@
         <v>30.27</v>
       </c>
       <c r="BI3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BJ3" t="n">
         <v>100</v>
       </c>
       <c r="BK3" t="n">
-        <v>30</v>
+        <v>33.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="BM3" t="n">
         <v>44.1</v>
@@ -1238,10 +1238,10 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>57.3</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>51.7</v>
+        <v>52.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 57.3; priority 51.7; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 58.0; priority 52.8; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 57.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.7%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 58.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.3%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>9.43</v>
+        <v>9.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>54.52</v>
+        <v>56.47</v>
       </c>
       <c r="AA4" t="n">
         <v>23.32</v>
@@ -1350,53 +1350,53 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>9.914999999999999</v>
+        <v>10.082</v>
       </c>
       <c r="AH4" t="n">
-        <v>29.3</v>
+        <v>29.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>90.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>31.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>75.7</v>
+        <v>77.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>-4.35</v>
+        <v>-6.59</v>
       </c>
       <c r="AM4" t="n">
-        <v>22.25</v>
+        <v>22.47</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.85</v>
+        <v>1.42</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.1931</v>
+        <v>10.2175</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.769</v>
+        <v>8.7845</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
         <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>90.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AU4" t="n">
         <v>36.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>75.7</v>
+        <v>77.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX4" t="n">
         <v>9.914999999999999</v>
@@ -1405,10 +1405,10 @@
         <v>11.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-2.73</v>
+        <v>-1.33</v>
       </c>
       <c r="BA4" t="n">
-        <v>13.07</v>
+        <v>14.77</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58.2</v>
+        <v>59.5</v>
       </c>
       <c r="F5" t="n">
-        <v>37.5</v>
+        <v>38.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 58.2; priority 37.5; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 59.5; priority 38.8; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 8.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 58.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>-10.85</v>
+        <v>-7.54</v>
       </c>
       <c r="Z5" t="n">
-        <v>-18.82</v>
+        <v>-18.06</v>
       </c>
       <c r="AA5" t="n">
         <v>36.26</v>
@@ -1544,10 +1544,10 @@
         <v>-34.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.66</v>
+        <v>20.61</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.72</v>
+        <v>15.68</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1556,57 +1556,57 @@
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>568.4299999999999</v>
+        <v>566.98</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-5.73</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>-13.33</v>
+        <v>-12.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.46</v>
+        <v>28.31</v>
       </c>
       <c r="AO5" t="n">
         <v>0.78</v>
       </c>
       <c r="AP5" t="n">
-        <v>622.0728</v>
+        <v>621.8278</v>
       </c>
       <c r="AQ5" t="n">
-        <v>658.3557</v>
+        <v>657.4289</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
         <v>35</v>
       </c>
       <c r="AT5" t="n">
-        <v>22.1</v>
+        <v>27.3</v>
       </c>
       <c r="AU5" t="n">
         <v>29.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="AW5" t="n">
         <v>753</v>
       </c>
       <c r="AX5" t="n">
-        <v>568.4299999999999</v>
+        <v>566.98</v>
       </c>
       <c r="AY5" t="n">
         <v>635.29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.82</v>
       </c>
       <c r="BA5" t="n">
-        <v>-13.66</v>
+        <v>-13.76</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1442915942400</v>
+        <v>1439235178496</v>
       </c>
       <c r="BE5" t="n">
         <v>32.84</v>
@@ -1640,16 +1640,16 @@
         <v>100</v>
       </c>
       <c r="BK5" t="n">
-        <v>22.1</v>
+        <v>27.3</v>
       </c>
       <c r="BL5" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="BM5" t="n">
         <v>29.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>39.4</v>
+        <v>40.6</v>
       </c>
       <c r="F6" t="n">
-        <v>32.9</v>
+        <v>34.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 39.4; priority 32.9; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 40.6; priority 34.2; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 39.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
+          <t>TSLA: scenario base High Risk, score 40.6, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1764,22 +1764,22 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>3.89</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.4</v>
+        <v>24.51</v>
       </c>
       <c r="AA6" t="n">
-        <v>57.99</v>
+        <v>57.97</v>
       </c>
       <c r="AB6" t="n">
         <v>-53.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>359.59</v>
+        <v>376.32</v>
       </c>
       <c r="AD6" t="n">
-        <v>159.54</v>
+        <v>162.45</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1788,36 +1788,36 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>399.15</v>
+        <v>406.43</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-7.91</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="AM6" t="n">
-        <v>-10.34</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>16.98</v>
+        <v>16.32</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="AP6" t="n">
-        <v>397.7966</v>
+        <v>398.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>415.4206</v>
+        <v>415.6944</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
         <v>55</v>
       </c>
       <c r="AT6" t="n">
-        <v>50.9</v>
+        <v>55.6</v>
       </c>
       <c r="AU6" t="n">
         <v>0</v>
@@ -1832,13 +1832,13 @@
         <v>381.59</v>
       </c>
       <c r="AY6" t="n">
-        <v>443.3</v>
+        <v>442.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.34</v>
+        <v>2.04</v>
       </c>
       <c r="BA6" t="n">
-        <v>-3.92</v>
+        <v>-2.23</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1499097071616</v>
+        <v>1526438821888</v>
       </c>
       <c r="BE6" t="n">
         <v>3.95</v>
@@ -1870,7 +1870,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>50.9</v>
+        <v>55.6</v>
       </c>
       <c r="BL6" t="n">
         <v>0</v>
@@ -1896,20 +1896,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>62.2</v>
+        <v>39.1</v>
       </c>
       <c r="F7" t="n">
-        <v>27.2</v>
+        <v>33.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 62.2; priority 27.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 39.1; priority 33.1; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo 16.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 62.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1963,24 +1963,24 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>362.53</v>
+        <v>20.205</v>
       </c>
       <c r="T7" t="n">
-        <v>637.9</v>
+        <v>30.11</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1994,16 +1994,16 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>57.02</v>
+        <v>6.79</v>
       </c>
       <c r="Z7" t="n">
-        <v>133.28</v>
+        <v>-17.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>35.11</v>
+        <v>33.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>-35.74</v>
+        <v>-48.6</v>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
@@ -2014,69 +2014,69 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>609.45</v>
+        <v>25.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>57.9</v>
+        <v>21.7</v>
       </c>
       <c r="AI7" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24.3</v>
+        <v>15.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>33.8</v>
+        <v>68.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>8.59</v>
+        <v>12.78</v>
       </c>
       <c r="AM7" t="n">
-        <v>65.68000000000001</v>
+        <v>-11.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.17</v>
+        <v>-3.47</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.71</v>
+        <v>-0.1</v>
       </c>
       <c r="AP7" t="n">
-        <v>524.3108</v>
+        <v>24.3892</v>
       </c>
       <c r="AQ7" t="n">
-        <v>402.2962</v>
+        <v>26.9372</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>29.3</v>
+        <v>20.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>33.8</v>
+        <v>68.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="AX7" t="n">
-        <v>543.96</v>
+        <v>24.07</v>
       </c>
       <c r="AY7" t="n">
-        <v>637.9</v>
+        <v>30.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.24</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>51.49</v>
+        <v>-3.66</v>
       </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -2102,20 +2102,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>38.5</v>
+        <v>61.6</v>
       </c>
       <c r="F8" t="n">
-        <v>27.1</v>
+        <v>24.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 38.5; priority 27.1; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 61.6; priority 24.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo 9.0% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 17.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 38.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 61.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.2%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2169,24 +2169,24 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>20.205</v>
+        <v>362.53</v>
       </c>
       <c r="T8" t="n">
-        <v>30.11</v>
+        <v>637.9</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2200,16 +2200,16 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>7.98</v>
+        <v>60.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>-16.09</v>
+        <v>137.47</v>
       </c>
       <c r="AA8" t="n">
-        <v>33.98</v>
+        <v>35.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>-48.6</v>
+        <v>-35.74</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
@@ -2220,69 +2220,69 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>26.52</v>
+        <v>619.96</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>58.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>51.8</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.3</v>
+        <v>24.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>58.3</v>
+        <v>29.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>11.29</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>-8.960000000000001</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>-2.77</v>
+        <v>60.35</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.08</v>
+        <v>1.72</v>
       </c>
       <c r="AP8" t="n">
-        <v>24.3314</v>
+        <v>528.8706</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.9534</v>
+        <v>403.9168</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AT8" t="n">
-        <v>51.8</v>
+        <v>100</v>
       </c>
       <c r="AU8" t="n">
-        <v>20.3</v>
+        <v>29.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>58.3</v>
+        <v>29.9</v>
       </c>
       <c r="AW8" t="n">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="AX8" t="n">
-        <v>23.625</v>
+        <v>543.96</v>
       </c>
       <c r="AY8" t="n">
-        <v>30.11</v>
+        <v>637.9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.99</v>
+        <v>17.22</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.61</v>
+        <v>53.49</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="F9" t="n">
-        <v>26.2</v>
+        <v>12.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 62.6; priority 26.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 60.5; priority 12.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 16.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 20.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 62.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 16.1%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.5%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1514.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1576.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2391,7 +2391,7 @@
         <v>1109.5466</v>
       </c>
       <c r="T9" t="n">
-        <v>1514.6</v>
+        <v>1576</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>25.88</v>
+        <v>31.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>128.6</v>
+        <v>137.07</v>
       </c>
       <c r="AA9" t="n">
-        <v>38.1</v>
+        <v>38.16</v>
       </c>
       <c r="AB9" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>60.8</v>
+        <v>63.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>37.99</v>
+        <v>39.28</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2430,29 +2430,29 @@
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>1507.2</v>
+        <v>1576</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>19.07</v>
+        <v>18.76</v>
       </c>
       <c r="AM9" t="n">
-        <v>57.03</v>
+        <v>65.98</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.64</v>
+        <v>33.54</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="AP9" t="n">
-        <v>1298.5627</v>
+        <v>1307.8918</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1056.5172</v>
+        <v>1061.1137</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
@@ -2462,25 +2462,25 @@
         <v>100</v>
       </c>
       <c r="AU9" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>34.5</v>
+        <v>16.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AX9" t="n">
         <v>1249</v>
       </c>
       <c r="AY9" t="n">
-        <v>1514.6</v>
+        <v>1576</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.07</v>
+        <v>20.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>42.66</v>
+        <v>48.52</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>607418253312</v>
+        <v>628076642304</v>
       </c>
       <c r="BE9" t="n">
         <v>29.71</v>
@@ -2508,7 +2508,7 @@
         <v>12.99</v>
       </c>
       <c r="BI9" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="BJ9" t="n">
         <v>100</v>
@@ -2517,13 +2517,13 @@
         <v>100</v>
       </c>
       <c r="BL9" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BM9" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>34.5</v>
+        <v>16.8</v>
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
@@ -2550,10 +2550,10 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>78.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 77.0; priority 78.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.9; priority 79.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>EIMI.MI: scenario base Accumulate Carefully, score 77.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>10.31</v>
+        <v>12.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>38.53</v>
+        <v>38.75</v>
       </c>
       <c r="AA10" t="n">
         <v>15.99</v>
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>45.945</v>
+        <v>46.425</v>
       </c>
       <c r="AH10" t="n">
-        <v>67.8</v>
+        <v>68.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>87.2</v>
+        <v>90.2</v>
       </c>
       <c r="AJ10" t="n">
         <v>65.5</v>
@@ -2677,29 +2677,29 @@
         <v>82.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.89</v>
+        <v>-0.78</v>
       </c>
       <c r="AM10" t="n">
-        <v>21.82</v>
+        <v>22.72</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.46</v>
+        <v>17.84</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AP10" t="n">
-        <v>45.0355</v>
+        <v>45.1736</v>
       </c>
       <c r="AQ10" t="n">
-        <v>40.42</v>
+        <v>40.4772</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
         <v>85</v>
       </c>
       <c r="AT10" t="n">
-        <v>87.2</v>
+        <v>90.2</v>
       </c>
       <c r="AU10" t="n">
         <v>65.5</v>
@@ -2708,7 +2708,7 @@
         <v>82.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX10" t="n">
         <v>44.985</v>
@@ -2717,10 +2717,10 @@
         <v>49.485</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.67</v>
+        <v>14.69</v>
       </c>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
@@ -2746,20 +2746,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>80.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>76.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2768,12 +2772,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 8.1% sopra MA50: evitare inseguimento.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 80.9; priority 76.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 79.0; priority 76.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2783,27 +2787,27 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.1%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 79.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2818,131 +2822,153 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>54.81</v>
+        <v>273.3367</v>
       </c>
       <c r="T11" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>21.52</v>
+        <v>19.06</v>
       </c>
       <c r="Z11" t="n">
-        <v>56.02</v>
+        <v>103.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.66</v>
+        <v>29.71</v>
       </c>
       <c r="AB11" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>24.84</v>
+      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>Value globale</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="n">
-        <v>68.89</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>66.3</v>
-      </c>
+        <v>359.68</v>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>5.58</v>
+        <v>-10.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>34.16</v>
+        <v>12.47</v>
       </c>
       <c r="AN11" t="n">
-        <v>24.56</v>
+        <v>43.31</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AP11" t="n">
-        <v>63.7216</v>
+        <v>362.0613</v>
       </c>
       <c r="AQ11" t="n">
-        <v>54.9753</v>
+        <v>307.5641</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT11" t="n">
         <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>69.40000000000001</v>
+        <v>40.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>66.3</v>
+        <v>78.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="AX11" t="n">
-        <v>65.27</v>
+        <v>356.38</v>
       </c>
       <c r="AY11" t="n">
-        <v>72.27</v>
+        <v>396.7031</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.109999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BA11" t="n">
-        <v>25.31</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
+        <v>16.94</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>4386274148352</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>78.8</v>
+      </c>
       <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2952,21 +2978,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>76.2</v>
@@ -2978,12 +3000,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 8.2% sopra MA50: evitare inseguimento.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 79.0; priority 76.2; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 80.9; priority 76.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2993,27 +3015,27 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 79.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.8%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.2%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3028,153 +3050,131 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>273.3367</v>
+        <v>54.81</v>
       </c>
       <c r="T12" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+        <v>72.27</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>17.93</v>
+        <v>22.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>100.89</v>
+        <v>56.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>29.71</v>
+        <v>13.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>24.71</v>
-      </c>
+        <v>-17.8</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Value globale</t>
+        </is>
+      </c>
       <c r="AG12" t="n">
-        <v>357.77</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
+        <v>69.23</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>66.09999999999999</v>
+      </c>
       <c r="AL12" t="n">
-        <v>-7.58</v>
+        <v>4.03</v>
       </c>
       <c r="AM12" t="n">
-        <v>12.98</v>
+        <v>34.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.12</v>
+        <v>24.72</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="AP12" t="n">
-        <v>360.8119</v>
+        <v>64.0026</v>
       </c>
       <c r="AQ12" t="n">
-        <v>306.7984</v>
+        <v>55.0882</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT12" t="n">
         <v>100</v>
       </c>
       <c r="AU12" t="n">
-        <v>40.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>78.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="AX12" t="n">
-        <v>356.38</v>
+        <v>65.27</v>
       </c>
       <c r="AY12" t="n">
-        <v>400.8306</v>
+        <v>72.27</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.84</v>
+        <v>8.17</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>4362981605376</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>25</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>78.5</v>
-      </c>
+        <v>25.67</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
       <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3194,10 +3194,10 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 74.6; priority 75.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.9; priority 75.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3282,13 +3282,13 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>7.2</v>
+        <v>7.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>22.23</v>
+        <v>22.46</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="AB13" t="n">
         <v>-21.07</v>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>159.24</v>
+        <v>159.56</v>
       </c>
       <c r="AH13" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AJ13" t="n">
         <v>67.7</v>
@@ -3321,29 +3321,29 @@
         <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.45</v>
+        <v>0.26</v>
       </c>
       <c r="AM13" t="n">
-        <v>10.45</v>
+        <v>10.39</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.53</v>
+        <v>16.59</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AP13" t="n">
-        <v>155.7484</v>
+        <v>156.1016</v>
       </c>
       <c r="AQ13" t="n">
-        <v>146.8745</v>
+        <v>146.9946</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AU13" t="n">
         <v>67.7</v>
@@ -3352,7 +3352,7 @@
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AX13" t="n">
         <v>158.2</v>
@@ -3361,10 +3361,10 @@
         <v>164.88</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.42</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>73.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 73.7; priority 74.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.9; priority 74.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 73.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -3488,13 +3488,13 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>6.83</v>
+        <v>7.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.14</v>
+        <v>20.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.16</v>
+        <v>13.15</v>
       </c>
       <c r="AB14" t="n">
         <v>-21.63</v>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>120.73</v>
+        <v>120.89</v>
       </c>
       <c r="AH14" t="n">
         <v>70.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>66.90000000000001</v>
@@ -3527,29 +3527,29 @@
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.3</v>
+        <v>0.38</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.74</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>16.45</v>
+        <v>16.48</v>
       </c>
       <c r="AO14" t="n">
         <v>1.25</v>
       </c>
       <c r="AP14" t="n">
-        <v>118.2122</v>
+        <v>118.4654</v>
       </c>
       <c r="AQ14" t="n">
-        <v>112.2751</v>
+        <v>112.3568</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="AU14" t="n">
         <v>66.90000000000001</v>
@@ -3558,7 +3558,7 @@
         <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX14" t="n">
         <v>120.3</v>
@@ -3567,10 +3567,10 @@
         <v>124.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.53</v>
+        <v>7.59</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3596,20 +3596,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>73.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>74.3</v>
+        <v>74.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 73.5; priority 74.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.6; priority 74.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3643,17 +3643,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.7%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3672,15 +3672,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>597.92</v>
+        <v>56.7</v>
       </c>
       <c r="T15" t="n">
-        <v>703.9400000000001</v>
+        <v>63.94</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>8.41</v>
+        <v>4.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.66</v>
+        <v>15.52</v>
       </c>
       <c r="AA15" t="n">
-        <v>14.12</v>
+        <v>12.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3714,69 +3714,69 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>681.7</v>
+        <v>62.56</v>
       </c>
       <c r="AH15" t="n">
-        <v>69.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>72.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AJ15" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AK15" t="n">
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="AM15" t="n">
-        <v>8.460000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AN15" t="n">
-        <v>17.67</v>
+        <v>13.58</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AP15" t="n">
-        <v>664.1452</v>
+        <v>61.5328</v>
       </c>
       <c r="AQ15" t="n">
-        <v>630.4322</v>
+        <v>58.6502</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>72.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AV15" t="n">
         <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AX15" t="n">
-        <v>680.9400000000001</v>
+        <v>60.81</v>
       </c>
       <c r="AY15" t="n">
-        <v>703.9400000000001</v>
+        <v>63.94</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.64</v>
+        <v>1.67</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.130000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3802,20 +3802,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>73.5</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 18.17. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 71.0; priority 74.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
+          <t>score 73.5; priority 74.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.2%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3878,38 +3878,38 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>12.936</v>
+        <v>597.92</v>
       </c>
       <c r="T16" t="n">
-        <v>18.17</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>20.67</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="Z16" t="n">
-        <v>34.73</v>
+        <v>21.44</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.36</v>
+        <v>14.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>-29.37</v>
+        <v>-23.32</v>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
@@ -3920,69 +3920,69 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>17.092</v>
+        <v>681.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>49.7</v>
+        <v>69.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>100</v>
+        <v>72.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>45.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK16" t="n">
-        <v>77.8</v>
+        <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AM16" t="n">
-        <v>21.76</v>
+        <v>8.32</v>
       </c>
       <c r="AN16" t="n">
-        <v>16.12</v>
+        <v>17.62</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AP16" t="n">
-        <v>16.2409</v>
+        <v>665.7612</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.4862</v>
+        <v>630.9031</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>100</v>
+        <v>72.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>50.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>77.8</v>
+        <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="AX16" t="n">
-        <v>16.544</v>
+        <v>680.9400000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>18.17</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.24</v>
+        <v>2.32</v>
       </c>
       <c r="BA16" t="n">
-        <v>17.99</v>
+        <v>7.98</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4008,20 +4008,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 72.8; priority 73.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 72.4; priority 73.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4050,22 +4050,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 72.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.2%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4084,20 +4084,20 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>56.7</v>
+        <v>66.58</v>
       </c>
       <c r="T17" t="n">
-        <v>63.94</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -4106,16 +4106,16 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>3.59</v>
+        <v>6.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.49</v>
+        <v>17.86</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.85</v>
+        <v>12.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>-16.33</v>
+        <v>-20.6</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
@@ -4126,69 +4126,69 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>62.16</v>
+        <v>74.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>69.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="AI17" t="n">
-        <v>63.9</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AJ17" t="n">
-        <v>71.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK17" t="n">
         <v>82.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="AM17" t="n">
-        <v>8.83</v>
+        <v>9.42</v>
       </c>
       <c r="AN17" t="n">
-        <v>13.35</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AP17" t="n">
-        <v>61.4344</v>
+        <v>72.1952</v>
       </c>
       <c r="AQ17" t="n">
-        <v>58.6138</v>
+        <v>68.804</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>63.9</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>71.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV17" t="n">
         <v>82.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="AX17" t="n">
-        <v>60.81</v>
+        <v>72.94</v>
       </c>
       <c r="AY17" t="n">
-        <v>63.94</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.05</v>
+        <v>8.08</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>74.3</v>
+        <v>74.5</v>
       </c>
       <c r="F18" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 74.3; priority 73.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 74.5; priority 73.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4312,22 +4312,22 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>15.7</v>
+        <v>16.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>46.45</v>
+        <v>47.04</v>
       </c>
       <c r="AA18" t="n">
-        <v>25.96</v>
+        <v>25.97</v>
       </c>
       <c r="AB18" t="n">
         <v>-33.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>35.83</v>
+        <v>35.29</v>
       </c>
       <c r="AD18" t="n">
-        <v>30.81</v>
+        <v>30.34</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -4336,39 +4336,39 @@
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>295.63</v>
+        <v>291.13</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.28</v>
+        <v>-2.59</v>
       </c>
       <c r="AM18" t="n">
-        <v>6.85</v>
+        <v>4.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>17.79</v>
+        <v>17.29</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>284.6474</v>
+        <v>285.3621</v>
       </c>
       <c r="AQ18" t="n">
-        <v>266.1441</v>
+        <v>266.4564</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="AV18" t="n">
         <v>82.8</v>
@@ -4383,10 +4383,10 @@
         <v>315.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.86</v>
+        <v>2.02</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.08</v>
+        <v>9.26</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>4342023192576</v>
+        <v>4275929874432</v>
       </c>
       <c r="BE18" t="n">
         <v>27.15</v>
@@ -4420,13 +4420,13 @@
         <v>100</v>
       </c>
       <c r="BK18" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="BL18" t="n">
-        <v>42.6</v>
+        <v>43.9</v>
       </c>
       <c r="BM18" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="BN18" t="n">
         <v>82.8</v>
@@ -4446,17 +4446,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>71.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F19" t="n">
         <v>73.40000000000001</v>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 18.17. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 71.9; priority 73.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 70.8; priority 73.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 71.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4522,38 +4522,38 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>66.58</v>
+        <v>12.936</v>
       </c>
       <c r="T19" t="n">
-        <v>74.95999999999999</v>
+        <v>18.17</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>5.73</v>
+        <v>22.78</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.05</v>
+        <v>35.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.88</v>
+        <v>21.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>-20.6</v>
+        <v>-29.37</v>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
@@ -4564,69 +4564,69 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>74.01000000000001</v>
+        <v>17.272</v>
       </c>
       <c r="AH19" t="n">
-        <v>64.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="AI19" t="n">
-        <v>67.8</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
-        <v>68.09999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="AK19" t="n">
-        <v>82.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.63</v>
+        <v>0.43</v>
       </c>
       <c r="AM19" t="n">
-        <v>9.130000000000001</v>
+        <v>21.69</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.84</v>
+        <v>16.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AP19" t="n">
-        <v>72.047</v>
+        <v>16.3266</v>
       </c>
       <c r="AQ19" t="n">
-        <v>68.7529</v>
+        <v>14.5083</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>67.8</v>
+        <v>100</v>
       </c>
       <c r="AU19" t="n">
-        <v>68.09999999999999</v>
+        <v>50.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>82.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX19" t="n">
-        <v>72.94</v>
+        <v>16.544</v>
       </c>
       <c r="AY19" t="n">
-        <v>74.95999999999999</v>
+        <v>18.17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.72</v>
+        <v>5.79</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.65</v>
+        <v>19.05</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4662,10 +4662,10 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 68.8; priority 70.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 69.1; priority 71.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.3%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.5%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>-1.26</v>
+        <v>-0.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.47</v>
+        <v>1.28</v>
       </c>
       <c r="AA20" t="n">
         <v>9.56</v>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>64.18000000000001</v>
+        <v>64.31</v>
       </c>
       <c r="AH20" t="n">
         <v>61.9</v>
       </c>
       <c r="AI20" t="n">
-        <v>49.9</v>
+        <v>51.4</v>
       </c>
       <c r="AJ20" t="n">
         <v>78.2</v>
@@ -4789,29 +4789,29 @@
         <v>82.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.86</v>
+        <v>6.93</v>
       </c>
       <c r="AO20" t="n">
         <v>0.72</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.3432</v>
+        <v>63.3538</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.1035</v>
+        <v>63.1068</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>49.9</v>
+        <v>51.4</v>
       </c>
       <c r="AU20" t="n">
         <v>78.2</v>
@@ -4820,19 +4820,19 @@
         <v>82.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX20" t="n">
-        <v>63.28</v>
+        <v>63.37</v>
       </c>
       <c r="AY20" t="n">
         <v>64.68000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="F21" t="n">
-        <v>54.8</v>
+        <v>55.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 71.9; priority 54.8; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 72.8; priority 55.7; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 72.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>13.97</v>
       </c>
       <c r="Z21" t="n">
-        <v>42.51</v>
+        <v>43.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.98</v>
+        <v>46.93</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
@@ -4971,7 +4971,7 @@
         <v>31.37</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.1</v>
+        <v>16.12</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,42 +4980,42 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>204.87</v>
+        <v>205.19</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-7.1</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="AM21" t="n">
-        <v>10.89</v>
+        <v>11.79</v>
       </c>
       <c r="AN21" t="n">
-        <v>73.62</v>
+        <v>71.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AP21" t="n">
-        <v>206.1116</v>
+        <v>206.7045</v>
       </c>
       <c r="AQ21" t="n">
-        <v>188.919</v>
+        <v>189.0373</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
         <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>84</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AU21" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="AW21" t="n">
         <v>753</v>
@@ -5024,13 +5024,13 @@
         <v>200.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>235.4656</v>
+        <v>225.0577</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.6</v>
+        <v>-0.73</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.44</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4962156281856</v>
+        <v>4969906831360</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5058,22 +5058,22 @@
         <v>6.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="BJ21" t="n">
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>84</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="BL21" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="F22" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 49.8; priority 50.8; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 49.2; priority 50.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 9.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 49.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.6%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 49.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.1%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.71 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 340.82 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>343.71</v>
+        <v>340.82</v>
       </c>
       <c r="T22" t="n">
         <v>417.5</v>
@@ -5188,16 +5188,16 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-20.47</v>
+        <v>-20.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.99</v>
+        <v>21.3</v>
       </c>
       <c r="AA22" t="n">
         <v>17.91</v>
       </c>
       <c r="AB22" t="n">
-        <v>-21.24</v>
+        <v>-21.9</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,65 +5212,65 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>343.71</v>
+        <v>340.82</v>
       </c>
       <c r="AH22" t="n">
-        <v>66.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>26</v>
+        <v>25.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>61.5</v>
+        <v>61</v>
       </c>
       <c r="AK22" t="n">
-        <v>60.9</v>
+        <v>60.1</v>
       </c>
       <c r="AL22" t="n">
-        <v>-10.14</v>
+        <v>-11.65</v>
       </c>
       <c r="AM22" t="n">
-        <v>-1.43</v>
+        <v>-2.08</v>
       </c>
       <c r="AN22" t="n">
-        <v>25.05</v>
+        <v>24.66</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AP22" t="n">
-        <v>380.0256</v>
+        <v>379.2068</v>
       </c>
       <c r="AQ22" t="n">
-        <v>362.4847</v>
+        <v>362.8027</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>26</v>
+        <v>25.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>61.5</v>
+        <v>61</v>
       </c>
       <c r="AV22" t="n">
-        <v>60.9</v>
+        <v>60.1</v>
       </c>
       <c r="AW22" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX22" t="n">
-        <v>343.71</v>
+        <v>340.82</v>
       </c>
       <c r="AY22" t="n">
-        <v>386.38</v>
+        <v>377.9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-9.56</v>
+        <v>-10.12</v>
       </c>
       <c r="BA22" t="n">
-        <v>-5.18</v>
+        <v>-6.06</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="F2" t="n">
-        <v>64.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 65.5; priority 64.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 66.7; priority 66.4; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 6.4% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.7%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>14.87</v>
+        <v>16.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.89</v>
+        <v>15.37</v>
       </c>
       <c r="AA2" t="n">
-        <v>30.98</v>
+        <v>31.05</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>31.26</v>
+        <v>32.63</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.19</v>
+        <v>24.95</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,45 +888,45 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>238.55</v>
+        <v>246.02</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-11.69</v>
+        <v>-7.93</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.92</v>
+        <v>6.84</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.6</v>
+        <v>25.34</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="AP2" t="n">
-        <v>254.7736</v>
+        <v>255.4986</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.5094</v>
+        <v>232.5939</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>75.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="AV2" t="n">
-        <v>70.2</v>
+        <v>74.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX2" t="n">
         <v>238</v>
@@ -935,10 +935,10 @@
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-6.37</v>
+        <v>-3.71</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.6</v>
+        <v>5.77</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2566108479488</v>
+        <v>2646464266240</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>75.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>57.3</v>
+        <v>54.7</v>
       </c>
       <c r="BM2" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="BN2" t="n">
-        <v>70.2</v>
+        <v>74.2</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -996,24 +996,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>62.4</v>
+        <v>68.8</v>
       </c>
       <c r="F3" t="n">
-        <v>56.7</v>
+        <v>64.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1027,12 +1023,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 62.4; priority 56.7; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 68.8; priority 64.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1042,22 +1038,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 5.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.0%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1067,158 +1063,136 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>355.9989</v>
+        <v>12.936</v>
       </c>
       <c r="T3" t="n">
-        <v>460.52</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>18.17</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>-1</v>
+        <v>29.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>-16.66</v>
+        <v>40.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.99</v>
+        <v>21.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>-33.91</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>-29.37</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Robotica e automazione</t>
+        </is>
+      </c>
       <c r="AG3" t="n">
-        <v>390.74</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+        <v>17.972</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>61.1</v>
+      </c>
       <c r="AL3" t="n">
-        <v>-3.36</v>
+        <v>3.56</v>
       </c>
       <c r="AM3" t="n">
-        <v>-17.99</v>
+        <v>26.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.19</v>
+        <v>17.57</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.26</v>
+        <v>0.82</v>
       </c>
       <c r="AP3" t="n">
-        <v>411.1971</v>
+        <v>16.4273</v>
       </c>
       <c r="AQ3" t="n">
-        <v>451.873</v>
+        <v>14.5329</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT3" t="n">
-        <v>33.6</v>
+        <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>44.1</v>
+        <v>50.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>67.8</v>
+        <v>61.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AX3" t="n">
-        <v>390.34</v>
+        <v>16.544</v>
       </c>
       <c r="AY3" t="n">
-        <v>460.52</v>
+        <v>18.17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-4.98</v>
+        <v>9.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>-13.53</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>Software - Infrastructure</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>2902586556416</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>93</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>67.8</v>
-      </c>
+        <v>23.66</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1228,20 +1202,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>63.2</v>
       </c>
       <c r="F4" t="n">
-        <v>52.8</v>
+        <v>58.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1255,17 +1233,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 58.0; priority 52.8; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 63.2; priority 58.2; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1275,17 +1253,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 58.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.3%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 63.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.9%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1300,131 +1278,153 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8.7643</v>
+        <v>355.9989</v>
       </c>
       <c r="T4" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>460.52</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>9.83</v>
+        <v>0.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>56.47</v>
+        <v>-15.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.32</v>
+        <v>23.96</v>
       </c>
       <c r="AB4" t="n">
-        <v>-44.26</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+        <v>-33.91</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>20.66</v>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Energia pulita</t>
-        </is>
-      </c>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>10.082</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>77.8</v>
-      </c>
+        <v>399.76</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-6.59</v>
+        <v>-2.15</v>
       </c>
       <c r="AM4" t="n">
-        <v>22.47</v>
+        <v>-16.95</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.42</v>
+        <v>6.17</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.2175</v>
+        <v>411.7392</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.7845</v>
+        <v>451.3541</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AT4" t="n">
-        <v>91.40000000000001</v>
+        <v>36.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>36.6</v>
+        <v>44.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>77.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.914999999999999</v>
+        <v>390.34</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.61</v>
+        <v>460.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1.33</v>
+        <v>-2.91</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+        <v>-11.43</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>2969591349248</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>93</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>70.90000000000001</v>
+      </c>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1434,24 +1434,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>59.5</v>
+        <v>63.7</v>
       </c>
       <c r="F5" t="n">
-        <v>38.8</v>
+        <v>57.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1465,12 +1461,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 59.5; priority 38.8; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 63.7; priority 57.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1480,22 +1476,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 63.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.5%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1510,153 +1506,131 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>525.72</v>
+        <v>8.7643</v>
       </c>
       <c r="T5" t="n">
-        <v>688.55</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>11.61</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>-7.54</v>
+        <v>12.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>-18.06</v>
+        <v>59.54</v>
       </c>
       <c r="AA5" t="n">
-        <v>36.26</v>
+        <v>23.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>20.61</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15.68</v>
-      </c>
+        <v>-43.61</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Energia pulita</t>
+        </is>
+      </c>
       <c r="AG5" t="n">
-        <v>566.98</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>31</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL5" t="n">
-        <v>-8.050000000000001</v>
+        <v>-3.59</v>
       </c>
       <c r="AM5" t="n">
-        <v>-12.64</v>
+        <v>25.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.31</v>
+        <v>2.87</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.78</v>
+        <v>0.12</v>
       </c>
       <c r="AP5" t="n">
-        <v>621.8278</v>
+        <v>10.2478</v>
       </c>
       <c r="AQ5" t="n">
-        <v>657.4289</v>
+        <v>8.801</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT5" t="n">
-        <v>27.3</v>
+        <v>97.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>29.2</v>
+        <v>37</v>
       </c>
       <c r="AV5" t="n">
-        <v>62</v>
+        <v>82.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AX5" t="n">
-        <v>566.98</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>635.29</v>
+        <v>11.61</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-8.82</v>
+        <v>1.49</v>
       </c>
       <c r="BA5" t="n">
-        <v>-13.76</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>1439235178496</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>37</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>62</v>
-      </c>
+        <v>18.17</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1666,12 +1640,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1680,10 +1654,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.6</v>
+        <v>61.2</v>
       </c>
       <c r="F6" t="n">
-        <v>34.2</v>
+        <v>42</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1697,12 +1671,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 40.6; priority 34.2; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 61.2; priority 42.0; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1712,22 +1686,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 40.6, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.0%.</t>
+          <t>META: scenario base Hold / Monitor, score 61.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1737,23 +1711,23 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>343.25</v>
+        <v>525.72</v>
       </c>
       <c r="T6" t="n">
-        <v>445.27</v>
+        <v>688.55</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1764,22 +1738,22 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>3.89</v>
+        <v>-5.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>24.51</v>
+        <v>-14.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>57.97</v>
+        <v>36.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>-53.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>376.32</v>
+        <v>21.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>162.45</v>
+        <v>16.37</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1788,103 +1762,105 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>406.43</v>
+        <v>593.48</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-8.720000000000001</v>
+        <v>-4.03</v>
       </c>
       <c r="AM6" t="n">
-        <v>-9.970000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>16.32</v>
+        <v>28.85</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.28</v>
+        <v>0.79</v>
       </c>
       <c r="AP6" t="n">
-        <v>398.3</v>
+        <v>622.2082</v>
       </c>
       <c r="AQ6" t="n">
-        <v>415.6944</v>
+        <v>656.6682</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AT6" t="n">
-        <v>55.6</v>
+        <v>33.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AV6" t="n">
-        <v>78.2</v>
+        <v>68.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX6" t="n">
-        <v>381.59</v>
+        <v>566.98</v>
       </c>
       <c r="AY6" t="n">
-        <v>442.1</v>
+        <v>635.29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.04</v>
+        <v>-4.62</v>
       </c>
       <c r="BA6" t="n">
-        <v>-2.23</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1526438821888</v>
+        <v>1506503426048</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.95</v>
+        <v>32.84</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.9</v>
+        <v>32.93</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.8</v>
+        <v>33.1</v>
       </c>
       <c r="BH6" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="BI6" t="inlineStr"/>
+        <v>35.61</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>37</v>
+      </c>
       <c r="BJ6" t="n">
-        <v>64.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="BK6" t="n">
-        <v>55.6</v>
+        <v>33.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BN6" t="n">
-        <v>78.2</v>
+        <v>68.3</v>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
@@ -1896,20 +1872,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>39.1</v>
+        <v>41.1</v>
       </c>
       <c r="F7" t="n">
-        <v>33.1</v>
+        <v>34.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1923,7 +1903,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 39.1; priority 33.1; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 41.1; priority 34.7; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1943,17 +1923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
+          <t>TSLA: scenario base High Risk, score 41.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1972,127 +1952,147 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>20.205</v>
+        <v>343.25</v>
       </c>
       <c r="T7" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>6.79</v>
+        <v>3.94</v>
       </c>
       <c r="Z7" t="n">
-        <v>-17.3</v>
+        <v>28.84</v>
       </c>
       <c r="AA7" t="n">
-        <v>33.98</v>
+        <v>58.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>-48.6</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>373.77</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>164.46</v>
+      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>68.7</v>
-      </c>
+        <v>411.15</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>12.78</v>
+        <v>-7.25</v>
       </c>
       <c r="AM7" t="n">
-        <v>-11.45</v>
+        <v>-8</v>
       </c>
       <c r="AN7" t="n">
-        <v>-3.47</v>
+        <v>16.54</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.1</v>
+        <v>0.29</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.3892</v>
+        <v>399.3112</v>
       </c>
       <c r="AQ7" t="n">
-        <v>26.9372</v>
+        <v>416.0022</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
         <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>48.3</v>
+        <v>57.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>68.7</v>
+        <v>78.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="AX7" t="n">
-        <v>24.07</v>
+        <v>381.59</v>
       </c>
       <c r="AY7" t="n">
-        <v>30.11</v>
+        <v>442.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="BA7" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+        <v>-1.17</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1544165785600</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
+      <c r="BJ7" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>78.2</v>
+      </c>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2102,20 +2102,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>61.6</v>
+        <v>38.8</v>
       </c>
       <c r="F8" t="n">
-        <v>24.2</v>
+        <v>32.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 61.6; priority 24.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 38.8; priority 32.8; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo 17.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 61.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 17.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 38.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 637.90 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2169,24 +2169,24 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>362.53</v>
+        <v>20.205</v>
       </c>
       <c r="T8" t="n">
-        <v>637.9</v>
+        <v>30.11</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2200,16 +2200,16 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>60.06</v>
+        <v>6.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>137.47</v>
+        <v>-16.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>35.12</v>
+        <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>-35.74</v>
+        <v>-48.6</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
@@ -2220,69 +2220,69 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>619.96</v>
+        <v>26.02</v>
       </c>
       <c r="AH8" t="n">
-        <v>58.1</v>
+        <v>21.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24.3</v>
+        <v>15.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>29.9</v>
+        <v>68.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>8.300000000000001</v>
+        <v>10.14</v>
       </c>
       <c r="AM8" t="n">
-        <v>66.23999999999999</v>
+        <v>-12.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.35</v>
+        <v>-3.77</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.72</v>
+        <v>-0.11</v>
       </c>
       <c r="AP8" t="n">
-        <v>528.8706</v>
+        <v>24.4489</v>
       </c>
       <c r="AQ8" t="n">
-        <v>403.9168</v>
+        <v>26.9215</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>29.3</v>
+        <v>20.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>29.9</v>
+        <v>68.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AX8" t="n">
-        <v>543.96</v>
+        <v>24.705</v>
       </c>
       <c r="AY8" t="n">
-        <v>637.9</v>
+        <v>30.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.22</v>
+        <v>6.43</v>
       </c>
       <c r="BA8" t="n">
-        <v>53.49</v>
+        <v>-3.35</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2308,24 +2308,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>60.5</v>
+        <v>59.4</v>
       </c>
       <c r="F9" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2339,7 +2335,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 60.5; priority 12.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 59.4; priority 12.1; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2354,22 +2350,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 20.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 21.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.5, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.5%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 59.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.2%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1576.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 647.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2388,71 +2384,83 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>1109.5466</v>
+        <v>362.53</v>
       </c>
       <c r="T9" t="n">
-        <v>1576</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+        <v>647.1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>31.76</v>
+        <v>64.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>137.07</v>
+        <v>146.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>38.16</v>
+        <v>35.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>-44.77</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>63.04</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>39.28</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG9" t="n">
-        <v>1576</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+        <v>647.1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>14</v>
+      </c>
       <c r="AL9" t="n">
-        <v>18.76</v>
+        <v>11.89</v>
       </c>
       <c r="AM9" t="n">
-        <v>65.98</v>
+        <v>75.02</v>
       </c>
       <c r="AN9" t="n">
-        <v>33.54</v>
+        <v>62.84</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.88</v>
+        <v>1.78</v>
       </c>
       <c r="AP9" t="n">
-        <v>1307.8918</v>
+        <v>533.9662</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1061.1137</v>
+        <v>405.6687</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
@@ -2462,142 +2470,112 @@
         <v>100</v>
       </c>
       <c r="AU9" t="n">
-        <v>18.4</v>
+        <v>29.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>16.8</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>766</v>
+        <v>751</v>
       </c>
       <c r="AX9" t="n">
-        <v>1249</v>
+        <v>543.96</v>
       </c>
       <c r="AY9" t="n">
-        <v>1576</v>
+        <v>647.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20.5</v>
+        <v>21.19</v>
       </c>
       <c r="BA9" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>628076642304</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>52.24</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>69</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>16.8</v>
-      </c>
+        <v>59.51</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>Europe / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>2. Rischio da controllare</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>77.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="F10" t="n">
-        <v>79.09999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟥 Riduci rischio / non aumentare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Non aumentare esposizione: controlla peso in portafoglio, stop mentale e correlazione con posizioni simili.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 77.9; priority 79.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 59.3; priority 3.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Accumulate Carefully, score 77.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 59.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1629.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2607,7 +2585,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2616,178 +2594,196 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>39.31</v>
+        <v>1109.5466</v>
       </c>
       <c r="T10" t="n">
-        <v>49.485</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>1629.6</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>12.08</v>
+        <v>38.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>38.75</v>
+        <v>146.64</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.99</v>
+        <v>38.24</v>
       </c>
       <c r="AB10" t="n">
-        <v>-19.17</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+        <v>-44.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>62.61</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>39.1</v>
+      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Mercati emergenti</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>46.425</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>82.8</v>
-      </c>
+        <v>1629.6</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>-0.78</v>
+        <v>19.21</v>
       </c>
       <c r="AM10" t="n">
-        <v>22.72</v>
+        <v>72.87</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.84</v>
+        <v>34.97</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.12</v>
+        <v>0.91</v>
       </c>
       <c r="AP10" t="n">
-        <v>45.1736</v>
+        <v>1318.1492</v>
       </c>
       <c r="AQ10" t="n">
-        <v>40.4772</v>
+        <v>1066.0075</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
         <v>85</v>
       </c>
       <c r="AT10" t="n">
-        <v>90.2</v>
+        <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>65.5</v>
+        <v>18.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>82.8</v>
+        <v>4.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="AX10" t="n">
-        <v>44.985</v>
+        <v>1249</v>
       </c>
       <c r="AY10" t="n">
-        <v>49.485</v>
+        <v>1629.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.77</v>
+        <v>23.63</v>
       </c>
       <c r="BA10" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
+        <v>52.87</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment &amp; Materials</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>625224515584</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>66</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.2</v>
+      </c>
       <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>Europe / Semiconductors</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>76.3</v>
+        <v>79.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 79.0; priority 76.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 79.6; priority 79.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2797,17 +2793,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 79.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.5%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2822,153 +2818,131 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>273.3367</v>
+        <v>39.31</v>
       </c>
       <c r="T11" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+        <v>49.485</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>19.06</v>
+        <v>17.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>103.39</v>
+        <v>42.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>29.71</v>
+        <v>16.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>27.48</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>24.84</v>
-      </c>
+        <v>-19.17</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Mercati emergenti</t>
+        </is>
+      </c>
       <c r="AG11" t="n">
-        <v>359.68</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+        <v>47.86</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>76.59999999999999</v>
+      </c>
       <c r="AL11" t="n">
-        <v>-10.61</v>
+        <v>1.47</v>
       </c>
       <c r="AM11" t="n">
-        <v>12.47</v>
+        <v>25.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.31</v>
+        <v>18.82</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AP11" t="n">
-        <v>362.0613</v>
+        <v>45.3446</v>
       </c>
       <c r="AQ11" t="n">
-        <v>307.5641</v>
+        <v>40.5402</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT11" t="n">
         <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>40.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>78.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AX11" t="n">
-        <v>356.38</v>
+        <v>44.985</v>
       </c>
       <c r="AY11" t="n">
-        <v>396.7031</v>
+        <v>49.485</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.66</v>
+        <v>5.55</v>
       </c>
       <c r="BA11" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>4386274148352</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>78.8</v>
-      </c>
+        <v>18.06</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2978,20 +2952,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>80.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>76.2</v>
+        <v>77.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3000,12 +2978,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 8.2% sopra MA50: evitare inseguimento.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 80.9; priority 76.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 80.0; priority 77.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3015,27 +2993,27 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>prezzo 8.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.2%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3054,83 +3032,71 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>54.81</v>
+        <v>273.3367</v>
       </c>
       <c r="T12" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>22.4</v>
+        <v>20.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>56.7</v>
+        <v>110.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.66</v>
+        <v>29.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>25.51</v>
+      </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>Value globale</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
-        <v>69.23</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>66.09999999999999</v>
-      </c>
+        <v>369.35</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>4.03</v>
+        <v>-7.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>34.19</v>
+        <v>18.37</v>
       </c>
       <c r="AN12" t="n">
-        <v>24.72</v>
+        <v>44.84</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AP12" t="n">
-        <v>64.0026</v>
+        <v>363.5364</v>
       </c>
       <c r="AQ12" t="n">
-        <v>55.0882</v>
+        <v>308.3764</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
@@ -3140,41 +3106,75 @@
         <v>100</v>
       </c>
       <c r="AU12" t="n">
-        <v>69.40000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>66.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="AX12" t="n">
-        <v>65.27</v>
+        <v>356.38</v>
       </c>
       <c r="AY12" t="n">
-        <v>72.27</v>
+        <v>396.7031</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8.17</v>
+        <v>1.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>25.67</v>
-      </c>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
+        <v>19.77</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>4504199102464</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>59</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3194,10 +3194,10 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>74.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="F13" t="n">
-        <v>75.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 74.9; priority 75.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.3; priority 76.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3282,13 +3282,13 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>7.81</v>
+        <v>10.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>22.46</v>
+        <v>24.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.88</v>
+        <v>12.92</v>
       </c>
       <c r="AB13" t="n">
         <v>-21.07</v>
@@ -3306,53 +3306,53 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>159.56</v>
+        <v>162.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>72.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AK13" t="n">
         <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.26</v>
+        <v>0.89</v>
       </c>
       <c r="AM13" t="n">
-        <v>10.39</v>
+        <v>11.92</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.59</v>
+        <v>17.11</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>156.1016</v>
+        <v>156.5144</v>
       </c>
       <c r="AQ13" t="n">
-        <v>146.9946</v>
+        <v>147.1249</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>72.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AV13" t="n">
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AX13" t="n">
         <v>158.2</v>
@@ -3361,10 +3361,10 @@
         <v>164.88</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.550000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3390,20 +3390,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>73.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>74.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.2349. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 73.9; priority 74.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.0; priority 76.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3432,22 +3432,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.23 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.07 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3466,15 +3466,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>107.5</v>
+        <v>56.0747</v>
       </c>
       <c r="T14" t="n">
-        <v>124.27</v>
+        <v>63.2349</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3484,20 +3484,20 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>7.35</v>
+        <v>7.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.35</v>
+        <v>18.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.15</v>
+        <v>12.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3508,69 +3508,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>120.89</v>
+        <v>63.0272</v>
       </c>
       <c r="AH14" t="n">
-        <v>70.8</v>
+        <v>70.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>70.5</v>
+        <v>72</v>
       </c>
       <c r="AJ14" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AK14" t="n">
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.38</v>
+        <v>2.92</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.609999999999999</v>
+        <v>11.69</v>
       </c>
       <c r="AN14" t="n">
-        <v>16.48</v>
+        <v>13.98</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AP14" t="n">
-        <v>118.4654</v>
+        <v>60.9692</v>
       </c>
       <c r="AQ14" t="n">
-        <v>112.3568</v>
+        <v>58.0466</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>70.5</v>
+        <v>72</v>
       </c>
       <c r="AU14" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AV14" t="n">
         <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AX14" t="n">
-        <v>120.3</v>
+        <v>60.5943</v>
       </c>
       <c r="AY14" t="n">
-        <v>124.27</v>
+        <v>63.2349</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.05</v>
+        <v>3.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.59</v>
+        <v>8.58</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3596,20 +3596,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>73.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>74.5</v>
+        <v>75.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 73.6; priority 74.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.1; priority 75.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3643,17 +3643,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 73.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.7%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.70 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3672,15 +3672,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>56.7</v>
+        <v>107.5</v>
       </c>
       <c r="T15" t="n">
-        <v>63.94</v>
+        <v>124.27</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3690,20 +3690,20 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>4.85</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.52</v>
+        <v>22.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.85</v>
+        <v>13.19</v>
       </c>
       <c r="AB15" t="n">
-        <v>-16.33</v>
+        <v>-21.63</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3714,69 +3714,69 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>62.56</v>
+        <v>122.82</v>
       </c>
       <c r="AH15" t="n">
-        <v>69.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>66.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>71.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK15" t="n">
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.11</v>
+        <v>0.68</v>
       </c>
       <c r="AM15" t="n">
-        <v>9.470000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AN15" t="n">
-        <v>13.58</v>
+        <v>16.93</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AP15" t="n">
-        <v>61.5328</v>
+        <v>118.7594</v>
       </c>
       <c r="AQ15" t="n">
-        <v>58.6502</v>
+        <v>112.4454</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>66.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="AU15" t="n">
-        <v>71.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV15" t="n">
         <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="AX15" t="n">
-        <v>60.81</v>
+        <v>120.3</v>
       </c>
       <c r="AY15" t="n">
-        <v>63.94</v>
+        <v>124.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.67</v>
+        <v>3.42</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.67</v>
+        <v>9.23</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>73.5</v>
+        <v>74.7</v>
       </c>
       <c r="F16" t="n">
-        <v>74.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 73.5; priority 74.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.7; priority 75.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3896,17 +3896,17 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>8.470000000000001</v>
+        <v>10.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.44</v>
+        <v>23.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.11</v>
+        <v>14.15</v>
       </c>
       <c r="AB16" t="n">
         <v>-23.32</v>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>681.24</v>
+        <v>691.86</v>
       </c>
       <c r="AH16" t="n">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>72.2</v>
+        <v>76.5</v>
       </c>
       <c r="AJ16" t="n">
         <v>64.40000000000001</v>
@@ -3939,29 +3939,29 @@
         <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>8.32</v>
+        <v>9.42</v>
       </c>
       <c r="AN16" t="n">
-        <v>17.62</v>
+        <v>18.05</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AP16" t="n">
-        <v>665.7612</v>
+        <v>667.596</v>
       </c>
       <c r="AQ16" t="n">
-        <v>630.9031</v>
+        <v>631.4109</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>72.2</v>
+        <v>76.5</v>
       </c>
       <c r="AU16" t="n">
         <v>64.40000000000001</v>
@@ -3970,7 +3970,7 @@
         <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AX16" t="n">
         <v>680.9400000000001</v>
@@ -3979,10 +3979,10 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.32</v>
+        <v>3.63</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.98</v>
+        <v>9.57</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>72.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="F17" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 74.96. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 75.27. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 72.4; priority 73.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.2; priority 74.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 72.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 74.96 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -4087,7 +4087,7 @@
         <v>66.58</v>
       </c>
       <c r="T17" t="n">
-        <v>74.95999999999999</v>
+        <v>75.27</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>6.66</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.86</v>
+        <v>19.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.87</v>
+        <v>12.89</v>
       </c>
       <c r="AB17" t="n">
         <v>-20.6</v>
@@ -4130,65 +4130,65 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>74.36</v>
+        <v>75.27</v>
       </c>
       <c r="AH17" t="n">
         <v>65</v>
       </c>
       <c r="AI17" t="n">
-        <v>69.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AJ17" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AM17" t="n">
-        <v>9.42</v>
+        <v>10.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>15</v>
+        <v>15.11</v>
       </c>
       <c r="AO17" t="n">
         <v>1.17</v>
       </c>
       <c r="AP17" t="n">
-        <v>72.1952</v>
+        <v>72.36199999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>68.804</v>
+        <v>68.8582</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>69.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AU17" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="AW17" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX17" t="n">
         <v>72.94</v>
       </c>
       <c r="AY17" t="n">
-        <v>74.95999999999999</v>
+        <v>75.27</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3</v>
+        <v>4.02</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.08</v>
+        <v>9.31</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 74.5; priority 73.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 75.0; priority 74.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.0%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4312,22 +4312,22 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>17.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>47.04</v>
+        <v>49.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>25.97</v>
+        <v>26.02</v>
       </c>
       <c r="AB18" t="n">
         <v>-33.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>35.29</v>
+        <v>35.84</v>
       </c>
       <c r="AD18" t="n">
-        <v>30.34</v>
+        <v>30.89</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -4336,36 +4336,36 @@
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>291.13</v>
+        <v>296.42</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>-2.59</v>
+        <v>-0.6</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.62</v>
+        <v>6.81</v>
       </c>
       <c r="AN18" t="n">
-        <v>17.29</v>
+        <v>17.7</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AP18" t="n">
-        <v>285.3621</v>
+        <v>286.1768</v>
       </c>
       <c r="AQ18" t="n">
-        <v>266.4564</v>
+        <v>266.7893</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>87.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="AU18" t="n">
         <v>42.1</v>
@@ -4374,7 +4374,7 @@
         <v>82.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX18" t="n">
         <v>290.55</v>
@@ -4383,10 +4383,10 @@
         <v>315.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.02</v>
+        <v>3.58</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.26</v>
+        <v>11.11</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>4275929874432</v>
+        <v>4353626210304</v>
       </c>
       <c r="BE18" t="n">
         <v>27.15</v>
@@ -4420,10 +4420,10 @@
         <v>100</v>
       </c>
       <c r="BK18" t="n">
-        <v>87.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="BL18" t="n">
-        <v>43.9</v>
+        <v>42.4</v>
       </c>
       <c r="BM18" t="n">
         <v>42.1</v>
@@ -4446,20 +4446,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>70.8</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>73.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 18.17. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 70.8; priority 73.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
+          <t>score 69.0; priority 71.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4483,27 +4483,27 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4522,111 +4522,111 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>12.936</v>
+        <v>62.06</v>
       </c>
       <c r="T19" t="n">
-        <v>18.17</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>22.78</v>
+        <v>-1.03</v>
       </c>
       <c r="Z19" t="n">
-        <v>35.7</v>
+        <v>1.32</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.35</v>
+        <v>9.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>17.272</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="AH19" t="n">
-        <v>50</v>
+        <v>62.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>50.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>45.9</v>
+        <v>78.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>75.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.43</v>
+        <v>1.6</v>
       </c>
       <c r="AM19" t="n">
-        <v>21.69</v>
+        <v>2.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>16.5</v>
+        <v>7.04</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="AP19" t="n">
-        <v>16.3266</v>
+        <v>63.3706</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.5083</v>
+        <v>63.1116</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>100</v>
+        <v>50.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>50.9</v>
+        <v>78.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>75.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX19" t="n">
-        <v>16.544</v>
+        <v>63.51</v>
       </c>
       <c r="AY19" t="n">
-        <v>18.17</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.79</v>
+        <v>1.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>19.05</v>
+        <v>1.87</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>69.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>71.2</v>
+        <v>68.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 65.25. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 10.7% sopra MA50: evitare inseguimento.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 69.1; priority 71.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 79.6; priority 68.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.5%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.7%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 65.25 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4728,20 +4728,20 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>62.06</v>
+        <v>54.81</v>
       </c>
       <c r="T20" t="n">
-        <v>65.25</v>
+        <v>72.27</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4750,89 +4750,89 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>-0.42</v>
+        <v>26.93</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.28</v>
+        <v>60.57</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.56</v>
+        <v>13.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>-12.85</v>
+        <v>-17.8</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>64.31</v>
+        <v>71.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>61.9</v>
+        <v>78.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>51.4</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>78.2</v>
+        <v>69.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>82.8</v>
+        <v>55.9</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.16</v>
+        <v>5.64</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.73</v>
+        <v>37.44</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.93</v>
+        <v>25.63</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.72</v>
+        <v>1.86</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.3538</v>
+        <v>64.3308</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.1068</v>
+        <v>55.2088</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>51.4</v>
+        <v>100</v>
       </c>
       <c r="AU20" t="n">
-        <v>78.2</v>
+        <v>69.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>82.8</v>
+        <v>55.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX20" t="n">
-        <v>63.37</v>
+        <v>65.27</v>
       </c>
       <c r="AY20" t="n">
-        <v>64.68000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.51</v>
+        <v>10.71</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.91</v>
+        <v>29</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>72.8</v>
+        <v>75.8</v>
       </c>
       <c r="F21" t="n">
-        <v>55.7</v>
+        <v>59.1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 72.8; priority 55.7; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 75.8; priority 59.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 72.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>13.97</v>
+        <v>16.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>43.85</v>
+        <v>46.71</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.93</v>
+        <v>46.96</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>31.37</v>
+        <v>31.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.12</v>
+        <v>16.69</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,57 +4980,57 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>205.19</v>
+        <v>212.45</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.77</v>
       </c>
       <c r="AM21" t="n">
-        <v>11.79</v>
+        <v>17.56</v>
       </c>
       <c r="AN21" t="n">
-        <v>71.5</v>
+        <v>71.45</v>
       </c>
       <c r="AO21" t="n">
         <v>1.52</v>
       </c>
       <c r="AP21" t="n">
-        <v>206.7045</v>
+        <v>207.4098</v>
       </c>
       <c r="AQ21" t="n">
-        <v>189.0373</v>
+        <v>189.1928</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT21" t="n">
-        <v>87.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>78.7</v>
+        <v>82.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX21" t="n">
         <v>200.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>225.0577</v>
+        <v>224.0988</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.73</v>
+        <v>2.43</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.539999999999999</v>
+        <v>12.29</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4969906831360</v>
+        <v>5145751453696</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5064,16 +5064,16 @@
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>87.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="BL21" t="n">
-        <v>68.7</v>
+        <v>67.8</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="BN21" t="n">
-        <v>78.7</v>
+        <v>82.8</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>49.2</v>
+        <v>51.7</v>
       </c>
       <c r="F22" t="n">
-        <v>50.1</v>
+        <v>53.1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 49.2; priority 50.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 51.7; priority 53.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,17 +5132,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 49.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.1%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 51.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 417.50 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 407.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -5169,7 +5169,7 @@
         <v>340.82</v>
       </c>
       <c r="T22" t="n">
-        <v>417.5</v>
+        <v>407.57</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-20.7</v>
+        <v>-18.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.3</v>
+        <v>24.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>17.91</v>
+        <v>17.99</v>
       </c>
       <c r="AB22" t="n">
         <v>-21.9</v>
@@ -5212,53 +5212,53 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>340.82</v>
+        <v>350.52</v>
       </c>
       <c r="AH22" t="n">
-        <v>65.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="AI22" t="n">
-        <v>25.1</v>
+        <v>31</v>
       </c>
       <c r="AJ22" t="n">
-        <v>61</v>
+        <v>60.9</v>
       </c>
       <c r="AK22" t="n">
-        <v>60.1</v>
+        <v>64.2</v>
       </c>
       <c r="AL22" t="n">
-        <v>-11.65</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AM22" t="n">
-        <v>-2.08</v>
+        <v>0.52</v>
       </c>
       <c r="AN22" t="n">
-        <v>24.66</v>
+        <v>26.62</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AP22" t="n">
-        <v>379.2068</v>
+        <v>378.5036</v>
       </c>
       <c r="AQ22" t="n">
-        <v>362.8027</v>
+        <v>363.1672</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>25.1</v>
+        <v>31</v>
       </c>
       <c r="AU22" t="n">
-        <v>61</v>
+        <v>60.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>60.1</v>
+        <v>64.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX22" t="n">
         <v>340.82</v>
@@ -5267,10 +5267,10 @@
         <v>377.9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-10.12</v>
+        <v>-7.39</v>
       </c>
       <c r="BA22" t="n">
-        <v>-6.06</v>
+        <v>-3.48</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>66.7</v>
+        <v>66.5</v>
       </c>
       <c r="F2" t="n">
-        <v>66.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 66.7; priority 66.4; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 66.5; priority 66.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.7%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.0%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>16.19</v>
+        <v>14.31</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.37</v>
+        <v>15.98</v>
       </c>
       <c r="AA2" t="n">
         <v>31.05</v>
@@ -876,7 +876,7 @@
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>32.63</v>
+        <v>31.66</v>
       </c>
       <c r="AD2" t="n">
         <v>24.95</v>
@@ -888,42 +888,42 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>246.02</v>
+        <v>246</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-7.93</v>
+        <v>-6.87</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.84</v>
+        <v>8.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.34</v>
+        <v>25.24</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>255.4986</v>
+        <v>256.1628</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.5939</v>
+        <v>232.6659</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>80.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="AU2" t="n">
         <v>38</v>
       </c>
       <c r="AV2" t="n">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="AW2" t="n">
         <v>751</v>
@@ -935,10 +935,10 @@
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-3.71</v>
+        <v>-3.97</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.77</v>
+        <v>5.73</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2646464266240</v>
+        <v>2646249046016</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>80.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="BL2" t="n">
-        <v>54.7</v>
+        <v>55.8</v>
       </c>
       <c r="BM2" t="n">
         <v>38</v>
       </c>
       <c r="BN2" t="n">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -996,20 +996,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>68.8</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>64.5</v>
+        <v>57.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 68.8; priority 64.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 64.0; priority 57.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1033,27 +1033,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.17 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1072,15 +1072,15 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>12.936</v>
+        <v>8.7643</v>
       </c>
       <c r="T3" t="n">
-        <v>18.17</v>
+        <v>11.61</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1094,89 +1094,89 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>29.69</v>
+        <v>12.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.98</v>
+        <v>58.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.47</v>
+        <v>23.42</v>
       </c>
       <c r="AB3" t="n">
-        <v>-29.37</v>
+        <v>-43.51</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>17.972</v>
+        <v>10.384</v>
       </c>
       <c r="AH3" t="n">
-        <v>50.9</v>
+        <v>31</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>45.7</v>
+        <v>32.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>61.1</v>
+        <v>82.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.56</v>
+        <v>-3.16</v>
       </c>
       <c r="AM3" t="n">
-        <v>26.21</v>
+        <v>26.85</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.57</v>
+        <v>2.88</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.82</v>
+        <v>0.12</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.4273</v>
+        <v>10.2735</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5329</v>
+        <v>8.817500000000001</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
         <v>85</v>
       </c>
       <c r="AT3" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>50.7</v>
+        <v>37.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>61.1</v>
+        <v>82.8</v>
       </c>
       <c r="AW3" t="n">
         <v>755</v>
       </c>
       <c r="AX3" t="n">
-        <v>16.544</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>18.17</v>
+        <v>11.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.4</v>
+        <v>1.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>23.66</v>
+        <v>17.77</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>63.2</v>
+        <v>62.5</v>
       </c>
       <c r="F4" t="n">
-        <v>58.2</v>
+        <v>57</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 63.2; priority 58.2; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 62.5; priority 57.0; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 63.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -2.9%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.5%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1300,22 +1300,22 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>0.17</v>
+        <v>-1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>-15.85</v>
+        <v>-16.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.96</v>
+        <v>23.97</v>
       </c>
       <c r="AB4" t="n">
         <v>-33.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.8</v>
+        <v>23.46</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.66</v>
+        <v>20.36</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1324,42 +1324,42 @@
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>399.76</v>
+        <v>393.83</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-2.15</v>
+        <v>-6.46</v>
       </c>
       <c r="AM4" t="n">
-        <v>-16.95</v>
+        <v>-17.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.17</v>
+        <v>6.09</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AP4" t="n">
-        <v>411.7392</v>
+        <v>412.1744</v>
       </c>
       <c r="AQ4" t="n">
-        <v>451.3541</v>
+        <v>450.7911</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
         <v>35</v>
       </c>
       <c r="AT4" t="n">
-        <v>36.1</v>
+        <v>33.8</v>
       </c>
       <c r="AU4" t="n">
         <v>44.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>70.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AW4" t="n">
         <v>751</v>
@@ -1371,10 +1371,10 @@
         <v>460.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-2.91</v>
+        <v>-4.45</v>
       </c>
       <c r="BA4" t="n">
-        <v>-11.43</v>
+        <v>-12.64</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>2969591349248</v>
+        <v>2925540409344</v>
       </c>
       <c r="BE4" t="n">
         <v>39.34</v>
@@ -1402,22 +1402,22 @@
         <v>30.27</v>
       </c>
       <c r="BI4" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="BJ4" t="n">
         <v>100</v>
       </c>
       <c r="BK4" t="n">
-        <v>36.1</v>
+        <v>33.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>71.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="BM4" t="n">
         <v>44.1</v>
       </c>
       <c r="BN4" t="n">
-        <v>70.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>63.7</v>
+        <v>67.3</v>
       </c>
       <c r="F5" t="n">
-        <v>57.5</v>
+        <v>56.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1461,37 +1461,37 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 63.7; priority 57.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 67.3; priority 56.1; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 12.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 63.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.5%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.54 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1510,15 +1510,15 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>8.7643</v>
+        <v>12.936</v>
       </c>
       <c r="T5" t="n">
-        <v>11.61</v>
+        <v>18.54</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1532,89 +1532,89 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>12.29</v>
+        <v>35.01</v>
       </c>
       <c r="Z5" t="n">
-        <v>59.54</v>
+        <v>45.39</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.42</v>
+        <v>21.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>-43.61</v>
+        <v>-29.37</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>10.4</v>
+        <v>18.54</v>
       </c>
       <c r="AH5" t="n">
-        <v>31</v>
+        <v>51.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>45.6</v>
       </c>
       <c r="AK5" t="n">
-        <v>82.8</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.59</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>25.6</v>
+        <v>30.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.87</v>
+        <v>18.79</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.12</v>
+        <v>0.87</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.2478</v>
+        <v>16.5267</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.801</v>
+        <v>14.5605</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
         <v>85</v>
       </c>
       <c r="AT5" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="AU5" t="n">
-        <v>37</v>
+        <v>50.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>82.8</v>
+        <v>50</v>
       </c>
       <c r="AW5" t="n">
         <v>755</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.914999999999999</v>
+        <v>16.544</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.61</v>
+        <v>18.54</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.49</v>
+        <v>12.18</v>
       </c>
       <c r="BA5" t="n">
-        <v>18.17</v>
+        <v>27.33</v>
       </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61.2</v>
+        <v>62.5</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>43.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 61.2; priority 42.0; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 62.5; priority 43.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 4.6% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 61.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.6%.</t>
+          <t>META: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.5%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 688.55 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.72 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>525.72</v>
+        <v>525.2332</v>
       </c>
       <c r="T6" t="n">
-        <v>688.55</v>
+        <v>687.9124</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-5.41</v>
+        <v>-3.52</v>
       </c>
       <c r="Z6" t="n">
-        <v>-14.14</v>
+        <v>-11.75</v>
       </c>
       <c r="AA6" t="n">
         <v>36.36</v>
@@ -1750,10 +1750,10 @@
         <v>-34.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.58</v>
+        <v>21.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.37</v>
+        <v>16.56</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1762,57 +1762,57 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>593.48</v>
+        <v>600.21</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-4.03</v>
+        <v>-2.19</v>
       </c>
       <c r="AM6" t="n">
-        <v>-8.92</v>
+        <v>-6.59</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.85</v>
+        <v>28.87</v>
       </c>
       <c r="AO6" t="n">
         <v>0.79</v>
       </c>
       <c r="AP6" t="n">
-        <v>622.2082</v>
+        <v>622.1975</v>
       </c>
       <c r="AQ6" t="n">
-        <v>656.6682</v>
+        <v>655.3206</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
         <v>35</v>
       </c>
       <c r="AT6" t="n">
-        <v>33.5</v>
+        <v>38.2</v>
       </c>
       <c r="AU6" t="n">
         <v>29</v>
       </c>
       <c r="AV6" t="n">
-        <v>68.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>751</v>
       </c>
       <c r="AX6" t="n">
-        <v>566.98</v>
+        <v>566.455</v>
       </c>
       <c r="AY6" t="n">
-        <v>635.29</v>
+        <v>634.7017</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-4.62</v>
+        <v>-3.53</v>
       </c>
       <c r="BA6" t="n">
-        <v>-9.619999999999999</v>
+        <v>-8.41</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1506503426048</v>
+        <v>1523587088384</v>
       </c>
       <c r="BE6" t="n">
         <v>32.84</v>
@@ -1840,22 +1840,22 @@
         <v>35.61</v>
       </c>
       <c r="BI6" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="BJ6" t="n">
         <v>100</v>
       </c>
       <c r="BK6" t="n">
-        <v>33.5</v>
+        <v>38.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>79.8</v>
+        <v>79.2</v>
       </c>
       <c r="BM6" t="n">
         <v>29</v>
       </c>
       <c r="BN6" t="n">
-        <v>68.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41.1</v>
+        <v>39.4</v>
       </c>
       <c r="F7" t="n">
-        <v>34.7</v>
+        <v>32.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 41.1; priority 34.7; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 39.4; priority 32.9; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 41.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.0%.</t>
+          <t>TSLA: scenario base High Risk, score 39.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1970,22 +1970,22 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>3.94</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>28.84</v>
+        <v>24.39</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.04</v>
+        <v>57.97</v>
       </c>
       <c r="AB7" t="n">
         <v>-53.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>373.77</v>
+        <v>364.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>164.46</v>
+        <v>161.87</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1994,36 +1994,36 @@
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>411.15</v>
+        <v>404.66</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>-7.25</v>
+        <v>-4.16</v>
       </c>
       <c r="AM7" t="n">
-        <v>-8</v>
+        <v>-11.83</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.54</v>
+        <v>13.92</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="AP7" t="n">
-        <v>399.3112</v>
+        <v>400.348</v>
       </c>
       <c r="AQ7" t="n">
-        <v>416.0022</v>
+        <v>416.2956</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
         <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>57.9</v>
+        <v>50.9</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
@@ -2041,10 +2041,10 @@
         <v>442.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.96</v>
+        <v>1.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>-1.17</v>
+        <v>-2.8</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1544165785600</v>
+        <v>1519791243264</v>
       </c>
       <c r="BE7" t="n">
         <v>3.95</v>
@@ -2076,7 +2076,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>57.9</v>
+        <v>50.9</v>
       </c>
       <c r="BL7" t="n">
         <v>0</v>
@@ -2102,20 +2102,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>38.8</v>
+        <v>63.2</v>
       </c>
       <c r="F8" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 38.8; priority 32.8; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 63.2; priority 32.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 14.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 38.8, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 6.4%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.4%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 647.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2169,24 +2169,24 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>20.205</v>
+        <v>362.53</v>
       </c>
       <c r="T8" t="n">
-        <v>30.11</v>
+        <v>647.1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2200,16 +2200,16 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>6.62</v>
+        <v>55.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>-16.21</v>
+        <v>140.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>34</v>
+        <v>35.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>-48.6</v>
+        <v>-35.74</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
@@ -2220,69 +2220,69 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>26.02</v>
+        <v>616</v>
       </c>
       <c r="AH8" t="n">
-        <v>21.5</v>
+        <v>57.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.3</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>68.5</v>
+        <v>41.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>10.14</v>
+        <v>10.72</v>
       </c>
       <c r="AM8" t="n">
-        <v>-12.8</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>-3.77</v>
+        <v>60.36</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.11</v>
+        <v>1.71</v>
       </c>
       <c r="AP8" t="n">
-        <v>24.4489</v>
+        <v>538.3665999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.9215</v>
+        <v>407.2589</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AT8" t="n">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="AU8" t="n">
-        <v>20.3</v>
+        <v>29</v>
       </c>
       <c r="AV8" t="n">
-        <v>68.5</v>
+        <v>41.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="AX8" t="n">
-        <v>24.705</v>
+        <v>543.96</v>
       </c>
       <c r="AY8" t="n">
-        <v>30.11</v>
+        <v>647.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.43</v>
+        <v>14.42</v>
       </c>
       <c r="BA8" t="n">
-        <v>-3.35</v>
+        <v>51.26</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2308,20 +2308,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>59.4</v>
+        <v>39.3</v>
       </c>
       <c r="F9" t="n">
-        <v>12.1</v>
+        <v>29.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 59.4; priority 12.1; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 39.3; priority 29.8; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 21.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.2% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 59.4, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.2%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 647.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2375,24 +2375,24 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>362.53</v>
+        <v>20.205</v>
       </c>
       <c r="T9" t="n">
-        <v>647.1</v>
+        <v>30.11</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2406,16 +2406,16 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>64.27</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>146.67</v>
+        <v>-12.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>35.23</v>
+        <v>34.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>-35.74</v>
+        <v>-48.6</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
@@ -2426,69 +2426,69 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>647.1</v>
+        <v>26.53</v>
       </c>
       <c r="AH9" t="n">
-        <v>59.1</v>
+        <v>21.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>24.1</v>
+        <v>15.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>61.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>11.89</v>
+        <v>10.22</v>
       </c>
       <c r="AM9" t="n">
-        <v>75.02</v>
+        <v>-11.93</v>
       </c>
       <c r="AN9" t="n">
-        <v>62.84</v>
+        <v>-3.11</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.78</v>
+        <v>-0.09</v>
       </c>
       <c r="AP9" t="n">
-        <v>533.9662</v>
+        <v>24.5113</v>
       </c>
       <c r="AQ9" t="n">
-        <v>405.6687</v>
+        <v>26.9103</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AT9" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>29.1</v>
+        <v>20.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>61.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AX9" t="n">
-        <v>543.96</v>
+        <v>24.93</v>
       </c>
       <c r="AY9" t="n">
-        <v>647.1</v>
+        <v>30.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21.19</v>
+        <v>8.24</v>
       </c>
       <c r="BA9" t="n">
-        <v>59.51</v>
+        <v>-1.41</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 59.3; priority 3.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 60.0; priority 7.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 22.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 59.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 22.3%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>38.36</v>
+        <v>37.83</v>
       </c>
       <c r="Z10" t="n">
-        <v>146.64</v>
+        <v>145.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.24</v>
+        <v>38.22</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>62.61</v>
+        <v>61.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>39.1</v>
+        <v>38.36</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1629.6</v>
+        <v>1622.2</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>19.21</v>
+        <v>24.15</v>
       </c>
       <c r="AM10" t="n">
-        <v>72.87</v>
+        <v>73.02</v>
       </c>
       <c r="AN10" t="n">
-        <v>34.97</v>
+        <v>35.71</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="AP10" t="n">
-        <v>1318.1492</v>
+        <v>1326.8936</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1066.0075</v>
+        <v>1070.9524</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2671,7 +2671,7 @@
         <v>18.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AW10" t="n">
         <v>764</v>
@@ -2683,10 +2683,10 @@
         <v>1629.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23.63</v>
+        <v>22.26</v>
       </c>
       <c r="BA10" t="n">
-        <v>52.87</v>
+        <v>51.47</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>625224515584</v>
+        <v>613276581888</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2714,7 +2714,7 @@
         <v>12.99</v>
       </c>
       <c r="BI10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BJ10" t="n">
         <v>100</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="BM10" t="n">
         <v>18.3</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2741,44 +2741,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>3. Interessanti ma da attendere</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>79.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>79.8</v>
+        <v>65.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟠 Attendi pullback</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Non inseguire il prezzo: imposta alert su pullback o tenuta supporto. Supporto 60D: 54.81.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 79.6; priority 79.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 79.1; priority 65.3; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 11.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.5%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.8%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2822,83 +2822,83 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>39.31</v>
+        <v>54.81</v>
       </c>
       <c r="T11" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>17.75</v>
+        <v>28.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>42.7</v>
+        <v>63.26</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.1</v>
+        <v>13.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>-19.17</v>
+        <v>-17.8</v>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>47.86</v>
+        <v>72.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>69.2</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="n">
         <v>100</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>76.59999999999999</v>
+        <v>51.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.47</v>
+        <v>9.25</v>
       </c>
       <c r="AM11" t="n">
-        <v>25.42</v>
+        <v>39.61</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.82</v>
+        <v>26.16</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.17</v>
+        <v>1.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>45.3446</v>
+        <v>64.64360000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>40.5402</v>
+        <v>55.3358</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
@@ -2908,25 +2908,25 @@
         <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>65.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>76.59999999999999</v>
+        <v>51.7</v>
       </c>
       <c r="AW11" t="n">
         <v>755</v>
       </c>
       <c r="AX11" t="n">
-        <v>44.985</v>
+        <v>65.27</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.485</v>
+        <v>72.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.55</v>
+        <v>11.77</v>
       </c>
       <c r="BA11" t="n">
-        <v>18.06</v>
+        <v>30.57</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 80.0; priority 77.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 79.9; priority 77.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -3050,22 +3050,22 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>20.95</v>
+        <v>20.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>110.82</v>
+        <v>114.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>29.77</v>
+        <v>29.78</v>
       </c>
       <c r="AB12" t="n">
         <v>-29.81</v>
       </c>
       <c r="AC12" t="n">
-        <v>28.22</v>
+        <v>28.47</v>
       </c>
       <c r="AD12" t="n">
-        <v>25.51</v>
+        <v>25.78</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -3074,29 +3074,29 @@
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
-        <v>369.35</v>
+        <v>373.25</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>-7.85</v>
+        <v>-5.87</v>
       </c>
       <c r="AM12" t="n">
-        <v>18.37</v>
+        <v>20.84</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.84</v>
+        <v>45.52</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AP12" t="n">
-        <v>363.5364</v>
+        <v>365.0052</v>
       </c>
       <c r="AQ12" t="n">
-        <v>308.3764</v>
+        <v>309.1874</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
@@ -3118,13 +3118,13 @@
         <v>356.38</v>
       </c>
       <c r="AY12" t="n">
-        <v>396.7031</v>
+        <v>389.8971</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="BA12" t="n">
-        <v>19.77</v>
+        <v>20.72</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>4504199102464</v>
+        <v>4554610442240</v>
       </c>
       <c r="BE12" t="n">
         <v>37.92</v>
@@ -3161,7 +3161,7 @@
         <v>100</v>
       </c>
       <c r="BL12" t="n">
-        <v>59</v>
+        <v>58.3</v>
       </c>
       <c r="BM12" t="n">
         <v>40.4</v>
@@ -3194,10 +3194,10 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>76.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 76.3; priority 76.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.9; priority 76.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.9%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3282,13 +3282,13 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>10.55</v>
+        <v>12.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>24.62</v>
+        <v>27.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.92</v>
+        <v>12.94</v>
       </c>
       <c r="AB13" t="n">
         <v>-21.07</v>
@@ -3306,50 +3306,50 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>162.46</v>
+        <v>164.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="AI13" t="n">
-        <v>78.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="AJ13" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AK13" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.89</v>
+        <v>3.24</v>
       </c>
       <c r="AM13" t="n">
-        <v>11.92</v>
+        <v>13.6</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.11</v>
+        <v>17.48</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AP13" t="n">
-        <v>156.5144</v>
+        <v>156.9084</v>
       </c>
       <c r="AQ13" t="n">
-        <v>147.1249</v>
+        <v>147.2667</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>78.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="AU13" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AW13" t="n">
         <v>758</v>
@@ -3361,10 +3361,10 @@
         <v>164.88</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.42</v>
+        <v>11.77</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>75.3</v>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>76.3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 75.0; priority 76.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.3; priority 76.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>7.44</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.08</v>
+        <v>19.3</v>
       </c>
       <c r="AA14" t="n">
         <v>12.9</v>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>63.0272</v>
+        <v>63.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>70.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AI14" t="n">
-        <v>72</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AJ14" t="n">
         <v>71.5</v>
@@ -3527,29 +3527,29 @@
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.92</v>
+        <v>4.89</v>
       </c>
       <c r="AM14" t="n">
-        <v>11.69</v>
+        <v>11.91</v>
       </c>
       <c r="AN14" t="n">
-        <v>13.98</v>
+        <v>13.81</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AP14" t="n">
-        <v>60.9692</v>
+        <v>61.0566</v>
       </c>
       <c r="AQ14" t="n">
-        <v>58.0466</v>
+        <v>58.0921</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>72</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AU14" t="n">
         <v>71.5</v>
@@ -3561,16 +3561,16 @@
         <v>759</v>
       </c>
       <c r="AX14" t="n">
-        <v>60.5943</v>
+        <v>60.6339</v>
       </c>
       <c r="AY14" t="n">
         <v>63.2349</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.58</v>
+        <v>8.59</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>75.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="F15" t="n">
-        <v>75.8</v>
+        <v>76.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 75.1; priority 75.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.8; priority 76.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3694,13 +3694,13 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>9.630000000000001</v>
+        <v>11.06</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.2</v>
+        <v>23.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="AB15" t="n">
         <v>-21.63</v>
@@ -3718,50 +3718,50 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>122.82</v>
+        <v>124.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>78.3</v>
       </c>
       <c r="AJ15" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="AK15" t="n">
-        <v>82.8</v>
+        <v>81.2</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.68</v>
+        <v>2.67</v>
       </c>
       <c r="AM15" t="n">
-        <v>9.960000000000001</v>
+        <v>11.43</v>
       </c>
       <c r="AN15" t="n">
-        <v>16.93</v>
+        <v>17.21</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AP15" t="n">
-        <v>118.7594</v>
+        <v>119.0378</v>
       </c>
       <c r="AQ15" t="n">
-        <v>112.4454</v>
+        <v>112.5415</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>75</v>
+        <v>78.3</v>
       </c>
       <c r="AU15" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>82.8</v>
+        <v>81.2</v>
       </c>
       <c r="AW15" t="n">
         <v>755</v>
@@ -3773,10 +3773,10 @@
         <v>124.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.42</v>
+        <v>4.39</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.23</v>
+        <v>10.41</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>74.7</v>
+        <v>75.3</v>
       </c>
       <c r="F16" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 74.7; priority 75.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.3; priority 75.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 74.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.8%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>10.75</v>
+        <v>12.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>23.25</v>
+        <v>26.29</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.15</v>
+        <v>14.17</v>
       </c>
       <c r="AB16" t="n">
         <v>-23.32</v>
@@ -3924,50 +3924,50 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>691.86</v>
+        <v>701.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>70.2</v>
+        <v>70.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>76.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>82.8</v>
+        <v>79.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.1</v>
+        <v>2.02</v>
       </c>
       <c r="AM16" t="n">
-        <v>9.42</v>
+        <v>11.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.05</v>
+        <v>18.43</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AP16" t="n">
-        <v>667.596</v>
+        <v>669.422</v>
       </c>
       <c r="AQ16" t="n">
-        <v>631.4109</v>
+        <v>631.965</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>76.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>82.8</v>
+        <v>79.5</v>
       </c>
       <c r="AW16" t="n">
         <v>758</v>
@@ -3979,10 +3979,10 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.63</v>
+        <v>4.81</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.57</v>
+        <v>11.02</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4008,20 +4008,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>73.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>74.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4030,17 +4030,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 75.27. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 49.485. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 73.2; priority 74.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.4; priority 75.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4055,17 +4055,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4084,111 +4084,111 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>66.58</v>
+        <v>39.31</v>
       </c>
       <c r="T17" t="n">
-        <v>75.27</v>
+        <v>49.485</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>8.470000000000001</v>
+        <v>20.67</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.1</v>
+        <v>45.72</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.89</v>
+        <v>16.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>-20.6</v>
+        <v>-19.17</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>75.27</v>
+        <v>49.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>65</v>
+        <v>70.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>72.8</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>68.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>82.7</v>
+        <v>67</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.3</v>
+        <v>7.08</v>
       </c>
       <c r="AM17" t="n">
-        <v>10.25</v>
+        <v>29.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>15.11</v>
+        <v>19.84</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AP17" t="n">
-        <v>72.36199999999999</v>
+        <v>45.5145</v>
       </c>
       <c r="AQ17" t="n">
-        <v>68.8582</v>
+        <v>40.6089</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>72.8</v>
+        <v>100</v>
       </c>
       <c r="AU17" t="n">
-        <v>68.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="AV17" t="n">
-        <v>82.7</v>
+        <v>67</v>
       </c>
       <c r="AW17" t="n">
         <v>755</v>
       </c>
       <c r="AX17" t="n">
-        <v>72.94</v>
+        <v>44.985</v>
       </c>
       <c r="AY17" t="n">
-        <v>75.27</v>
+        <v>49.485</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.02</v>
+        <v>7.94</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.31</v>
+        <v>20.98</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4214,24 +4214,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>73.5</v>
       </c>
       <c r="F18" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4240,42 +4236,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 75.89. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 75.0; priority 74.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 73.5; priority 74.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.6%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4294,149 +4290,127 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>246.403</v>
+        <v>66.58</v>
       </c>
       <c r="T18" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+        <v>75.89</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>17.35</v>
+        <v>9.59</v>
       </c>
       <c r="Z18" t="n">
-        <v>49.4</v>
+        <v>20.21</v>
       </c>
       <c r="AA18" t="n">
-        <v>26.02</v>
+        <v>12.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>-33.36</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>35.84</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>30.89</v>
-      </c>
+        <v>-20.6</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Quality globale</t>
+        </is>
+      </c>
       <c r="AG18" t="n">
-        <v>296.42</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+        <v>75.89</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>68</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>80.09999999999999</v>
+      </c>
       <c r="AL18" t="n">
-        <v>-0.6</v>
+        <v>3.56</v>
       </c>
       <c r="AM18" t="n">
-        <v>6.81</v>
+        <v>11.65</v>
       </c>
       <c r="AN18" t="n">
-        <v>17.7</v>
+        <v>15.18</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.68</v>
+        <v>1.18</v>
       </c>
       <c r="AP18" t="n">
-        <v>286.1768</v>
+        <v>72.51600000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>266.7893</v>
+        <v>68.9156</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>90.7</v>
+        <v>75.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>42.1</v>
+        <v>68</v>
       </c>
       <c r="AV18" t="n">
-        <v>82.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AX18" t="n">
-        <v>290.55</v>
+        <v>73.11</v>
       </c>
       <c r="AY18" t="n">
-        <v>315.2</v>
+        <v>75.89</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.58</v>
+        <v>4.65</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>4353626210304</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>37</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>82.8</v>
-      </c>
+        <v>10.12</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
       <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4446,20 +4420,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>75.3</v>
       </c>
       <c r="F19" t="n">
-        <v>71.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,42 +4446,42 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 69.0; priority 71.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.3; priority 74.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.4%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4522,127 +4500,149 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>62.06</v>
+        <v>246.403</v>
       </c>
       <c r="T19" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>-1.03</v>
+        <v>17.81</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.32</v>
+        <v>52.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.57</v>
+        <v>26.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>31.19</v>
+      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>Min volatility</t>
-        </is>
-      </c>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>82.8</v>
-      </c>
+        <v>299.24</v>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>1.6</v>
+        <v>-0.33</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.62</v>
+        <v>7.73</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.04</v>
+        <v>18.06</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP19" t="n">
-        <v>63.3706</v>
+        <v>286.9892</v>
       </c>
       <c r="AQ19" t="n">
-        <v>63.1116</v>
+        <v>267.126</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>50.5</v>
+        <v>92.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>78.2</v>
+        <v>42.1</v>
       </c>
       <c r="AV19" t="n">
-        <v>82.8</v>
+        <v>81.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="AX19" t="n">
-        <v>63.51</v>
+        <v>290.55</v>
       </c>
       <c r="AY19" t="n">
-        <v>64.68000000000001</v>
+        <v>315.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.45</v>
+        <v>4.27</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="inlineStr"/>
-      <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="inlineStr"/>
+        <v>12.02</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>4395044175872</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>81.7</v>
+      </c>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>79.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>68.5</v>
+        <v>70.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 10.7% sopra MA50: evitare inseguimento.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 79.6; priority 68.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 68.6; priority 70.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo 10.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 79.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.7%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.1%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4728,20 +4728,20 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>54.81</v>
+        <v>62.06</v>
       </c>
       <c r="T20" t="n">
-        <v>72.27</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4750,89 +4750,89 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>26.93</v>
+        <v>-1.79</v>
       </c>
       <c r="Z20" t="n">
-        <v>60.57</v>
+        <v>1.57</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.75</v>
+        <v>9.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>-17.8</v>
+        <v>-12.85</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>71.22</v>
+        <v>64.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>78.3</v>
+        <v>61.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>100</v>
+        <v>49.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>69.3</v>
+        <v>78.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>55.9</v>
+        <v>82.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.64</v>
+        <v>1.17</v>
       </c>
       <c r="AM20" t="n">
-        <v>37.44</v>
+        <v>2.81</v>
       </c>
       <c r="AN20" t="n">
-        <v>25.63</v>
+        <v>6.71</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.86</v>
+        <v>0.7</v>
       </c>
       <c r="AP20" t="n">
-        <v>64.3308</v>
+        <v>63.3822</v>
       </c>
       <c r="AQ20" t="n">
-        <v>55.2088</v>
+        <v>63.1178</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>100</v>
+        <v>49.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>69.3</v>
+        <v>78.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>55.9</v>
+        <v>82.8</v>
       </c>
       <c r="AW20" t="n">
         <v>755</v>
       </c>
       <c r="AX20" t="n">
-        <v>65.27</v>
+        <v>63.51</v>
       </c>
       <c r="AY20" t="n">
-        <v>72.27</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10.71</v>
+        <v>1.15</v>
       </c>
       <c r="BA20" t="n">
-        <v>29</v>
+        <v>1.57</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>75.8</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
-        <v>59.1</v>
+        <v>57.1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 75.8; priority 59.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 74.0; priority 57.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 74.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.3%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>16.09</v>
+        <v>14.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>46.71</v>
+        <v>46.29</v>
       </c>
       <c r="AA21" t="n">
         <v>46.96</v>
@@ -4968,10 +4968,10 @@
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>31.43</v>
+        <v>31.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.69</v>
+        <v>16.3</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,42 +4980,42 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>212.45</v>
+        <v>207.41</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-9.77</v>
+        <v>-7.84</v>
       </c>
       <c r="AM21" t="n">
-        <v>17.56</v>
+        <v>18.65</v>
       </c>
       <c r="AN21" t="n">
-        <v>71.45</v>
+        <v>68.61</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AP21" t="n">
-        <v>207.4098</v>
+        <v>208.0094</v>
       </c>
       <c r="AQ21" t="n">
-        <v>189.1928</v>
+        <v>189.3302</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>94.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AU21" t="n">
         <v>14.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="AW21" t="n">
         <v>751</v>
@@ -5027,10 +5027,10 @@
         <v>224.0988</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.43</v>
+        <v>-0.29</v>
       </c>
       <c r="BA21" t="n">
-        <v>12.29</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>5145751453696</v>
+        <v>5023677808640</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5058,22 +5058,22 @@
         <v>6.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="BJ21" t="n">
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>94.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="BL21" t="n">
-        <v>67.8</v>
+        <v>68</v>
       </c>
       <c r="BM21" t="n">
         <v>14.1</v>
       </c>
       <c r="BN21" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>51.7</v>
+        <v>54.5</v>
       </c>
       <c r="F22" t="n">
-        <v>53.1</v>
+        <v>56.6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 51.7; priority 53.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 54.5; priority 56.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,17 +5132,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 7.4% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 4.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 51.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.4%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 407.57 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 396.71 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -5169,7 +5169,7 @@
         <v>340.82</v>
       </c>
       <c r="T22" t="n">
-        <v>407.57</v>
+        <v>396.71</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-18.23</v>
+        <v>-14.96</v>
       </c>
       <c r="Z22" t="n">
-        <v>24.9</v>
+        <v>28.99</v>
       </c>
       <c r="AA22" t="n">
-        <v>17.99</v>
+        <v>18.06</v>
       </c>
       <c r="AB22" t="n">
         <v>-21.9</v>
@@ -5212,50 +5212,50 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>350.52</v>
+        <v>361.04</v>
       </c>
       <c r="AH22" t="n">
-        <v>67.7</v>
+        <v>68.7</v>
       </c>
       <c r="AI22" t="n">
-        <v>31</v>
+        <v>38.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="AK22" t="n">
-        <v>64.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AL22" t="n">
-        <v>-9.279999999999999</v>
+        <v>-4.01</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.52</v>
+        <v>3.91</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.62</v>
+        <v>27.8</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AP22" t="n">
-        <v>378.5036</v>
+        <v>377.802</v>
       </c>
       <c r="AQ22" t="n">
-        <v>363.1672</v>
+        <v>363.5818</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>31</v>
+        <v>38.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>64.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AW22" t="n">
         <v>755</v>
@@ -5267,10 +5267,10 @@
         <v>377.9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-7.39</v>
+        <v>-4.44</v>
       </c>
       <c r="BA22" t="n">
-        <v>-3.48</v>
+        <v>-0.7</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>66.5</v>
+        <v>65.3</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>63.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 66.5; priority 66.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 65.3; priority 63.5; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 7.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 66.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.0%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 65.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.5%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>14.31</v>
+        <v>13.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.98</v>
+        <v>9.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.05</v>
+        <v>31.1</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>31.66</v>
+        <v>30.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.95</v>
+        <v>24.09</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,57 +888,57 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>246</v>
+        <v>237.5</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-6.87</v>
+        <v>-10.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.76</v>
+        <v>6.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.24</v>
+        <v>23.74</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AP2" t="n">
-        <v>256.1628</v>
+        <v>256.6374</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.6659</v>
+        <v>232.7084</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>79.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AU2" t="n">
         <v>38</v>
       </c>
       <c r="AV2" t="n">
-        <v>73.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX2" t="n">
-        <v>238</v>
+        <v>237.5</v>
       </c>
       <c r="AY2" t="n">
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-3.97</v>
+        <v>-7.46</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.73</v>
+        <v>2.06</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2646249046016</v>
+        <v>2554813480960</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>79.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>55.8</v>
+        <v>58.3</v>
       </c>
       <c r="BM2" t="n">
         <v>38</v>
       </c>
       <c r="BN2" t="n">
-        <v>73.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -996,20 +996,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>57.8</v>
+        <v>62.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 64.0; priority 57.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 68.6; priority 62.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1033,27 +1033,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 9.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.54 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1072,15 +1072,15 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>8.7643</v>
+        <v>12.936</v>
       </c>
       <c r="T3" t="n">
-        <v>11.61</v>
+        <v>18.54</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1094,89 +1094,89 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>12.61</v>
+        <v>31.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>58.57</v>
+        <v>45.01</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.42</v>
+        <v>21.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>-43.51</v>
+        <v>-29.37</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>10.384</v>
+        <v>18.274</v>
       </c>
       <c r="AH3" t="n">
-        <v>31</v>
+        <v>51.6</v>
       </c>
       <c r="AI3" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32.1</v>
+        <v>45.6</v>
       </c>
       <c r="AK3" t="n">
-        <v>82.8</v>
+        <v>59</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3.16</v>
+        <v>9.52</v>
       </c>
       <c r="AM3" t="n">
-        <v>26.85</v>
+        <v>28.44</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.88</v>
+        <v>18.48</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.12</v>
+        <v>0.86</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.2735</v>
+        <v>16.6226</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.817500000000001</v>
+        <v>14.5869</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
         <v>85</v>
       </c>
       <c r="AT3" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>37.1</v>
+        <v>50.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>82.8</v>
+        <v>59</v>
       </c>
       <c r="AW3" t="n">
         <v>755</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.914999999999999</v>
+        <v>17.092</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.61</v>
+        <v>18.54</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.08</v>
+        <v>9.93</v>
       </c>
       <c r="BA3" t="n">
-        <v>17.77</v>
+        <v>25.28</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1202,24 +1202,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>62.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>58.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1233,37 +1229,37 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 62.5; priority 57.0; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 64.4; priority 58.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo 4.5% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.5%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1278,153 +1274,131 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>355.9989</v>
+        <v>8.7643</v>
       </c>
       <c r="T4" t="n">
-        <v>460.52</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>11.61</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>-1.18</v>
+        <v>13.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>-16.42</v>
+        <v>61.81</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.97</v>
+        <v>23.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>-33.91</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>23.46</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>20.36</v>
-      </c>
+        <v>-43.46</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Energia pulita</t>
+        </is>
+      </c>
       <c r="AG4" t="n">
-        <v>393.83</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+        <v>10.466</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL4" t="n">
-        <v>-6.46</v>
+        <v>-0.36</v>
       </c>
       <c r="AM4" t="n">
-        <v>-17.33</v>
+        <v>27.41</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.09</v>
+        <v>3.18</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="AP4" t="n">
-        <v>412.1744</v>
+        <v>10.3021</v>
       </c>
       <c r="AQ4" t="n">
-        <v>450.7911</v>
+        <v>8.8345</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT4" t="n">
-        <v>33.8</v>
+        <v>100</v>
       </c>
       <c r="AU4" t="n">
-        <v>44.1</v>
+        <v>37.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>68.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AX4" t="n">
-        <v>390.34</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>460.52</v>
+        <v>11.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-4.45</v>
+        <v>1.59</v>
       </c>
       <c r="BA4" t="n">
-        <v>-12.64</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>Software - Infrastructure</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>2925540409344</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>91</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>68.59999999999999</v>
-      </c>
+        <v>18.47</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1434,20 +1408,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>67.3</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>56.1</v>
+        <v>54.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1461,12 +1439,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 67.3; priority 56.1; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Medium-high risk</t>
+          <t>score 61.0; priority 54.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1476,22 +1454,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 12.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.2%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.1%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.54 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1506,131 +1484,153 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>12.936</v>
+        <v>355.9989</v>
       </c>
       <c r="T5" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>460.52</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>35.01</v>
+        <v>-3.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>45.39</v>
+        <v>-20.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.54</v>
+        <v>24.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>-29.37</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+        <v>-33.91</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>19.59</v>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Robotica e automazione</t>
-        </is>
-      </c>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>50</v>
-      </c>
+        <v>378.91</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>9.279999999999999</v>
+        <v>-10.34</v>
       </c>
       <c r="AM5" t="n">
-        <v>30.75</v>
+        <v>-19.84</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.79</v>
+        <v>4.72</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.87</v>
+        <v>0.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>16.5267</v>
+        <v>412.3229</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5605</v>
+        <v>450.1681</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT5" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>752</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>460.52</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-15.83</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>2814708285440</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>92</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>100</v>
       </c>
-      <c r="AU5" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>755</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>16.544</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>27.33</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+      <c r="BK5" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>74</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>63.1</v>
+      </c>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>62.5</v>
+        <v>59.4</v>
       </c>
       <c r="F6" t="n">
-        <v>43.7</v>
+        <v>38.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 62.5; priority 43.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 59.4; priority 38.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 62.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -3.5%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-3.52</v>
+        <v>-7.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>-11.75</v>
+        <v>-18.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.36</v>
+        <v>36.48</v>
       </c>
       <c r="AB6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.84</v>
+        <v>20.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.56</v>
+        <v>15.66</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1762,45 +1762,45 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>600.21</v>
+        <v>567.58</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-2.19</v>
+        <v>-7.05</v>
       </c>
       <c r="AM6" t="n">
-        <v>-6.59</v>
+        <v>-12.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.87</v>
+        <v>26.44</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="AP6" t="n">
-        <v>622.1975</v>
+        <v>622.0587</v>
       </c>
       <c r="AQ6" t="n">
-        <v>655.3206</v>
+        <v>654.4771</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
         <v>35</v>
       </c>
       <c r="AT6" t="n">
-        <v>38.2</v>
+        <v>27.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>69.90000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX6" t="n">
         <v>566.455</v>
@@ -1809,10 +1809,10 @@
         <v>634.7017</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-3.53</v>
+        <v>-8.76</v>
       </c>
       <c r="BA6" t="n">
-        <v>-8.41</v>
+        <v>-13.28</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1523587088384</v>
+        <v>1440758366208</v>
       </c>
       <c r="BE6" t="n">
         <v>32.84</v>
@@ -1846,16 +1846,16 @@
         <v>100</v>
       </c>
       <c r="BK6" t="n">
-        <v>38.2</v>
+        <v>27.1</v>
       </c>
       <c r="BL6" t="n">
-        <v>79.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="BN6" t="n">
-        <v>69.90000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
@@ -1872,24 +1872,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="F7" t="n">
-        <v>32.9</v>
+        <v>34</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1903,7 +1899,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 39.4; priority 32.9; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 39.3; priority 34.0; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1923,17 +1919,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 39.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.1%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.3%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1952,147 +1948,127 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>343.25</v>
+        <v>20.205</v>
       </c>
       <c r="T7" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+        <v>30.11</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>6.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.39</v>
+        <v>-13.31</v>
       </c>
       <c r="AA7" t="n">
-        <v>57.97</v>
+        <v>34.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>364.56</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>161.87</v>
-      </c>
+        <v>-48.6</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
       <c r="AG7" t="n">
-        <v>404.66</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+        <v>25.865</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="AL7" t="n">
-        <v>-4.16</v>
+        <v>4.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>-11.83</v>
+        <v>-14.81</v>
       </c>
       <c r="AN7" t="n">
-        <v>13.92</v>
+        <v>-3.93</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.24</v>
+        <v>-0.12</v>
       </c>
       <c r="AP7" t="n">
-        <v>400.348</v>
+        <v>24.5557</v>
       </c>
       <c r="AQ7" t="n">
-        <v>416.2956</v>
+        <v>26.8912</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
         <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>50.9</v>
+        <v>46.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>78.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AX7" t="n">
-        <v>381.59</v>
+        <v>24.93</v>
       </c>
       <c r="AY7" t="n">
-        <v>442.1</v>
+        <v>30.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.08</v>
+        <v>5.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>1519791243264</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>18.74</v>
-      </c>
+        <v>-3.82</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>78.2</v>
-      </c>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>USA / EV</t>
-        </is>
-      </c>
+      <c r="BP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2112,10 +2088,10 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="F8" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2129,7 +2105,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 63.2; priority 32.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 62.9; priority 31.1; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2144,12 +2120,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo 14.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 14.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 63.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.4%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 62.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.9%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2200,13 +2176,13 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>55.21</v>
+        <v>58.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>140.44</v>
+        <v>137.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>35.35</v>
+        <v>35.33</v>
       </c>
       <c r="AB8" t="n">
         <v>-35.74</v>
@@ -2224,10 +2200,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>616</v>
+        <v>623.97</v>
       </c>
       <c r="AH8" t="n">
-        <v>57.8</v>
+        <v>58.2</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
@@ -2236,25 +2212,25 @@
         <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>41.1</v>
+        <v>39</v>
       </c>
       <c r="AL8" t="n">
-        <v>10.72</v>
+        <v>14.25</v>
       </c>
       <c r="AM8" t="n">
-        <v>74.48999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.36</v>
+        <v>60.95</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AP8" t="n">
-        <v>538.3665999999999</v>
+        <v>542.848</v>
       </c>
       <c r="AQ8" t="n">
-        <v>407.2589</v>
+        <v>408.9318</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
@@ -2267,22 +2243,22 @@
         <v>29</v>
       </c>
       <c r="AV8" t="n">
-        <v>41.1</v>
+        <v>39</v>
       </c>
       <c r="AW8" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX8" t="n">
-        <v>543.96</v>
+        <v>564.66</v>
       </c>
       <c r="AY8" t="n">
         <v>647.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.42</v>
+        <v>14.94</v>
       </c>
       <c r="BA8" t="n">
-        <v>51.26</v>
+        <v>52.59</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2308,20 +2284,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E9" t="n">
-        <v>39.3</v>
+        <v>36.8</v>
       </c>
       <c r="F9" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2335,12 +2315,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 39.3; priority 29.8; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 36.8; priority 29.9; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2350,22 +2330,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 8.2% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.2%.</t>
+          <t>TSLA: scenario base High Risk, score 36.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.2%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2380,131 +2360,151 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>20.205</v>
+        <v>343.25</v>
       </c>
       <c r="T9" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>9.720000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="Z9" t="n">
-        <v>-12.74</v>
+        <v>20.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>34.02</v>
+        <v>57.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>-48.6</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>363.65</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>158.56</v>
+      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>26.53</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>61.3</v>
-      </c>
+        <v>396.38</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>10.22</v>
+        <v>-3.32</v>
       </c>
       <c r="AM9" t="n">
-        <v>-11.93</v>
+        <v>-16.61</v>
       </c>
       <c r="AN9" t="n">
-        <v>-3.11</v>
+        <v>13.11</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.09</v>
+        <v>0.23</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.5113</v>
+        <v>401.3426</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26.9103</v>
+        <v>416.6081</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AT9" t="n">
-        <v>53.3</v>
+        <v>46.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>61.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="AX9" t="n">
-        <v>24.93</v>
+        <v>381.59</v>
       </c>
       <c r="AY9" t="n">
-        <v>30.11</v>
+        <v>442.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>8.24</v>
+        <v>-1.24</v>
       </c>
       <c r="BA9" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+        <v>-4.86</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>1488693755904</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
+      <c r="BJ9" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>73.40000000000001</v>
+      </c>
       <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>60.9</v>
       </c>
       <c r="F10" t="n">
-        <v>7.7</v>
+        <v>16.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 60.0; priority 7.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 60.9; priority 16.8; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 22.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 19.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 22.3%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.1%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>37.83</v>
+        <v>33.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>145.89</v>
+        <v>145.59</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.22</v>
+        <v>38.24</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>61.7</v>
+        <v>63.86</v>
       </c>
       <c r="AD10" t="n">
-        <v>38.36</v>
+        <v>39.93</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1622.2</v>
+        <v>1591.2</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>24.15</v>
+        <v>25.85</v>
       </c>
       <c r="AM10" t="n">
-        <v>73.02</v>
+        <v>72.58</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.71</v>
+        <v>34.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="AP10" t="n">
-        <v>1326.8936</v>
+        <v>1335.5488</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1070.9524</v>
+        <v>1075.7448</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2671,22 +2671,22 @@
         <v>18.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.699999999999999</v>
+        <v>22.2</v>
       </c>
       <c r="AW10" t="n">
         <v>764</v>
       </c>
       <c r="AX10" t="n">
-        <v>1249</v>
+        <v>1333</v>
       </c>
       <c r="AY10" t="n">
         <v>1629.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22.26</v>
+        <v>19.14</v>
       </c>
       <c r="BA10" t="n">
-        <v>51.47</v>
+        <v>47.92</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>613276581888</v>
+        <v>638405836800</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2714,7 +2714,7 @@
         <v>12.99</v>
       </c>
       <c r="BI10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BJ10" t="n">
         <v>100</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="BM10" t="n">
         <v>18.3</v>
       </c>
       <c r="BN10" t="n">
-        <v>9.699999999999999</v>
+        <v>22.2</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2741,44 +2741,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3. Interessanti ma da attendere</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="F11" t="n">
-        <v>65.3</v>
+        <v>78.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟠 Attendi pullback</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Non inseguire il prezzo: imposta alert su pullback o tenuta supporto. Supporto 60D: 54.81.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 79.1; priority 65.3; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Normal risk</t>
+          <t>score 79.3; priority 78.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>prezzo 11.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 79.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.8%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 79.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.3%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2822,83 +2822,83 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>54.81</v>
+        <v>39.31</v>
       </c>
       <c r="T11" t="n">
-        <v>72.27</v>
+        <v>49.485</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>28.28</v>
+        <v>17.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>63.26</v>
+        <v>45.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.77</v>
+        <v>16.18</v>
       </c>
       <c r="AB11" t="n">
-        <v>-17.8</v>
+        <v>-19.17</v>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>72.25</v>
+        <v>48.575</v>
       </c>
       <c r="AH11" t="n">
-        <v>79</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AI11" t="n">
         <v>100</v>
       </c>
       <c r="AJ11" t="n">
-        <v>69.2</v>
+        <v>65.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>51.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AL11" t="n">
-        <v>9.25</v>
+        <v>6.65</v>
       </c>
       <c r="AM11" t="n">
-        <v>39.61</v>
+        <v>27.81</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.16</v>
+        <v>19.55</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.9</v>
+        <v>1.21</v>
       </c>
       <c r="AP11" t="n">
-        <v>64.64360000000001</v>
+        <v>45.6843</v>
       </c>
       <c r="AQ11" t="n">
-        <v>55.3358</v>
+        <v>40.6756</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
@@ -2908,25 +2908,25 @@
         <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>69.2</v>
+        <v>65.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>51.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AW11" t="n">
         <v>755</v>
       </c>
       <c r="AX11" t="n">
-        <v>65.27</v>
+        <v>45.845</v>
       </c>
       <c r="AY11" t="n">
-        <v>72.27</v>
+        <v>49.485</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11.77</v>
+        <v>6.33</v>
       </c>
       <c r="BA11" t="n">
-        <v>30.57</v>
+        <v>19.42</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2952,24 +2952,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>79.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>77.7</v>
+        <v>77.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2978,42 +2974,42 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 79.9; priority 77.7; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 77.0; priority 77.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.3%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3023,7 +3019,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -3032,149 +3028,127 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>273.3367</v>
+        <v>140.98</v>
       </c>
       <c r="T12" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+        <v>164.88</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>20.12</v>
+        <v>11.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>114.3</v>
+        <v>27.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>29.78</v>
+        <v>12.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>28.47</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>25.78</v>
-      </c>
+        <v>-21.07</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Azionario globale</t>
+        </is>
+      </c>
       <c r="AG12" t="n">
-        <v>373.25</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
+        <v>164.16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>81.3</v>
+      </c>
       <c r="AL12" t="n">
-        <v>-5.87</v>
+        <v>3.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>20.84</v>
+        <v>13.23</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.52</v>
+        <v>17.59</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AP12" t="n">
-        <v>365.0052</v>
+        <v>157.2968</v>
       </c>
       <c r="AQ12" t="n">
-        <v>309.1874</v>
+        <v>147.4076</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>40.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>82.8</v>
+        <v>81.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="AX12" t="n">
-        <v>356.38</v>
+        <v>159.24</v>
       </c>
       <c r="AY12" t="n">
-        <v>389.8971</v>
+        <v>164.88</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.26</v>
+        <v>4.36</v>
       </c>
       <c r="BA12" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>4554610442240</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>82.8</v>
-      </c>
+        <v>11.36</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
       <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3184,20 +3158,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>76.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="F13" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3206,12 +3180,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 76.9; priority 76.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.0; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3231,17 +3205,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.9%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3260,15 +3234,15 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>140.98</v>
+        <v>107.5</v>
       </c>
       <c r="T13" t="n">
-        <v>164.88</v>
+        <v>124.27</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3282,16 +3256,16 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>12.14</v>
+        <v>10.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>27.42</v>
+        <v>24.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.94</v>
+        <v>13.19</v>
       </c>
       <c r="AB13" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
@@ -3302,69 +3276,69 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>164.6</v>
+        <v>124.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>73</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AI13" t="n">
-        <v>82</v>
+        <v>77.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK13" t="n">
-        <v>79.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.24</v>
+        <v>3.09</v>
       </c>
       <c r="AM13" t="n">
-        <v>13.6</v>
+        <v>11.19</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.48</v>
+        <v>17.41</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>156.9084</v>
+        <v>119.3124</v>
       </c>
       <c r="AQ13" t="n">
-        <v>147.2667</v>
+        <v>112.638</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>82</v>
+        <v>77.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>79.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AX13" t="n">
-        <v>158.2</v>
+        <v>120.73</v>
       </c>
       <c r="AY13" t="n">
-        <v>164.88</v>
+        <v>124.27</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.9</v>
+        <v>4.02</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.77</v>
+        <v>10.18</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3400,10 +3374,10 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>75.3</v>
+        <v>75.5</v>
       </c>
       <c r="F14" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3412,12 +3386,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.2349. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.25. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 75.3; priority 76.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.5; priority 76.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,12 +3411,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.23 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.25 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -3469,7 +3443,7 @@
         <v>56.0747</v>
       </c>
       <c r="T14" t="n">
-        <v>63.2349</v>
+        <v>63.25</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
@@ -3488,13 +3462,13 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>8.130000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.3</v>
+        <v>19.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.9</v>
+        <v>12.88</v>
       </c>
       <c r="AB14" t="n">
         <v>-16.33</v>
@@ -3512,13 +3486,13 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>63.08</v>
+        <v>63.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="AJ14" t="n">
         <v>71.5</v>
@@ -3527,29 +3501,29 @@
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.89</v>
+        <v>4.38</v>
       </c>
       <c r="AM14" t="n">
-        <v>11.91</v>
+        <v>12.15</v>
       </c>
       <c r="AN14" t="n">
-        <v>13.81</v>
+        <v>14.3</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AP14" t="n">
-        <v>61.0566</v>
+        <v>61.1499</v>
       </c>
       <c r="AQ14" t="n">
-        <v>58.0921</v>
+        <v>58.1382</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="AU14" t="n">
         <v>71.5</v>
@@ -3561,16 +3535,16 @@
         <v>759</v>
       </c>
       <c r="AX14" t="n">
-        <v>60.6339</v>
+        <v>61.4745</v>
       </c>
       <c r="AY14" t="n">
-        <v>63.2349</v>
+        <v>63.25</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.31</v>
+        <v>3.43</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.59</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3596,17 +3570,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>75.8</v>
+        <v>78.8</v>
       </c>
       <c r="F15" t="n">
         <v>76.2</v>
@@ -3618,42 +3596,42 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 75.8; priority 76.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.8; priority 76.2; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 75.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3663,136 +3641,158 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>107.5</v>
+        <v>273.3367</v>
       </c>
       <c r="T15" t="n">
-        <v>124.27</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>11.06</v>
+        <v>18.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>23.73</v>
+        <v>106.39</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.2</v>
+        <v>29.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>-21.63</v>
-      </c>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>25.12</v>
+      </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>Azionario globale sviluppato</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="n">
-        <v>124.26</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>81.2</v>
-      </c>
+        <v>363.79</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>2.67</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AM15" t="n">
-        <v>11.43</v>
+        <v>18.18</v>
       </c>
       <c r="AN15" t="n">
-        <v>17.21</v>
+        <v>44.21</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AP15" t="n">
-        <v>119.0378</v>
+        <v>366.1754</v>
       </c>
       <c r="AQ15" t="n">
-        <v>112.5415</v>
+        <v>309.9449</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT15" t="n">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="AU15" t="n">
-        <v>66.90000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>81.2</v>
+        <v>78.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="AX15" t="n">
-        <v>120.3</v>
+        <v>356.38</v>
       </c>
       <c r="AY15" t="n">
-        <v>124.27</v>
+        <v>389.8971</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.39</v>
+        <v>-0.65</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="inlineStr"/>
+        <v>17.37</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>4439174283264</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>78.8</v>
+      </c>
       <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3812,10 +3812,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>75.3</v>
+        <v>75.5</v>
       </c>
       <c r="F16" t="n">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 75.3; priority 75.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.5; priority 76.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>12.33</v>
+        <v>11.88</v>
       </c>
       <c r="Z16" t="n">
-        <v>26.29</v>
+        <v>26.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="AB16" t="n">
         <v>-23.32</v>
@@ -3924,65 +3924,65 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>701.6</v>
+        <v>699.6799999999999</v>
       </c>
       <c r="AH16" t="n">
-        <v>70.5</v>
+        <v>70.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>80.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="AJ16" t="n">
         <v>64.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="AM16" t="n">
-        <v>11.22</v>
+        <v>10.79</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.43</v>
+        <v>18.52</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AP16" t="n">
-        <v>669.422</v>
+        <v>671.184</v>
       </c>
       <c r="AQ16" t="n">
-        <v>631.965</v>
+        <v>632.5137</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>80.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="AU16" t="n">
         <v>64.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
       <c r="AW16" t="n">
         <v>758</v>
       </c>
       <c r="AX16" t="n">
-        <v>680.9400000000001</v>
+        <v>681.24</v>
       </c>
       <c r="AY16" t="n">
         <v>703.9400000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.81</v>
+        <v>4.25</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.02</v>
+        <v>10.62</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4008,17 +4008,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>78.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="F17" t="n">
         <v>75.09999999999999</v>
@@ -4030,12 +4034,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 49.485. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 78.4; priority 75.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 75.7; priority 75.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4045,27 +4049,27 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4075,7 +4079,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4084,127 +4088,149 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>39.31</v>
+        <v>246.403</v>
       </c>
       <c r="T17" t="n">
-        <v>49.485</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>20.67</v>
+        <v>18.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>45.72</v>
+        <v>49.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>16.17</v>
+        <v>26.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>-19.17</v>
-      </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>30.84</v>
+      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>Mercati emergenti</t>
-        </is>
-      </c>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
-        <v>49.13</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>67</v>
-      </c>
+        <v>295.95</v>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>7.08</v>
+        <v>-0.63</v>
       </c>
       <c r="AM17" t="n">
-        <v>29.2</v>
+        <v>8.17</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.84</v>
+        <v>17.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.23</v>
+        <v>0.68</v>
       </c>
       <c r="AP17" t="n">
-        <v>45.5145</v>
+        <v>287.8428</v>
       </c>
       <c r="AQ17" t="n">
-        <v>40.6089</v>
+        <v>267.4483</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>752</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>4346723172352</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>100</v>
       </c>
-      <c r="AU17" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>67</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>755</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>44.985</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>49.485</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="inlineStr"/>
-      <c r="BM17" t="inlineStr"/>
-      <c r="BN17" t="inlineStr"/>
+      <c r="BK17" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4224,10 +4250,10 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="F18" t="n">
-        <v>74.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4241,7 +4267,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 73.5; priority 74.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.8; priority 75.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4261,7 +4287,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4308,17 +4334,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>9.59</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.21</v>
+        <v>21.21</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="AB18" t="n">
         <v>-20.6</v>
@@ -4336,65 +4362,65 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>75.89</v>
+        <v>75.77</v>
       </c>
       <c r="AH18" t="n">
-        <v>65.2</v>
+        <v>65.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK18" t="n">
-        <v>80.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.56</v>
+        <v>3.88</v>
       </c>
       <c r="AM18" t="n">
-        <v>11.65</v>
+        <v>11.57</v>
       </c>
       <c r="AN18" t="n">
-        <v>15.18</v>
+        <v>15.41</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AP18" t="n">
-        <v>72.51600000000001</v>
+        <v>72.667</v>
       </c>
       <c r="AQ18" t="n">
-        <v>68.9156</v>
+        <v>68.973</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>80.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="AW18" t="n">
         <v>755</v>
       </c>
       <c r="AX18" t="n">
-        <v>73.11</v>
+        <v>73.59</v>
       </c>
       <c r="AY18" t="n">
         <v>75.89</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.65</v>
+        <v>4.27</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.12</v>
+        <v>9.85</v>
       </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
@@ -4420,24 +4446,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>75.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>74.5</v>
+        <v>70.7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4446,42 +4468,42 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 75.3; priority 74.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 68.6; priority 70.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.9%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4500,149 +4522,127 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>246.403</v>
+        <v>62.06</v>
       </c>
       <c r="T19" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+        <v>64.68000000000001</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>17.81</v>
+        <v>-1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>52.93</v>
+        <v>1.83</v>
       </c>
       <c r="AA19" t="n">
-        <v>26.02</v>
+        <v>9.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>-33.36</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>36.18</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>31.19</v>
-      </c>
+        <v>-12.85</v>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Min volatility</t>
+        </is>
+      </c>
       <c r="AG19" t="n">
-        <v>299.24</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
+        <v>63.98</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL19" t="n">
-        <v>-0.33</v>
+        <v>0.52</v>
       </c>
       <c r="AM19" t="n">
-        <v>7.73</v>
+        <v>2.76</v>
       </c>
       <c r="AN19" t="n">
-        <v>18.06</v>
+        <v>6.82</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AP19" t="n">
-        <v>286.9892</v>
+        <v>63.3816</v>
       </c>
       <c r="AQ19" t="n">
-        <v>267.126</v>
+        <v>63.1244</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>92.8</v>
+        <v>49.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>42.1</v>
+        <v>78.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>81.7</v>
+        <v>82.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AX19" t="n">
-        <v>290.55</v>
+        <v>63.51</v>
       </c>
       <c r="AY19" t="n">
-        <v>315.2</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>4395044175872</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>81.7</v>
-      </c>
+        <v>1.36</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>68.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>70.7</v>
+        <v>69.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 10.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 68.6; priority 70.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 79.9; priority 69.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.1%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.4%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4728,20 +4728,20 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>62.06</v>
+        <v>54.81</v>
       </c>
       <c r="T20" t="n">
-        <v>64.68000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4750,89 +4750,89 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>-1.79</v>
+        <v>26.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.57</v>
+        <v>63.23</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.56</v>
+        <v>13.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>-12.85</v>
+        <v>-17.8</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>64.11</v>
+        <v>71.7</v>
       </c>
       <c r="AH20" t="n">
-        <v>61.5</v>
+        <v>78.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>49.6</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>78.2</v>
+        <v>69.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>82.8</v>
+        <v>57.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.17</v>
+        <v>9.48</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.81</v>
+        <v>38.02</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.71</v>
+        <v>26.04</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.7</v>
+        <v>1.89</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.3822</v>
+        <v>64.94840000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.1178</v>
+        <v>55.4611</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>49.6</v>
+        <v>100</v>
       </c>
       <c r="AU20" t="n">
-        <v>78.2</v>
+        <v>69.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>82.8</v>
+        <v>57.2</v>
       </c>
       <c r="AW20" t="n">
         <v>755</v>
       </c>
       <c r="AX20" t="n">
-        <v>63.51</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>64.68000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.15</v>
+        <v>10.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.57</v>
+        <v>29.28</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 74.0; priority 57.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 73.0; priority 55.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 74.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.3%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 73.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.9%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>14.14</v>
+        <v>13.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>46.29</v>
+        <v>41.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.96</v>
+        <v>46.94</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>31.81</v>
+        <v>31.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.3</v>
+        <v>16.08</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>207.41</v>
+        <v>204.65</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
@@ -4990,35 +4990,35 @@
         <v>-7.84</v>
       </c>
       <c r="AM21" t="n">
-        <v>18.65</v>
+        <v>16.23</v>
       </c>
       <c r="AN21" t="n">
-        <v>68.61</v>
+        <v>67.73</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AP21" t="n">
-        <v>208.0094</v>
+        <v>208.5445</v>
       </c>
       <c r="AQ21" t="n">
-        <v>189.3302</v>
+        <v>189.4837</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
         <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>92.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AU21" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>79.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX21" t="n">
         <v>200.42</v>
@@ -5027,10 +5027,10 @@
         <v>224.0988</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.29</v>
+        <v>-1.87</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.550000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>5023677808640</v>
+        <v>4956827418624</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5057,23 +5057,21 @@
       <c r="BH21" t="n">
         <v>6.55</v>
       </c>
-      <c r="BI21" t="n">
-        <v>47</v>
-      </c>
+      <c r="BI21" t="inlineStr"/>
       <c r="BJ21" t="n">
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>92.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="BL21" t="n">
-        <v>68</v>
+        <v>68.8</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>79.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5100,10 +5098,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="F22" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5115,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 54.5; priority 56.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 54.4; priority 56.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,12 +5130,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 4.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.4%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5188,13 +5186,13 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-14.96</v>
+        <v>-14</v>
       </c>
       <c r="Z22" t="n">
-        <v>28.99</v>
+        <v>27.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>18.06</v>
+        <v>18.07</v>
       </c>
       <c r="AB22" t="n">
         <v>-21.9</v>
@@ -5212,50 +5210,50 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>361.04</v>
+        <v>358.64</v>
       </c>
       <c r="AH22" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="AJ22" t="n">
         <v>60.8</v>
       </c>
       <c r="AK22" t="n">
-        <v>68.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AL22" t="n">
-        <v>-4.01</v>
+        <v>-4.43</v>
       </c>
       <c r="AM22" t="n">
-        <v>3.91</v>
+        <v>2.74</v>
       </c>
       <c r="AN22" t="n">
-        <v>27.8</v>
+        <v>27.66</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AP22" t="n">
-        <v>377.802</v>
+        <v>377.1878</v>
       </c>
       <c r="AQ22" t="n">
-        <v>363.5818</v>
+        <v>363.9777</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="AU22" t="n">
         <v>60.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>68.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AW22" t="n">
         <v>755</v>
@@ -5267,10 +5265,10 @@
         <v>377.9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-4.44</v>
+        <v>-4.92</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0.7</v>
+        <v>-1.47</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>63.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 65.3; priority 63.5; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 67.4; priority 66.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 7.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 65.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.5%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>13.17</v>
+        <v>17.07</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.9</v>
+        <v>13.77</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.1</v>
+        <v>31.12</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>30.57</v>
+        <v>31.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.09</v>
+        <v>24.79</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,45 +888,45 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>237.5</v>
+        <v>244.39</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-10.33</v>
+        <v>-5.76</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.72</v>
+        <v>9.81</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.74</v>
+        <v>24.89</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
-        <v>256.6374</v>
+        <v>257.1002</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.7084</v>
+        <v>232.8037</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>74.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>68.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX2" t="n">
         <v>237.5</v>
@@ -935,10 +935,10 @@
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-7.46</v>
+        <v>-4.94</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.06</v>
+        <v>4.98</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2554813480960</v>
+        <v>2628929978368</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>74.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="BL2" t="n">
-        <v>58.3</v>
+        <v>56.3</v>
       </c>
       <c r="BM2" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>68.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -1006,10 +1006,10 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="F3" t="n">
-        <v>62.9</v>
+        <v>62.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 68.6; priority 62.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 68.5; priority 62.3; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 9.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.2%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>31.75</v>
+        <v>33.76</v>
       </c>
       <c r="Z3" t="n">
-        <v>45.01</v>
+        <v>47.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="AB3" t="n">
         <v>-29.37</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>18.274</v>
+        <v>18.422</v>
       </c>
       <c r="AH3" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="AI3" t="n">
         <v>100</v>
@@ -1130,25 +1130,25 @@
         <v>45.6</v>
       </c>
       <c r="AK3" t="n">
-        <v>59</v>
+        <v>58.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>9.52</v>
+        <v>11.35</v>
       </c>
       <c r="AM3" t="n">
-        <v>28.44</v>
+        <v>30.52</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.48</v>
+        <v>18.77</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.6226</v>
+        <v>16.7222</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5869</v>
+        <v>14.6136</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
@@ -1161,10 +1161,10 @@
         <v>50.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>59</v>
+        <v>58.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX3" t="n">
         <v>17.092</v>
@@ -1173,10 +1173,10 @@
         <v>18.54</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.93</v>
+        <v>10.16</v>
       </c>
       <c r="BA3" t="n">
-        <v>25.28</v>
+        <v>26.06</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>64.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="F4" t="n">
-        <v>58.2</v>
+        <v>57.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 64.4; priority 58.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 63.6; priority 57.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 63.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.1%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>13.52</v>
+        <v>11.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>61.81</v>
+        <v>59.99</v>
       </c>
       <c r="AA4" t="n">
         <v>23.42</v>
@@ -1324,13 +1324,13 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>10.466</v>
+        <v>10.342</v>
       </c>
       <c r="AH4" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>32.1</v>
@@ -1339,29 +1339,29 @@
         <v>82.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AM4" t="n">
-        <v>27.41</v>
+        <v>27.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.18</v>
+        <v>2.76</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.3021</v>
+        <v>10.3337</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.8345</v>
+        <v>8.850899999999999</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
         <v>85</v>
       </c>
       <c r="AT4" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AU4" t="n">
         <v>37.1</v>
@@ -1370,7 +1370,7 @@
         <v>82.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX4" t="n">
         <v>9.914999999999999</v>
@@ -1379,10 +1379,10 @@
         <v>11.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.59</v>
+        <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.47</v>
+        <v>16.85</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>61.3</v>
       </c>
       <c r="F5" t="n">
-        <v>54.1</v>
+        <v>54.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 61.0; priority 54.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 61.3; priority 54.5; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 8.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.1%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 61.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.0%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1506,22 +1506,22 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>-3.08</v>
+        <v>-2.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>-20.29</v>
+        <v>-20</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.05</v>
+        <v>24.04</v>
       </c>
       <c r="AB5" t="n">
         <v>-33.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="AD5" t="n">
-        <v>19.59</v>
+        <v>19.61</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>378.91</v>
+        <v>379.4</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-10.34</v>
+        <v>-8.91</v>
       </c>
       <c r="AM5" t="n">
-        <v>-19.84</v>
+        <v>-20</v>
       </c>
       <c r="AN5" t="n">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
       <c r="AO5" t="n">
         <v>0.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>412.3229</v>
+        <v>412.4404</v>
       </c>
       <c r="AQ5" t="n">
-        <v>450.1681</v>
+        <v>449.5554</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
         <v>35</v>
       </c>
       <c r="AT5" t="n">
-        <v>28.7</v>
+        <v>29.8</v>
       </c>
       <c r="AU5" t="n">
         <v>44</v>
       </c>
       <c r="AV5" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX5" t="n">
         <v>378.91</v>
@@ -1577,10 +1577,10 @@
         <v>460.52</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-8.1</v>
+        <v>-8.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>-15.83</v>
+        <v>-15.61</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2814708285440</v>
+        <v>2818348154880</v>
       </c>
       <c r="BE5" t="n">
         <v>39.34</v>
@@ -1614,16 +1614,16 @@
         <v>100</v>
       </c>
       <c r="BK5" t="n">
-        <v>28.7</v>
+        <v>29.8</v>
       </c>
       <c r="BL5" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="BM5" t="n">
         <v>44</v>
       </c>
       <c r="BN5" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59.4</v>
+        <v>60.7</v>
       </c>
       <c r="F6" t="n">
-        <v>38.7</v>
+        <v>40.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 59.4; priority 38.7; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 60.7; priority 40.6; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.8%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-7.73</v>
+        <v>-4.77</v>
       </c>
       <c r="Z6" t="n">
-        <v>-18.9</v>
+        <v>-16.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.48</v>
+        <v>36.47</v>
       </c>
       <c r="AB6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.65</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.66</v>
+        <v>15.93</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1762,45 +1762,45 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>567.58</v>
+        <v>577.22</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-7.05</v>
+        <v>-4.12</v>
       </c>
       <c r="AM6" t="n">
-        <v>-12.19</v>
+        <v>-12.01</v>
       </c>
       <c r="AN6" t="n">
-        <v>26.44</v>
+        <v>27.11</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="AP6" t="n">
-        <v>622.0587</v>
+        <v>621.3661</v>
       </c>
       <c r="AQ6" t="n">
-        <v>654.4771</v>
+        <v>653.6996</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
         <v>35</v>
       </c>
       <c r="AT6" t="n">
-        <v>27.1</v>
+        <v>31.9</v>
       </c>
       <c r="AU6" t="n">
         <v>28.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>62.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX6" t="n">
         <v>566.455</v>
@@ -1809,10 +1809,10 @@
         <v>634.7017</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-8.76</v>
+        <v>-7.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>-13.28</v>
+        <v>-11.7</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1440758366208</v>
+        <v>1465228591104</v>
       </c>
       <c r="BE6" t="n">
         <v>32.84</v>
@@ -1846,16 +1846,16 @@
         <v>100</v>
       </c>
       <c r="BK6" t="n">
-        <v>27.1</v>
+        <v>31.9</v>
       </c>
       <c r="BL6" t="n">
-        <v>81.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="BM6" t="n">
         <v>28.9</v>
       </c>
       <c r="BN6" t="n">
-        <v>62.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
@@ -1882,10 +1882,10 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 39.3; priority 34.0; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 39.1; priority 33.9; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.3%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>6.44</v>
+        <v>5.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>-13.31</v>
+        <v>-13.81</v>
       </c>
       <c r="AA7" t="n">
-        <v>34.05</v>
+        <v>34.03</v>
       </c>
       <c r="AB7" t="n">
         <v>-48.6</v>
@@ -1994,53 +1994,53 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>25.865</v>
+        <v>25.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>46.8</v>
+        <v>45.6</v>
       </c>
       <c r="AJ7" t="n">
         <v>15.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.7</v>
+        <v>2.31</v>
       </c>
       <c r="AM7" t="n">
-        <v>-14.81</v>
+        <v>-14.98</v>
       </c>
       <c r="AN7" t="n">
-        <v>-3.93</v>
+        <v>-3.91</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.5557</v>
+        <v>24.6063</v>
       </c>
       <c r="AQ7" t="n">
-        <v>26.8912</v>
+        <v>26.87</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
         <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>46.8</v>
+        <v>45.6</v>
       </c>
       <c r="AU7" t="n">
         <v>20.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX7" t="n">
         <v>24.93</v>
@@ -2049,10 +2049,10 @@
         <v>30.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.33</v>
+        <v>5.18</v>
       </c>
       <c r="BA7" t="n">
-        <v>-3.82</v>
+        <v>-3.68</v>
       </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -2078,20 +2078,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E8" t="n">
-        <v>62.9</v>
+        <v>38.6</v>
       </c>
       <c r="F8" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2105,12 +2109,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 62.9; priority 31.1; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 38.6; priority 32.0; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2120,22 +2124,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo 14.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 62.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.9%.</t>
+          <t>TSLA: scenario base High Risk, score 38.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.5%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 647.10 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2145,136 +2149,156 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>362.53</v>
+        <v>343.25</v>
       </c>
       <c r="T8" t="n">
-        <v>647.1</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>58.5</v>
+        <v>5.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>137.65</v>
+        <v>26.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>35.33</v>
+        <v>57.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>160.2</v>
+      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>623.97</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>39</v>
-      </c>
+        <v>400.49</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>14.25</v>
+        <v>-0.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>77.36</v>
+        <v>-18.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.95</v>
+        <v>13.48</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.73</v>
+        <v>0.23</v>
       </c>
       <c r="AP8" t="n">
-        <v>542.848</v>
+        <v>402.4874</v>
       </c>
       <c r="AQ8" t="n">
-        <v>408.9318</v>
+        <v>416.9638</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT8" t="n">
-        <v>100</v>
+        <v>53.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>39</v>
+        <v>74.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX8" t="n">
-        <v>564.66</v>
+        <v>381.59</v>
       </c>
       <c r="AY8" t="n">
-        <v>647.1</v>
+        <v>442.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.94</v>
+        <v>-0.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>52.59</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+        <v>-3.95</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>1504129843200</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
+      <c r="BJ8" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2284,24 +2308,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>36.8</v>
+        <v>59.9</v>
       </c>
       <c r="F9" t="n">
-        <v>29.9</v>
+        <v>14.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2315,12 +2335,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 36.8; priority 29.9; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 59.9; priority 14.1; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2330,22 +2350,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 20.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 36.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -1.2%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 59.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.5%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 659.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2355,156 +2375,136 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>343.25</v>
+        <v>362.53</v>
       </c>
       <c r="T9" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+        <v>659.88</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0.92</v>
+        <v>67.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.43</v>
+        <v>153.04</v>
       </c>
       <c r="AA9" t="n">
-        <v>57.94</v>
+        <v>35.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>363.65</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>158.56</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG9" t="n">
-        <v>396.38</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+        <v>659.88</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>16.7</v>
+      </c>
       <c r="AL9" t="n">
-        <v>-3.32</v>
+        <v>21.31</v>
       </c>
       <c r="AM9" t="n">
-        <v>-16.61</v>
+        <v>88.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>13.11</v>
+        <v>63.89</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.23</v>
+        <v>1.8</v>
       </c>
       <c r="AP9" t="n">
-        <v>401.3426</v>
+        <v>547.5872000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>416.6081</v>
+        <v>410.8032</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT9" t="n">
-        <v>46.4</v>
+        <v>100</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>73.40000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX9" t="n">
-        <v>381.59</v>
+        <v>567.88</v>
       </c>
       <c r="AY9" t="n">
-        <v>442.1</v>
+        <v>659.88</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1.24</v>
+        <v>20.51</v>
       </c>
       <c r="BA9" t="n">
-        <v>-4.86</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>1488693755904</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>18.74</v>
-      </c>
+        <v>60.63</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>73.40000000000001</v>
-      </c>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>USA / EV</t>
-        </is>
-      </c>
+      <c r="BP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60.9</v>
+        <v>59.2</v>
       </c>
       <c r="F10" t="n">
-        <v>16.8</v>
+        <v>5.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 60.9; priority 16.8; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 59.2; priority 5.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 19.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 23.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 19.1%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 59.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.0%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1629.60 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1656.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>1109.5466</v>
       </c>
       <c r="T10" t="n">
-        <v>1629.6</v>
+        <v>1656.4</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>33.18</v>
+        <v>39.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>145.59</v>
+        <v>156.71</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.24</v>
+        <v>38.28</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>63.86</v>
+        <v>64.61</v>
       </c>
       <c r="AD10" t="n">
-        <v>39.93</v>
+        <v>40.4</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1591.2</v>
+        <v>1656.4</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>25.85</v>
+        <v>32.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>72.58</v>
+        <v>78.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>34.75</v>
+        <v>36.49</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AP10" t="n">
-        <v>1335.5488</v>
+        <v>1346.4499</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1075.7448</v>
+        <v>1080.9571</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2668,25 +2668,25 @@
         <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>22.2</v>
+        <v>6.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AX10" t="n">
-        <v>1333</v>
+        <v>1345.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>1629.6</v>
+        <v>1656.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19.14</v>
+        <v>23.02</v>
       </c>
       <c r="BA10" t="n">
-        <v>47.92</v>
+        <v>53.23</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>638405836800</v>
+        <v>645959974912</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BM10" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="BN10" t="n">
-        <v>22.2</v>
+        <v>6.7</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2741,49 +2741,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>79.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>78.8</v>
+        <v>77.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 79.3; priority 78.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.1; priority 77.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2793,17 +2797,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 79.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.3%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 80.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.2%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2822,83 +2826,71 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>39.31</v>
+        <v>273.3367</v>
       </c>
       <c r="T11" t="n">
-        <v>49.485</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>17.6</v>
+        <v>19.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>45.39</v>
+        <v>109.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.18</v>
+        <v>29.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>-19.17</v>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>25.42</v>
+      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>Mercati emergenti</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="n">
-        <v>48.575</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>73.40000000000001</v>
-      </c>
+        <v>368.03</v>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>6.65</v>
+        <v>-5.01</v>
       </c>
       <c r="AM11" t="n">
-        <v>27.81</v>
+        <v>20.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.55</v>
+        <v>44.7</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>45.6843</v>
+        <v>367.1934</v>
       </c>
       <c r="AQ11" t="n">
-        <v>40.6756</v>
+        <v>310.7313</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
@@ -2908,41 +2900,75 @@
         <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>65.3</v>
+        <v>40.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>73.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AX11" t="n">
-        <v>45.845</v>
+        <v>356.38</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.485</v>
+        <v>389.8971</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.33</v>
+        <v>0.23</v>
       </c>
       <c r="BA11" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
+        <v>18.44</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>4490912595968</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2962,10 +2988,10 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2979,7 +3005,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 77.0; priority 77.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.1; priority 77.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2999,7 +3025,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -3053,10 +3079,10 @@
         <v>11.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>27.67</v>
+        <v>27.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="AB12" t="n">
         <v>-21.07</v>
@@ -3074,53 +3100,53 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>164.16</v>
+        <v>164.64</v>
       </c>
       <c r="AH12" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AJ12" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AK12" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.61</v>
+        <v>4.07</v>
       </c>
       <c r="AM12" t="n">
-        <v>13.23</v>
+        <v>13.76</v>
       </c>
       <c r="AN12" t="n">
-        <v>17.59</v>
+        <v>17.68</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AP12" t="n">
-        <v>157.2968</v>
+        <v>157.7112</v>
       </c>
       <c r="AQ12" t="n">
-        <v>147.4076</v>
+        <v>147.5467</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AU12" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AX12" t="n">
         <v>159.24</v>
@@ -3129,10 +3155,10 @@
         <v>164.88</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.36</v>
+        <v>11.59</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -3158,20 +3184,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>78.8</v>
       </c>
       <c r="F13" t="n">
-        <v>76.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3180,17 +3206,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 49.485. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 76.0; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.8; priority 77.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3205,17 +3231,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.3%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3225,7 +3251,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3234,15 +3260,15 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>107.5</v>
+        <v>39.31</v>
       </c>
       <c r="T13" t="n">
-        <v>124.27</v>
+        <v>49.485</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3256,89 +3282,89 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>10.65</v>
+        <v>18.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>24.62</v>
+        <v>49.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.19</v>
+        <v>16.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>-21.63</v>
+        <v>-19.17</v>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>124.11</v>
+        <v>49.225</v>
       </c>
       <c r="AH13" t="n">
-        <v>72.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="n">
-        <v>66.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>82.7</v>
+        <v>69.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.09</v>
+        <v>9.43</v>
       </c>
       <c r="AM13" t="n">
-        <v>11.19</v>
+        <v>29.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.41</v>
+        <v>20.05</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AP13" t="n">
-        <v>119.3124</v>
+        <v>45.8697</v>
       </c>
       <c r="AQ13" t="n">
-        <v>112.638</v>
+        <v>40.7463</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="AU13" t="n">
-        <v>66.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>82.7</v>
+        <v>69.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX13" t="n">
-        <v>120.73</v>
+        <v>45.945</v>
       </c>
       <c r="AY13" t="n">
-        <v>124.27</v>
+        <v>49.485</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.02</v>
+        <v>7.31</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.18</v>
+        <v>20.81</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3364,20 +3390,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>76.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3386,12 +3412,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.25. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 75.5; priority 76.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.0; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3411,17 +3437,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.4%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.25 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.07 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3440,15 +3466,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>56.0747</v>
+        <v>107.5</v>
       </c>
       <c r="T14" t="n">
-        <v>63.25</v>
+        <v>124.27</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3462,16 +3488,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>7.96</v>
+        <v>10.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.11</v>
+        <v>25.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.88</v>
+        <v>13.19</v>
       </c>
       <c r="AB14" t="n">
-        <v>-16.33</v>
+        <v>-21.63</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3482,69 +3508,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>63.25</v>
+        <v>124.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>70.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AI14" t="n">
-        <v>73.2</v>
+        <v>77.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>71.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK14" t="n">
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.38</v>
+        <v>3.22</v>
       </c>
       <c r="AM14" t="n">
-        <v>12.15</v>
+        <v>11.49</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.3</v>
+        <v>17.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AP14" t="n">
-        <v>61.1499</v>
+        <v>119.601</v>
       </c>
       <c r="AQ14" t="n">
-        <v>58.1382</v>
+        <v>112.7309</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>73.2</v>
+        <v>77.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>71.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV14" t="n">
         <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="AX14" t="n">
-        <v>61.4745</v>
+        <v>120.73</v>
       </c>
       <c r="AY14" t="n">
-        <v>63.25</v>
+        <v>124.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.43</v>
+        <v>3.82</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.789999999999999</v>
+        <v>10.15</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3570,24 +3596,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>78.8</v>
+        <v>75.7</v>
       </c>
       <c r="F15" t="n">
-        <v>76.2</v>
+        <v>76.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3596,42 +3618,42 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.63. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 78.8; priority 76.2; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 75.7; priority 76.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.8, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.7%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3641,158 +3663,136 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>273.3367</v>
+        <v>56.4209</v>
       </c>
       <c r="T15" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+        <v>63.63</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>18.3</v>
+        <v>7.88</v>
       </c>
       <c r="Z15" t="n">
-        <v>106.39</v>
+        <v>20.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>29.8</v>
+        <v>12.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>27.77</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>25.12</v>
-      </c>
+        <v>-16.33</v>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
       <c r="AG15" t="n">
-        <v>363.79</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+        <v>63.63</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL15" t="n">
-        <v>-8.300000000000001</v>
+        <v>4.94</v>
       </c>
       <c r="AM15" t="n">
-        <v>18.18</v>
+        <v>12.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>44.21</v>
+        <v>14.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AP15" t="n">
-        <v>366.1754</v>
+        <v>61.2626</v>
       </c>
       <c r="AQ15" t="n">
-        <v>309.9449</v>
+        <v>58.1866</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>100</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>40.4</v>
+        <v>71.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="AX15" t="n">
-        <v>356.38</v>
+        <v>61.4745</v>
       </c>
       <c r="AY15" t="n">
-        <v>389.8971</v>
+        <v>63.63</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0.65</v>
+        <v>3.86</v>
       </c>
       <c r="BA15" t="n">
-        <v>17.37</v>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD15" t="n">
-        <v>4439174283264</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>24</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>78.8</v>
-      </c>
+        <v>9.359999999999999</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
       <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3812,10 +3812,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 75.5; priority 76.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.4; priority 76.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>11.88</v>
+        <v>11.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>26.31</v>
+        <v>25.56</v>
       </c>
       <c r="AA16" t="n">
         <v>14.16</v>
@@ -3924,53 +3924,53 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>699.6799999999999</v>
+        <v>698.02</v>
       </c>
       <c r="AH16" t="n">
-        <v>70.7</v>
+        <v>70.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK16" t="n">
-        <v>81.8</v>
+        <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="AM16" t="n">
-        <v>10.79</v>
+        <v>10.82</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.52</v>
+        <v>18.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AP16" t="n">
-        <v>671.184</v>
+        <v>672.9712</v>
       </c>
       <c r="AQ16" t="n">
-        <v>632.5137</v>
+        <v>633.0239</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>79.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>81.8</v>
+        <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AX16" t="n">
         <v>681.24</v>
@@ -3979,10 +3979,10 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.25</v>
+        <v>3.72</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.62</v>
+        <v>10.27</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>75.7</v>
+        <v>76.3</v>
       </c>
       <c r="F17" t="n">
-        <v>75.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 75.7; priority 75.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 76.3; priority 75.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.8%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.2%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -4106,22 +4106,22 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>18.52</v>
+        <v>19.81</v>
       </c>
       <c r="Z17" t="n">
-        <v>49.75</v>
+        <v>52.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>26.02</v>
+        <v>26</v>
       </c>
       <c r="AB17" t="n">
         <v>-33.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>35.83</v>
+        <v>36.08</v>
       </c>
       <c r="AD17" t="n">
-        <v>30.84</v>
+        <v>31.06</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -4130,36 +4130,36 @@
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
-        <v>295.95</v>
+        <v>298.01</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>-0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="AM17" t="n">
-        <v>8.17</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.6</v>
+        <v>17.84</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP17" t="n">
-        <v>287.8428</v>
+        <v>288.6298</v>
       </c>
       <c r="AQ17" t="n">
-        <v>267.4483</v>
+        <v>267.793</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>93.3</v>
+        <v>96.2</v>
       </c>
       <c r="AU17" t="n">
         <v>42.1</v>
@@ -4168,7 +4168,7 @@
         <v>82.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX17" t="n">
         <v>290.55</v>
@@ -4177,10 +4177,10 @@
         <v>315.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.66</v>
+        <v>11.28</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>4346723172352</v>
+        <v>4376979046400</v>
       </c>
       <c r="BE17" t="n">
         <v>27.15</v>
@@ -4214,10 +4214,10 @@
         <v>100</v>
       </c>
       <c r="BK17" t="n">
-        <v>93.3</v>
+        <v>96.2</v>
       </c>
       <c r="BL17" t="n">
-        <v>42.5</v>
+        <v>41.9</v>
       </c>
       <c r="BM17" t="n">
         <v>42.1</v>
@@ -4250,10 +4250,10 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 73.8; priority 75.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 73.9; priority 75.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>9.210000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.21</v>
+        <v>22.13</v>
       </c>
       <c r="AA18" t="n">
         <v>12.88</v>
@@ -4362,25 +4362,25 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>75.77</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="AH18" t="n">
         <v>65.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AJ18" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AK18" t="n">
-        <v>81.7</v>
+        <v>82.3</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="AM18" t="n">
-        <v>11.57</v>
+        <v>11.88</v>
       </c>
       <c r="AN18" t="n">
         <v>15.41</v>
@@ -4389,38 +4389,38 @@
         <v>1.2</v>
       </c>
       <c r="AP18" t="n">
-        <v>72.667</v>
+        <v>72.83</v>
       </c>
       <c r="AQ18" t="n">
-        <v>68.973</v>
+        <v>69.0282</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>81.7</v>
+        <v>82.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX18" t="n">
-        <v>73.59</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>75.89</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.27</v>
+        <v>4.11</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
@@ -4446,20 +4446,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>68.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="F19" t="n">
-        <v>70.7</v>
+        <v>71</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,17 +4468,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 9.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 68.6; priority 70.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.2; priority 71.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -4522,20 +4522,20 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>62.06</v>
+        <v>54.81</v>
       </c>
       <c r="T19" t="n">
-        <v>64.68000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -4544,89 +4544,89 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>-1.95</v>
+        <v>25.74</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.83</v>
+        <v>63.26</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.56</v>
+        <v>13.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>-12.85</v>
+        <v>-17.8</v>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>63.98</v>
+        <v>71.72</v>
       </c>
       <c r="AH19" t="n">
-        <v>61.7</v>
+        <v>78.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>49.4</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
-        <v>78.2</v>
+        <v>69.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>82.8</v>
+        <v>59.1</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.52</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.76</v>
+        <v>37.82</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.82</v>
+        <v>26.02</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.71</v>
+        <v>1.89</v>
       </c>
       <c r="AP19" t="n">
-        <v>63.3816</v>
+        <v>65.258</v>
       </c>
       <c r="AQ19" t="n">
-        <v>63.1244</v>
+        <v>55.5858</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>49.4</v>
+        <v>100</v>
       </c>
       <c r="AU19" t="n">
-        <v>78.2</v>
+        <v>69.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>82.8</v>
+        <v>59.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX19" t="n">
-        <v>63.51</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>64.68000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.36</v>
+        <v>29.03</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>79.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="F20" t="n">
-        <v>69.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 10.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 79.9; priority 69.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 68.5; priority 70.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo 10.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 79.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.4%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4728,20 +4728,20 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>54.81</v>
+        <v>62.06</v>
       </c>
       <c r="T20" t="n">
-        <v>72.27</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4750,89 +4750,89 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>26.25</v>
+        <v>-2.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>63.23</v>
+        <v>1.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.78</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB20" t="n">
-        <v>-17.8</v>
+        <v>-12.85</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>71.7</v>
+        <v>63.85</v>
       </c>
       <c r="AH20" t="n">
-        <v>78.8</v>
+        <v>61.7</v>
       </c>
       <c r="AI20" t="n">
-        <v>100</v>
+        <v>49.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>69.2</v>
+        <v>78.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>57.2</v>
+        <v>82.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>9.48</v>
+        <v>-1.04</v>
       </c>
       <c r="AM20" t="n">
-        <v>38.02</v>
+        <v>2.88</v>
       </c>
       <c r="AN20" t="n">
-        <v>26.04</v>
+        <v>6.74</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.89</v>
+        <v>0.71</v>
       </c>
       <c r="AP20" t="n">
-        <v>64.94840000000001</v>
+        <v>63.3858</v>
       </c>
       <c r="AQ20" t="n">
-        <v>55.4611</v>
+        <v>63.1282</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>100</v>
+        <v>49.1</v>
       </c>
       <c r="AU20" t="n">
-        <v>69.2</v>
+        <v>78.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>57.2</v>
+        <v>82.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX20" t="n">
-        <v>66.59999999999999</v>
+        <v>63.51</v>
       </c>
       <c r="AY20" t="n">
-        <v>72.27</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10.4</v>
+        <v>0.73</v>
       </c>
       <c r="BA20" t="n">
-        <v>29.28</v>
+        <v>1.14</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 73.0; priority 55.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 76.6; priority 60.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 73.0, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -1.9%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>13.57</v>
+        <v>18.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>41.63</v>
+        <v>46.39</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.94</v>
+        <v>46.93</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>31.34</v>
+        <v>32.26</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.08</v>
+        <v>16.55</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,45 +4980,45 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-7.84</v>
+        <v>-4.39</v>
       </c>
       <c r="AM21" t="n">
-        <v>16.23</v>
+        <v>18.7</v>
       </c>
       <c r="AN21" t="n">
-        <v>67.73</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AP21" t="n">
-        <v>208.5445</v>
+        <v>209.121</v>
       </c>
       <c r="AQ21" t="n">
-        <v>189.4837</v>
+        <v>189.6844</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT21" t="n">
-        <v>89.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AU21" t="n">
         <v>14.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>76.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX21" t="n">
         <v>200.42</v>
@@ -5027,10 +5027,10 @@
         <v>224.0988</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-1.87</v>
+        <v>0.75</v>
       </c>
       <c r="BA21" t="n">
-        <v>8</v>
+        <v>11.07</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4956827418624</v>
+        <v>5103122644992</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5062,16 +5062,16 @@
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>89.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="BL21" t="n">
-        <v>68.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="BM21" t="n">
         <v>14.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>76.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5098,10 +5098,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54.4</v>
+        <v>55.2</v>
       </c>
       <c r="F22" t="n">
-        <v>56.4</v>
+        <v>57.4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 54.4; priority 56.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 55.2; priority 57.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.9%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.0%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5182,17 +5182,17 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-14</v>
+        <v>-13.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>27.17</v>
+        <v>26.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>18.07</v>
+        <v>18.06</v>
       </c>
       <c r="AB22" t="n">
         <v>-21.9</v>
@@ -5210,53 +5210,53 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>358.64</v>
+        <v>361.71</v>
       </c>
       <c r="AH22" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="AJ22" t="n">
         <v>60.8</v>
       </c>
       <c r="AK22" t="n">
-        <v>67.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="AL22" t="n">
-        <v>-4.43</v>
+        <v>-3.15</v>
       </c>
       <c r="AM22" t="n">
-        <v>2.74</v>
+        <v>4.18</v>
       </c>
       <c r="AN22" t="n">
-        <v>27.66</v>
+        <v>27.98</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AP22" t="n">
-        <v>377.1878</v>
+        <v>376.6952</v>
       </c>
       <c r="AQ22" t="n">
-        <v>363.9777</v>
+        <v>364.3808</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="AU22" t="n">
         <v>60.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>67.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="AW22" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AX22" t="n">
         <v>340.82</v>
@@ -5265,10 +5265,10 @@
         <v>377.9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-4.92</v>
+        <v>-3.98</v>
       </c>
       <c r="BA22" t="n">
-        <v>-1.47</v>
+        <v>-0.73</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -996,20 +996,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>68.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>62.3</v>
+        <v>58.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 68.5; priority 62.3; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 64.4; priority 58.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1033,27 +1033,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 10.2% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.2%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.54 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1072,15 +1072,15 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>12.936</v>
+        <v>8.7643</v>
       </c>
       <c r="T3" t="n">
-        <v>18.54</v>
+        <v>11.61</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1094,61 +1094,61 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>33.76</v>
+        <v>13.74</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.66</v>
+        <v>59.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.55</v>
+        <v>23.42</v>
       </c>
       <c r="AB3" t="n">
-        <v>-29.37</v>
+        <v>-43.46</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>18.422</v>
+        <v>10.512</v>
       </c>
       <c r="AH3" t="n">
-        <v>51.7</v>
+        <v>31.4</v>
       </c>
       <c r="AI3" t="n">
         <v>100</v>
       </c>
       <c r="AJ3" t="n">
-        <v>45.6</v>
+        <v>32.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>58.1</v>
+        <v>82.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>11.35</v>
+        <v>-0.51</v>
       </c>
       <c r="AM3" t="n">
-        <v>30.52</v>
+        <v>28.57</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.77</v>
+        <v>3.32</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.87</v>
+        <v>0.14</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.7222</v>
+        <v>10.3619</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.6136</v>
+        <v>8.867800000000001</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
@@ -1158,25 +1158,25 @@
         <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>50.6</v>
+        <v>37.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>58.1</v>
+        <v>82.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX3" t="n">
-        <v>17.092</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AY3" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BA3" t="n">
         <v>18.54</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>26.06</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1202,20 +1202,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>63.6</v>
+        <v>67.8</v>
       </c>
       <c r="F4" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1229,37 +1229,37 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 63.6; priority 57.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 67.8; priority 57.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 11.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 63.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.1%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1278,15 +1278,15 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8.7643</v>
+        <v>12.936</v>
       </c>
       <c r="T4" t="n">
-        <v>11.61</v>
+        <v>18.786</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1300,89 +1300,89 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>11.15</v>
+        <v>36.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>59.99</v>
+        <v>48.91</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.42</v>
+        <v>21.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>-43.46</v>
+        <v>-29.37</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>10.342</v>
+        <v>18.786</v>
       </c>
       <c r="AH4" t="n">
-        <v>31.1</v>
+        <v>52.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32.1</v>
+        <v>45.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>82.8</v>
+        <v>51.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.53</v>
+        <v>9.9</v>
       </c>
       <c r="AM4" t="n">
-        <v>27.11</v>
+        <v>34.03</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.76</v>
+        <v>19.52</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.12</v>
+        <v>0.91</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.3337</v>
+        <v>16.8126</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.850899999999999</v>
+        <v>14.6416</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
         <v>85</v>
       </c>
       <c r="AT4" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AU4" t="n">
-        <v>37.1</v>
+        <v>50.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>82.8</v>
+        <v>51.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.914999999999999</v>
+        <v>17.092</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.61</v>
+        <v>18.786</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.08</v>
+        <v>11.74</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.85</v>
+        <v>28.31</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1784,7 +1784,7 @@
         <v>621.3661</v>
       </c>
       <c r="AQ6" t="n">
-        <v>653.6996</v>
+        <v>653.6997</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
@@ -1882,10 +1882,10 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>39.1</v>
+        <v>38.2</v>
       </c>
       <c r="F7" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 39.1; priority 33.9; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 38.2; priority 33.8; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.1, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 5.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 38.2, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.8%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>5.76</v>
+        <v>3.02</v>
       </c>
       <c r="Z7" t="n">
-        <v>-13.81</v>
+        <v>-16.84</v>
       </c>
       <c r="AA7" t="n">
-        <v>34.03</v>
+        <v>34.05</v>
       </c>
       <c r="AB7" t="n">
         <v>-48.6</v>
@@ -1994,65 +1994,65 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>25.88</v>
+        <v>25.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>45.6</v>
+        <v>39.8</v>
       </c>
       <c r="AJ7" t="n">
         <v>15.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>73.5</v>
+        <v>78.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.31</v>
+        <v>-0.32</v>
       </c>
       <c r="AM7" t="n">
-        <v>-14.98</v>
+        <v>-16.98</v>
       </c>
       <c r="AN7" t="n">
-        <v>-3.91</v>
+        <v>-4.89</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.6063</v>
+        <v>24.6398</v>
       </c>
       <c r="AQ7" t="n">
-        <v>26.87</v>
+        <v>26.8449</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
         <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>45.6</v>
+        <v>39.8</v>
       </c>
       <c r="AU7" t="n">
         <v>20.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>73.5</v>
+        <v>78.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AX7" t="n">
-        <v>24.93</v>
+        <v>25.09</v>
       </c>
       <c r="AY7" t="n">
         <v>30.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.18</v>
+        <v>1.83</v>
       </c>
       <c r="BA7" t="n">
-        <v>-3.68</v>
+        <v>-6.54</v>
       </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 59.2; priority 5.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 59.1; priority 3.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 23.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 59.2, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.0%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 59.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1656.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>1109.5466</v>
       </c>
       <c r="T10" t="n">
-        <v>1656.4</v>
+        <v>1676</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>39.06</v>
+        <v>41.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>156.71</v>
+        <v>152.64</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.28</v>
+        <v>38.26</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>64.61</v>
+        <v>63.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>40.4</v>
+        <v>39.96</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1656.4</v>
+        <v>1676</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>32.62</v>
+        <v>25.73</v>
       </c>
       <c r="AM10" t="n">
-        <v>78.55</v>
+        <v>85.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.49</v>
+        <v>36.97</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="AP10" t="n">
-        <v>1346.4499</v>
+        <v>1355.7714</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1080.9571</v>
+        <v>1086.2272</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2668,25 +2668,25 @@
         <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AX10" t="n">
-        <v>1345.2</v>
+        <v>1376.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1656.4</v>
+        <v>1676</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23.02</v>
+        <v>23.62</v>
       </c>
       <c r="BA10" t="n">
-        <v>53.23</v>
+        <v>54.3</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>645959974912</v>
+        <v>638945394688</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BM10" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2988,10 +2988,10 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>77.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 164.88. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 165.46. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 77.1; priority 77.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.6; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.7%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 164.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 165.46 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -3057,7 +3057,7 @@
         <v>140.98</v>
       </c>
       <c r="T12" t="n">
-        <v>164.88</v>
+        <v>165.46</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
@@ -3076,13 +3076,13 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>11.39</v>
+        <v>12.71</v>
       </c>
       <c r="Z12" t="n">
-        <v>27.43</v>
+        <v>28.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="AB12" t="n">
         <v>-21.07</v>
@@ -3100,65 +3100,65 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>164.64</v>
+        <v>165.46</v>
       </c>
       <c r="AH12" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>81.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AJ12" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AK12" t="n">
-        <v>81.2</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.07</v>
+        <v>3.57</v>
       </c>
       <c r="AM12" t="n">
-        <v>13.76</v>
+        <v>14.84</v>
       </c>
       <c r="AN12" t="n">
-        <v>17.68</v>
+        <v>17.85</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AP12" t="n">
-        <v>157.7112</v>
+        <v>158.0588</v>
       </c>
       <c r="AQ12" t="n">
-        <v>147.5467</v>
+        <v>147.6913</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>81.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AU12" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>81.2</v>
+        <v>80</v>
       </c>
       <c r="AW12" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AX12" t="n">
         <v>159.24</v>
       </c>
       <c r="AY12" t="n">
-        <v>164.88</v>
+        <v>165.46</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.39</v>
+        <v>4.68</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.59</v>
+        <v>12.03</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -3184,20 +3184,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>78.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3206,17 +3206,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 49.485. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 124.67. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 78.8; priority 77.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 76.6; priority 77.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3231,17 +3231,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.3%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 49.48 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.67 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3260,15 +3260,15 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>39.31</v>
+        <v>107.5</v>
       </c>
       <c r="T13" t="n">
-        <v>49.485</v>
+        <v>124.67</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3282,89 +3282,89 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>18.29</v>
+        <v>11.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>49.05</v>
+        <v>25.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>16.18</v>
+        <v>13.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>-19.17</v>
+        <v>-21.63</v>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>49.225</v>
+        <v>124.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>70.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>65.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK13" t="n">
-        <v>69.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AL13" t="n">
-        <v>9.43</v>
+        <v>2.74</v>
       </c>
       <c r="AM13" t="n">
-        <v>29.3</v>
+        <v>12.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>20.05</v>
+        <v>17.54</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AP13" t="n">
-        <v>45.8697</v>
+        <v>119.8436</v>
       </c>
       <c r="AQ13" t="n">
-        <v>40.7463</v>
+        <v>112.8274</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AU13" t="n">
-        <v>65.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>69.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX13" t="n">
-        <v>45.945</v>
+        <v>120.73</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.485</v>
+        <v>124.67</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.31</v>
+        <v>4.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>20.81</v>
+        <v>10.5</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3390,20 +3390,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>76.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.27. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 76.0; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.1; priority 76.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3466,15 +3466,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>107.5</v>
+        <v>597.92</v>
       </c>
       <c r="T14" t="n">
-        <v>124.27</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3488,16 +3488,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>10.46</v>
+        <v>12.74</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.15</v>
+        <v>26.23</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.19</v>
+        <v>14.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>-21.63</v>
+        <v>-23.32</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3508,69 +3508,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>124.17</v>
+        <v>701.66</v>
       </c>
       <c r="AH14" t="n">
-        <v>72.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="AI14" t="n">
-        <v>77.8</v>
+        <v>81.7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK14" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.22</v>
+        <v>2.24</v>
       </c>
       <c r="AM14" t="n">
-        <v>11.49</v>
+        <v>12.11</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.4</v>
+        <v>18.58</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AP14" t="n">
-        <v>119.601</v>
+        <v>674.5712</v>
       </c>
       <c r="AQ14" t="n">
-        <v>112.7309</v>
+        <v>633.5651</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>77.8</v>
+        <v>81.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="AX14" t="n">
-        <v>120.73</v>
+        <v>681.24</v>
       </c>
       <c r="AY14" t="n">
-        <v>124.27</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.82</v>
+        <v>4.02</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.15</v>
+        <v>10.75</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
         <v>75.7</v>
       </c>
       <c r="F15" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 75.7; priority 76.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.7; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3694,13 +3694,13 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>7.88</v>
+        <v>8.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.89</v>
+        <v>20.84</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="AB15" t="n">
         <v>-16.33</v>
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>63.63</v>
+        <v>63.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>71.2</v>
+        <v>70.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>73.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="AJ15" t="n">
         <v>71.5</v>
@@ -3733,29 +3733,29 @@
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.94</v>
+        <v>2.79</v>
       </c>
       <c r="AM15" t="n">
-        <v>12.22</v>
+        <v>12.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.5</v>
+        <v>14.32</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AP15" t="n">
-        <v>61.2626</v>
+        <v>61.3231</v>
       </c>
       <c r="AQ15" t="n">
-        <v>58.1866</v>
+        <v>58.2354</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>73.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="AU15" t="n">
         <v>71.5</v>
@@ -3764,7 +3764,7 @@
         <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AX15" t="n">
         <v>61.4745</v>
@@ -3773,10 +3773,10 @@
         <v>63.63</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.86</v>
+        <v>3.32</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.359999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3802,20 +3802,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>75.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="F16" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 75.89. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 75.4; priority 76.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 74.3; priority 75.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 75.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3878,20 +3878,20 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>597.92</v>
+        <v>66.58</v>
       </c>
       <c r="T16" t="n">
-        <v>703.9400000000001</v>
+        <v>75.89</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3900,16 +3900,16 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>11.47</v>
+        <v>9.99</v>
       </c>
       <c r="Z16" t="n">
-        <v>25.56</v>
+        <v>21.87</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.16</v>
+        <v>12.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>-23.32</v>
+        <v>-20.6</v>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
@@ -3920,69 +3920,69 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>698.02</v>
+        <v>75.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>70.5</v>
+        <v>65.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK16" t="n">
         <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.51</v>
+        <v>3.04</v>
       </c>
       <c r="AM16" t="n">
-        <v>10.82</v>
+        <v>12.04</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.4</v>
+        <v>15.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AP16" t="n">
-        <v>672.9712</v>
+        <v>72.95780000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>633.0239</v>
+        <v>69.0853</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>78.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AX16" t="n">
-        <v>681.24</v>
+        <v>73.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>703.9400000000001</v>
+        <v>75.89</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.72</v>
+        <v>3.94</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.27</v>
+        <v>9.76</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4240,20 +4240,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>73.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>75.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4262,17 +4262,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 75.89. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 50.16. Trigger: prezzo 9.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 73.9; priority 75.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.0; priority 72.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -4282,22 +4282,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 73.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.1%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -4316,111 +4316,111 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>66.58</v>
+        <v>39.31</v>
       </c>
       <c r="T18" t="n">
-        <v>75.89</v>
+        <v>50.16</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>9.119999999999999</v>
+        <v>21.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.13</v>
+        <v>50.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.88</v>
+        <v>16.21</v>
       </c>
       <c r="AB18" t="n">
-        <v>-20.6</v>
+        <v>-19.17</v>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>75.81999999999999</v>
+        <v>50.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>65.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AI18" t="n">
-        <v>75.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>68.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>82.3</v>
+        <v>62.9</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.71</v>
+        <v>9.41</v>
       </c>
       <c r="AM18" t="n">
-        <v>11.88</v>
+        <v>32.73</v>
       </c>
       <c r="AN18" t="n">
-        <v>15.41</v>
+        <v>20.78</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AP18" t="n">
-        <v>72.83</v>
+        <v>46.0295</v>
       </c>
       <c r="AQ18" t="n">
-        <v>69.0282</v>
+        <v>40.8219</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
         <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>75.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="AU18" t="n">
-        <v>68.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>82.3</v>
+        <v>62.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX18" t="n">
-        <v>73.73999999999999</v>
+        <v>45.945</v>
       </c>
       <c r="AY18" t="n">
-        <v>75.89</v>
+        <v>50.16</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.11</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.84</v>
+        <v>22.88</v>
       </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
@@ -4446,20 +4446,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>80.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>71</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,17 +4468,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.27. Trigger: prezzo 9.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 80.2; priority 71.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 68.4; priority 70.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo 9.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.9%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.1%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -4522,20 +4522,20 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>54.81</v>
+        <v>62.06</v>
       </c>
       <c r="T19" t="n">
-        <v>72.27</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -4544,89 +4544,89 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>25.74</v>
+        <v>-1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>63.26</v>
+        <v>1.21</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.77</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>-17.8</v>
+        <v>-12.85</v>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>71.72</v>
+        <v>63.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>78.8</v>
+        <v>61.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>49.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>69.2</v>
+        <v>78.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>59.1</v>
+        <v>82.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>9.880000000000001</v>
+        <v>-1.21</v>
       </c>
       <c r="AM19" t="n">
-        <v>37.82</v>
+        <v>2.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.02</v>
+        <v>6.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.89</v>
+        <v>0.68</v>
       </c>
       <c r="AP19" t="n">
-        <v>65.258</v>
+        <v>63.3808</v>
       </c>
       <c r="AQ19" t="n">
-        <v>55.5858</v>
+        <v>63.1322</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>100</v>
+        <v>49.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>69.2</v>
+        <v>78.3</v>
       </c>
       <c r="AV19" t="n">
-        <v>59.1</v>
+        <v>82.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX19" t="n">
-        <v>66.84999999999999</v>
+        <v>63.44</v>
       </c>
       <c r="AY19" t="n">
-        <v>72.27</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9.9</v>
+        <v>0.09</v>
       </c>
       <c r="BA19" t="n">
-        <v>29.03</v>
+        <v>0.49</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>68.5</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>70.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.4. Trigger: prezzo 10.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 68.5; priority 70.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.0; priority 69.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 10.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.7%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.5%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4728,20 +4728,20 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>62.06</v>
+        <v>54.81</v>
       </c>
       <c r="T20" t="n">
-        <v>64.68000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4750,89 +4750,89 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>-2.15</v>
+        <v>27</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.4</v>
+        <v>64.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.550000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>-12.85</v>
+        <v>-17.8</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>63.85</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AH20" t="n">
-        <v>61.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AI20" t="n">
-        <v>49.1</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>78.3</v>
+        <v>69.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>82.8</v>
+        <v>56.9</v>
       </c>
       <c r="AL20" t="n">
-        <v>-1.04</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.88</v>
+        <v>38.54</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.74</v>
+        <v>26.37</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.71</v>
+        <v>1.92</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.3858</v>
+        <v>65.5444</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.1282</v>
+        <v>55.7142</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>49.1</v>
+        <v>100</v>
       </c>
       <c r="AU20" t="n">
-        <v>78.3</v>
+        <v>69.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>82.8</v>
+        <v>56.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX20" t="n">
-        <v>63.51</v>
+        <v>68.45</v>
       </c>
       <c r="AY20" t="n">
-        <v>64.68000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.73</v>
+        <v>10.46</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.14</v>
+        <v>29.95</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -5098,10 +5098,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>55.2</v>
+        <v>54.2</v>
       </c>
       <c r="F22" t="n">
-        <v>57.4</v>
+        <v>56.1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 55.2; priority 57.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 54.2; priority 56.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 5.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -4.0%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5182,17 +5182,17 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-13.36</v>
+        <v>-12.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>26.81</v>
+        <v>25.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>18.06</v>
+        <v>18.09</v>
       </c>
       <c r="AB22" t="n">
         <v>-21.9</v>
@@ -5210,53 +5210,53 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>361.71</v>
+        <v>354.79</v>
       </c>
       <c r="AH22" t="n">
-        <v>68.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="AI22" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
       <c r="AJ22" t="n">
         <v>60.8</v>
       </c>
       <c r="AK22" t="n">
-        <v>69.3</v>
+        <v>66.8</v>
       </c>
       <c r="AL22" t="n">
-        <v>-3.15</v>
+        <v>-5.46</v>
       </c>
       <c r="AM22" t="n">
-        <v>4.18</v>
+        <v>1.67</v>
       </c>
       <c r="AN22" t="n">
-        <v>27.98</v>
+        <v>27.12</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>376.6952</v>
+        <v>375.9604</v>
       </c>
       <c r="AQ22" t="n">
-        <v>364.3808</v>
+        <v>364.7486</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
       <c r="AU22" t="n">
         <v>60.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>69.3</v>
+        <v>66.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AX22" t="n">
         <v>340.82</v>
@@ -5265,10 +5265,10 @@
         <v>377.9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-3.98</v>
+        <v>-5.63</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0.73</v>
+        <v>-2.73</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="F2" t="n">
-        <v>66.59999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,12 +797,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 67.4; priority 66.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 63.1; priority 60.5; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 67.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 63.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.4%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -864,81 +864,81 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>17.07</v>
+        <v>13.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.77</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.12</v>
+        <v>31.19</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>31.45</v>
+        <v>30.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.79</v>
+        <v>23.56</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>244.39</v>
+        <v>232.79</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-5.76</v>
+        <v>-12.16</v>
       </c>
       <c r="AM2" t="n">
-        <v>9.81</v>
+        <v>5.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.89</v>
+        <v>21.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AP2" t="n">
-        <v>257.1002</v>
+        <v>257.083</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.8037</v>
+        <v>232.8377</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AT2" t="n">
-        <v>83.2</v>
+        <v>74.2</v>
       </c>
       <c r="AU2" t="n">
         <v>37.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>72.3</v>
+        <v>61.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX2" t="n">
-        <v>237.5</v>
+        <v>232.79</v>
       </c>
       <c r="AY2" t="n">
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-4.94</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.98</v>
+        <v>-0.02</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2628929978368</v>
+        <v>2504147599360</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>83.2</v>
+        <v>74.2</v>
       </c>
       <c r="BL2" t="n">
-        <v>56.3</v>
+        <v>59.5</v>
       </c>
       <c r="BM2" t="n">
         <v>37.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>72.3</v>
+        <v>61.1</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -1006,10 +1006,10 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>64.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="F3" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 64.4; priority 58.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 64.8; priority 58.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.4%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>13.74</v>
+        <v>16.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>59.97</v>
+        <v>68.37</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.42</v>
+        <v>23.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>-43.46</v>
+        <v>-43.36</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
@@ -1118,37 +1118,37 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>10.512</v>
+        <v>10.684</v>
       </c>
       <c r="AH3" t="n">
-        <v>31.4</v>
+        <v>32.9</v>
       </c>
       <c r="AI3" t="n">
         <v>100</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="AK3" t="n">
         <v>82.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.51</v>
+        <v>-1.35</v>
       </c>
       <c r="AM3" t="n">
-        <v>28.57</v>
+        <v>32.93</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.32</v>
+        <v>5.04</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.3619</v>
+        <v>10.3918</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.867800000000001</v>
+        <v>8.886100000000001</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
@@ -1158,13 +1158,13 @@
         <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="AV3" t="n">
         <v>82.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX3" t="n">
         <v>9.914999999999999</v>
@@ -1173,10 +1173,10 @@
         <v>11.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="BA3" t="n">
-        <v>18.54</v>
+        <v>20.23</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>57.5</v>
+        <v>57.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 67.8; priority 57.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Medium-high risk</t>
+          <t>score 67.9; priority 57.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.7%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 18.92 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1281,7 +1281,7 @@
         <v>12.936</v>
       </c>
       <c r="T4" t="n">
-        <v>18.786</v>
+        <v>18.916</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
@@ -1300,13 +1300,13 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>36.27</v>
+        <v>39.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>48.91</v>
+        <v>50.51</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="AB4" t="n">
         <v>-29.37</v>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>18.786</v>
+        <v>18.916</v>
       </c>
       <c r="AH4" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="AI4" t="n">
         <v>100</v>
@@ -1336,25 +1336,25 @@
         <v>45.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>9.9</v>
+        <v>10.32</v>
       </c>
       <c r="AM4" t="n">
-        <v>34.03</v>
+        <v>36.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.52</v>
+        <v>20.98</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AP4" t="n">
-        <v>16.8126</v>
+        <v>16.9072</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.6416</v>
+        <v>14.671</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
@@ -1367,22 +1367,22 @@
         <v>50.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX4" t="n">
         <v>17.092</v>
       </c>
       <c r="AY4" t="n">
-        <v>18.786</v>
+        <v>18.916</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.74</v>
+        <v>11.88</v>
       </c>
       <c r="BA4" t="n">
-        <v>28.31</v>
+        <v>28.93</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61.3</v>
+        <v>60.2</v>
       </c>
       <c r="F5" t="n">
-        <v>54.5</v>
+        <v>52.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 61.3; priority 54.5; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 60.2; priority 52.3; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 8.0% sotto MA50: attendere recupero</t>
+          <t>prezzo 10.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 61.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.0%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.9%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1506,22 +1506,22 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>-2.26</v>
+        <v>-3.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>-20</v>
+        <v>-22.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.04</v>
+        <v>24.09</v>
       </c>
       <c r="AB5" t="n">
         <v>-33.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.61</v>
+        <v>21.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>19.61</v>
+        <v>18.99</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1530,57 +1530,57 @@
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>379.4</v>
+        <v>367.34</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-8.91</v>
+        <v>-12.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>-20</v>
+        <v>-22.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AP5" t="n">
-        <v>412.4404</v>
+        <v>412.342</v>
       </c>
       <c r="AQ5" t="n">
-        <v>449.5554</v>
+        <v>448.8813</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
         <v>35</v>
       </c>
       <c r="AT5" t="n">
-        <v>29.8</v>
+        <v>25.7</v>
       </c>
       <c r="AU5" t="n">
         <v>44</v>
       </c>
       <c r="AV5" t="n">
-        <v>63.2</v>
+        <v>58.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX5" t="n">
-        <v>378.91</v>
+        <v>367.34</v>
       </c>
       <c r="AY5" t="n">
         <v>460.52</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-8.01</v>
+        <v>-10.91</v>
       </c>
       <c r="BA5" t="n">
-        <v>-15.61</v>
+        <v>-18.17</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2818348154880</v>
+        <v>2728761229312</v>
       </c>
       <c r="BE5" t="n">
         <v>39.34</v>
@@ -1608,22 +1608,22 @@
         <v>30.27</v>
       </c>
       <c r="BI5" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="BJ5" t="n">
         <v>100</v>
       </c>
       <c r="BK5" t="n">
-        <v>29.8</v>
+        <v>25.7</v>
       </c>
       <c r="BL5" t="n">
-        <v>73.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="BM5" t="n">
         <v>44</v>
       </c>
       <c r="BN5" t="n">
-        <v>63.2</v>
+        <v>58.9</v>
       </c>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60.7</v>
+        <v>60.2</v>
       </c>
       <c r="F6" t="n">
-        <v>40.6</v>
+        <v>39.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 60.7; priority 40.6; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 60.2; priority 39.4; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.1%.</t>
+          <t>META: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-4.77</v>
+        <v>-4.93</v>
       </c>
       <c r="Z6" t="n">
-        <v>-16.94</v>
+        <v>-18.69</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.47</v>
+        <v>36.53</v>
       </c>
       <c r="AB6" t="n">
         <v>-34.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>21</v>
+        <v>20.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.93</v>
+        <v>15.56</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1762,57 +1762,57 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>577.22</v>
+        <v>563.85</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-4.12</v>
+        <v>-6.72</v>
       </c>
       <c r="AM6" t="n">
-        <v>-12.01</v>
+        <v>-13.03</v>
       </c>
       <c r="AN6" t="n">
-        <v>27.11</v>
+        <v>25.55</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AP6" t="n">
-        <v>621.3661</v>
+        <v>620.0869</v>
       </c>
       <c r="AQ6" t="n">
-        <v>653.6997</v>
+        <v>652.8457</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
         <v>35</v>
       </c>
       <c r="AT6" t="n">
-        <v>31.9</v>
+        <v>30.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>64.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX6" t="n">
-        <v>566.455</v>
+        <v>563.85</v>
       </c>
       <c r="AY6" t="n">
         <v>634.7017</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-7.1</v>
+        <v>-9.07</v>
       </c>
       <c r="BA6" t="n">
-        <v>-11.7</v>
+        <v>-13.63</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1465228591104</v>
+        <v>1431289856000</v>
       </c>
       <c r="BE6" t="n">
         <v>32.84</v>
@@ -1840,22 +1840,22 @@
         <v>35.61</v>
       </c>
       <c r="BI6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BJ6" t="n">
         <v>100</v>
       </c>
       <c r="BK6" t="n">
-        <v>31.9</v>
+        <v>30.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>81.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="BM6" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>64.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
@@ -1872,20 +1872,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>38.2</v>
+        <v>42.3</v>
       </c>
       <c r="F7" t="n">
-        <v>33.8</v>
+        <v>36</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1899,7 +1903,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 38.2; priority 33.8; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 42.3; priority 36.0; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1919,17 +1923,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 38.2, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.8%.</t>
+          <t>TSLA: scenario base High Risk, score 42.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1948,127 +1952,147 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>20.205</v>
+        <v>343.25</v>
       </c>
       <c r="T7" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>3.02</v>
+        <v>10.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>-16.84</v>
+        <v>25.77</v>
       </c>
       <c r="AA7" t="n">
-        <v>34.05</v>
+        <v>57.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>-48.6</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>375.05</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>162.02</v>
+      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>25.09</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>78.2</v>
-      </c>
+        <v>405.05</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>-0.32</v>
+        <v>-2.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>-16.98</v>
+        <v>-13.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>-4.89</v>
+        <v>16.55</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.14</v>
+        <v>0.29</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.6398</v>
+        <v>403.676</v>
       </c>
       <c r="AQ7" t="n">
-        <v>26.8449</v>
+        <v>417.3186</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
         <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>39.8</v>
+        <v>62.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
         <v>78.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="AX7" t="n">
-        <v>25.09</v>
+        <v>381.59</v>
       </c>
       <c r="AY7" t="n">
-        <v>30.11</v>
+        <v>442.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.83</v>
+        <v>0.34</v>
       </c>
       <c r="BA7" t="n">
-        <v>-6.54</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+        <v>-2.94</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1521255841792</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
+      <c r="BJ7" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>78.2</v>
+      </c>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2078,24 +2102,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>38.6</v>
+        <v>39.5</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2109,12 +2129,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 38.6; priority 32.0; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 39.5; priority 35.0; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2129,17 +2149,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 38.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.5%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 39.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2154,151 +2174,131 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>343.25</v>
+        <v>20.205</v>
       </c>
       <c r="T8" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+        <v>30.11</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>5.31</v>
+        <v>5.04</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.6</v>
+        <v>-15.71</v>
       </c>
       <c r="AA8" t="n">
-        <v>57.91</v>
+        <v>34.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>367.42</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>160.2</v>
-      </c>
+        <v>-48.6</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
       <c r="AG8" t="n">
-        <v>400.49</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+        <v>25.315</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>78.2</v>
+      </c>
       <c r="AL8" t="n">
-        <v>-0.9</v>
+        <v>1.54</v>
       </c>
       <c r="AM8" t="n">
-        <v>-18.25</v>
+        <v>-15.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>13.48</v>
+        <v>-3.11</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.23</v>
+        <v>-0.09</v>
       </c>
       <c r="AP8" t="n">
-        <v>402.4874</v>
+        <v>24.7195</v>
       </c>
       <c r="AQ8" t="n">
-        <v>416.9638</v>
+        <v>26.8206</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>53.1</v>
+        <v>44</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>74.5</v>
+        <v>78.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AX8" t="n">
-        <v>381.59</v>
+        <v>25.09</v>
       </c>
       <c r="AY8" t="n">
-        <v>442.1</v>
+        <v>30.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.5</v>
+        <v>2.41</v>
       </c>
       <c r="BA8" t="n">
-        <v>-3.95</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>1504129843200</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>18.74</v>
-      </c>
+        <v>-5.61</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>74.5</v>
-      </c>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>USA / EV</t>
-        </is>
-      </c>
+      <c r="BP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2321,7 +2321,7 @@
         <v>59.9</v>
       </c>
       <c r="F9" t="n">
-        <v>14.1</v>
+        <v>12.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 59.9; priority 14.1; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 59.9; priority 12.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 20.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 21.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 59.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.5%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 59.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.1%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 659.88 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2387,7 +2387,7 @@
         <v>362.53</v>
       </c>
       <c r="T9" t="n">
-        <v>659.88</v>
+        <v>668.91</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>67.09</v>
+        <v>73.86</v>
       </c>
       <c r="Z9" t="n">
-        <v>153.04</v>
+        <v>155.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>35.45</v>
+        <v>35.46</v>
       </c>
       <c r="AB9" t="n">
         <v>-35.74</v>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>659.88</v>
+        <v>668.91</v>
       </c>
       <c r="AH9" t="n">
-        <v>59.4</v>
+        <v>60.8</v>
       </c>
       <c r="AI9" t="n">
         <v>100</v>
@@ -2442,25 +2442,25 @@
         <v>23.9</v>
       </c>
       <c r="AK9" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>21.31</v>
+        <v>18.46</v>
       </c>
       <c r="AM9" t="n">
-        <v>88.08</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>63.89</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AP9" t="n">
-        <v>547.5872000000001</v>
+        <v>552.3592</v>
       </c>
       <c r="AQ9" t="n">
-        <v>410.8032</v>
+        <v>412.7201</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
@@ -2473,22 +2473,22 @@
         <v>28.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX9" t="n">
-        <v>567.88</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>659.88</v>
+        <v>668.91</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20.51</v>
+        <v>21.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>60.63</v>
+        <v>62.07</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59.1</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 59.1; priority 3.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 60.0; priority 9.8; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 23.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 21.5% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 59.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 23.6%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.5%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>41.03</v>
+        <v>42.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>152.64</v>
+        <v>141.69</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.26</v>
+        <v>38.3</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>63.91</v>
+        <v>64.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>39.96</v>
+        <v>39.51</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1676</v>
+        <v>1657.8</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>25.73</v>
+        <v>23.24</v>
       </c>
       <c r="AM10" t="n">
-        <v>85.12</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.97</v>
+        <v>37.23</v>
       </c>
       <c r="AO10" t="n">
         <v>0.97</v>
       </c>
       <c r="AP10" t="n">
-        <v>1355.7714</v>
+        <v>1364.2859</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1086.2272</v>
+        <v>1091.2953</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2668,13 +2668,13 @@
         <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.3</v>
+        <v>12.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AX10" t="n">
         <v>1376.4</v>
@@ -2683,10 +2683,10 @@
         <v>1676</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23.62</v>
+        <v>21.51</v>
       </c>
       <c r="BA10" t="n">
-        <v>54.3</v>
+        <v>51.91</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>638945394688</v>
+        <v>638174560256</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2714,7 +2714,7 @@
         <v>12.99</v>
       </c>
       <c r="BI10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="BJ10" t="n">
         <v>100</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.3</v>
+        <v>12.7</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2741,73 +2741,69 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>80.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="F11" t="n">
-        <v>77.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 80.1; priority 77.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 78.8; priority 78.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 80.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.2%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 165.46 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2826,164 +2822,142 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>273.3367</v>
+        <v>140.98</v>
       </c>
       <c r="T11" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+        <v>165.46</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>19.9</v>
+        <v>14.67</v>
       </c>
       <c r="Z11" t="n">
-        <v>109.76</v>
+        <v>28.49</v>
       </c>
       <c r="AA11" t="n">
-        <v>29.78</v>
+        <v>12.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>28.09</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>25.42</v>
-      </c>
+        <v>-21.07</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Azionario globale</t>
+        </is>
+      </c>
       <c r="AG11" t="n">
-        <v>368.03</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+        <v>165.44</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>87</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>81</v>
+      </c>
       <c r="AL11" t="n">
-        <v>-5.01</v>
+        <v>3.45</v>
       </c>
       <c r="AM11" t="n">
-        <v>20.2</v>
+        <v>15.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.7</v>
+        <v>18.44</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP11" t="n">
-        <v>367.1934</v>
+        <v>158.4044</v>
       </c>
       <c r="AQ11" t="n">
-        <v>310.7313</v>
+        <v>147.8411</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
         <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AU11" t="n">
-        <v>40.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>82.8</v>
+        <v>81</v>
       </c>
       <c r="AW11" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="AX11" t="n">
-        <v>356.38</v>
+        <v>159.24</v>
       </c>
       <c r="AY11" t="n">
-        <v>389.8971</v>
+        <v>165.46</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.23</v>
+        <v>4.44</v>
       </c>
       <c r="BA11" t="n">
-        <v>18.44</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>4490912595968</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>82.8</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2991,21 +2965,21 @@
         <v>77.59999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>77.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 165.46. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 77.6; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.6; priority 78.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3025,17 +2999,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.7%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 165.46 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 124.82 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3054,15 +3028,15 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>140.98</v>
+        <v>107.5</v>
       </c>
       <c r="T12" t="n">
-        <v>165.46</v>
+        <v>124.82</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -3076,16 +3050,16 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>12.71</v>
+        <v>13.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>28.4</v>
+        <v>25.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.92</v>
+        <v>13.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
@@ -3096,69 +3070,69 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>165.46</v>
+        <v>124.82</v>
       </c>
       <c r="AH12" t="n">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK12" t="n">
-        <v>80</v>
+        <v>82.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="AM12" t="n">
-        <v>14.84</v>
+        <v>13.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>17.85</v>
+        <v>18.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AP12" t="n">
-        <v>158.0588</v>
+        <v>120.086</v>
       </c>
       <c r="AQ12" t="n">
-        <v>147.6913</v>
+        <v>112.9285</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>83.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>80</v>
+        <v>82.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="AX12" t="n">
-        <v>159.24</v>
+        <v>120.73</v>
       </c>
       <c r="AY12" t="n">
-        <v>165.46</v>
+        <v>124.82</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.68</v>
+        <v>3.94</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.03</v>
+        <v>10.53</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -3184,20 +3158,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>76.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="F13" t="n">
-        <v>77.2</v>
+        <v>77.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3206,12 +3180,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 124.67. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 76.6; priority 77.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.2; priority 77.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3231,17 +3205,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.67 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3260,15 +3234,15 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>107.5</v>
+        <v>597.92</v>
       </c>
       <c r="T13" t="n">
-        <v>124.67</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3282,16 +3256,16 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>11.61</v>
+        <v>14.71</v>
       </c>
       <c r="Z13" t="n">
-        <v>25.17</v>
+        <v>26.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.18</v>
+        <v>14.16</v>
       </c>
       <c r="AB13" t="n">
-        <v>-21.63</v>
+        <v>-23.32</v>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
@@ -3302,69 +3276,69 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>124.67</v>
+        <v>703.54</v>
       </c>
       <c r="AH13" t="n">
-        <v>72.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK13" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.74</v>
+        <v>2.37</v>
       </c>
       <c r="AM13" t="n">
-        <v>12.36</v>
+        <v>13.13</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.54</v>
+        <v>19.16</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AP13" t="n">
-        <v>119.8436</v>
+        <v>676.1572</v>
       </c>
       <c r="AQ13" t="n">
-        <v>112.8274</v>
+        <v>634.1368</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>80</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV13" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AX13" t="n">
-        <v>120.73</v>
+        <v>681.24</v>
       </c>
       <c r="AY13" t="n">
-        <v>124.67</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.5</v>
+        <v>10.94</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3390,20 +3364,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>76.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="F14" t="n">
-        <v>76.8</v>
+        <v>77.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3412,12 +3386,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.63. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 76.1; priority 76.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.7; priority 77.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,17 +3411,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3466,15 +3440,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>597.92</v>
+        <v>56.4209</v>
       </c>
       <c r="T14" t="n">
-        <v>703.9400000000001</v>
+        <v>63.63</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3488,16 +3462,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>12.74</v>
+        <v>10.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>26.23</v>
+        <v>21.57</v>
       </c>
       <c r="AA14" t="n">
-        <v>14.15</v>
+        <v>12.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3508,69 +3482,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>701.66</v>
+        <v>63.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>70.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AI14" t="n">
-        <v>81.7</v>
+        <v>77.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="AM14" t="n">
-        <v>12.11</v>
+        <v>11.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.58</v>
+        <v>14.87</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AP14" t="n">
-        <v>674.5712</v>
+        <v>61.3819</v>
       </c>
       <c r="AQ14" t="n">
-        <v>633.5651</v>
+        <v>58.2829</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>81.7</v>
+        <v>77.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AX14" t="n">
-        <v>681.24</v>
+        <v>61.4745</v>
       </c>
       <c r="AY14" t="n">
-        <v>703.9400000000001</v>
+        <v>63.63</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.02</v>
+        <v>2.99</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.75</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3596,17 +3570,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>75.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F15" t="n">
         <v>76.59999999999999</v>
@@ -3618,12 +3592,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.63. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 75.89. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 75.7; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.1; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3643,17 +3617,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 75.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3672,20 +3646,20 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>56.4209</v>
+        <v>66.58</v>
       </c>
       <c r="T15" t="n">
-        <v>63.63</v>
+        <v>75.89</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -3694,16 +3668,16 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>8.24</v>
+        <v>11.59</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.84</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>-16.33</v>
+        <v>-20.6</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3714,69 +3688,69 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>63.36</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>70.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AI15" t="n">
-        <v>74.2</v>
+        <v>79</v>
       </c>
       <c r="AJ15" t="n">
-        <v>71.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK15" t="n">
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="AM15" t="n">
-        <v>12.38</v>
+        <v>12.05</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.32</v>
+        <v>15.86</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AP15" t="n">
-        <v>61.3231</v>
+        <v>73.0796</v>
       </c>
       <c r="AQ15" t="n">
-        <v>58.2354</v>
+        <v>69.1437</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>74.2</v>
+        <v>79</v>
       </c>
       <c r="AU15" t="n">
-        <v>71.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV15" t="n">
         <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="AX15" t="n">
-        <v>61.4745</v>
+        <v>73.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>63.63</v>
+        <v>75.89</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.32</v>
+        <v>3.67</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3802,17 +3776,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>74.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F16" t="n">
         <v>75.90000000000001</v>
@@ -3824,42 +3802,42 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 75.89. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 74.3; priority 75.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.4; priority 75.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3878,127 +3856,149 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>66.58</v>
+        <v>246.403</v>
       </c>
       <c r="T16" t="n">
-        <v>75.89</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>9.99</v>
+        <v>19.88</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.87</v>
+        <v>51.69</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.87</v>
+        <v>26.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>30.94</v>
+      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>Quality globale</t>
-        </is>
-      </c>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
-        <v>75.83</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>82.8</v>
-      </c>
+        <v>297.01</v>
+      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="n">
-        <v>3.04</v>
+        <v>-1.73</v>
       </c>
       <c r="AM16" t="n">
-        <v>12.04</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AN16" t="n">
-        <v>15.4</v>
+        <v>17.41</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.2</v>
+        <v>0.67</v>
       </c>
       <c r="AP16" t="n">
-        <v>72.95780000000001</v>
+        <v>289.365</v>
       </c>
       <c r="AQ16" t="n">
-        <v>69.0853</v>
+        <v>268.0891</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>76.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>68.09999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="AV16" t="n">
         <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="AX16" t="n">
-        <v>73.8</v>
+        <v>290.55</v>
       </c>
       <c r="AY16" t="n">
-        <v>75.89</v>
+        <v>315.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.94</v>
+        <v>2.64</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="inlineStr"/>
+        <v>10.79</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>4362291642368</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4008,24 +4008,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>76.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>75.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4034,12 +4030,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 50.16. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 76.3; priority 75.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 78.9; priority 75.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4049,27 +4045,27 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 76.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.2%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.8%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4079,7 +4075,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4088,149 +4084,127 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>246.403</v>
+        <v>39.31</v>
       </c>
       <c r="T17" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+        <v>50.16</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>19.81</v>
+        <v>23.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>52.93</v>
+        <v>50.16</v>
       </c>
       <c r="AA17" t="n">
-        <v>26</v>
+        <v>16.21</v>
       </c>
       <c r="AB17" t="n">
-        <v>-33.36</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>36.08</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>31.06</v>
-      </c>
+        <v>-19.17</v>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Mercati emergenti</t>
+        </is>
+      </c>
       <c r="AG17" t="n">
-        <v>298.01</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+        <v>49.8</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>67.40000000000001</v>
+      </c>
       <c r="AL17" t="n">
-        <v>-0.32</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AM17" t="n">
-        <v>8.720000000000001</v>
+        <v>32.96</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.84</v>
+        <v>21.55</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="AP17" t="n">
-        <v>288.6298</v>
+        <v>46.1851</v>
       </c>
       <c r="AQ17" t="n">
-        <v>267.793</v>
+        <v>40.8969</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="AU17" t="n">
-        <v>42.1</v>
+        <v>65.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>82.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AX17" t="n">
-        <v>290.55</v>
+        <v>45.945</v>
       </c>
       <c r="AY17" t="n">
-        <v>315.2</v>
+        <v>50.16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.25</v>
+        <v>7.83</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
-        </is>
-      </c>
-      <c r="BD17" t="n">
-        <v>4376979046400</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>82.8</v>
-      </c>
+        <v>21.77</v>
+      </c>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
       <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4240,20 +4214,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>72.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4262,12 +4240,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 50.16. Trigger: prezzo 9.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 4.9% sotto MA50: attendere recupero.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 78.0; priority 72.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 78.6; priority 74.5; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4277,27 +4255,27 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo 9.0% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.0%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4312,131 +4290,153 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>39.31</v>
+        <v>273.3367</v>
       </c>
       <c r="T18" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>21.38</v>
+        <v>16.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>50.25</v>
+        <v>102.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>16.21</v>
+        <v>29.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>-19.17</v>
-      </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>24.12</v>
+      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Mercati emergenti</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>62.9</v>
-      </c>
+        <v>349.68</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>9.41</v>
+        <v>-10.03</v>
       </c>
       <c r="AM18" t="n">
-        <v>32.73</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>20.78</v>
+        <v>42.67</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AP18" t="n">
-        <v>46.0295</v>
+        <v>367.821</v>
       </c>
       <c r="AQ18" t="n">
-        <v>40.8219</v>
+        <v>311.3296</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT18" t="n">
         <v>100</v>
       </c>
       <c r="AU18" t="n">
-        <v>65.2</v>
+        <v>40.3</v>
       </c>
       <c r="AV18" t="n">
-        <v>62.9</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="AX18" t="n">
-        <v>45.945</v>
+        <v>349.68</v>
       </c>
       <c r="AY18" t="n">
-        <v>50.16</v>
+        <v>389.8971</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8.970000000000001</v>
+        <v>-4.93</v>
       </c>
       <c r="BA18" t="n">
-        <v>22.88</v>
-      </c>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
-      <c r="BM18" t="inlineStr"/>
-      <c r="BN18" t="inlineStr"/>
+        <v>12.32</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>4266995482624</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>72.40000000000001</v>
+      </c>
       <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4456,10 +4456,10 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>68.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>70.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 68.4; priority 70.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 69.0; priority 71.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 68.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.1%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.2%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>-1.73</v>
+        <v>-0.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AB19" t="n">
         <v>-12.85</v>
@@ -4568,53 +4568,53 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>63.44</v>
+        <v>63.52</v>
       </c>
       <c r="AH19" t="n">
-        <v>61.2</v>
+        <v>61.9</v>
       </c>
       <c r="AI19" t="n">
-        <v>49.2</v>
+        <v>51</v>
       </c>
       <c r="AJ19" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="AK19" t="n">
         <v>82.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.21</v>
+        <v>-1.03</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.5</v>
+        <v>6.87</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="AP19" t="n">
-        <v>63.3808</v>
+        <v>63.3784</v>
       </c>
       <c r="AQ19" t="n">
-        <v>63.1322</v>
+        <v>63.1369</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>49.2</v>
+        <v>51</v>
       </c>
       <c r="AU19" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="AV19" t="n">
         <v>82.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX19" t="n">
         <v>63.44</v>
@@ -4623,10 +4623,10 @@
         <v>64.68000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.49</v>
+        <v>0.61</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4662,10 +4662,10 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>69.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.4. Trigger: prezzo 10.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 72.51. Trigger: prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 80.0; priority 69.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 80.4; priority 70.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo 10.5% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.5%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 80.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 72.51 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -4731,7 +4731,7 @@
         <v>54.81</v>
       </c>
       <c r="T20" t="n">
-        <v>72.40000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
@@ -4750,13 +4750,13 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>27</v>
+        <v>29.69</v>
       </c>
       <c r="Z20" t="n">
-        <v>64.62</v>
+        <v>66.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.77</v>
+        <v>13.76</v>
       </c>
       <c r="AB20" t="n">
         <v>-17.8</v>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>72.40000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="AH20" t="n">
-        <v>79.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AI20" t="n">
         <v>100</v>
@@ -4786,25 +4786,25 @@
         <v>69.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>8.710000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AM20" t="n">
-        <v>38.54</v>
+        <v>39.09</v>
       </c>
       <c r="AN20" t="n">
-        <v>26.37</v>
+        <v>27.29</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AP20" t="n">
-        <v>65.5444</v>
+        <v>65.83459999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>55.7142</v>
+        <v>55.8445</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
@@ -4817,22 +4817,22 @@
         <v>69.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX20" t="n">
-        <v>68.45</v>
+        <v>68.89</v>
       </c>
       <c r="AY20" t="n">
-        <v>72.40000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10.46</v>
+        <v>10.14</v>
       </c>
       <c r="BA20" t="n">
-        <v>29.95</v>
+        <v>29.84</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>76.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="F21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 76.6; priority 60.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 75.7; priority 59.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 76.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 75.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.5%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>18.13</v>
+        <v>20.96</v>
       </c>
       <c r="Z21" t="n">
-        <v>46.39</v>
+        <v>43.61</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.93</v>
+        <v>46.97</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>32.26</v>
+        <v>31.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.55</v>
+        <v>16.39</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,45 +4980,45 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>210.69</v>
+        <v>208.65</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-4.39</v>
+        <v>-6.52</v>
       </c>
       <c r="AM21" t="n">
-        <v>18.7</v>
+        <v>22.21</v>
       </c>
       <c r="AN21" t="n">
-        <v>69.26000000000001</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AP21" t="n">
-        <v>209.121</v>
+        <v>209.62</v>
       </c>
       <c r="AQ21" t="n">
-        <v>189.6844</v>
+        <v>189.8757</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="AU21" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AW21" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX21" t="n">
         <v>200.42</v>
@@ -5027,10 +5027,10 @@
         <v>224.0988</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.75</v>
+        <v>-0.46</v>
       </c>
       <c r="BA21" t="n">
-        <v>11.07</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>5103122644992</v>
+        <v>5053711646720</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5057,21 +5057,23 @@
       <c r="BH21" t="n">
         <v>6.55</v>
       </c>
-      <c r="BI21" t="inlineStr"/>
+      <c r="BI21" t="n">
+        <v>47</v>
+      </c>
       <c r="BJ21" t="n">
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="BL21" t="n">
-        <v>67.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="BN21" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5098,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54.2</v>
+        <v>54.8</v>
       </c>
       <c r="F22" t="n">
-        <v>56.1</v>
+        <v>56.3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5115,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 54.2; priority 56.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 54.8; priority 56.3; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5130,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 5.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 54.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5186,13 +5188,13 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-12.95</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>25.28</v>
+        <v>23.18</v>
       </c>
       <c r="AA22" t="n">
-        <v>18.09</v>
+        <v>18.12</v>
       </c>
       <c r="AB22" t="n">
         <v>-21.9</v>
@@ -5210,53 +5212,53 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>354.79</v>
+        <v>348.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>39.2</v>
+        <v>42.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="AK22" t="n">
-        <v>66.8</v>
+        <v>64.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>-5.46</v>
+        <v>-6.97</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.67</v>
+        <v>-0.86</v>
       </c>
       <c r="AN22" t="n">
-        <v>27.12</v>
+        <v>27.39</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AP22" t="n">
-        <v>375.9604</v>
+        <v>375.0458</v>
       </c>
       <c r="AQ22" t="n">
-        <v>364.7486</v>
+        <v>365.0718</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>39.2</v>
+        <v>42.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="AV22" t="n">
-        <v>66.8</v>
+        <v>64.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX22" t="n">
         <v>340.82</v>
@@ -5265,10 +5267,10 @@
         <v>377.9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-5.63</v>
+        <v>-7.15</v>
       </c>
       <c r="BA22" t="n">
-        <v>-2.73</v>
+        <v>-4.61</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>63.1</v>
+        <v>63.9</v>
       </c>
       <c r="F2" t="n">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,12 +797,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 63.1; priority 60.5; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 63.9; priority 61.7; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 63.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.4%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 63.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.9%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -864,66 +864,66 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>13.35</v>
+        <v>11.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.539999999999999</v>
+        <v>11.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.19</v>
+        <v>31.18</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>30.15</v>
+        <v>31.81</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.56</v>
+        <v>23.69</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>232.79</v>
+        <v>234.11</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-12.16</v>
+        <v>-12.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.21</v>
+        <v>3.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.8</v>
+        <v>22.67</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP2" t="n">
-        <v>257.083</v>
+        <v>256.9976</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.8377</v>
+        <v>232.8298</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>74.2</v>
+        <v>70.8</v>
       </c>
       <c r="AU2" t="n">
         <v>37.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>61.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>751</v>
@@ -935,10 +935,10 @@
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-9.449999999999999</v>
+        <v>-8.91</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.02</v>
+        <v>0.55</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2504147599360</v>
+        <v>2518346891264</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>74.2</v>
+        <v>70.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>59.5</v>
+        <v>57.4</v>
       </c>
       <c r="BM2" t="n">
         <v>37.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>61.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -1009,7 +1009,7 @@
         <v>64.8</v>
       </c>
       <c r="F3" t="n">
-        <v>58.4</v>
+        <v>58.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 64.8; priority 58.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 64.8; priority 58.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>16.69</v>
+        <v>19.01</v>
       </c>
       <c r="Z3" t="n">
-        <v>68.37</v>
+        <v>71.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.44</v>
+        <v>23.45</v>
       </c>
       <c r="AB3" t="n">
         <v>-43.36</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>10.684</v>
+        <v>10.872</v>
       </c>
       <c r="AH3" t="n">
-        <v>32.9</v>
+        <v>33.6</v>
       </c>
       <c r="AI3" t="n">
         <v>100</v>
@@ -1130,25 +1130,25 @@
         <v>32.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>82.8</v>
+        <v>81.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.35</v>
+        <v>-2.05</v>
       </c>
       <c r="AM3" t="n">
-        <v>32.93</v>
+        <v>34.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.04</v>
+        <v>6.06</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.3918</v>
+        <v>10.4235</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.886100000000001</v>
+        <v>8.9054</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
@@ -1161,7 +1161,7 @@
         <v>37.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>82.8</v>
+        <v>81.5</v>
       </c>
       <c r="AW3" t="n">
         <v>755</v>
@@ -1173,10 +1173,10 @@
         <v>11.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.81</v>
+        <v>4.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>20.23</v>
+        <v>22.08</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>67.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>57.2</v>
+        <v>54.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 67.9; priority 57.2; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Medium-high risk</t>
+          <t>score 67.6; priority 54.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo 11.9% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 12.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
+          <t>RBOT.MI: scenario base Hold / Monitor, score 67.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.7%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 18.92 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1281,7 +1281,7 @@
         <v>12.936</v>
       </c>
       <c r="T4" t="n">
-        <v>18.916</v>
+        <v>19.164</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>39.4</v>
+        <v>42.76</v>
       </c>
       <c r="Z4" t="n">
-        <v>50.51</v>
+        <v>52.41</v>
       </c>
       <c r="AA4" t="n">
         <v>21.57</v>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>18.916</v>
+        <v>19.164</v>
       </c>
       <c r="AH4" t="n">
-        <v>53.5</v>
+        <v>54.3</v>
       </c>
       <c r="AI4" t="n">
         <v>100</v>
@@ -1336,25 +1336,25 @@
         <v>45.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>51.2</v>
+        <v>47.9</v>
       </c>
       <c r="AL4" t="n">
-        <v>10.32</v>
+        <v>8.44</v>
       </c>
       <c r="AM4" t="n">
-        <v>36.4</v>
+        <v>38.47</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.98</v>
+        <v>21.84</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="AP4" t="n">
-        <v>16.9072</v>
+        <v>17.0039</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.671</v>
+        <v>14.7015</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
@@ -1367,7 +1367,7 @@
         <v>50.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>51.2</v>
+        <v>47.9</v>
       </c>
       <c r="AW4" t="n">
         <v>755</v>
@@ -1376,13 +1376,13 @@
         <v>17.092</v>
       </c>
       <c r="AY4" t="n">
-        <v>18.916</v>
+        <v>19.164</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.88</v>
+        <v>12.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>28.93</v>
+        <v>30.35</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60.2</v>
+        <v>60.9</v>
       </c>
       <c r="F5" t="n">
-        <v>52.3</v>
+        <v>53.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 60.2; priority 52.3; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 60.9; priority 53.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 10.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.9%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.3%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>-3.6</v>
+        <v>-2.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>-22.9</v>
+        <v>-21.05</v>
       </c>
       <c r="AA5" t="n">
         <v>24.09</v>
@@ -1518,10 +1518,10 @@
         <v>-33.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.85</v>
+        <v>22.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.99</v>
+        <v>19.33</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1530,42 +1530,42 @@
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>367.34</v>
+        <v>373.94</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-12.57</v>
+        <v>-10.77</v>
       </c>
       <c r="AM5" t="n">
-        <v>-22.5</v>
+        <v>-22.39</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.95</v>
+        <v>5.26</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="AP5" t="n">
-        <v>412.342</v>
+        <v>412.4194</v>
       </c>
       <c r="AQ5" t="n">
-        <v>448.8813</v>
+        <v>448.2271</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
         <v>35</v>
       </c>
       <c r="AT5" t="n">
-        <v>25.7</v>
+        <v>28.3</v>
       </c>
       <c r="AU5" t="n">
         <v>44</v>
       </c>
       <c r="AV5" t="n">
-        <v>58.9</v>
+        <v>61.3</v>
       </c>
       <c r="AW5" t="n">
         <v>751</v>
@@ -1577,10 +1577,10 @@
         <v>460.52</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-10.91</v>
+        <v>-9.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>-18.17</v>
+        <v>-16.57</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2728761229312</v>
+        <v>2777788973056</v>
       </c>
       <c r="BE5" t="n">
         <v>39.34</v>
@@ -1608,22 +1608,22 @@
         <v>30.27</v>
       </c>
       <c r="BI5" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="BJ5" t="n">
         <v>100</v>
       </c>
       <c r="BK5" t="n">
-        <v>25.7</v>
+        <v>28.3</v>
       </c>
       <c r="BL5" t="n">
-        <v>75.7</v>
+        <v>74.7</v>
       </c>
       <c r="BM5" t="n">
         <v>44</v>
       </c>
       <c r="BN5" t="n">
-        <v>58.9</v>
+        <v>61.3</v>
       </c>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
@@ -1640,24 +1640,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>60.2</v>
+        <v>64.8</v>
       </c>
       <c r="F6" t="n">
-        <v>39.4</v>
+        <v>40.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,12 +1667,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 60.2; priority 39.4; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 64.8; priority 40.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1686,22 +1682,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 11.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 60.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1716,153 +1712,131 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>525.2332</v>
+        <v>362.53</v>
       </c>
       <c r="T6" t="n">
-        <v>687.9124</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+        <v>668.91</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-4.93</v>
+        <v>58.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>-18.69</v>
+        <v>139.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.53</v>
+        <v>35.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>15.56</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG6" t="n">
-        <v>563.85</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+        <v>622.05</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>51.3</v>
+      </c>
       <c r="AL6" t="n">
-        <v>-6.72</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>-13.03</v>
+        <v>79.69</v>
       </c>
       <c r="AN6" t="n">
-        <v>25.55</v>
+        <v>63.06</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.7</v>
+        <v>1.77</v>
       </c>
       <c r="AP6" t="n">
-        <v>620.0869</v>
+        <v>556.0626</v>
       </c>
       <c r="AQ6" t="n">
-        <v>652.8457</v>
+        <v>414.3855</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT6" t="n">
-        <v>30.6</v>
+        <v>100</v>
       </c>
       <c r="AU6" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>61.6</v>
+        <v>51.3</v>
       </c>
       <c r="AW6" t="n">
         <v>751</v>
       </c>
       <c r="AX6" t="n">
-        <v>563.85</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>634.7017</v>
+        <v>668.91</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-9.07</v>
+        <v>11.87</v>
       </c>
       <c r="BA6" t="n">
-        <v>-13.63</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>1431289856000</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>61.6</v>
-      </c>
+        <v>50.11</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1872,12 +1846,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1886,10 +1860,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42.3</v>
+        <v>59.4</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>38.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1903,12 +1877,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 42.3; priority 36.0; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 59.4; priority 38.5; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1918,22 +1892,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 42.3, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.3%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1943,23 +1917,23 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>343.25</v>
+        <v>525.2332</v>
       </c>
       <c r="T7" t="n">
-        <v>445.27</v>
+        <v>687.9124</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1970,22 +1944,22 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>10.08</v>
+        <v>-6.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>25.77</v>
+        <v>-17.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>57.86</v>
+        <v>36.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>-53.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>375.05</v>
+        <v>20.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>162.02</v>
+        <v>15.51</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1994,103 +1968,105 @@
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>405.05</v>
+        <v>562.2</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>-2.93</v>
+        <v>-7.35</v>
       </c>
       <c r="AM7" t="n">
-        <v>-13.31</v>
+        <v>-15.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.55</v>
+        <v>26.96</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.29</v>
+        <v>0.74</v>
       </c>
       <c r="AP7" t="n">
-        <v>403.676</v>
+        <v>618.7454</v>
       </c>
       <c r="AQ7" t="n">
-        <v>417.3186</v>
+        <v>651.9257</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AT7" t="n">
-        <v>62.6</v>
+        <v>26.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>78.2</v>
+        <v>61.5</v>
       </c>
       <c r="AW7" t="n">
         <v>751</v>
       </c>
       <c r="AX7" t="n">
-        <v>381.59</v>
+        <v>562.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>442.1</v>
+        <v>634.7017</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.34</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>-2.94</v>
+        <v>-13.76</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1521255841792</v>
+        <v>1427101581312</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.95</v>
+        <v>32.84</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>32.93</v>
       </c>
       <c r="BG7" t="n">
-        <v>15.8</v>
+        <v>33.1</v>
       </c>
       <c r="BH7" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="BI7" t="inlineStr"/>
+        <v>35.61</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>37</v>
+      </c>
       <c r="BJ7" t="n">
-        <v>64.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="BK7" t="n">
-        <v>62.6</v>
+        <v>26.9</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>82.3</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="BN7" t="n">
-        <v>78.2</v>
+        <v>61.5</v>
       </c>
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
@@ -2112,10 +2088,10 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>39.5</v>
+        <v>35.2</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>31.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2129,12 +2105,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 39.5; priority 35.0; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 35.2; priority 31.8; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2149,7 +2125,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 39.5, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.4%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 35.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.1%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2174,7 +2150,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -2200,13 +2176,13 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>-15.71</v>
+        <v>-16.31</v>
       </c>
       <c r="AA8" t="n">
-        <v>34.04</v>
+        <v>34.06</v>
       </c>
       <c r="AB8" t="n">
         <v>-48.6</v>
@@ -2224,65 +2200,65 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>25.315</v>
+        <v>24.785</v>
       </c>
       <c r="AH8" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>44</v>
+        <v>41.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>78.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.54</v>
+        <v>-2.65</v>
       </c>
       <c r="AM8" t="n">
-        <v>-15.22</v>
+        <v>-15.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>-3.11</v>
+        <v>-3.6</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="AP8" t="n">
-        <v>24.7195</v>
+        <v>24.8111</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.8206</v>
+        <v>26.7978</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AT8" t="n">
-        <v>44</v>
+        <v>41.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>78.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AW8" t="n">
         <v>756</v>
       </c>
       <c r="AX8" t="n">
-        <v>25.09</v>
+        <v>24.785</v>
       </c>
       <c r="AY8" t="n">
         <v>30.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.41</v>
+        <v>-0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>-5.61</v>
+        <v>-7.51</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2308,20 +2284,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E9" t="n">
-        <v>59.9</v>
+        <v>35.1</v>
       </c>
       <c r="F9" t="n">
-        <v>12.5</v>
+        <v>26.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2335,12 +2315,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 59.9; priority 12.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 35.1; priority 26.8; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2350,22 +2330,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 21.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 5.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 59.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.1%.</t>
+          <t>TSLA: scenario base High Risk, score 35.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2375,136 +2355,156 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>362.53</v>
+        <v>343.25</v>
       </c>
       <c r="T9" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>73.86</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>155.53</v>
+        <v>18.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>35.46</v>
+        <v>57.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>152.65</v>
+      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>14.3</v>
-      </c>
+        <v>381.61</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>18.46</v>
+        <v>-8.67</v>
       </c>
       <c r="AM9" t="n">
-        <v>97.79000000000001</v>
+        <v>-21.05</v>
       </c>
       <c r="AN9" t="n">
-        <v>66.81999999999999</v>
+        <v>16.67</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.88</v>
+        <v>0.29</v>
       </c>
       <c r="AP9" t="n">
-        <v>552.3592</v>
+        <v>404.3292</v>
       </c>
       <c r="AQ9" t="n">
-        <v>412.7201</v>
+        <v>417.534</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT9" t="n">
-        <v>100</v>
+        <v>42.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>14.3</v>
+        <v>66.8</v>
       </c>
       <c r="AW9" t="n">
         <v>751</v>
       </c>
       <c r="AX9" t="n">
-        <v>569.6900000000001</v>
+        <v>381.59</v>
       </c>
       <c r="AY9" t="n">
-        <v>668.91</v>
+        <v>442.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21.1</v>
+        <v>-5.62</v>
       </c>
       <c r="BA9" t="n">
-        <v>62.07</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+        <v>-8.6</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>1433221726208</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
+      <c r="BJ9" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>66.8</v>
+      </c>
       <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>60.9</v>
       </c>
       <c r="F10" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 60.0; priority 9.8; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 60.9; priority 12.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 21.5% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 20.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.5%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 60.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.7%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>42.18</v>
+        <v>47.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>141.69</v>
+        <v>140.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.3</v>
+        <v>38.29</v>
       </c>
       <c r="AB10" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>64.03</v>
+        <v>60.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>39.51</v>
+        <v>37.25</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1657.8</v>
+        <v>1655.8</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>23.24</v>
+        <v>17.52</v>
       </c>
       <c r="AM10" t="n">
-        <v>90.34999999999999</v>
+        <v>86.14</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.23</v>
+        <v>37.95</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="AP10" t="n">
-        <v>1364.2859</v>
+        <v>1372.058</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1091.2953</v>
+        <v>1096.2908</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2671,7 +2671,7 @@
         <v>18.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>12.7</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
         <v>764</v>
@@ -2683,10 +2683,10 @@
         <v>1676</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21.51</v>
+        <v>20.68</v>
       </c>
       <c r="BA10" t="n">
-        <v>51.91</v>
+        <v>51.04</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>638174560256</v>
+        <v>601559924736</v>
       </c>
       <c r="BE10" t="n">
         <v>29.71</v>
@@ -2723,13 +2723,13 @@
         <v>100</v>
       </c>
       <c r="BL10" t="n">
-        <v>7.8</v>
+        <v>11.1</v>
       </c>
       <c r="BM10" t="n">
         <v>18.2</v>
       </c>
       <c r="BN10" t="n">
-        <v>12.7</v>
+        <v>16</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
@@ -2756,10 +2756,10 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>78.8</v>
+        <v>79.5</v>
       </c>
       <c r="F11" t="n">
-        <v>78.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 78.8; priority 78.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 79.5; priority 79.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.4%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 79.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.6%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 165.46 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2825,7 +2825,7 @@
         <v>140.98</v>
       </c>
       <c r="T11" t="n">
-        <v>165.46</v>
+        <v>166.04</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>14.67</v>
+        <v>16.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>28.49</v>
+        <v>30.1</v>
       </c>
       <c r="AA11" t="n">
         <v>12.93</v>
@@ -2868,50 +2868,50 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>165.44</v>
+        <v>166.04</v>
       </c>
       <c r="AH11" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>87</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AK11" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.45</v>
+        <v>2.73</v>
       </c>
       <c r="AM11" t="n">
-        <v>15.55</v>
+        <v>15.74</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.44</v>
+        <v>18.66</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AP11" t="n">
-        <v>158.4044</v>
+        <v>158.754</v>
       </c>
       <c r="AQ11" t="n">
-        <v>147.8411</v>
+        <v>147.9919</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
         <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>87</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AW11" t="n">
         <v>758</v>
@@ -2920,13 +2920,13 @@
         <v>159.24</v>
       </c>
       <c r="AY11" t="n">
-        <v>165.46</v>
+        <v>166.04</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.44</v>
+        <v>4.59</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2952,20 +2952,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="F12" t="n">
-        <v>78.2</v>
+        <v>78.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 77.6; priority 78.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.0; priority 78.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2999,17 +2999,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 78.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 124.82 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3028,15 +3028,15 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>107.5</v>
+        <v>56.4209</v>
       </c>
       <c r="T12" t="n">
-        <v>124.82</v>
+        <v>63.63</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>13.63</v>
+        <v>13.47</v>
       </c>
       <c r="Z12" t="n">
-        <v>25.6</v>
+        <v>22.08</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.19</v>
+        <v>12.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
@@ -3070,69 +3070,69 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>124.82</v>
+        <v>63.63</v>
       </c>
       <c r="AH12" t="n">
-        <v>73</v>
+        <v>72.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AK12" t="n">
         <v>82.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="AM12" t="n">
-        <v>13.12</v>
+        <v>12.44</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.1</v>
+        <v>15.28</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AP12" t="n">
-        <v>120.086</v>
+        <v>61.4452</v>
       </c>
       <c r="AQ12" t="n">
-        <v>112.9285</v>
+        <v>58.3367</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>83.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AV12" t="n">
         <v>82.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="AX12" t="n">
-        <v>120.73</v>
+        <v>61.4745</v>
       </c>
       <c r="AY12" t="n">
-        <v>124.82</v>
+        <v>63.63</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.94</v>
+        <v>3.56</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.53</v>
+        <v>9.07</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -3153,39 +3153,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>77.2</v>
+        <v>78.2</v>
       </c>
       <c r="F13" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 77.2; priority 77.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.2; priority 78.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3205,17 +3205,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
+          <t>SWDA.MI: scenario base Buy Watchlist, score 78.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3234,15 +3234,15 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>597.92</v>
+        <v>107.5</v>
       </c>
       <c r="T13" t="n">
-        <v>703.9400000000001</v>
+        <v>125.04</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3256,89 +3256,89 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>14.71</v>
+        <v>14.99</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.63</v>
+        <v>25.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>14.16</v>
+        <v>13.19</v>
       </c>
       <c r="AB13" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>703.54</v>
+        <v>125.04</v>
       </c>
       <c r="AH13" t="n">
-        <v>71.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AJ13" t="n">
-        <v>64.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK13" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>13.13</v>
+        <v>13.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>19.16</v>
+        <v>18.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AP13" t="n">
-        <v>676.1572</v>
+        <v>120.327</v>
       </c>
       <c r="AQ13" t="n">
-        <v>634.1368</v>
+        <v>113.0294</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>85.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>64.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AX13" t="n">
-        <v>681.24</v>
+        <v>120.73</v>
       </c>
       <c r="AY13" t="n">
-        <v>703.9400000000001</v>
+        <v>125.04</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.94</v>
+        <v>10.63</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3359,39 +3359,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>76.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>77.5</v>
+        <v>78.3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.63. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 76.7; priority 77.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.6; priority 78.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3440,15 +3440,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>56.4209</v>
+        <v>597.92</v>
       </c>
       <c r="T14" t="n">
-        <v>63.63</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>10.75</v>
+        <v>15.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.57</v>
+        <v>27.73</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.88</v>
+        <v>14.16</v>
       </c>
       <c r="AB14" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3482,69 +3482,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>63.22</v>
+        <v>703.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>71.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>77.2</v>
+        <v>86.7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK14" t="n">
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.56</v>
+        <v>1.26</v>
       </c>
       <c r="AM14" t="n">
-        <v>11.25</v>
+        <v>13.16</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.87</v>
+        <v>19.08</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AP14" t="n">
-        <v>61.3819</v>
+        <v>677.7148</v>
       </c>
       <c r="AQ14" t="n">
-        <v>58.2829</v>
+        <v>634.7016</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>77.2</v>
+        <v>86.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV14" t="n">
         <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AX14" t="n">
-        <v>61.4745</v>
+        <v>681.24</v>
       </c>
       <c r="AY14" t="n">
-        <v>63.63</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.99</v>
+        <v>3.82</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.470000000000001</v>
+        <v>10.86</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3565,44 +3565,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>3. Interessanti ma da attendere</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>75.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>76.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟠 Attendi pullback</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 75.89. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Non inseguire il prezzo: imposta alert su pullback o tenuta supporto. Supporto 60D: 54.81.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 75.1; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.1; priority 67.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3612,22 +3612,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
+          <t>XDEV.MI: scenario base Accumulate Carefully, score 80.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.1%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.89 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3646,15 +3646,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>66.58</v>
+        <v>54.81</v>
       </c>
       <c r="T15" t="n">
-        <v>75.89</v>
+        <v>73.47</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3664,93 +3664,93 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>11.59</v>
+        <v>33.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>22</v>
+        <v>68.09</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.88</v>
+        <v>13.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>-20.6</v>
+        <v>-17.8</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>75.76000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="AH15" t="n">
-        <v>66.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="n">
-        <v>68.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>82.8</v>
+        <v>54.4</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.74</v>
+        <v>7.33</v>
       </c>
       <c r="AM15" t="n">
-        <v>12.05</v>
+        <v>40.88</v>
       </c>
       <c r="AN15" t="n">
-        <v>15.86</v>
+        <v>28.13</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.23</v>
+        <v>2.04</v>
       </c>
       <c r="AP15" t="n">
-        <v>73.0796</v>
+        <v>66.1416</v>
       </c>
       <c r="AQ15" t="n">
-        <v>69.1437</v>
+        <v>55.9789</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AU15" t="n">
-        <v>68.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>82.8</v>
+        <v>54.4</v>
       </c>
       <c r="AW15" t="n">
         <v>755</v>
       </c>
       <c r="AX15" t="n">
-        <v>73.8</v>
+        <v>68.89</v>
       </c>
       <c r="AY15" t="n">
-        <v>75.89</v>
+        <v>73.47</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.67</v>
+        <v>11.08</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.57</v>
+        <v>31.25</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3776,24 +3776,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>76.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>75.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3802,42 +3798,42 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 75.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 76.4; priority 75.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 75.6; priority 77.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 76.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 2.6%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3856,149 +3852,127 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>246.403</v>
+        <v>66.58</v>
       </c>
       <c r="T16" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+        <v>75.94</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>19.88</v>
+        <v>12.82</v>
       </c>
       <c r="Z16" t="n">
-        <v>51.69</v>
+        <v>22.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>26.02</v>
+        <v>12.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>-33.36</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>30.94</v>
-      </c>
+        <v>-20.6</v>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Quality globale</t>
+        </is>
+      </c>
       <c r="AG16" t="n">
-        <v>297.01</v>
-      </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+        <v>75.94</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>81</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL16" t="n">
-        <v>-1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AM16" t="n">
-        <v>9.460000000000001</v>
+        <v>12.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>17.41</v>
+        <v>15.95</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.67</v>
+        <v>1.24</v>
       </c>
       <c r="AP16" t="n">
-        <v>289.365</v>
+        <v>73.2024</v>
       </c>
       <c r="AQ16" t="n">
-        <v>268.0891</v>
+        <v>69.2025</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>96.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="AU16" t="n">
-        <v>42.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AX16" t="n">
-        <v>290.55</v>
+        <v>73.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>315.2</v>
+        <v>75.94</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.64</v>
+        <v>3.74</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
-        </is>
-      </c>
-      <c r="BD16" t="n">
-        <v>4362291642368</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>36</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>82.8</v>
-      </c>
+        <v>9.74</v>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
       <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4008,20 +3982,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>78.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>75.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4030,12 +4008,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 50.16. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 78.9; priority 75.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 75.1; priority 74.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4045,27 +4023,27 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.9, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.8%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.5%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4075,7 +4053,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4084,127 +4062,149 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>39.31</v>
+        <v>246.403</v>
       </c>
       <c r="T17" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>23.05</v>
+        <v>17.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>50.16</v>
+        <v>47</v>
       </c>
       <c r="AA17" t="n">
-        <v>16.21</v>
+        <v>26.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>-19.17</v>
-      </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>30.65</v>
+      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>Mercati emergenti</t>
-        </is>
-      </c>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>72</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>67.40000000000001</v>
-      </c>
+        <v>294.3</v>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>8.390000000000001</v>
+        <v>-3.51</v>
       </c>
       <c r="AM17" t="n">
-        <v>32.96</v>
+        <v>8.32</v>
       </c>
       <c r="AN17" t="n">
-        <v>21.55</v>
+        <v>17.35</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP17" t="n">
-        <v>46.1851</v>
+        <v>290.0462</v>
       </c>
       <c r="AQ17" t="n">
-        <v>40.8969</v>
+        <v>268.365</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>751</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>4322488745984</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>100</v>
       </c>
-      <c r="AU17" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>755</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>45.945</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>21.77</v>
-      </c>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="inlineStr"/>
-      <c r="BM17" t="inlineStr"/>
-      <c r="BN17" t="inlineStr"/>
+      <c r="BK17" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>43</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4231,7 +4231,7 @@
         <v>78.59999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>74.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 4.9% sotto MA50: attendere recupero.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 6.0% sotto MA50: attendere recupero.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 78.6; priority 74.5; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 78.6; priority 74.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.0% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.0%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4312,22 +4312,22 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>16.24</v>
+        <v>14.66</v>
       </c>
       <c r="Z18" t="n">
-        <v>102.33</v>
+        <v>108.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>29.92</v>
+        <v>29.86</v>
       </c>
       <c r="AB18" t="n">
         <v>-29.81</v>
       </c>
       <c r="AC18" t="n">
-        <v>26.69</v>
+        <v>26.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>24.12</v>
+        <v>23.78</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -4336,29 +4336,29 @@
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>349.68</v>
+        <v>346.13</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>-10.03</v>
+        <v>-10.66</v>
       </c>
       <c r="AM18" t="n">
-        <v>18</v>
+        <v>14.59</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.67</v>
+        <v>43.78</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AP18" t="n">
-        <v>367.821</v>
+        <v>368.4026</v>
       </c>
       <c r="AQ18" t="n">
-        <v>311.3296</v>
+        <v>311.9021</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
@@ -4371,22 +4371,22 @@
         <v>40.3</v>
       </c>
       <c r="AV18" t="n">
-        <v>72.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="AW18" t="n">
         <v>751</v>
       </c>
       <c r="AX18" t="n">
-        <v>349.68</v>
+        <v>346.13</v>
       </c>
       <c r="AY18" t="n">
         <v>389.8971</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-4.93</v>
+        <v>-6.05</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.32</v>
+        <v>10.97</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>4266995482624</v>
+        <v>4223676710912</v>
       </c>
       <c r="BE18" t="n">
         <v>37.92</v>
@@ -4414,7 +4414,7 @@
         <v>20.03</v>
       </c>
       <c r="BI18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BJ18" t="n">
         <v>100</v>
@@ -4423,13 +4423,13 @@
         <v>100</v>
       </c>
       <c r="BL18" t="n">
-        <v>62.7</v>
+        <v>63.6</v>
       </c>
       <c r="BM18" t="n">
         <v>40.3</v>
       </c>
       <c r="BN18" t="n">
-        <v>72.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
@@ -4456,10 +4456,10 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 69.0; priority 71.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 69.4; priority 71.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.2%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.3%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AA19" t="n">
         <v>9.56</v>
@@ -4568,13 +4568,13 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>63.52</v>
+        <v>63.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
       <c r="AI19" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
       <c r="AJ19" t="n">
         <v>78.2</v>
@@ -4583,29 +4583,29 @@
         <v>82.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.03</v>
+        <v>-1.38</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.87</v>
+        <v>6.76</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="AP19" t="n">
-        <v>63.3784</v>
+        <v>63.3914</v>
       </c>
       <c r="AQ19" t="n">
-        <v>63.1369</v>
+        <v>63.1403</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
       <c r="AU19" t="n">
         <v>78.2</v>
@@ -4620,13 +4620,13 @@
         <v>63.44</v>
       </c>
       <c r="AY19" t="n">
-        <v>64.68000000000001</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>80.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="F20" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 72.51. Trigger: prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 50.73. Trigger: prezzo 9.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 80.4; priority 70.5; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 78.3; priority 70.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo 10.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 9.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 80.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.1%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 72.51 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4728,20 +4728,20 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>54.81</v>
+        <v>39.31</v>
       </c>
       <c r="T20" t="n">
-        <v>72.51000000000001</v>
+        <v>50.73</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4750,61 +4750,61 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>29.69</v>
+        <v>27.69</v>
       </c>
       <c r="Z20" t="n">
-        <v>66.14</v>
+        <v>53.38</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.76</v>
+        <v>16.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>-17.8</v>
+        <v>-19.17</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>72.51000000000001</v>
+        <v>50.73</v>
       </c>
       <c r="AH20" t="n">
-        <v>80.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="AI20" t="n">
         <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>69.2</v>
+        <v>65.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>58.2</v>
+        <v>61</v>
       </c>
       <c r="AL20" t="n">
-        <v>8.470000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AM20" t="n">
-        <v>39.09</v>
+        <v>35.12</v>
       </c>
       <c r="AN20" t="n">
-        <v>27.29</v>
+        <v>22.65</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>65.83459999999999</v>
+        <v>46.3517</v>
       </c>
       <c r="AQ20" t="n">
-        <v>55.8445</v>
+        <v>40.9763</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
@@ -4814,25 +4814,25 @@
         <v>100</v>
       </c>
       <c r="AU20" t="n">
-        <v>69.2</v>
+        <v>65.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>58.2</v>
+        <v>61</v>
       </c>
       <c r="AW20" t="n">
         <v>755</v>
       </c>
       <c r="AX20" t="n">
-        <v>68.89</v>
+        <v>45.945</v>
       </c>
       <c r="AY20" t="n">
-        <v>72.51000000000001</v>
+        <v>50.73</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10.14</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BA20" t="n">
-        <v>29.84</v>
+        <v>23.8</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>75.7</v>
+        <v>72.7</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>54.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 75.7; priority 59.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 72.7; priority 54.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 4.7% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 75.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -0.5%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 72.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.7%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>20.96</v>
+        <v>14.02</v>
       </c>
       <c r="Z21" t="n">
-        <v>43.61</v>
+        <v>39.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.97</v>
+        <v>46.98</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>31.95</v>
+        <v>30.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.39</v>
+        <v>15.72</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,57 +4980,57 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>208.65</v>
+        <v>200.04</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-6.52</v>
+        <v>-8.76</v>
       </c>
       <c r="AM21" t="n">
-        <v>22.21</v>
+        <v>15.01</v>
       </c>
       <c r="AN21" t="n">
-        <v>71.06999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="AO21" t="n">
         <v>1.51</v>
       </c>
       <c r="AP21" t="n">
-        <v>209.62</v>
+        <v>209.8526</v>
       </c>
       <c r="AQ21" t="n">
-        <v>189.8757</v>
+        <v>190.0187</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
         <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="AU21" t="n">
         <v>14.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>79.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="AW21" t="n">
         <v>751</v>
       </c>
       <c r="AX21" t="n">
-        <v>200.42</v>
+        <v>200.04</v>
       </c>
       <c r="AY21" t="n">
         <v>224.0988</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.46</v>
+        <v>-4.68</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.890000000000001</v>
+        <v>5.27</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>5053711646720</v>
+        <v>4845168754688</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5058,22 +5058,22 @@
         <v>6.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BJ21" t="n">
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="BL21" t="n">
-        <v>67.7</v>
+        <v>70.2</v>
       </c>
       <c r="BM21" t="n">
         <v>14.1</v>
       </c>
       <c r="BN21" t="n">
-        <v>79.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54.8</v>
+        <v>55.8</v>
       </c>
       <c r="F22" t="n">
-        <v>56.3</v>
+        <v>57.6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 54.8; priority 56.3; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 55.8; priority 57.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 7.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 5.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 54.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.9%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5184,14 +5184,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-9.029999999999999</v>
+        <v>-7.69</v>
       </c>
       <c r="Z22" t="n">
-        <v>23.18</v>
+        <v>24.36</v>
       </c>
       <c r="AA22" t="n">
         <v>18.12</v>
@@ -5212,50 +5212,50 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>348.23</v>
+        <v>352.3</v>
       </c>
       <c r="AH22" t="n">
         <v>68.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>42.6</v>
+        <v>45.5</v>
       </c>
       <c r="AJ22" t="n">
         <v>60.7</v>
       </c>
       <c r="AK22" t="n">
-        <v>64.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AL22" t="n">
-        <v>-6.97</v>
+        <v>-6</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.86</v>
+        <v>0.21</v>
       </c>
       <c r="AN22" t="n">
-        <v>27.39</v>
+        <v>27.41</v>
       </c>
       <c r="AO22" t="n">
         <v>1.51</v>
       </c>
       <c r="AP22" t="n">
-        <v>375.0458</v>
+        <v>374.2578</v>
       </c>
       <c r="AQ22" t="n">
-        <v>365.0718</v>
+        <v>365.4025</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>42.6</v>
+        <v>45.5</v>
       </c>
       <c r="AU22" t="n">
         <v>60.7</v>
       </c>
       <c r="AV22" t="n">
-        <v>64.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AW22" t="n">
         <v>755</v>
@@ -5264,13 +5264,13 @@
         <v>340.82</v>
       </c>
       <c r="AY22" t="n">
-        <v>377.9</v>
+        <v>377.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-7.15</v>
+        <v>-5.87</v>
       </c>
       <c r="BA22" t="n">
-        <v>-4.61</v>
+        <v>-3.59</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>63.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>61.7</v>
+        <v>62.4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 63.9; priority 61.7; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 64.6; priority 62.4; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 8.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 63.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.9%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 64.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.8%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 199.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 200.95 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>199.34</v>
+        <v>200.95</v>
       </c>
       <c r="T2" t="n">
         <v>274.99</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>11.41</v>
+        <v>13.04</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.65</v>
+        <v>12.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.18</v>
+        <v>31.16</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.69</v>
+        <v>23.71</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,17 +888,17 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>234.11</v>
+        <v>234.27</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-12.8</v>
+        <v>-12.03</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AN2" t="n">
         <v>22.67</v>
@@ -907,26 +907,26 @@
         <v>0.73</v>
       </c>
       <c r="AP2" t="n">
-        <v>256.9976</v>
+        <v>256.8852</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.8298</v>
+        <v>232.8395</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>70.8</v>
+        <v>73.2</v>
       </c>
       <c r="AU2" t="n">
         <v>37.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX2" t="n">
         <v>232.79</v>
@@ -935,10 +935,10 @@
         <v>274</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-8.91</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2518346891264</v>
+        <v>2520068128768</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>70.8</v>
+        <v>73.2</v>
       </c>
       <c r="BL2" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
       <c r="BM2" t="n">
         <v>37.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -1009,7 +1009,7 @@
         <v>64.8</v>
       </c>
       <c r="F3" t="n">
-        <v>58.1</v>
+        <v>58.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 64.8; priority 58.1; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 64.8; priority 58.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 4.3%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>19.01</v>
+        <v>17.81</v>
       </c>
       <c r="Z3" t="n">
-        <v>71.66</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.45</v>
+        <v>23.52</v>
       </c>
       <c r="AB3" t="n">
         <v>-43.36</v>
@@ -1118,37 +1118,37 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>10.872</v>
+        <v>10.53</v>
       </c>
       <c r="AH3" t="n">
-        <v>33.6</v>
+        <v>32.7</v>
       </c>
       <c r="AI3" t="n">
         <v>100</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>81.5</v>
+        <v>82.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2.05</v>
+        <v>-6.17</v>
       </c>
       <c r="AM3" t="n">
-        <v>34.35</v>
+        <v>32.64</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.06</v>
+        <v>4.83</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.4235</v>
+        <v>10.4492</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.9054</v>
+        <v>8.923400000000001</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
@@ -1158,10 +1158,10 @@
         <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>81.5</v>
+        <v>82.8</v>
       </c>
       <c r="AW3" t="n">
         <v>755</v>
@@ -1173,10 +1173,10 @@
         <v>11.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.3</v>
+        <v>0.77</v>
       </c>
       <c r="BA3" t="n">
-        <v>22.08</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1202,20 +1202,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>67.59999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="F4" t="n">
-        <v>54.7</v>
+        <v>52.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1229,12 +1233,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 67.6; priority 54.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Medium-high risk</t>
+          <t>score 60.4; priority 52.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1244,22 +1248,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo 12.7% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 11.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Hold / Monitor, score 67.6, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.7%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 60.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.3%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 358.18 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1274,131 +1278,153 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>12.936</v>
+        <v>358.1842</v>
       </c>
       <c r="T4" t="n">
-        <v>19.164</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>460.52</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>42.76</v>
+        <v>-1.74</v>
       </c>
       <c r="Z4" t="n">
-        <v>52.41</v>
+        <v>-24.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.57</v>
+        <v>24.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>-29.37</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+        <v>-33.91</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>18.89</v>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Robotica e automazione</t>
-        </is>
-      </c>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>19.164</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>47.9</v>
-      </c>
+        <v>365.46</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>8.44</v>
+        <v>-12.69</v>
       </c>
       <c r="AM4" t="n">
-        <v>38.47</v>
+        <v>-24.46</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.84</v>
+        <v>4.44</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.01</v>
+        <v>0.18</v>
       </c>
       <c r="AP4" t="n">
-        <v>17.0039</v>
+        <v>412.0578</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.7015</v>
+        <v>447.595</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT4" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>752</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>365.46</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>460.52</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-11.31</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-18.35</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>2714795769856</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>97</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>100</v>
       </c>
-      <c r="AU4" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>755</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>17.092</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>19.164</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>30.35</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+      <c r="BK4" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>58.3</v>
+      </c>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1408,24 +1434,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>60.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>53.6</v>
+        <v>44.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1439,37 +1461,37 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 60.9; priority 53.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 65.6; priority 44.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 9.3% sotto MA50: attendere recupero</t>
+          <t>prezzo 10.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.3%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 65.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.6%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 356.00 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1484,153 +1506,131 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>355.9989</v>
+        <v>362.53</v>
       </c>
       <c r="T5" t="n">
-        <v>460.52</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>668.91</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>-2.15</v>
+        <v>56.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>-21.05</v>
+        <v>137.04</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.09</v>
+        <v>35.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>-33.91</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>19.33</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG5" t="n">
-        <v>373.94</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+        <v>618.92</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>56.3</v>
+      </c>
       <c r="AL5" t="n">
-        <v>-10.77</v>
+        <v>7.39</v>
       </c>
       <c r="AM5" t="n">
-        <v>-22.39</v>
+        <v>74.28</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.26</v>
+        <v>62.68</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.22</v>
+        <v>1.76</v>
       </c>
       <c r="AP5" t="n">
-        <v>412.4194</v>
+        <v>559.5742</v>
       </c>
       <c r="AQ5" t="n">
-        <v>448.2271</v>
+        <v>416.0183</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT5" t="n">
-        <v>28.3</v>
+        <v>100</v>
       </c>
       <c r="AU5" t="n">
-        <v>44</v>
+        <v>28.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>61.3</v>
+        <v>56.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX5" t="n">
-        <v>367.34</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>460.52</v>
+        <v>668.91</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-9.33</v>
+        <v>10.61</v>
       </c>
       <c r="BA5" t="n">
-        <v>-16.57</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>Software - Infrastructure</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>2777788973056</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>99</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>61.3</v>
-      </c>
+        <v>48.77</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1640,20 +1640,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>64.8</v>
+        <v>59.5</v>
       </c>
       <c r="F6" t="n">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1667,12 +1671,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 64.8; priority 40.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 59.5; priority 38.5; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1682,22 +1686,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 11.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 9.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.9%.</t>
+          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.7%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 535.88 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1712,131 +1716,153 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>362.53</v>
+        <v>535.8834000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>687.9124</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>58.95</v>
+        <v>-5.86</v>
       </c>
       <c r="Z6" t="n">
-        <v>139.75</v>
+        <v>-19.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>35.7</v>
+        <v>36.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+        <v>-34.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15.39</v>
+      </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>622.05</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>51.3</v>
-      </c>
+        <v>557.67</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>9.539999999999999</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>79.69</v>
+        <v>-15.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>63.06</v>
+        <v>26.57</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.77</v>
+        <v>0.73</v>
       </c>
       <c r="AP6" t="n">
-        <v>556.0626</v>
+        <v>617.2199000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>414.3855</v>
+        <v>650.9641</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>752</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>557.67</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>634.7017</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-9.65</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-14.33</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>1415602503680</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>37</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>100</v>
       </c>
-      <c r="AU6" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>751</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>569.6900000000001</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>50.11</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>60.8</v>
+      </c>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>USA / Social &amp; AI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1846,24 +1872,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>59.4</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>38.5</v>
+        <v>35.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1877,12 +1899,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 59.4; priority 38.5; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 40.0; priority 35.5; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1892,22 +1914,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.1%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 40.0, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 525.23 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1917,158 +1939,136 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>525.2332</v>
+        <v>20.205</v>
       </c>
       <c r="T7" t="n">
-        <v>687.9124</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+        <v>30.11</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>-6.84</v>
+        <v>5.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>-17.34</v>
+        <v>-15.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>36.47</v>
+        <v>34.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15.51</v>
-      </c>
+        <v>-48.6</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
       <c r="AG7" t="n">
-        <v>562.2</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+        <v>25.305</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>78.2</v>
+      </c>
       <c r="AL7" t="n">
-        <v>-7.35</v>
+        <v>-1.06</v>
       </c>
       <c r="AM7" t="n">
-        <v>-15.24</v>
+        <v>-13.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>26.96</v>
+        <v>-3.03</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.74</v>
+        <v>-0.09</v>
       </c>
       <c r="AP7" t="n">
-        <v>618.7454</v>
+        <v>24.8966</v>
       </c>
       <c r="AQ7" t="n">
-        <v>651.9257</v>
+        <v>26.778</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>26.9</v>
+        <v>46.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>28.9</v>
+        <v>20.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>61.5</v>
+        <v>78.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AX7" t="n">
-        <v>562.2</v>
+        <v>24.785</v>
       </c>
       <c r="AY7" t="n">
-        <v>634.7017</v>
+        <v>30.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-9.140000000000001</v>
+        <v>1.64</v>
       </c>
       <c r="BA7" t="n">
-        <v>-13.76</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>1427101581312</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>37</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>61.5</v>
-      </c>
+        <v>-5.5</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2078,20 +2078,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E8" t="n">
-        <v>35.2</v>
+        <v>63.9</v>
       </c>
       <c r="F8" t="n">
-        <v>31.8</v>
+        <v>34.6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2105,12 +2109,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 35.2; priority 31.8; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 63.9; priority 34.6; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2120,22 +2124,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 13.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 35.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -0.1%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 63.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.2%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2145,136 +2149,158 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>20.205</v>
+        <v>1109.5466</v>
       </c>
       <c r="T8" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>1676</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>3.25</v>
+        <v>33.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>-16.31</v>
+        <v>132.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>34.06</v>
+        <v>38.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>-48.6</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+        <v>-44.77</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>59.97</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>37.08</v>
+      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>24.785</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>75.09999999999999</v>
-      </c>
+        <v>1560.8</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>-2.65</v>
+        <v>9.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>-15.55</v>
+        <v>73.73</v>
       </c>
       <c r="AN8" t="n">
-        <v>-3.6</v>
+        <v>34.84</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.11</v>
+        <v>0.91</v>
       </c>
       <c r="AP8" t="n">
-        <v>24.8111</v>
+        <v>1378.1336</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.7978</v>
+        <v>1100.7298</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT8" t="n">
-        <v>41.1</v>
+        <v>100</v>
       </c>
       <c r="AU8" t="n">
-        <v>20.2</v>
+        <v>18.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>75.09999999999999</v>
+        <v>45.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="AX8" t="n">
-        <v>24.785</v>
+        <v>1376.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>30.11</v>
+        <v>1676</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.11</v>
+        <v>13.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>-7.51</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
+        <v>41.8</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment &amp; Materials</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>598862004224</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>69</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>45.7</v>
+      </c>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>Europe / Semiconductors</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2298,10 +2324,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
       <c r="F9" t="n">
-        <v>26.8</v>
+        <v>24.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2315,7 +2341,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 35.1; priority 26.8; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 33.3; priority 24.5; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2330,12 +2356,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 5.6% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 35.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.6%.</t>
+          <t>TSLA: scenario base High Risk, score 33.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2382,22 +2408,22 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>-1.96</v>
       </c>
       <c r="Z9" t="n">
-        <v>18.45</v>
+        <v>7.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>57.85</v>
+        <v>57.82</v>
       </c>
       <c r="AB9" t="n">
         <v>-53.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>350.1</v>
+        <v>338.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>152.65</v>
+        <v>150.21</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2406,57 +2432,57 @@
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>381.61</v>
+        <v>375.53</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>-8.67</v>
+        <v>-11.85</v>
       </c>
       <c r="AM9" t="n">
-        <v>-21.05</v>
+        <v>-21.96</v>
       </c>
       <c r="AN9" t="n">
-        <v>16.67</v>
+        <v>16.02</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="AP9" t="n">
-        <v>404.3292</v>
+        <v>404.7914</v>
       </c>
       <c r="AQ9" t="n">
-        <v>417.534</v>
+        <v>417.6574</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
         <v>35</v>
       </c>
       <c r="AT9" t="n">
-        <v>42.3</v>
+        <v>36</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>66.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX9" t="n">
-        <v>381.59</v>
+        <v>375.53</v>
       </c>
       <c r="AY9" t="n">
         <v>442.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-5.62</v>
+        <v>-7.23</v>
       </c>
       <c r="BA9" t="n">
-        <v>-8.6</v>
+        <v>-10.09</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -2469,7 +2495,7 @@
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1433221726208</v>
+        <v>1410386886656</v>
       </c>
       <c r="BE9" t="n">
         <v>3.95</v>
@@ -2488,7 +2514,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>42.3</v>
+        <v>36</v>
       </c>
       <c r="BL9" t="n">
         <v>0</v>
@@ -2497,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>66.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
@@ -2509,73 +2535,69 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. Rischio da controllare</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>60.9</v>
+        <v>80.7</v>
       </c>
       <c r="F10" t="n">
-        <v>12.5</v>
+        <v>81.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🟥 Riduci rischio / non aumentare</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Non aumentare esposizione: controlla peso in portafoglio, stop mentale e correlazione con posizioni simili.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 60.9; priority 12.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 80.7; priority 81.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 20.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 60.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 20.7%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2585,7 +2607,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2594,71 +2616,83 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>1109.5466</v>
+        <v>39.31</v>
       </c>
       <c r="T10" t="n">
-        <v>1676</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+        <v>50.73</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>47.09</v>
+        <v>20.73</v>
       </c>
       <c r="Z10" t="n">
-        <v>140.32</v>
+        <v>48.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.29</v>
+        <v>16.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>-44.77</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>37.25</v>
-      </c>
+        <v>-19.17</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Mercati emergenti</t>
+        </is>
+      </c>
       <c r="AG10" t="n">
-        <v>1655.8</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+        <v>48.45</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>81.8</v>
+      </c>
       <c r="AL10" t="n">
-        <v>17.52</v>
+        <v>2.23</v>
       </c>
       <c r="AM10" t="n">
-        <v>86.14</v>
+        <v>30.88</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.95</v>
+        <v>20.7</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.99</v>
+        <v>1.26</v>
       </c>
       <c r="AP10" t="n">
-        <v>1372.058</v>
+        <v>46.4756</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1096.2908</v>
+        <v>41.0446</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2668,75 +2702,41 @@
         <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>18.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>81.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="AX10" t="n">
-        <v>1376.4</v>
+        <v>45.945</v>
       </c>
       <c r="AY10" t="n">
-        <v>1676</v>
+        <v>50.73</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20.68</v>
+        <v>4.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>601559924736</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>52.24</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>65</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>16</v>
-      </c>
+        <v>18.04</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>Europe / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2756,10 +2756,10 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>79.5</v>
+        <v>78.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79.5</v>
+        <v>79.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 79.5; priority 79.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.8; priority 79.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 79.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.6%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>16.4</v>
+        <v>14.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>30.1</v>
+        <v>28.02</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.93</v>
+        <v>12.95</v>
       </c>
       <c r="AB11" t="n">
         <v>-21.07</v>
@@ -2868,50 +2868,50 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>166.04</v>
+        <v>163.92</v>
       </c>
       <c r="AH11" t="n">
-        <v>74.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>89.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="AJ11" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AK11" t="n">
-        <v>80.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.73</v>
+        <v>0.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>15.74</v>
+        <v>15.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.66</v>
+        <v>18.23</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AP11" t="n">
-        <v>158.754</v>
+        <v>159.0628</v>
       </c>
       <c r="AQ11" t="n">
-        <v>147.9919</v>
+        <v>148.1395</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
         <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>89.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="AU11" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>80.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AW11" t="n">
         <v>758</v>
@@ -2923,10 +2923,10 @@
         <v>166.04</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.59</v>
+        <v>3.05</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.2</v>
+        <v>10.65</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2952,20 +2952,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="F12" t="n">
-        <v>78.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 78.0; priority 78.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.5; priority 78.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2999,17 +2999,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 78.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.6%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3028,15 +3028,15 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>56.4209</v>
+        <v>107.5</v>
       </c>
       <c r="T12" t="n">
-        <v>63.63</v>
+        <v>125.04</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>13.47</v>
+        <v>13.53</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.08</v>
+        <v>25.72</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.88</v>
+        <v>13.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>-16.33</v>
+        <v>-21.63</v>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
@@ -3070,69 +3070,69 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>63.63</v>
+        <v>123.92</v>
       </c>
       <c r="AH12" t="n">
-        <v>72.3</v>
+        <v>72.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>81.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>71.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK12" t="n">
         <v>82.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.32</v>
+        <v>0.31</v>
       </c>
       <c r="AM12" t="n">
-        <v>12.44</v>
+        <v>12.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>15.28</v>
+        <v>17.93</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AP12" t="n">
-        <v>61.4452</v>
+        <v>120.5462</v>
       </c>
       <c r="AQ12" t="n">
-        <v>58.3367</v>
+        <v>113.1305</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>81.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>71.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>82.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="AX12" t="n">
-        <v>61.4745</v>
+        <v>120.73</v>
       </c>
       <c r="AY12" t="n">
-        <v>63.63</v>
+        <v>125.04</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.07</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -3158,20 +3158,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>78.2</v>
+        <v>77.2</v>
       </c>
       <c r="F13" t="n">
-        <v>78.7</v>
+        <v>78</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 78.2; priority 78.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.2; priority 78.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3205,17 +3205,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Buy Watchlist, score 78.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.9%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3234,15 +3234,15 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>107.5</v>
+        <v>56.4209</v>
       </c>
       <c r="T13" t="n">
-        <v>125.04</v>
+        <v>63.63</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3256,89 +3256,89 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>14.99</v>
+        <v>11.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>25.88</v>
+        <v>21.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.19</v>
+        <v>12.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>125.04</v>
+        <v>63.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>73.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AK13" t="n">
         <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>-0.09</v>
       </c>
       <c r="AM13" t="n">
-        <v>13.18</v>
+        <v>11.78</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.2</v>
+        <v>15.02</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AP13" t="n">
-        <v>120.327</v>
+        <v>61.5015</v>
       </c>
       <c r="AQ13" t="n">
-        <v>113.0294</v>
+        <v>58.3864</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>85.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="AU13" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AV13" t="n">
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="AX13" t="n">
-        <v>120.73</v>
+        <v>61.4745</v>
       </c>
       <c r="AY13" t="n">
-        <v>125.04</v>
+        <v>63.63</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.92</v>
+        <v>2.73</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.63</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3359,7 +3359,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3374,24 +3374,24 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="F14" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="F14" t="n">
-        <v>78.3</v>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 77.6; priority 78.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.9; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.8%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -3462,13 +3462,13 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>15.62</v>
+        <v>14.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>27.73</v>
+        <v>26.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="AB14" t="n">
         <v>-23.32</v>
@@ -3486,47 +3486,47 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>703.6</v>
+        <v>698.0599999999999</v>
       </c>
       <c r="AH14" t="n">
-        <v>71.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AI14" t="n">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="AK14" t="n">
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.26</v>
+        <v>0.22</v>
       </c>
       <c r="AM14" t="n">
-        <v>13.16</v>
+        <v>13.01</v>
       </c>
       <c r="AN14" t="n">
-        <v>19.08</v>
+        <v>18.9</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AP14" t="n">
-        <v>677.7148</v>
+        <v>679.1627999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>634.7016</v>
+        <v>635.2736</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="AV14" t="n">
         <v>82.8</v>
@@ -3541,10 +3541,10 @@
         <v>703.9400000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.82</v>
+        <v>2.78</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.86</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3565,44 +3565,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3. Interessanti ma da attendere</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>80.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>67.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🟠 Attendi pullback</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Non inseguire il prezzo: imposta alert su pullback o tenuta supporto. Supporto 60D: 54.81.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 75.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 80.1; priority 67.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: Normal risk</t>
+          <t>score 74.9; priority 76.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3612,22 +3612,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>prezzo 11.1% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Accumulate Carefully, score 80.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 11.1%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3646,15 +3646,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>54.81</v>
+        <v>66.58</v>
       </c>
       <c r="T15" t="n">
-        <v>73.47</v>
+        <v>75.94</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3664,93 +3664,93 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>33.05</v>
+        <v>11.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>68.09</v>
+        <v>22.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.78</v>
+        <v>12.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>-17.8</v>
+        <v>-20.6</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>73.47</v>
+        <v>75.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>81.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>100</v>
+        <v>78.7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>69.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK15" t="n">
-        <v>54.4</v>
+        <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>7.33</v>
+        <v>0.45</v>
       </c>
       <c r="AM15" t="n">
-        <v>40.88</v>
+        <v>12.12</v>
       </c>
       <c r="AN15" t="n">
-        <v>28.13</v>
+        <v>15.77</v>
       </c>
       <c r="AO15" t="n">
-        <v>2.04</v>
+        <v>1.22</v>
       </c>
       <c r="AP15" t="n">
-        <v>66.1416</v>
+        <v>73.31440000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>55.9789</v>
+        <v>69.2615</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>100</v>
+        <v>78.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>69.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>54.4</v>
+        <v>82.8</v>
       </c>
       <c r="AW15" t="n">
         <v>755</v>
       </c>
       <c r="AX15" t="n">
-        <v>68.89</v>
+        <v>73.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>73.47</v>
+        <v>75.94</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11.08</v>
+        <v>2.71</v>
       </c>
       <c r="BA15" t="n">
-        <v>31.25</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3776,20 +3776,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>75.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>77.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3798,17 +3798,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 75.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 73.47. Trigger: prezzo 8.4% sopra MA50: evitare inseguimento.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 75.6; priority 77.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 81.4; priority 75.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3818,22 +3818,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.4% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.7%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 81.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.4%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -3852,15 +3852,15 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>66.58</v>
+        <v>54.81</v>
       </c>
       <c r="T16" t="n">
-        <v>75.94</v>
+        <v>73.47</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -3874,89 +3874,89 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>12.82</v>
+        <v>30.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>22.74</v>
+        <v>65.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.88</v>
+        <v>13.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>-20.6</v>
+        <v>-17.8</v>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>75.94</v>
+        <v>72</v>
       </c>
       <c r="AH16" t="n">
-        <v>66.3</v>
+        <v>80.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="n">
-        <v>68.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>82.8</v>
+        <v>65.2</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="AM16" t="n">
-        <v>12.22</v>
+        <v>39.13</v>
       </c>
       <c r="AN16" t="n">
-        <v>15.95</v>
+        <v>27.29</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="AP16" t="n">
-        <v>73.2024</v>
+        <v>66.42359999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>69.2025</v>
+        <v>56.108</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AU16" t="n">
-        <v>68.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>82.8</v>
+        <v>65.2</v>
       </c>
       <c r="AW16" t="n">
         <v>755</v>
       </c>
       <c r="AX16" t="n">
-        <v>73.8</v>
+        <v>68.89</v>
       </c>
       <c r="AY16" t="n">
-        <v>75.94</v>
+        <v>73.47</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.74</v>
+        <v>8.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.74</v>
+        <v>28.32</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>75.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>74.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4008,12 +4008,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 6.4% sotto MA50: attendere recupero.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 75.1; priority 74.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 78.6; priority 74.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 6.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.5%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4053,23 +4053,23 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>246.403</v>
+        <v>273.3367</v>
       </c>
       <c r="T17" t="n">
-        <v>315.2</v>
+        <v>402.3797</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -4080,129 +4080,129 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>17.13</v>
+        <v>18.96</v>
       </c>
       <c r="Z17" t="n">
-        <v>47</v>
+        <v>109.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>26.02</v>
+        <v>29.84</v>
       </c>
       <c r="AB17" t="n">
-        <v>-33.36</v>
+        <v>-29.81</v>
       </c>
       <c r="AC17" t="n">
-        <v>35.63</v>
+        <v>26.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>30.65</v>
+        <v>23.73</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
-        <v>294.3</v>
+        <v>345.29</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>-3.51</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="AM17" t="n">
-        <v>8.32</v>
+        <v>12.56</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.35</v>
+        <v>43.59</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.67</v>
+        <v>1.46</v>
       </c>
       <c r="AP17" t="n">
-        <v>290.0462</v>
+        <v>368.886</v>
       </c>
       <c r="AQ17" t="n">
-        <v>268.365</v>
+        <v>312.4569</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT17" t="n">
-        <v>90.7</v>
+        <v>100</v>
       </c>
       <c r="AU17" t="n">
-        <v>42.1</v>
+        <v>40.3</v>
       </c>
       <c r="AV17" t="n">
-        <v>82.8</v>
+        <v>70.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX17" t="n">
-        <v>290.55</v>
+        <v>345.29</v>
       </c>
       <c r="AY17" t="n">
-        <v>315.2</v>
+        <v>389.8971</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.47</v>
+        <v>-6.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.66</v>
+        <v>10.51</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>4322488745984</v>
+        <v>4213426356224</v>
       </c>
       <c r="BE17" t="n">
-        <v>27.15</v>
+        <v>37.92</v>
       </c>
       <c r="BF17" t="n">
-        <v>141.47</v>
+        <v>38.88</v>
       </c>
       <c r="BG17" t="n">
-        <v>16.6</v>
+        <v>21.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>79.55</v>
+        <v>20.03</v>
       </c>
       <c r="BI17" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BJ17" t="n">
         <v>100</v>
       </c>
       <c r="BK17" t="n">
-        <v>90.7</v>
+        <v>100</v>
       </c>
       <c r="BL17" t="n">
-        <v>43</v>
+        <v>63.7</v>
       </c>
       <c r="BM17" t="n">
-        <v>42.1</v>
+        <v>40.3</v>
       </c>
       <c r="BN17" t="n">
-        <v>82.8</v>
+        <v>70.2</v>
       </c>
       <c r="BO17" t="inlineStr"/>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>78.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="F18" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 6.0% sotto MA50: attendere recupero.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 78.6; priority 74.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 74.8; priority 74.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4260,22 +4260,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo 6.0% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.0%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4285,23 +4285,23 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>273.3367</v>
+        <v>246.403</v>
       </c>
       <c r="T18" t="n">
-        <v>402.3797</v>
+        <v>315.2</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -4312,129 +4312,129 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>14.66</v>
+        <v>16.58</v>
       </c>
       <c r="Z18" t="n">
-        <v>108.3</v>
+        <v>46.03</v>
       </c>
       <c r="AA18" t="n">
-        <v>29.86</v>
+        <v>26</v>
       </c>
       <c r="AB18" t="n">
-        <v>-29.81</v>
+        <v>-33.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>26.4</v>
+        <v>35.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>23.78</v>
+        <v>30.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>346.13</v>
+        <v>293.08</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>-10.66</v>
+        <v>-5.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>14.59</v>
+        <v>7.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>43.78</v>
+        <v>17.16</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.47</v>
+        <v>0.66</v>
       </c>
       <c r="AP18" t="n">
-        <v>368.4026</v>
+        <v>290.7286</v>
       </c>
       <c r="AQ18" t="n">
-        <v>311.9021</v>
+        <v>268.6354</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT18" t="n">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>40.3</v>
+        <v>42.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>70.7</v>
+        <v>82.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX18" t="n">
-        <v>346.13</v>
+        <v>290.55</v>
       </c>
       <c r="AY18" t="n">
-        <v>389.8971</v>
+        <v>315.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-6.05</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.97</v>
+        <v>9.1</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>4223676710912</v>
+        <v>4304570155008</v>
       </c>
       <c r="BE18" t="n">
-        <v>37.92</v>
+        <v>27.15</v>
       </c>
       <c r="BF18" t="n">
-        <v>38.88</v>
+        <v>141.47</v>
       </c>
       <c r="BG18" t="n">
-        <v>21.8</v>
+        <v>16.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>20.03</v>
+        <v>79.55</v>
       </c>
       <c r="BI18" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="BJ18" t="n">
         <v>100</v>
       </c>
       <c r="BK18" t="n">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="BL18" t="n">
-        <v>63.6</v>
+        <v>43.5</v>
       </c>
       <c r="BM18" t="n">
-        <v>40.3</v>
+        <v>42.1</v>
       </c>
       <c r="BN18" t="n">
-        <v>70.7</v>
+        <v>82.8</v>
       </c>
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>USA / Internet</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -4456,10 +4456,10 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>69.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="F19" t="n">
-        <v>71.5</v>
+        <v>72.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 69.4; priority 71.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 70.2; priority 72.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 69.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 0.3%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.0%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>0.55</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.79</v>
+        <v>2.76</v>
       </c>
       <c r="AA19" t="n">
         <v>9.56</v>
@@ -4568,13 +4568,13 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>63.57</v>
+        <v>64.06</v>
       </c>
       <c r="AH19" t="n">
-        <v>61.7</v>
+        <v>62.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>52.5</v>
+        <v>54.9</v>
       </c>
       <c r="AJ19" t="n">
         <v>78.2</v>
@@ -4583,29 +4583,29 @@
         <v>82.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.38</v>
+        <v>-0.96</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.14</v>
+        <v>3.39</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.76</v>
+        <v>7.26</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>63.3914</v>
+        <v>63.4182</v>
       </c>
       <c r="AQ19" t="n">
-        <v>63.1403</v>
+        <v>63.1468</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>52.5</v>
+        <v>54.9</v>
       </c>
       <c r="AU19" t="n">
         <v>78.2</v>
@@ -4623,10 +4623,10 @@
         <v>64.51000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.28</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.68</v>
+        <v>1.45</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>78.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>70.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 50.73. Trigger: prezzo 9.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 19.164. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 78.3; priority 70.9; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 70.1; priority 69.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4689,27 +4689,27 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo 9.4% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.4%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4728,83 +4728,83 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>39.31</v>
+        <v>12.936</v>
       </c>
       <c r="T20" t="n">
-        <v>50.73</v>
+        <v>19.164</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>27.69</v>
+        <v>35.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>53.38</v>
+        <v>48.67</v>
       </c>
       <c r="AA20" t="n">
-        <v>16.23</v>
+        <v>21.69</v>
       </c>
       <c r="AB20" t="n">
-        <v>-19.17</v>
+        <v>-29.37</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>50.73</v>
+        <v>18.45</v>
       </c>
       <c r="AH20" t="n">
-        <v>73.3</v>
+        <v>52.8</v>
       </c>
       <c r="AI20" t="n">
         <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>65.2</v>
+        <v>45.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>61</v>
+        <v>66.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>8.9</v>
+        <v>2.43</v>
       </c>
       <c r="AM20" t="n">
-        <v>35.12</v>
+        <v>34.95</v>
       </c>
       <c r="AN20" t="n">
-        <v>22.65</v>
+        <v>20.21</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>0.93</v>
       </c>
       <c r="AP20" t="n">
-        <v>46.3517</v>
+        <v>17.0849</v>
       </c>
       <c r="AQ20" t="n">
-        <v>40.9763</v>
+        <v>14.7297</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
@@ -4814,25 +4814,25 @@
         <v>100</v>
       </c>
       <c r="AU20" t="n">
-        <v>65.2</v>
+        <v>50.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>61</v>
+        <v>66.8</v>
       </c>
       <c r="AW20" t="n">
         <v>755</v>
       </c>
       <c r="AX20" t="n">
-        <v>45.945</v>
+        <v>17.092</v>
       </c>
       <c r="AY20" t="n">
-        <v>50.73</v>
+        <v>19.164</v>
       </c>
       <c r="AZ20" t="n">
-        <v>9.449999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="BA20" t="n">
-        <v>23.8</v>
+        <v>25.26</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>72.7</v>
+        <v>71.7</v>
       </c>
       <c r="F21" t="n">
-        <v>54.3</v>
+        <v>53.1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 72.7; priority 54.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 71.7; priority 53.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>prezzo 4.7% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 72.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.7%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 71.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.3%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4956,22 +4956,22 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>14.02</v>
+        <v>13.72</v>
       </c>
       <c r="Z21" t="n">
-        <v>39.25</v>
+        <v>38.22</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.98</v>
+        <v>46.95</v>
       </c>
       <c r="AB21" t="n">
         <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>30.63</v>
+        <v>30.52</v>
       </c>
       <c r="AD21" t="n">
-        <v>15.72</v>
+        <v>15.63</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -4980,57 +4980,57 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>200.04</v>
+        <v>199</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-8.76</v>
+        <v>-7.48</v>
       </c>
       <c r="AM21" t="n">
-        <v>15.01</v>
+        <v>10.08</v>
       </c>
       <c r="AN21" t="n">
-        <v>70.83</v>
+        <v>70.41</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>209.8526</v>
+        <v>210.0508</v>
       </c>
       <c r="AQ21" t="n">
-        <v>190.0187</v>
+        <v>190.1797</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
         <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>88.5</v>
+        <v>84.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX21" t="n">
-        <v>200.04</v>
+        <v>199</v>
       </c>
       <c r="AY21" t="n">
         <v>224.0988</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-4.68</v>
+        <v>-5.26</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.27</v>
+        <v>4.64</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4845168754688</v>
+        <v>4819978813440</v>
       </c>
       <c r="BE21" t="n">
         <v>62.97</v>
@@ -5058,22 +5058,22 @@
         <v>6.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BJ21" t="n">
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>88.5</v>
+        <v>84.8</v>
       </c>
       <c r="BL21" t="n">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>55.8</v>
+        <v>56.7</v>
       </c>
       <c r="F22" t="n">
-        <v>57.6</v>
+        <v>58.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 55.8; priority 57.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 56.7; priority 58.5; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 5.9% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -5.9%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 56.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-7.69</v>
+        <v>-3.89</v>
       </c>
       <c r="Z22" t="n">
-        <v>24.36</v>
+        <v>23.49</v>
       </c>
       <c r="AA22" t="n">
-        <v>18.12</v>
+        <v>18.13</v>
       </c>
       <c r="AB22" t="n">
         <v>-21.9</v>
@@ -5212,50 +5212,50 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>352.3</v>
+        <v>349.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="AI22" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
         <v>60.7</v>
       </c>
       <c r="AK22" t="n">
-        <v>66.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AL22" t="n">
-        <v>-6</v>
+        <v>-7.55</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.21</v>
+        <v>-0.7</v>
       </c>
       <c r="AN22" t="n">
-        <v>27.41</v>
+        <v>27.04</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AP22" t="n">
-        <v>374.2578</v>
+        <v>373.4988</v>
       </c>
       <c r="AQ22" t="n">
-        <v>365.4025</v>
+        <v>365.6973</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="AU22" t="n">
         <v>60.7</v>
       </c>
       <c r="AV22" t="n">
-        <v>66.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AW22" t="n">
         <v>755</v>
@@ -5267,10 +5267,10 @@
         <v>377.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-5.87</v>
+        <v>-6.46</v>
       </c>
       <c r="BA22" t="n">
-        <v>-3.59</v>
+        <v>-4.47</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>64.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="F2" t="n">
-        <v>62.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 64.6; priority 62.4; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 69.5; priority 66.4; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,22 +812,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 8.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 5.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 64.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.8%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 69.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.5%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 200.95 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 253.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -846,14 +846,14 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>200.95</v>
+        <v>253.2667</v>
       </c>
       <c r="T2" t="n">
-        <v>274.99</v>
+        <v>315.2</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>13.04</v>
+        <v>9.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.38</v>
+        <v>37.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.16</v>
+        <v>26.23</v>
       </c>
       <c r="AB2" t="n">
-        <v>-30.88</v>
+        <v>-33.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>31.66</v>
+        <v>33.31</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.71</v>
+        <v>28.63</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,103 +888,105 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>234.27</v>
+        <v>275.15</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-12.03</v>
+        <v>-10.76</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.04</v>
+        <v>1.73</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.67</v>
+        <v>14.68</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>256.8852</v>
+        <v>291.0597</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.8395</v>
+        <v>268.8251</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>37.9</v>
+        <v>41.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>66.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX2" t="n">
-        <v>232.79</v>
+        <v>275.15</v>
       </c>
       <c r="AY2" t="n">
-        <v>274</v>
+        <v>315.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-8.800000000000001</v>
+        <v>-5.47</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.61</v>
+        <v>2.35</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2520068128768</v>
+        <v>4041225797632</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.22</v>
+        <v>27.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>24.29</v>
+        <v>141.47</v>
       </c>
       <c r="BG2" t="n">
         <v>16.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
+        <v>79.55</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>37</v>
+      </c>
       <c r="BJ2" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="BK2" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>57.6</v>
+        <v>48.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>37.9</v>
+        <v>41.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>66.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -996,20 +998,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>64.8</v>
+        <v>59.7</v>
       </c>
       <c r="F3" t="n">
-        <v>58.4</v>
+        <v>56.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1023,37 +1029,37 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 64.8; priority 58.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 59.7; priority 56.3; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 11.5% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 64.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 59.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.5%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 208.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1068,131 +1074,151 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>8.7643</v>
+        <v>208.27</v>
       </c>
       <c r="T3" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>274.99</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>17.81</v>
+        <v>7.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>67.45999999999999</v>
+        <v>6.69</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.52</v>
+        <v>31.19</v>
       </c>
       <c r="AB3" t="n">
-        <v>-43.36</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+        <v>-30.88</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>22.98</v>
+      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Energia pulita</t>
-        </is>
-      </c>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>82.8</v>
-      </c>
+        <v>227.01</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-6.17</v>
+        <v>-14.43</v>
       </c>
       <c r="AM3" t="n">
-        <v>32.64</v>
+        <v>-0.62</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.83</v>
+        <v>21.35</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.21</v>
+        <v>0.68</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.4492</v>
+        <v>256.445</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.923400000000001</v>
+        <v>232.7954</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT3" t="n">
-        <v>100</v>
+        <v>61.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>37.1</v>
+        <v>37.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>82.8</v>
+        <v>58</v>
       </c>
       <c r="AW3" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.914999999999999</v>
+        <v>227.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.61</v>
+        <v>274</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.77</v>
+        <v>-11.48</v>
       </c>
       <c r="BA3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+        <v>-2.49</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Internet Retail</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>2441971499008</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>53.3</v>
+      </c>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+      <c r="BJ3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>58</v>
+      </c>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>USA / Consumer &amp; Cloud</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1202,24 +1228,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>60.4</v>
+        <v>59.2</v>
       </c>
       <c r="F4" t="n">
-        <v>52.4</v>
+        <v>53.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1233,37 +1255,37 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 60.4; priority 52.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 59.2; priority 53.4; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo 11.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 60.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.3%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 59.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 358.18 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1278,153 +1300,131 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>358.1842</v>
+        <v>8.7643</v>
       </c>
       <c r="T4" t="n">
-        <v>460.52</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>11.61</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>-1.74</v>
+        <v>9.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>-24.2</v>
+        <v>62.26</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.11</v>
+        <v>23.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>-33.91</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>21.77</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>18.89</v>
-      </c>
+        <v>-43.36</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Energia pulita</t>
+        </is>
+      </c>
       <c r="AG4" t="n">
-        <v>365.46</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+        <v>10.19</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>75.59999999999999</v>
+      </c>
       <c r="AL4" t="n">
-        <v>-12.69</v>
+        <v>-10.66</v>
       </c>
       <c r="AM4" t="n">
-        <v>-24.46</v>
+        <v>27.93</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.44</v>
+        <v>3.68</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="AP4" t="n">
-        <v>412.0578</v>
+        <v>10.4803</v>
       </c>
       <c r="AQ4" t="n">
-        <v>447.595</v>
+        <v>8.9572</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>26.8</v>
+        <v>95.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>43.9</v>
+        <v>37</v>
       </c>
       <c r="AV4" t="n">
-        <v>58.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="AX4" t="n">
-        <v>365.46</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>460.52</v>
+        <v>11.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-11.31</v>
+        <v>-2.77</v>
       </c>
       <c r="BA4" t="n">
-        <v>-18.35</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>Software - Infrastructure</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>2714795769856</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>97</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>58.3</v>
-      </c>
+        <v>13.76</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1434,20 +1434,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>65.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>44.4</v>
+        <v>50.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1461,7 +1465,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 65.6; priority 44.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 69.4; priority 50.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1476,22 +1480,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 10.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 65.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 69.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 362.53 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 174.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1501,136 +1505,158 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>362.53</v>
+        <v>174.197</v>
       </c>
       <c r="T5" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>235.4656</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>56.85</v>
+        <v>9.68</v>
       </c>
       <c r="Z5" t="n">
-        <v>137.04</v>
+        <v>32.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>35.68</v>
+        <v>46.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+        <v>-36.88</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15.38</v>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>618.92</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>56.3</v>
-      </c>
+        <v>195.74</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>7.39</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>74.28</v>
+        <v>6.69</v>
       </c>
       <c r="AN5" t="n">
-        <v>62.68</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AP5" t="n">
-        <v>559.5742</v>
+        <v>210.04</v>
       </c>
       <c r="AQ5" t="n">
-        <v>416.0183</v>
+        <v>190.318</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>753</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>195.74</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>224.0988</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>4741018419200</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>100</v>
       </c>
-      <c r="AU5" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>752</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>569.6900000000001</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>48.77</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+      <c r="BK5" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>69.5</v>
+      </c>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>USA / Semiconductors</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1640,12 +1666,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1654,10 +1680,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59.5</v>
+        <v>58.6</v>
       </c>
       <c r="F6" t="n">
-        <v>38.5</v>
+        <v>49.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,7 +1697,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 59.5; priority 38.5; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 58.6; priority 49.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1681,27 +1707,27 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 9.6% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 14.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 59.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.7%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 58.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -14.2%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 535.88 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1720,14 +1746,14 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>535.8834000000001</v>
+        <v>352.83</v>
       </c>
       <c r="T6" t="n">
-        <v>687.9124</v>
+        <v>460.52</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1738,129 +1764,129 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-5.86</v>
+        <v>-4.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>-19.9</v>
+        <v>-27.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.45</v>
+        <v>24.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>-34.15</v>
+        <v>-34.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.29</v>
+        <v>21.04</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.39</v>
+        <v>18.22</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>557.67</v>
+        <v>352.83</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-8.529999999999999</v>
+        <v>-15.19</v>
       </c>
       <c r="AM6" t="n">
-        <v>-15.2</v>
+        <v>-26.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>26.57</v>
+        <v>3.21</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.73</v>
+        <v>0.13</v>
       </c>
       <c r="AP6" t="n">
-        <v>617.2199000000001</v>
+        <v>411.2692</v>
       </c>
       <c r="AQ6" t="n">
-        <v>650.9641</v>
+        <v>446.8838</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
         <v>35</v>
       </c>
       <c r="AT6" t="n">
-        <v>27.7</v>
+        <v>20.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>28.9</v>
+        <v>43.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>60.8</v>
+        <v>53.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX6" t="n">
-        <v>557.67</v>
+        <v>352.83</v>
       </c>
       <c r="AY6" t="n">
-        <v>634.7017</v>
+        <v>460.52</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-9.65</v>
+        <v>-14.21</v>
       </c>
       <c r="BA6" t="n">
-        <v>-14.33</v>
+        <v>-21.05</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1415602503680</v>
+        <v>2620974694400</v>
       </c>
       <c r="BE6" t="n">
-        <v>32.84</v>
+        <v>39.34</v>
       </c>
       <c r="BF6" t="n">
-        <v>32.93</v>
+        <v>34.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>33.1</v>
+        <v>18.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>35.61</v>
+        <v>30.27</v>
       </c>
       <c r="BI6" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="BJ6" t="n">
         <v>100</v>
       </c>
       <c r="BK6" t="n">
-        <v>27.7</v>
+        <v>20.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>82.7</v>
+        <v>77.8</v>
       </c>
       <c r="BM6" t="n">
-        <v>28.9</v>
+        <v>43.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>60.8</v>
+        <v>53.9</v>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1872,20 +1898,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>64.3</v>
       </c>
       <c r="F7" t="n">
-        <v>35.5</v>
+        <v>36.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1899,12 +1925,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 40.0; priority 35.5; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 64.3; priority 36.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1914,22 +1940,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 13.1% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 40.0, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.1%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 383.40 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1939,24 +1965,24 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>20.205</v>
+        <v>383.4</v>
       </c>
       <c r="T7" t="n">
-        <v>30.11</v>
+        <v>668.91</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1970,16 +1996,16 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>5.61</v>
+        <v>59.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>-15.14</v>
+        <v>135.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>34.08</v>
+        <v>35.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>-48.6</v>
+        <v>-35.74</v>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
@@ -1990,69 +2016,69 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>25.305</v>
+        <v>636.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>21.8</v>
+        <v>59.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>46.1</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15.2</v>
+        <v>23.6</v>
       </c>
       <c r="AK7" t="n">
-        <v>78.2</v>
+        <v>46.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.06</v>
+        <v>5.77</v>
       </c>
       <c r="AM7" t="n">
-        <v>-13.31</v>
+        <v>77.06</v>
       </c>
       <c r="AN7" t="n">
-        <v>-3.03</v>
+        <v>64.14</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.09</v>
+        <v>1.8</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.8966</v>
+        <v>563.2718</v>
       </c>
       <c r="AQ7" t="n">
-        <v>26.778</v>
+        <v>417.7247</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AT7" t="n">
-        <v>46.1</v>
+        <v>100</v>
       </c>
       <c r="AU7" t="n">
-        <v>20.2</v>
+        <v>28.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>78.2</v>
+        <v>46.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="AX7" t="n">
-        <v>24.785</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>30.11</v>
+        <v>668.91</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.64</v>
+        <v>13.07</v>
       </c>
       <c r="BA7" t="n">
-        <v>-5.5</v>
+        <v>52.46</v>
       </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -2078,24 +2104,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>63.9</v>
+        <v>40.9</v>
       </c>
       <c r="F8" t="n">
-        <v>34.6</v>
+        <v>36.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2109,12 +2131,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 63.9; priority 34.6; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 40.9; priority 36.5; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2124,22 +2146,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>prezzo 13.3% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 63.9, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 40.9, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.0%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1109.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2149,158 +2171,136 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1109.5466</v>
+        <v>20.205</v>
       </c>
       <c r="T8" t="n">
-        <v>1676</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+        <v>30.11</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>33.08</v>
+        <v>8.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>132.25</v>
+        <v>-15.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>38.43</v>
+        <v>34.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>-44.77</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>59.97</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>37.08</v>
-      </c>
+        <v>-48.6</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
       <c r="AG8" t="n">
-        <v>1560.8</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+        <v>25.22</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>78.2</v>
+      </c>
       <c r="AL8" t="n">
-        <v>9.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM8" t="n">
-        <v>73.73</v>
+        <v>-14.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>34.84</v>
+        <v>-3.13</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.91</v>
+        <v>-0.09</v>
       </c>
       <c r="AP8" t="n">
-        <v>1378.1336</v>
+        <v>24.9784</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1100.7298</v>
+        <v>26.7573</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>100</v>
+        <v>49.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>18.1</v>
+        <v>20.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>45.7</v>
+        <v>78.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="AX8" t="n">
-        <v>1376.4</v>
+        <v>24.785</v>
       </c>
       <c r="AY8" t="n">
-        <v>1676</v>
+        <v>30.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.25</v>
+        <v>0.97</v>
       </c>
       <c r="BA8" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>598862004224</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>52.24</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>69</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>45.7</v>
-      </c>
+        <v>-5.75</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>Europe / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>33.3</v>
+        <v>57.9</v>
       </c>
       <c r="F9" t="n">
-        <v>24.5</v>
+        <v>36</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 33.3; priority 24.5; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 57.9; priority 36.0; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 7.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 11.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 33.3, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.2%.</t>
+          <t>META: scenario base Hold / Monitor, score 57.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.7%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -2390,14 +2390,14 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>343.25</v>
+        <v>542.87</v>
       </c>
       <c r="T9" t="n">
-        <v>445.27</v>
+        <v>687.9124</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -2408,22 +2408,22 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>-1.96</v>
+        <v>-8.66</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.7</v>
+        <v>-23.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>57.82</v>
+        <v>36.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>-53.77</v>
+        <v>-34.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>338.32</v>
+        <v>19.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>150.21</v>
+        <v>14.98</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2432,172 +2432,178 @@
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>375.53</v>
+        <v>542.87</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>-11.85</v>
+        <v>-11.26</v>
       </c>
       <c r="AM9" t="n">
-        <v>-21.96</v>
+        <v>-17.79</v>
       </c>
       <c r="AN9" t="n">
-        <v>16.02</v>
+        <v>25.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.28</v>
+        <v>0.7</v>
       </c>
       <c r="AP9" t="n">
-        <v>404.7914</v>
+        <v>614.8398</v>
       </c>
       <c r="AQ9" t="n">
-        <v>417.6574</v>
+        <v>649.9292</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
         <v>35</v>
       </c>
       <c r="AT9" t="n">
-        <v>36</v>
+        <v>21.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>64.40000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX9" t="n">
-        <v>375.53</v>
+        <v>542.87</v>
       </c>
       <c r="AY9" t="n">
-        <v>442.1</v>
+        <v>634.7017</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-7.23</v>
+        <v>-11.71</v>
       </c>
       <c r="BA9" t="n">
-        <v>-10.09</v>
+        <v>-16.47</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1410386886656</v>
+        <v>1378033860608</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.95</v>
+        <v>32.84</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>32.93</v>
       </c>
       <c r="BG9" t="n">
-        <v>15.8</v>
+        <v>33.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="BI9" t="inlineStr"/>
+        <v>35.61</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>38</v>
+      </c>
       <c r="BJ9" t="n">
-        <v>64.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="BK9" t="n">
-        <v>36</v>
+        <v>21.3</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="BN9" t="n">
-        <v>64.40000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>USA / EV</t>
+          <t>USA / Social &amp; AI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>2. Rischio da controllare</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>80.7</v>
+        <v>63.1</v>
       </c>
       <c r="F10" t="n">
-        <v>81.5</v>
+        <v>30.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟥 Riduci rischio / non aumentare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Non aumentare esposizione: controlla peso in portafoglio, stop mentale e correlazione con posizioni simili.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 80.7; priority 81.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 63.1; priority 30.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 14.6% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.2%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.6%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2607,7 +2613,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2616,83 +2622,71 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>39.31</v>
+        <v>1111.3427</v>
       </c>
       <c r="T10" t="n">
-        <v>50.73</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>1676</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>20.73</v>
+        <v>31.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>48.17</v>
+        <v>137.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.44</v>
+        <v>38.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>-19.17</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+        <v>-44.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>38.04</v>
+      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Mercati emergenti</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>48.45</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>81.8</v>
-      </c>
+        <v>1594</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>2.23</v>
+        <v>15.81</v>
       </c>
       <c r="AM10" t="n">
-        <v>30.88</v>
+        <v>77.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.7</v>
+        <v>35.67</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.26</v>
+        <v>0.93</v>
       </c>
       <c r="AP10" t="n">
-        <v>46.4756</v>
+        <v>1390.9165</v>
       </c>
       <c r="AQ10" t="n">
-        <v>41.0446</v>
+        <v>1109.6879</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2702,108 +2696,146 @@
         <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>64.90000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>81.8</v>
+        <v>40.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="AX10" t="n">
-        <v>45.945</v>
+        <v>1384.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>50.73</v>
+        <v>1676</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.25</v>
+        <v>14.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>18.04</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
+        <v>43.64</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment &amp; Materials</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>614355763200</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>70</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>40.3</v>
+      </c>
       <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>Europe / Semiconductors</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>2. Rischio da controllare</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>78.8</v>
+        <v>32.9</v>
       </c>
       <c r="F11" t="n">
-        <v>79.2</v>
+        <v>24.1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟥 Riduci rischio / non aumentare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Non aumentare esposizione: controlla peso in portafoglio, stop mentale e correlazione con posizioni simili.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 78.8; priority 79.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 32.9; priority 24.1; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 7.4% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.0%.</t>
+          <t>TSLA: scenario base High Risk, score 32.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 140.98 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2813,136 +2845,156 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>140.98</v>
+        <v>343.25</v>
       </c>
       <c r="T11" t="n">
-        <v>166.04</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>14.36</v>
+        <v>-2.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>28.02</v>
+        <v>10.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.95</v>
+        <v>57.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>344.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>150.04</v>
+      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>Azionario globale</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="n">
-        <v>163.92</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>82.8</v>
-      </c>
+        <v>375.12</v>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.7</v>
+        <v>-13.49</v>
       </c>
       <c r="AM11" t="n">
-        <v>15.08</v>
+        <v>-23.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.23</v>
+        <v>15.95</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.41</v>
+        <v>0.28</v>
       </c>
       <c r="AP11" t="n">
-        <v>159.0628</v>
+        <v>405.0098</v>
       </c>
       <c r="AQ11" t="n">
-        <v>148.1395</v>
+        <v>417.801</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT11" t="n">
-        <v>86.2</v>
+        <v>34.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>67.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>82.8</v>
+        <v>64.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="AX11" t="n">
-        <v>159.24</v>
+        <v>375.12</v>
       </c>
       <c r="AY11" t="n">
-        <v>166.04</v>
+        <v>442.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.05</v>
+        <v>-7.38</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+        <v>-10.22</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>1408847052800</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
+      <c r="BJ11" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>64.2</v>
+      </c>
       <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2952,20 +3004,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>77.5</v>
+        <v>80.7</v>
       </c>
       <c r="F12" t="n">
-        <v>78.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2979,7 +3031,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 77.5; priority 78.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.7; priority 81.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2994,22 +3046,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 107.50 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3019,7 +3071,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -3028,15 +3080,15 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>107.5</v>
+        <v>39.31</v>
       </c>
       <c r="T12" t="n">
-        <v>125.04</v>
+        <v>50.73</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -3050,89 +3102,89 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>13.53</v>
+        <v>19.75</v>
       </c>
       <c r="Z12" t="n">
-        <v>25.72</v>
+        <v>48.37</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.2</v>
+        <v>16.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>-21.63</v>
+        <v>-19.17</v>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>123.92</v>
+        <v>48.725</v>
       </c>
       <c r="AH12" t="n">
-        <v>72.8</v>
+        <v>70.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="n">
-        <v>66.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>82.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.31</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>12.92</v>
+        <v>30.02</v>
       </c>
       <c r="AN12" t="n">
-        <v>17.93</v>
+        <v>20.87</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AP12" t="n">
-        <v>120.5462</v>
+        <v>46.6981</v>
       </c>
       <c r="AQ12" t="n">
-        <v>113.1305</v>
+        <v>41.1816</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>83.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="AU12" t="n">
-        <v>66.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="AV12" t="n">
-        <v>82.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AX12" t="n">
-        <v>120.73</v>
+        <v>45.945</v>
       </c>
       <c r="AY12" t="n">
-        <v>125.04</v>
+        <v>50.73</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.8</v>
+        <v>4.34</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.539999999999999</v>
+        <v>18.32</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -3158,20 +3210,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>77.2</v>
+        <v>78.3</v>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>78.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3185,7 +3237,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 77.2; priority 78.0; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.3; priority 78.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3200,22 +3252,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.63 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.42 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 141.82 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3225,7 +3277,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3234,15 +3286,15 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>56.4209</v>
+        <v>141.82</v>
       </c>
       <c r="T13" t="n">
-        <v>63.63</v>
+        <v>166.04</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3256,89 +3308,89 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>11.8</v>
+        <v>13.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.68</v>
+        <v>27.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.89</v>
+        <v>12.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>-16.33</v>
+        <v>-21.07</v>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>63.18</v>
+        <v>164.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>71.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AI13" t="n">
-        <v>79</v>
+        <v>84.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>71.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AK13" t="n">
         <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.09</v>
+        <v>1.23</v>
       </c>
       <c r="AM13" t="n">
-        <v>11.78</v>
+        <v>14.41</v>
       </c>
       <c r="AN13" t="n">
-        <v>15.02</v>
+        <v>18.24</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AP13" t="n">
-        <v>61.5015</v>
+        <v>159.6216</v>
       </c>
       <c r="AQ13" t="n">
-        <v>58.3864</v>
+        <v>148.4266</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>79</v>
+        <v>84.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>71.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AV13" t="n">
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AX13" t="n">
-        <v>61.4745</v>
+        <v>159.24</v>
       </c>
       <c r="AY13" t="n">
-        <v>63.63</v>
+        <v>166.04</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.210000000000001</v>
+        <v>10.63</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3364,20 +3416,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>76.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="F14" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3386,12 +3438,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 125.04. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 76.9; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.2; priority 77.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3411,17 +3463,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.8%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 597.92 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 108.12 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3440,15 +3492,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>597.92</v>
+        <v>108.12</v>
       </c>
       <c r="T14" t="n">
-        <v>703.9400000000001</v>
+        <v>125.04</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3462,16 +3514,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>14.41</v>
+        <v>12.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>26.14</v>
+        <v>25.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>14.17</v>
+        <v>13.19</v>
       </c>
       <c r="AB14" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3482,69 +3534,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>698.0599999999999</v>
+        <v>124.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>71.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>84.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AJ14" t="n">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK14" t="n">
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.22</v>
+        <v>0.99</v>
       </c>
       <c r="AM14" t="n">
-        <v>13.01</v>
+        <v>12.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.9</v>
+        <v>17.93</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AP14" t="n">
-        <v>679.1627999999999</v>
+        <v>120.9462</v>
       </c>
       <c r="AQ14" t="n">
-        <v>635.2736</v>
+        <v>113.3263</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>84.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV14" t="n">
         <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AX14" t="n">
-        <v>681.24</v>
+        <v>120.73</v>
       </c>
       <c r="AY14" t="n">
-        <v>703.9400000000001</v>
+        <v>125.04</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.880000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3570,20 +3622,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>74.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>76.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3592,12 +3644,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 75.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.79. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 74.9; priority 76.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.9; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3617,17 +3669,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.58 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 57.28 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3646,20 +3698,20 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>66.58</v>
+        <v>57.2813</v>
       </c>
       <c r="T15" t="n">
-        <v>75.94</v>
+        <v>63.79</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -3668,16 +3720,16 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>11.26</v>
+        <v>10.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.72</v>
+        <v>22.39</v>
       </c>
       <c r="AA15" t="n">
         <v>12.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>-20.6</v>
+        <v>-16.33</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3688,69 +3740,69 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>75.3</v>
+        <v>63.79</v>
       </c>
       <c r="AH15" t="n">
-        <v>65.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>78.7</v>
+        <v>77.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>68.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AK15" t="n">
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.45</v>
+        <v>2.17</v>
       </c>
       <c r="AM15" t="n">
-        <v>12.12</v>
+        <v>11.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>15.77</v>
+        <v>15.34</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AP15" t="n">
-        <v>73.31440000000001</v>
+        <v>61.6106</v>
       </c>
       <c r="AQ15" t="n">
-        <v>69.2615</v>
+        <v>58.4865</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>78.7</v>
+        <v>77.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>68.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AV15" t="n">
         <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="AX15" t="n">
-        <v>73.8</v>
+        <v>61.4745</v>
       </c>
       <c r="AY15" t="n">
-        <v>75.94</v>
+        <v>63.79</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.71</v>
+        <v>3.54</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.720000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3776,20 +3828,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>81.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="F16" t="n">
-        <v>75.8</v>
+        <v>77.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3798,17 +3850,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 73.47. Trigger: prezzo 8.4% sopra MA50: evitare inseguimento.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.98. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 81.4; priority 75.8; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 76.5; priority 77.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3818,22 +3870,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>prezzo 8.4% sopra MA50: evitare inseguimento</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 81.4, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.4%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 600.12 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3843,7 +3895,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -3852,20 +3904,20 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>54.81</v>
+        <v>600.12</v>
       </c>
       <c r="T16" t="n">
-        <v>73.47</v>
+        <v>703.98</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3874,89 +3926,89 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>30.93</v>
+        <v>13.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>65.92</v>
+        <v>25.01</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.83</v>
+        <v>14.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>-17.8</v>
+        <v>-23.32</v>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>72</v>
+        <v>697.5599999999999</v>
       </c>
       <c r="AH16" t="n">
-        <v>80.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>100</v>
+        <v>82.8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>69.2</v>
+        <v>64.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>65.2</v>
+        <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.75</v>
+        <v>0.44</v>
       </c>
       <c r="AM16" t="n">
-        <v>39.13</v>
+        <v>12.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>27.29</v>
+        <v>18.82</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="AP16" t="n">
-        <v>66.42359999999999</v>
+        <v>681.798</v>
       </c>
       <c r="AQ16" t="n">
-        <v>56.108</v>
+        <v>636.3686</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>100</v>
+        <v>82.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>69.2</v>
+        <v>64.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>65.2</v>
+        <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="AX16" t="n">
-        <v>68.89</v>
+        <v>681.24</v>
       </c>
       <c r="AY16" t="n">
-        <v>73.47</v>
+        <v>703.98</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8.4</v>
+        <v>2.31</v>
       </c>
       <c r="BA16" t="n">
-        <v>28.32</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -3982,24 +4034,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>78.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4008,42 +4056,42 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 6.4% sotto MA50: attendere recupero.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 75.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 78.6; priority 74.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 74.9; priority 76.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo 6.4% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.4%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 273.34 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 66.93 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4053,158 +4101,136 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>273.3367</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+        <v>75.94</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>18.96</v>
+        <v>10.92</v>
       </c>
       <c r="Z17" t="n">
-        <v>109.62</v>
+        <v>23.26</v>
       </c>
       <c r="AA17" t="n">
-        <v>29.84</v>
+        <v>12.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>23.73</v>
-      </c>
+        <v>-20.6</v>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Quality globale</t>
+        </is>
+      </c>
       <c r="AG17" t="n">
-        <v>345.29</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+        <v>75.66</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL17" t="n">
-        <v>-9.789999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="AM17" t="n">
-        <v>12.56</v>
+        <v>11.82</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.59</v>
+        <v>15.91</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AP17" t="n">
-        <v>368.886</v>
+        <v>73.5318</v>
       </c>
       <c r="AQ17" t="n">
-        <v>312.4569</v>
+        <v>69.3764</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>40.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>70.2</v>
+        <v>82.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="AX17" t="n">
-        <v>345.29</v>
+        <v>73.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>389.8971</v>
+        <v>75.94</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-6.4</v>
+        <v>2.89</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD17" t="n">
-        <v>4213426356224</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>25</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>70.2</v>
-      </c>
+        <v>9.06</v>
+      </c>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
       <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4214,12 +4240,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4228,10 +4254,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>74.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>74</v>
+        <v>73.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4240,12 +4266,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 6.9% sotto MA50: attendere recupero.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 74.8; priority 74.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 78.6; priority 73.8; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4260,22 +4286,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 6.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 74.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 0.8%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.9%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 246.40 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 287.39 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4285,23 +4311,23 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>246.403</v>
+        <v>287.3883</v>
       </c>
       <c r="T18" t="n">
-        <v>315.2</v>
+        <v>402.3797</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -4312,129 +4338,129 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>16.58</v>
+        <v>18.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>46.03</v>
+        <v>106.69</v>
       </c>
       <c r="AA18" t="n">
-        <v>26</v>
+        <v>29.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>-33.36</v>
+        <v>-29.81</v>
       </c>
       <c r="AC18" t="n">
-        <v>35.44</v>
+        <v>26.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>30.5</v>
+        <v>23.62</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Business/momentum interessanti ma valutazione tirata: non inseguire senza pullback.</t>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>293.08</v>
+        <v>343.71</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>-5.1</v>
+        <v>-11.56</v>
       </c>
       <c r="AM18" t="n">
-        <v>7.29</v>
+        <v>11.1</v>
       </c>
       <c r="AN18" t="n">
-        <v>17.16</v>
+        <v>43.3</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.66</v>
+        <v>1.45</v>
       </c>
       <c r="AP18" t="n">
-        <v>290.7286</v>
+        <v>369.106</v>
       </c>
       <c r="AQ18" t="n">
-        <v>268.6354</v>
+        <v>313.0075</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT18" t="n">
-        <v>89.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="AU18" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>82.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AX18" t="n">
-        <v>290.55</v>
+        <v>343.71</v>
       </c>
       <c r="AY18" t="n">
-        <v>315.2</v>
+        <v>389.8971</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.8100000000000001</v>
+        <v>-6.88</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.1</v>
+        <v>9.81</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>4304570155008</v>
+        <v>4194146189312</v>
       </c>
       <c r="BE18" t="n">
-        <v>27.15</v>
+        <v>37.92</v>
       </c>
       <c r="BF18" t="n">
-        <v>141.47</v>
+        <v>38.88</v>
       </c>
       <c r="BG18" t="n">
-        <v>16.6</v>
+        <v>21.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>79.55</v>
+        <v>20.03</v>
       </c>
       <c r="BI18" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ18" t="n">
         <v>100</v>
       </c>
       <c r="BK18" t="n">
-        <v>89.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="BL18" t="n">
-        <v>43.5</v>
+        <v>64</v>
       </c>
       <c r="BM18" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="BN18" t="n">
-        <v>82.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Internet</t>
         </is>
       </c>
     </row>
@@ -4446,20 +4472,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>70.2</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>72.3</v>
+        <v>73</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4468,17 +4494,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 64.68. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 73.47. Trigger: prezzo 9.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 70.2; priority 72.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 81.0; priority 73.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4488,22 +4514,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.0%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 81.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.3%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.68 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4513,7 +4539,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -4522,20 +4548,20 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>62.06</v>
+        <v>54.81</v>
       </c>
       <c r="T19" t="n">
-        <v>64.68000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -4544,89 +4570,89 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>30.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.76</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.56</v>
+        <v>13.87</v>
       </c>
       <c r="AB19" t="n">
-        <v>-12.85</v>
+        <v>-17.8</v>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Min volatility</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>64.06</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="AH19" t="n">
-        <v>62.6</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AI19" t="n">
-        <v>54.9</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
-        <v>78.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AK19" t="n">
-        <v>82.8</v>
+        <v>61.4</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.96</v>
+        <v>4.78</v>
       </c>
       <c r="AM19" t="n">
-        <v>3.39</v>
+        <v>40.63</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.26</v>
+        <v>27.93</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.76</v>
+        <v>2.01</v>
       </c>
       <c r="AP19" t="n">
-        <v>63.4182</v>
+        <v>66.9888</v>
       </c>
       <c r="AQ19" t="n">
-        <v>63.1468</v>
+        <v>56.3684</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
         <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>54.9</v>
+        <v>100</v>
       </c>
       <c r="AU19" t="n">
-        <v>78.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>82.8</v>
+        <v>61.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AX19" t="n">
-        <v>63.44</v>
+        <v>68.89</v>
       </c>
       <c r="AY19" t="n">
-        <v>64.51000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>9.33</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.45</v>
+        <v>29.93</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4652,20 +4678,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="F20" t="n">
-        <v>69</v>
+        <v>72.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,42 +4700,42 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 19.164. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.7. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 70.1; priority 69.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 70.5; priority 72.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.1, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.70 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4728,111 +4754,111 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>12.936</v>
+        <v>62.06</v>
       </c>
       <c r="T20" t="n">
-        <v>19.164</v>
+        <v>64.7</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>35.5</v>
+        <v>1.98</v>
       </c>
       <c r="Z20" t="n">
-        <v>48.67</v>
+        <v>3.53</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.69</v>
+        <v>9.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>-29.37</v>
+        <v>-12.85</v>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>18.45</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="AH20" t="n">
-        <v>52.8</v>
+        <v>63.1</v>
       </c>
       <c r="AI20" t="n">
-        <v>100</v>
+        <v>55.7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>45.5</v>
+        <v>78.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>66.8</v>
+        <v>82.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.43</v>
+        <v>0.99</v>
       </c>
       <c r="AM20" t="n">
-        <v>34.95</v>
+        <v>3.36</v>
       </c>
       <c r="AN20" t="n">
-        <v>20.21</v>
+        <v>7.51</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="AP20" t="n">
-        <v>17.0849</v>
+        <v>63.495</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.7297</v>
+        <v>63.1648</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>100</v>
+        <v>55.7</v>
       </c>
       <c r="AU20" t="n">
-        <v>50.5</v>
+        <v>78.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>66.8</v>
+        <v>82.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AX20" t="n">
-        <v>17.092</v>
+        <v>63.44</v>
       </c>
       <c r="AY20" t="n">
-        <v>19.164</v>
+        <v>64.7</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.99</v>
+        <v>1.65</v>
       </c>
       <c r="BA20" t="n">
-        <v>25.26</v>
+        <v>2.18</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4853,43 +4879,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2. Rischio da controllare</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>71.7</v>
+        <v>70.2</v>
       </c>
       <c r="F21" t="n">
-        <v>53.1</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🟥 Solo size piccola</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tieni in osservazione senza azione immediata; rivaluta dopo aggiornamento dati o news rilevanti.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 19.164. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 71.7; priority 53.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 70.2; priority 69.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4899,27 +4921,27 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>prezzo 5.3% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 71.7, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.3%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 164.98 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4934,153 +4956,131 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>164.9777</v>
+        <v>12.936</v>
       </c>
       <c r="T21" t="n">
-        <v>235.4656</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+        <v>19.164</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>13.72</v>
+        <v>35.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>38.22</v>
+        <v>49.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>46.95</v>
+        <v>21.66</v>
       </c>
       <c r="AB21" t="n">
-        <v>-36.88</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>30.52</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>15.63</v>
-      </c>
+        <v>-29.37</v>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Robotica e automazione</t>
+        </is>
+      </c>
       <c r="AG21" t="n">
-        <v>199</v>
-      </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+        <v>18.592</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>53</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>67.3</v>
+      </c>
       <c r="AL21" t="n">
-        <v>-7.48</v>
+        <v>4.86</v>
       </c>
       <c r="AM21" t="n">
-        <v>10.08</v>
+        <v>35.95</v>
       </c>
       <c r="AN21" t="n">
-        <v>70.41</v>
+        <v>20.46</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP21" t="n">
-        <v>210.0508</v>
+        <v>17.2374</v>
       </c>
       <c r="AQ21" t="n">
-        <v>190.1797</v>
+        <v>14.7864</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT21" t="n">
-        <v>84.8</v>
+        <v>100</v>
       </c>
       <c r="AU21" t="n">
-        <v>14.2</v>
+        <v>50.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>71.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="AX21" t="n">
-        <v>199</v>
+        <v>17.092</v>
       </c>
       <c r="AY21" t="n">
-        <v>224.0988</v>
+        <v>19.164</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-5.26</v>
+        <v>7.86</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="BD21" t="n">
-        <v>4819978813440</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>114.29</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>50</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>71.90000000000001</v>
-      </c>
+        <v>25.74</v>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
       <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>USA / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>56.7</v>
+        <v>52.8</v>
       </c>
       <c r="F22" t="n">
-        <v>58.5</v>
+        <v>54.1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 56.7; priority 58.5; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 52.8; priority 54.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 6.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 56.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.5%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 52.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.5%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 340.82 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 339.65 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>340.82</v>
+        <v>339.65</v>
       </c>
       <c r="T22" t="n">
         <v>396.71</v>
@@ -5184,20 +5184,20 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-3.89</v>
+        <v>-10.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>23.49</v>
+        <v>20.32</v>
       </c>
       <c r="AA22" t="n">
-        <v>18.13</v>
+        <v>18.18</v>
       </c>
       <c r="AB22" t="n">
-        <v>-21.9</v>
+        <v>-22.17</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,65 +5212,65 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>349.36</v>
+        <v>339.98</v>
       </c>
       <c r="AH22" t="n">
-        <v>67.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>60.7</v>
+        <v>60.4</v>
       </c>
       <c r="AK22" t="n">
-        <v>65.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>-7.55</v>
+        <v>-7.38</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.7</v>
+        <v>-5.11</v>
       </c>
       <c r="AN22" t="n">
-        <v>27.04</v>
+        <v>25.82</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AP22" t="n">
-        <v>373.4988</v>
+        <v>371.4308</v>
       </c>
       <c r="AQ22" t="n">
-        <v>365.6973</v>
+        <v>366.1597</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>60.7</v>
+        <v>60.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>65.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AX22" t="n">
-        <v>340.82</v>
+        <v>339.65</v>
       </c>
       <c r="AY22" t="n">
         <v>377.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-6.46</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>-4.47</v>
+        <v>-7.15</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.5</v>
+        <v>61.5</v>
       </c>
       <c r="F2" t="n">
-        <v>66.40000000000001</v>
+        <v>59.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,12 +797,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 69.5; priority 66.4; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 61.5; priority 59.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -812,22 +812,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 5.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 69.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -5.5%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 61.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.2%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 253.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 209.77 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -837,23 +837,23 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>253.2667</v>
+        <v>209.77</v>
       </c>
       <c r="T2" t="n">
-        <v>315.2</v>
+        <v>274.99</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -864,129 +864,127 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>9.02</v>
+        <v>12.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>37.91</v>
+        <v>9.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>26.23</v>
+        <v>31.21</v>
       </c>
       <c r="AB2" t="n">
-        <v>-33.36</v>
+        <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>33.31</v>
+        <v>32.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>28.63</v>
+        <v>23.55</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>275.15</v>
+        <v>232.69</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-10.76</v>
+        <v>-14.41</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.73</v>
+        <v>0.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>14.68</v>
+        <v>21.77</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP2" t="n">
-        <v>291.0597</v>
+        <v>256.1288</v>
       </c>
       <c r="AQ2" t="n">
-        <v>268.8251</v>
+        <v>232.7676</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>41.8</v>
+        <v>37.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>71.59999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="AW2" t="n">
         <v>753</v>
       </c>
       <c r="AX2" t="n">
-        <v>275.15</v>
+        <v>227.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>315.2</v>
+        <v>270.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-5.47</v>
+        <v>-9.15</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.35</v>
+        <v>-0.03</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>4041225797632</v>
+        <v>2503072022528</v>
       </c>
       <c r="BE2" t="n">
-        <v>27.15</v>
+        <v>12.22</v>
       </c>
       <c r="BF2" t="n">
-        <v>141.47</v>
+        <v>24.29</v>
       </c>
       <c r="BG2" t="n">
         <v>16.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>37</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>73.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>48.6</v>
+        <v>56.9</v>
       </c>
       <c r="BM2" t="n">
-        <v>41.8</v>
+        <v>37.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>71.59999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Consumer &amp; Cloud</t>
         </is>
       </c>
     </row>
@@ -998,12 +996,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1012,10 +1010,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59.7</v>
+        <v>62</v>
       </c>
       <c r="F3" t="n">
-        <v>56.3</v>
+        <v>54.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1029,7 +1027,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 59.7; priority 56.3; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 62.0; priority 54.7; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1044,22 +1042,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 11.5% sotto MA50: attendere recupero</t>
+          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 59.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.5%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.2%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 274.99 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 208.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1078,14 +1076,14 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>208.27</v>
+        <v>352.83</v>
       </c>
       <c r="T3" t="n">
-        <v>274.99</v>
+        <v>460.52</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -1096,22 +1094,22 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>7.23</v>
+        <v>2.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.69</v>
+        <v>-23.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>31.19</v>
+        <v>24.38</v>
       </c>
       <c r="AB3" t="n">
-        <v>-30.88</v>
+        <v>-34.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>30.68</v>
+        <v>22.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>22.98</v>
+        <v>19.26</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1120,103 +1118,105 @@
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>227.01</v>
+        <v>372.97</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-14.43</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.62</v>
+        <v>-23.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.35</v>
+        <v>4.52</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.68</v>
+        <v>0.19</v>
       </c>
       <c r="AP3" t="n">
-        <v>256.445</v>
+        <v>410.522</v>
       </c>
       <c r="AQ3" t="n">
-        <v>232.7954</v>
+        <v>446.2723</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
         <v>35</v>
       </c>
       <c r="AT3" t="n">
-        <v>61.4</v>
+        <v>33.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>37.9</v>
+        <v>43.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>58</v>
+        <v>61.5</v>
       </c>
       <c r="AW3" t="n">
         <v>753</v>
       </c>
       <c r="AX3" t="n">
-        <v>227.01</v>
+        <v>352.83</v>
       </c>
       <c r="AY3" t="n">
-        <v>274</v>
+        <v>460.52</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-11.48</v>
+        <v>-9.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>-2.49</v>
+        <v>-16.43</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2441971499008</v>
+        <v>2770583420928</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.22</v>
+        <v>39.34</v>
       </c>
       <c r="BF3" t="n">
-        <v>24.29</v>
+        <v>34.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>16.6</v>
+        <v>18.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="BI3" t="inlineStr"/>
+        <v>30.27</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>103</v>
+      </c>
       <c r="BJ3" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="BK3" t="n">
-        <v>61.4</v>
+        <v>33.2</v>
       </c>
       <c r="BL3" t="n">
-        <v>59.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>37.9</v>
+        <v>43.1</v>
       </c>
       <c r="BN3" t="n">
-        <v>58</v>
+        <v>61.5</v>
       </c>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>USA / Consumer &amp; Cloud</t>
+          <t>USA / Technology</t>
         </is>
       </c>
     </row>
@@ -1228,20 +1228,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>59.2</v>
+        <v>66.8</v>
       </c>
       <c r="F4" t="n">
-        <v>53.4</v>
+        <v>52.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 59.2; priority 53.4; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 66.8; priority 52.3; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 59.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.8%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 391.97 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1300,19 +1300,19 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8.7643</v>
+        <v>391.97</v>
       </c>
       <c r="T4" t="n">
-        <v>11.61</v>
+        <v>668.91</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1326,16 +1326,16 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>9.19</v>
+        <v>60.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>62.26</v>
+        <v>122.93</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.56</v>
+        <v>35.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>-43.36</v>
+        <v>-35.74</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
@@ -1346,69 +1346,69 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>10.19</v>
+        <v>611.61</v>
       </c>
       <c r="AH4" t="n">
-        <v>31.8</v>
+        <v>57.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>23.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>75.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AL4" t="n">
-        <v>-10.66</v>
+        <v>2.71</v>
       </c>
       <c r="AM4" t="n">
-        <v>27.93</v>
+        <v>68.41</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.68</v>
+        <v>60.24</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.16</v>
+        <v>1.69</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.4803</v>
+        <v>566.444</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.9572</v>
+        <v>419.2983</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT4" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="AU4" t="n">
-        <v>37</v>
+        <v>28.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>75.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.914999999999999</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.61</v>
+        <v>668.91</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-2.77</v>
+        <v>7.97</v>
       </c>
       <c r="BA4" t="n">
-        <v>13.76</v>
+        <v>45.87</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1434,24 +1434,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>69.40000000000001</v>
+        <v>57.9</v>
       </c>
       <c r="F5" t="n">
-        <v>50.1</v>
+        <v>51.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1465,7 +1461,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 69.4; priority 50.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 57.9; priority 51.5; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1480,22 +1476,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
+          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 69.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 57.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 174.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1505,7 +1501,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1514,149 +1510,127 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>174.197</v>
+        <v>8.7643</v>
       </c>
       <c r="T5" t="n">
-        <v>235.4656</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>11.61</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>9.68</v>
+        <v>9.91</v>
       </c>
       <c r="Z5" t="n">
-        <v>32.52</v>
+        <v>57.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>46.93</v>
+        <v>23.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>-36.88</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15.38</v>
-      </c>
+        <v>-43.36</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Energia pulita</t>
+        </is>
+      </c>
       <c r="AG5" t="n">
-        <v>195.74</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>72.40000000000001</v>
+      </c>
       <c r="AL5" t="n">
-        <v>-8.789999999999999</v>
+        <v>-13.19</v>
       </c>
       <c r="AM5" t="n">
-        <v>6.69</v>
+        <v>23.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.34999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.48</v>
+        <v>0.13</v>
       </c>
       <c r="AP5" t="n">
-        <v>210.04</v>
+        <v>10.491</v>
       </c>
       <c r="AQ5" t="n">
-        <v>190.318</v>
+        <v>8.9716</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
         <v>65</v>
       </c>
       <c r="AT5" t="n">
-        <v>75.7</v>
+        <v>92.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>14.2</v>
+        <v>37</v>
       </c>
       <c r="AV5" t="n">
-        <v>69.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="AX5" t="n">
-        <v>195.74</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>224.0988</v>
+        <v>11.61</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-6.81</v>
+        <v>-4.87</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>4741018419200</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>114.29</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>69.5</v>
-      </c>
+        <v>11.24</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>USA / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1666,12 +1640,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1680,10 +1654,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58.6</v>
+        <v>69.2</v>
       </c>
       <c r="F6" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1697,37 +1671,37 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 58.6; priority 49.4; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 69.2; priority 49.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 14.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 58.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -14.2%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 69.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.3%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 175.55 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1737,23 +1711,23 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>352.83</v>
+        <v>175.5454</v>
       </c>
       <c r="T6" t="n">
-        <v>460.52</v>
+        <v>235.4656</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1764,81 +1738,81 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-4.7</v>
+        <v>12.56</v>
       </c>
       <c r="Z6" t="n">
-        <v>-27.44</v>
+        <v>24.93</v>
       </c>
       <c r="AA6" t="n">
-        <v>24.18</v>
+        <v>46.92</v>
       </c>
       <c r="AB6" t="n">
-        <v>-34.5</v>
+        <v>-36.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.04</v>
+        <v>29.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>18.22</v>
+        <v>15.13</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>352.83</v>
+        <v>192.53</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-15.19</v>
+        <v>-9.33</v>
       </c>
       <c r="AM6" t="n">
-        <v>-26.92</v>
+        <v>1.88</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.21</v>
+        <v>66.73</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.13</v>
+        <v>1.42</v>
       </c>
       <c r="AP6" t="n">
-        <v>411.2692</v>
+        <v>209.9179</v>
       </c>
       <c r="AQ6" t="n">
-        <v>446.8838</v>
+        <v>190.428</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AT6" t="n">
-        <v>20.4</v>
+        <v>75</v>
       </c>
       <c r="AU6" t="n">
-        <v>43.4</v>
+        <v>14.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>53.9</v>
+        <v>67.3</v>
       </c>
       <c r="AW6" t="n">
         <v>753</v>
       </c>
       <c r="AX6" t="n">
-        <v>352.83</v>
+        <v>192.53</v>
       </c>
       <c r="AY6" t="n">
-        <v>460.52</v>
+        <v>224.0988</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-14.21</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="BA6" t="n">
-        <v>-21.05</v>
+        <v>1.1</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1847,46 +1821,46 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>2620974694400</v>
+        <v>4663269130240</v>
       </c>
       <c r="BE6" t="n">
-        <v>39.34</v>
+        <v>62.97</v>
       </c>
       <c r="BF6" t="n">
-        <v>34.01</v>
+        <v>114.29</v>
       </c>
       <c r="BG6" t="n">
-        <v>18.3</v>
+        <v>85.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>30.27</v>
+        <v>6.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="BJ6" t="n">
         <v>100</v>
       </c>
       <c r="BK6" t="n">
-        <v>20.4</v>
+        <v>75</v>
       </c>
       <c r="BL6" t="n">
-        <v>77.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>43.4</v>
+        <v>14.2</v>
       </c>
       <c r="BN6" t="n">
-        <v>53.9</v>
+        <v>67.3</v>
       </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -1898,20 +1872,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>64.3</v>
+        <v>61.4</v>
       </c>
       <c r="F7" t="n">
-        <v>36.9</v>
+        <v>40.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1925,12 +1903,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 64.3; priority 36.9; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 61.4; priority 40.2; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1940,22 +1918,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo 13.1% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 10.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 64.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 13.1%.</t>
+          <t>META: scenario base Hold / Monitor, score 61.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.2%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 383.40 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1970,131 +1948,153 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>383.4</v>
+        <v>542.87</v>
       </c>
       <c r="T7" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>687.9124</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>59.61</v>
+        <v>0.59</v>
       </c>
       <c r="Z7" t="n">
-        <v>135.27</v>
+        <v>-22.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>35.69</v>
+        <v>36.42</v>
       </c>
       <c r="AB7" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+        <v>-34.15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15.18</v>
+      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>636.88</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>46.5</v>
-      </c>
+        <v>550.25</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>5.77</v>
+        <v>-13.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>77.06</v>
+        <v>-17.1</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.14</v>
+        <v>24.69</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.8</v>
+        <v>0.68</v>
       </c>
       <c r="AP7" t="n">
-        <v>563.2718</v>
+        <v>612.4256</v>
       </c>
       <c r="AQ7" t="n">
-        <v>417.7247</v>
+        <v>648.8645</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT7" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="AU7" t="n">
-        <v>28.6</v>
+        <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>46.5</v>
+        <v>60</v>
       </c>
       <c r="AW7" t="n">
         <v>753</v>
       </c>
       <c r="AX7" t="n">
-        <v>569.6900000000001</v>
+        <v>542.87</v>
       </c>
       <c r="AY7" t="n">
-        <v>668.91</v>
+        <v>631.9243</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.07</v>
+        <v>-10.15</v>
       </c>
       <c r="BA7" t="n">
-        <v>52.46</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
+        <v>-15.2</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1396767457280</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>39</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>35</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>60</v>
+      </c>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>USA / Social &amp; AI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2114,10 +2114,10 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="F8" t="n">
-        <v>36.5</v>
+        <v>37.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 40.9; priority 36.5; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 41.7; priority 37.3; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 40.9, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.0%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 41.7, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.4%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>8.85</v>
+        <v>11.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>-15.65</v>
+        <v>-13.41</v>
       </c>
       <c r="AA8" t="n">
-        <v>34.06</v>
+        <v>35.89</v>
       </c>
       <c r="AB8" t="n">
         <v>-48.6</v>
@@ -2226,53 +2226,53 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>25.22</v>
+        <v>26.055</v>
       </c>
       <c r="AH8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>49.8</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.2</v>
+        <v>13.1</v>
       </c>
       <c r="AK8" t="n">
         <v>78.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.79</v>
+        <v>1.26</v>
       </c>
       <c r="AM8" t="n">
-        <v>-14.45</v>
+        <v>-12.39</v>
       </c>
       <c r="AN8" t="n">
-        <v>-3.13</v>
+        <v>-2.07</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="AP8" t="n">
-        <v>24.9784</v>
+        <v>25.1883</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.7573</v>
+        <v>26.7331</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
         <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>49.8</v>
+        <v>55</v>
       </c>
       <c r="AU8" t="n">
-        <v>20.2</v>
+        <v>18.1</v>
       </c>
       <c r="AV8" t="n">
         <v>78.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AX8" t="n">
         <v>24.785</v>
@@ -2281,10 +2281,10 @@
         <v>30.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.97</v>
+        <v>3.44</v>
       </c>
       <c r="BA8" t="n">
-        <v>-5.75</v>
+        <v>-2.54</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57.9</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 57.9; priority 36.0; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 64.0; priority 35.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 11.7% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 12.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 57.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -11.7%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.9%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2386,18 +2386,18 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>542.87</v>
+        <v>1111.3427</v>
       </c>
       <c r="T9" t="n">
-        <v>687.9124</v>
+        <v>1676</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -2408,22 +2408,22 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>-8.66</v>
+        <v>35.67</v>
       </c>
       <c r="Z9" t="n">
-        <v>-23.53</v>
+        <v>138.07</v>
       </c>
       <c r="AA9" t="n">
-        <v>36.46</v>
+        <v>38.39</v>
       </c>
       <c r="AB9" t="n">
-        <v>-34.15</v>
+        <v>-44.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.75</v>
+        <v>61.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>14.98</v>
+        <v>37.51</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2432,105 +2432,105 @@
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>542.87</v>
+        <v>1578.2</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>-11.26</v>
+        <v>13.46</v>
       </c>
       <c r="AM9" t="n">
-        <v>-17.79</v>
+        <v>76.17</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.4</v>
+        <v>35.17</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="AP9" t="n">
-        <v>614.8398</v>
+        <v>1398.0824</v>
       </c>
       <c r="AQ9" t="n">
-        <v>649.9292</v>
+        <v>1114.1671</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT9" t="n">
-        <v>21.3</v>
+        <v>100</v>
       </c>
       <c r="AU9" t="n">
-        <v>28.9</v>
+        <v>18.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>57.7</v>
+        <v>47.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="AX9" t="n">
-        <v>542.87</v>
+        <v>1394</v>
       </c>
       <c r="AY9" t="n">
-        <v>634.7017</v>
+        <v>1676</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-11.71</v>
+        <v>12.88</v>
       </c>
       <c r="BA9" t="n">
-        <v>-16.47</v>
+        <v>41.65</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1378033860608</v>
+        <v>608266158080</v>
       </c>
       <c r="BE9" t="n">
-        <v>32.84</v>
+        <v>29.71</v>
       </c>
       <c r="BF9" t="n">
-        <v>32.93</v>
+        <v>52.24</v>
       </c>
       <c r="BG9" t="n">
-        <v>33.1</v>
+        <v>13.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>35.61</v>
+        <v>12.99</v>
       </c>
       <c r="BI9" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="BJ9" t="n">
         <v>100</v>
       </c>
       <c r="BK9" t="n">
-        <v>21.3</v>
+        <v>100</v>
       </c>
       <c r="BL9" t="n">
-        <v>83.90000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="BM9" t="n">
-        <v>28.9</v>
+        <v>18.1</v>
       </c>
       <c r="BN9" t="n">
-        <v>57.7</v>
+        <v>47.2</v>
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>USA / Social &amp; AI</t>
+          <t>Europe / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.1</v>
+        <v>35.4</v>
       </c>
       <c r="F10" t="n">
-        <v>30.5</v>
+        <v>27</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 63.1; priority 30.5; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 35.4; priority 27.0; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Extended - wait pullback</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2588,22 +2588,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 14.6% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.6%.</t>
+          <t>TSLA: scenario base High Risk, score 35.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2613,23 +2613,23 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>1111.3427</v>
+        <v>343.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1676</v>
+        <v>445.27</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -2640,22 +2640,22 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>31.85</v>
+        <v>2.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>137.12</v>
+        <v>15.92</v>
       </c>
       <c r="AA10" t="n">
-        <v>38.41</v>
+        <v>57.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>-44.77</v>
+        <v>-53.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>61.81</v>
+        <v>348.36</v>
       </c>
       <c r="AD10" t="n">
-        <v>38.04</v>
+        <v>151.76</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2664,178 +2664,172 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>1594</v>
+        <v>379.71</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>15.81</v>
+        <v>-13.77</v>
       </c>
       <c r="AM10" t="n">
-        <v>77.11</v>
+        <v>-21.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.67</v>
+        <v>14.98</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.93</v>
+        <v>0.26</v>
       </c>
       <c r="AP10" t="n">
-        <v>1390.9165</v>
+        <v>404.765</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1109.6879</v>
+        <v>417.9647</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT10" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>40.3</v>
+        <v>66</v>
       </c>
       <c r="AW10" t="n">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="AX10" t="n">
-        <v>1384.8</v>
+        <v>375.12</v>
       </c>
       <c r="AY10" t="n">
-        <v>1676</v>
+        <v>435.79</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.6</v>
+        <v>-6.19</v>
       </c>
       <c r="BA10" t="n">
-        <v>43.64</v>
+        <v>-9.15</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>614355763200</v>
+        <v>1426085904384</v>
       </c>
       <c r="BE10" t="n">
-        <v>29.71</v>
+        <v>3.95</v>
       </c>
       <c r="BF10" t="n">
-        <v>52.24</v>
+        <v>4.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>70</v>
-      </c>
+        <v>18.74</v>
+      </c>
+      <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="n">
-        <v>100</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="BL10" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>40.3</v>
+        <v>66</v>
       </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>Europe / Semiconductors</t>
+          <t>USA / EV</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2. Rischio da controllare</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>32.9</v>
+        <v>80.7</v>
       </c>
       <c r="F11" t="n">
-        <v>24.1</v>
+        <v>81.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟥 Riduci rischio / non aumentare</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Non aumentare esposizione: controlla peso in portafoglio, stop mentale e correlazione con posizioni simili.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 32.9; priority 24.1; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 80.7; priority 81.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>prezzo 7.4% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 32.9, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.4%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 39.95 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2845,156 +2839,136 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>343.25</v>
+        <v>39.955</v>
       </c>
       <c r="T11" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+        <v>50.73</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>-2.81</v>
+        <v>21.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.18</v>
+        <v>43.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>57.78</v>
+        <v>16.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>344.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>150.04</v>
-      </c>
+        <v>-19.17</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Mercati emergenti</t>
+        </is>
+      </c>
       <c r="AG11" t="n">
-        <v>375.12</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+        <v>48.16</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL11" t="n">
-        <v>-13.49</v>
+        <v>0.43</v>
       </c>
       <c r="AM11" t="n">
-        <v>-23.25</v>
+        <v>27.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>15.95</v>
+        <v>20.37</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.28</v>
+        <v>1.24</v>
       </c>
       <c r="AP11" t="n">
-        <v>405.0098</v>
+        <v>46.792</v>
       </c>
       <c r="AQ11" t="n">
-        <v>417.801</v>
+        <v>41.2472</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>34.7</v>
+        <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AV11" t="n">
-        <v>64.2</v>
+        <v>82.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="AX11" t="n">
-        <v>375.12</v>
+        <v>45.945</v>
       </c>
       <c r="AY11" t="n">
-        <v>442.1</v>
+        <v>50.73</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-7.38</v>
+        <v>2.92</v>
       </c>
       <c r="BA11" t="n">
-        <v>-10.22</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>1408847052800</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>18.74</v>
-      </c>
+        <v>16.76</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>64.2</v>
-      </c>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>USA / EV</t>
-        </is>
-      </c>
+      <c r="BP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3004,20 +2978,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>80.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>81.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3031,7 +3005,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 80.7; priority 81.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.4; priority 78.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3051,17 +3025,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.3%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.31 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 143.92 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3080,15 +3054,15 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>39.31</v>
+        <v>143.92</v>
       </c>
       <c r="T12" t="n">
-        <v>50.73</v>
+        <v>166.04</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -3102,16 +3076,16 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>19.75</v>
+        <v>14.51</v>
       </c>
       <c r="Z12" t="n">
-        <v>48.37</v>
+        <v>26.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>16.42</v>
+        <v>12.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
@@ -3122,69 +3096,69 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>48.725</v>
+        <v>163.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>70.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AK12" t="n">
-        <v>81.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.85</v>
+        <v>0.54</v>
       </c>
       <c r="AM12" t="n">
-        <v>30.02</v>
+        <v>13.54</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.87</v>
+        <v>18.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>46.6981</v>
+        <v>159.8616</v>
       </c>
       <c r="AQ12" t="n">
-        <v>41.1816</v>
+        <v>148.5673</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>100</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>65</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>81.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="AX12" t="n">
-        <v>45.945</v>
+        <v>159.24</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.73</v>
+        <v>166.04</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.34</v>
+        <v>2.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>18.32</v>
+        <v>10.19</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -3205,39 +3179,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>4. Alert / monitoraggio</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>78.3</v>
+        <v>77.2</v>
       </c>
       <c r="F13" t="n">
-        <v>78.7</v>
+        <v>77.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟡 Metti alert / monitora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 125.04. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 78.3; priority 78.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.2; priority 77.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3257,17 +3231,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.3, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 166.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 141.82 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 109.74 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3277,7 +3251,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3286,15 +3260,15 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>141.82</v>
+        <v>109.74</v>
       </c>
       <c r="T13" t="n">
-        <v>166.04</v>
+        <v>125.04</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3308,89 +3282,89 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>13.49</v>
+        <v>13.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>27.13</v>
+        <v>24.26</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.94</v>
+        <v>13.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>164.2</v>
+        <v>123.73</v>
       </c>
       <c r="AH13" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AI13" t="n">
-        <v>84.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AJ13" t="n">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK13" t="n">
         <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.23</v>
+        <v>0.46</v>
       </c>
       <c r="AM13" t="n">
-        <v>14.41</v>
+        <v>11.52</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.24</v>
+        <v>17.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AP13" t="n">
-        <v>159.6216</v>
+        <v>121.1144</v>
       </c>
       <c r="AQ13" t="n">
-        <v>148.4266</v>
+        <v>113.4222</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>84.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AV13" t="n">
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AX13" t="n">
-        <v>159.24</v>
+        <v>120.73</v>
       </c>
       <c r="AY13" t="n">
-        <v>166.04</v>
+        <v>125.04</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.87</v>
+        <v>2.16</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.63</v>
+        <v>9.09</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3416,20 +3390,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>77.2</v>
+        <v>76.8</v>
       </c>
       <c r="F14" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3438,12 +3412,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 125.04. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.79. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 77.2; priority 77.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.8; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3463,17 +3437,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.6%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 125.04 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 108.12 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 57.99 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3492,15 +3466,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>108.12</v>
+        <v>57.9933</v>
       </c>
       <c r="T14" t="n">
-        <v>125.04</v>
+        <v>63.79</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3514,16 +3488,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>12.65</v>
+        <v>11.23</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.78</v>
+        <v>21.44</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.19</v>
+        <v>12.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3534,69 +3508,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>124.08</v>
+        <v>63.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>81.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AK14" t="n">
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.99</v>
+        <v>1.82</v>
       </c>
       <c r="AM14" t="n">
-        <v>12.36</v>
+        <v>10.69</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.93</v>
+        <v>15.05</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AP14" t="n">
-        <v>120.9462</v>
+        <v>61.6633</v>
       </c>
       <c r="AQ14" t="n">
-        <v>113.3263</v>
+        <v>58.5344</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>81.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>66.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AV14" t="n">
         <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="AX14" t="n">
-        <v>120.73</v>
+        <v>61.4745</v>
       </c>
       <c r="AY14" t="n">
-        <v>125.04</v>
+        <v>63.79</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.49</v>
+        <v>8.19</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3622,20 +3596,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="F15" t="n">
-        <v>77.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3644,12 +3618,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.79. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 703.98. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 76.9; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.7; priority 77.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3664,22 +3638,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.5%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 57.28 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 608.66 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3698,15 +3672,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>57.2813</v>
+        <v>608.66</v>
       </c>
       <c r="T15" t="n">
-        <v>63.79</v>
+        <v>703.98</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3720,16 +3694,16 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>10.66</v>
+        <v>14.69</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.39</v>
+        <v>24.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.88</v>
+        <v>14.16</v>
       </c>
       <c r="AB15" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3740,51 +3714,51 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>63.79</v>
+        <v>696.42</v>
       </c>
       <c r="AH15" t="n">
-        <v>72.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>77.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AK15" t="n">
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.17</v>
+        <v>-0.18</v>
       </c>
       <c r="AM15" t="n">
-        <v>11.29</v>
+        <v>11.52</v>
       </c>
       <c r="AN15" t="n">
-        <v>15.34</v>
+        <v>18.73</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AP15" t="n">
-        <v>61.6106</v>
+        <v>682.8828</v>
       </c>
       <c r="AQ15" t="n">
-        <v>58.4865</v>
+        <v>636.9071</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>77.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>71.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AV15" t="n">
         <v>82.8</v>
@@ -3793,16 +3767,16 @@
         <v>761</v>
       </c>
       <c r="AX15" t="n">
-        <v>61.4745</v>
+        <v>681.24</v>
       </c>
       <c r="AY15" t="n">
-        <v>63.79</v>
+        <v>703.98</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.54</v>
+        <v>1.98</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.07</v>
+        <v>9.34</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3828,20 +3802,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>76.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>77.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3850,12 +3824,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.98. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 75.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 76.5; priority 77.2; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 75.1; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3875,17 +3849,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.3%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 600.12 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 67.67 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3904,20 +3878,20 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>600.12</v>
+        <v>67.67</v>
       </c>
       <c r="T16" t="n">
-        <v>703.98</v>
+        <v>75.94</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3926,16 +3900,16 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>13.75</v>
+        <v>12.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>25.01</v>
+        <v>22.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.17</v>
+        <v>12.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>-23.32</v>
+        <v>-20.6</v>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
@@ -3946,69 +3920,69 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>697.5599999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AH16" t="n">
-        <v>71.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>64.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AK16" t="n">
         <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.44</v>
+        <v>1.68</v>
       </c>
       <c r="AM16" t="n">
-        <v>12.12</v>
+        <v>11.37</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.82</v>
+        <v>15.86</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AP16" t="n">
-        <v>681.798</v>
+        <v>73.62820000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>636.3686</v>
+        <v>69.4346</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>64.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AX16" t="n">
-        <v>681.24</v>
+        <v>73.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>703.98</v>
+        <v>75.94</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.31</v>
+        <v>2.68</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.619999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4034,20 +4008,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>74.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4056,17 +4030,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 75.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 73.47. Trigger: prezzo 8.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 74.9; priority 76.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 81.6; priority 76.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4076,22 +4050,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 74.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 81.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.3%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 66.93 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.24 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4101,7 +4075,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4110,15 +4084,15 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>66.93000000000001</v>
+        <v>56.24</v>
       </c>
       <c r="T17" t="n">
-        <v>75.94</v>
+        <v>73.47</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -4132,89 +4106,89 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>10.92</v>
+        <v>30.87</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.26</v>
+        <v>66.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.88</v>
+        <v>13.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>-20.6</v>
+        <v>-17.8</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Quality globale</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>75.66</v>
+        <v>72.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>66.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>68.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>82.8</v>
+        <v>65.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.73</v>
+        <v>3.28</v>
       </c>
       <c r="AM17" t="n">
-        <v>11.82</v>
+        <v>38.94</v>
       </c>
       <c r="AN17" t="n">
-        <v>15.91</v>
+        <v>27.65</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="AP17" t="n">
-        <v>73.5318</v>
+        <v>67.2694</v>
       </c>
       <c r="AQ17" t="n">
-        <v>69.3764</v>
+        <v>56.499</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
         <v>85</v>
       </c>
       <c r="AT17" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="AU17" t="n">
-        <v>68.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>82.8</v>
+        <v>65.7</v>
       </c>
       <c r="AW17" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AX17" t="n">
-        <v>73.8</v>
+        <v>68.89</v>
       </c>
       <c r="AY17" t="n">
-        <v>75.94</v>
+        <v>73.47</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.89</v>
+        <v>8.27</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.06</v>
+        <v>28.9</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4240,24 +4214,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>78.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4266,17 +4236,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 6.9% sotto MA50: attendere recupero.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 19.164. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 78.6; priority 73.8; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 71.4; priority 73.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -4286,22 +4256,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>prezzo 6.9% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.9%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.7%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 287.39 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 13.44 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4311,158 +4281,136 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>287.3883</v>
+        <v>13.44</v>
       </c>
       <c r="T18" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+        <v>19.164</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>18.21</v>
+        <v>36.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>106.69</v>
+        <v>44.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>29.82</v>
+        <v>21.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>23.62</v>
-      </c>
+        <v>-29.37</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Robotica e automazione</t>
+        </is>
+      </c>
       <c r="AG18" t="n">
-        <v>343.71</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+        <v>18.288</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>76</v>
+      </c>
       <c r="AL18" t="n">
-        <v>-11.56</v>
+        <v>2</v>
       </c>
       <c r="AM18" t="n">
-        <v>11.1</v>
+        <v>32.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>43.3</v>
+        <v>19.77</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.45</v>
+        <v>0.91</v>
       </c>
       <c r="AP18" t="n">
-        <v>369.106</v>
+        <v>17.3019</v>
       </c>
       <c r="AQ18" t="n">
-        <v>313.0075</v>
+        <v>14.8131</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT18" t="n">
         <v>100</v>
       </c>
       <c r="AU18" t="n">
-        <v>40.4</v>
+        <v>50.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>69.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="AW18" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="AX18" t="n">
-        <v>343.71</v>
+        <v>17.092</v>
       </c>
       <c r="AY18" t="n">
-        <v>389.8971</v>
+        <v>19.164</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-6.88</v>
+        <v>5.7</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>4194146189312</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>64</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>69.40000000000001</v>
-      </c>
+        <v>23.46</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
       <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4472,20 +4420,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>78.5</v>
       </c>
       <c r="F19" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4494,12 +4446,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 73.47. Trigger: prezzo 9.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 8.6% sotto MA50: attendere recupero.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 81.0; priority 73.0; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 78.5; priority 73.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4509,27 +4461,27 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo 9.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 8.6% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 81.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.3%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.6%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 54.81 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 295.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4544,131 +4496,153 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>54.81</v>
+        <v>295.5934</v>
       </c>
       <c r="T19" t="n">
-        <v>73.47</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>30.41</v>
+        <v>20.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>69.15000000000001</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.87</v>
+        <v>29.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>23.18</v>
+      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>Value globale</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
-        <v>73.23999999999999</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>61.4</v>
-      </c>
+        <v>337.39</v>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>4.78</v>
+        <v>-13.18</v>
       </c>
       <c r="AM19" t="n">
-        <v>40.63</v>
+        <v>7.47</v>
       </c>
       <c r="AN19" t="n">
-        <v>27.93</v>
+        <v>42.42</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.01</v>
+        <v>1.42</v>
       </c>
       <c r="AP19" t="n">
-        <v>66.9888</v>
+        <v>369.1154</v>
       </c>
       <c r="AQ19" t="n">
-        <v>56.3684</v>
+        <v>313.4987</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT19" t="n">
         <v>100</v>
       </c>
       <c r="AU19" t="n">
-        <v>69.09999999999999</v>
+        <v>40.3</v>
       </c>
       <c r="AV19" t="n">
-        <v>61.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="AX19" t="n">
-        <v>68.89</v>
+        <v>337.39</v>
       </c>
       <c r="AY19" t="n">
-        <v>73.47</v>
+        <v>380.1129</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9.33</v>
+        <v>-8.59</v>
       </c>
       <c r="BA19" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="inlineStr"/>
-      <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="inlineStr"/>
+        <v>7.62</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>4117026308096</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>66.90000000000001</v>
+      </c>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4688,10 +4662,10 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>70.5</v>
+        <v>70.8</v>
       </c>
       <c r="F20" t="n">
-        <v>72.5</v>
+        <v>72.8</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4700,12 +4674,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 64.7. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.85. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 70.5; priority 72.5; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 70.8; priority 72.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4725,12 +4699,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.5, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.6%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.70 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -4757,7 +4731,7 @@
         <v>62.06</v>
       </c>
       <c r="T20" t="n">
-        <v>64.7</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
@@ -4776,13 +4750,13 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.53</v>
+        <v>3.96</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AB20" t="n">
         <v>-12.85</v>
@@ -4800,13 +4774,13 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>64.54000000000001</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AH20" t="n">
-        <v>63.1</v>
+        <v>63.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>55.7</v>
+        <v>56.5</v>
       </c>
       <c r="AJ20" t="n">
         <v>78.2</v>
@@ -4815,29 +4789,29 @@
         <v>82.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="AM20" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="AN20" t="n">
-        <v>7.51</v>
+        <v>7.67</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.495</v>
+        <v>63.5298</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.1648</v>
+        <v>63.1763</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
         <v>85</v>
       </c>
       <c r="AT20" t="n">
-        <v>55.7</v>
+        <v>56.5</v>
       </c>
       <c r="AU20" t="n">
         <v>78.2</v>
@@ -4846,19 +4820,19 @@
         <v>82.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AX20" t="n">
         <v>63.44</v>
       </c>
       <c r="AY20" t="n">
-        <v>64.7</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -4884,20 +4858,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>70.2</v>
+        <v>71.3</v>
       </c>
       <c r="F21" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4906,12 +4884,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 19.164. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 70.2; priority 69.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 71.3; priority 69.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4931,17 +4909,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.9%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 71.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.6%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 12.94 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 253.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4956,131 +4934,153 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>12.936</v>
+        <v>253.2667</v>
       </c>
       <c r="T21" t="n">
-        <v>19.164</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>35.85</v>
+        <v>12.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>49.45</v>
+        <v>41.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.66</v>
+        <v>26.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>-29.37</v>
-      </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>29.53</v>
+      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>Robotica e automazione</t>
-        </is>
-      </c>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>18.592</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>53</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>67.3</v>
-      </c>
+        <v>283.78</v>
+      </c>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>4.86</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="AM21" t="n">
-        <v>35.95</v>
+        <v>4.39</v>
       </c>
       <c r="AN21" t="n">
-        <v>20.46</v>
+        <v>15.3</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="AP21" t="n">
-        <v>17.2374</v>
+        <v>291.4116</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.7864</v>
+        <v>269.0755</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>753</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>4167977926656</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>39</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>100</v>
       </c>
-      <c r="AU21" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>757</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>17.092</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>19.164</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>25.74</v>
-      </c>
-      <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
-      <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr"/>
-      <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="inlineStr"/>
-      <c r="BL21" t="inlineStr"/>
-      <c r="BM21" t="inlineStr"/>
-      <c r="BN21" t="inlineStr"/>
+      <c r="BK21" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>75.8</v>
+      </c>
       <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>52.8</v>
+        <v>55.2</v>
       </c>
       <c r="F22" t="n">
-        <v>54.1</v>
+        <v>56.9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 52.8; priority 54.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 55.2; priority 56.9; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 8.5% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Avoid for Now, score 52.8, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.5%.</t>
+          <t>SGLD.MI: scenario base Hold / Monitor, score 55.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5184,14 +5184,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Evitare per ora</t>
+          <t>Osservare</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-10.18</v>
+        <v>-6.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.32</v>
+        <v>25.33</v>
       </c>
       <c r="AA22" t="n">
         <v>18.18</v>
@@ -5212,65 +5212,65 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>339.98</v>
+        <v>344.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>66.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>37.8</v>
+        <v>45.7</v>
       </c>
       <c r="AJ22" t="n">
         <v>60.4</v>
       </c>
       <c r="AK22" t="n">
-        <v>62.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AL22" t="n">
-        <v>-7.38</v>
+        <v>-6.94</v>
       </c>
       <c r="AM22" t="n">
-        <v>-5.11</v>
+        <v>-3.59</v>
       </c>
       <c r="AN22" t="n">
-        <v>25.82</v>
+        <v>26.3</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AP22" t="n">
-        <v>371.4308</v>
+        <v>370.4684</v>
       </c>
       <c r="AQ22" t="n">
-        <v>366.1597</v>
+        <v>366.4099</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>37.8</v>
+        <v>45.7</v>
       </c>
       <c r="AU22" t="n">
         <v>60.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>62.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AX22" t="n">
         <v>339.65</v>
       </c>
       <c r="AY22" t="n">
-        <v>377.2</v>
+        <v>372.59</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-8.470000000000001</v>
+        <v>-7.07</v>
       </c>
       <c r="BA22" t="n">
-        <v>-7.15</v>
+        <v>-6.04</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>61.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>59.1</v>
+        <v>66</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,12 +797,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 61.5; priority 59.1; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 67.1; priority 66.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 9.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 61.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 67.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.2%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -864,81 +864,81 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>12.12</v>
+        <v>20.47</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.76</v>
+        <v>10.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.21</v>
+        <v>31.28</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>32.45</v>
+        <v>32.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.55</v>
+        <v>24.3</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>232.69</v>
+        <v>240.14</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-14.41</v>
+        <v>-12.36</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.24</v>
+        <v>3.34</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.77</v>
+        <v>22.75</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP2" t="n">
-        <v>256.1288</v>
+        <v>255.9376</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.7676</v>
+        <v>232.8167</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>69.5</v>
+        <v>83.3</v>
       </c>
       <c r="AU2" t="n">
         <v>37.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>61.5</v>
+        <v>70.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX2" t="n">
         <v>227.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>270.64</v>
+        <v>261.26</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-9.15</v>
+        <v>-6.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.03</v>
+        <v>3.15</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2503072022528</v>
+        <v>2583212326912</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>69.5</v>
+        <v>83.3</v>
       </c>
       <c r="BL2" t="n">
-        <v>56.9</v>
+        <v>55.5</v>
       </c>
       <c r="BM2" t="n">
         <v>37.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>61.5</v>
+        <v>70.5</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="F3" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 62.0; priority 54.7; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 62.2; priority 54.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 9.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 10.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.0, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -9.2%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.0%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>2.13</v>
+        <v>3.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>-23.63</v>
+        <v>-25.32</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.38</v>
+        <v>24.4</v>
       </c>
       <c r="AB3" t="n">
         <v>-34.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.21</v>
+        <v>21.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.26</v>
+        <v>19.03</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1118,45 +1118,45 @@
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>372.97</v>
+        <v>368.57</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-9.619999999999999</v>
+        <v>-13.68</v>
       </c>
       <c r="AM3" t="n">
-        <v>-23.05</v>
+        <v>-24.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.52</v>
+        <v>3.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="AP3" t="n">
-        <v>410.522</v>
+        <v>409.5063</v>
       </c>
       <c r="AQ3" t="n">
-        <v>446.2723</v>
+        <v>445.629</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
         <v>35</v>
       </c>
       <c r="AT3" t="n">
-        <v>33.2</v>
+        <v>34.1</v>
       </c>
       <c r="AU3" t="n">
         <v>43.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>61.5</v>
+        <v>60.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX3" t="n">
         <v>352.83</v>
@@ -1165,10 +1165,10 @@
         <v>460.52</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-9.15</v>
+        <v>-10</v>
       </c>
       <c r="BA3" t="n">
-        <v>-16.43</v>
+        <v>-17.29</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2770583420928</v>
+        <v>2737898258432</v>
       </c>
       <c r="BE3" t="n">
         <v>39.34</v>
@@ -1196,22 +1196,22 @@
         <v>30.27</v>
       </c>
       <c r="BI3" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="BJ3" t="n">
         <v>100</v>
       </c>
       <c r="BK3" t="n">
-        <v>33.2</v>
+        <v>34.1</v>
       </c>
       <c r="BL3" t="n">
-        <v>74.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="BM3" t="n">
         <v>43.1</v>
       </c>
       <c r="BN3" t="n">
-        <v>61.5</v>
+        <v>60.3</v>
       </c>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr">
@@ -1228,20 +1228,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>66.8</v>
+        <v>57.1</v>
       </c>
       <c r="F4" t="n">
-        <v>52.3</v>
+        <v>50.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 66.8; priority 52.3; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 57.1; priority 50.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1270,22 +1270,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 6.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 66.8, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 57.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.1%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 391.97 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1300,19 +1300,19 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>391.97</v>
+        <v>8.7643</v>
       </c>
       <c r="T4" t="n">
-        <v>668.91</v>
+        <v>11.61</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1326,16 +1326,16 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>60.59</v>
+        <v>10.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>122.93</v>
+        <v>55.77</v>
       </c>
       <c r="AA4" t="n">
-        <v>35.73</v>
+        <v>23.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>-35.74</v>
+        <v>-43.36</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
@@ -1346,69 +1346,69 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>611.61</v>
+        <v>9.863</v>
       </c>
       <c r="AH4" t="n">
-        <v>57.3</v>
+        <v>30.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23.5</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>66.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.71</v>
+        <v>-14.61</v>
       </c>
       <c r="AM4" t="n">
-        <v>68.41</v>
+        <v>21.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.24</v>
+        <v>2.46</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.69</v>
+        <v>0.1</v>
       </c>
       <c r="AP4" t="n">
-        <v>566.444</v>
+        <v>10.4994</v>
       </c>
       <c r="AQ4" t="n">
-        <v>419.2983</v>
+        <v>8.9855</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>28.5</v>
+        <v>37</v>
       </c>
       <c r="AV4" t="n">
-        <v>66.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AX4" t="n">
-        <v>569.6900000000001</v>
+        <v>9.863</v>
       </c>
       <c r="AY4" t="n">
-        <v>668.91</v>
+        <v>11.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.97</v>
+        <v>-6.06</v>
       </c>
       <c r="BA4" t="n">
-        <v>45.87</v>
+        <v>9.77</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1434,20 +1434,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>57.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>51.5</v>
+        <v>43.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1461,12 +1465,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 57.9; priority 51.5; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 64.1; priority 43.8; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1476,22 +1480,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 4.9% sotto MA50: attendere recupero</t>
+          <t>prezzo 7.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 57.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.9%.</t>
+          <t>META: scenario base Hold / Monitor, score 64.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.8%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1506,131 +1510,153 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>8.7643</v>
+        <v>542.87</v>
       </c>
       <c r="T5" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>687.9124</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>9.91</v>
+        <v>7.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>57.5</v>
+        <v>-22.26</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.58</v>
+        <v>36.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>-43.36</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+        <v>-34.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15.52</v>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Energia pulita</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>72.40000000000001</v>
-      </c>
+        <v>562.6</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-13.19</v>
+        <v>-11.36</v>
       </c>
       <c r="AM5" t="n">
-        <v>23.33</v>
+        <v>-15.57</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.96</v>
+        <v>25.71</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.13</v>
+        <v>0.71</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.491</v>
+        <v>610.1527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.9716</v>
+        <v>647.9298</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AT5" t="n">
-        <v>92.3</v>
+        <v>45.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>37</v>
+        <v>28.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>72.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.914999999999999</v>
+        <v>542.87</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.61</v>
+        <v>626.9888999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-4.87</v>
+        <v>-7.79</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>-13.17</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>1428116865024</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>63.6</v>
+      </c>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>USA / Social &amp; AI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1640,24 +1666,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>69.2</v>
+        <v>65.2</v>
       </c>
       <c r="F6" t="n">
-        <v>49.3</v>
+        <v>43.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1671,7 +1693,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 69.2; priority 49.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 65.2; priority 43.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1686,22 +1708,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 8.3% sotto MA50: attendere recupero</t>
+          <t>prezzo 10.9% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NVDA: scenario base Accumulate Carefully, score 69.2, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.3%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 65.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.9%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 175.55 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 392.32 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1711,158 +1733,136 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>175.5454</v>
+        <v>392.32</v>
       </c>
       <c r="T6" t="n">
-        <v>235.4656</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+        <v>668.91</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>12.56</v>
+        <v>68.87</v>
       </c>
       <c r="Z6" t="n">
-        <v>24.93</v>
+        <v>128.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>46.92</v>
+        <v>35.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>-36.88</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>29.44</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>15.13</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG6" t="n">
-        <v>192.53</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+        <v>631.98</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>55.2</v>
+      </c>
       <c r="AL6" t="n">
-        <v>-9.33</v>
+        <v>5.36</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.88</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>66.73</v>
+        <v>61.95</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AP6" t="n">
-        <v>209.9179</v>
+        <v>569.9876</v>
       </c>
       <c r="AQ6" t="n">
-        <v>190.428</v>
+        <v>420.9587</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AU6" t="n">
-        <v>14.2</v>
+        <v>28.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>67.3</v>
+        <v>55.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX6" t="n">
-        <v>192.53</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>224.0988</v>
+        <v>668.91</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-8.279999999999999</v>
+        <v>10.88</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>4663269130240</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>114.29</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>51</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>75</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>67.3</v>
-      </c>
+        <v>50.13</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>USA / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1872,24 +1872,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>61.4</v>
+        <v>49.2</v>
       </c>
       <c r="F7" t="n">
-        <v>40.2</v>
+        <v>39.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1903,12 +1899,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 61.4; priority 40.2; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 49.2; priority 39.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1918,22 +1914,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo 10.2% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 61.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.2%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 49.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.7%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1943,158 +1939,136 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>542.87</v>
+        <v>20.205</v>
       </c>
       <c r="T7" t="n">
-        <v>687.9124</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+        <v>30.11</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>0.59</v>
+        <v>20.54</v>
       </c>
       <c r="Z7" t="n">
-        <v>-22.1</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>36.42</v>
+        <v>34.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15.18</v>
-      </c>
+        <v>-48.6</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
       <c r="AG7" t="n">
-        <v>550.25</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+        <v>27.145</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>68.09999999999999</v>
+      </c>
       <c r="AL7" t="n">
-        <v>-13.3</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>-17.1</v>
+        <v>-10.03</v>
       </c>
       <c r="AN7" t="n">
-        <v>24.69</v>
+        <v>-1.69</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.68</v>
+        <v>-0.05</v>
       </c>
       <c r="AP7" t="n">
-        <v>612.4256</v>
+        <v>25.214</v>
       </c>
       <c r="AQ7" t="n">
-        <v>648.8645</v>
+        <v>26.7012</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT7" t="n">
-        <v>35</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>29</v>
+        <v>20.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>60</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="AX7" t="n">
-        <v>542.87</v>
+        <v>24.785</v>
       </c>
       <c r="AY7" t="n">
-        <v>631.9243</v>
+        <v>29.005</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-10.15</v>
+        <v>7.66</v>
       </c>
       <c r="BA7" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>1396767457280</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>39</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>35</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>60</v>
-      </c>
+        <v>1.66</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2104,20 +2078,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E8" t="n">
-        <v>41.7</v>
+        <v>43.4</v>
       </c>
       <c r="F8" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2131,7 +2109,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 41.7; priority 37.3; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 43.4; priority 37.1; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2151,17 +2129,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 41.7, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.4%.</t>
+          <t>TSLA: scenario base High Risk, score 43.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2180,127 +2158,147 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>20.205</v>
+        <v>343.25</v>
       </c>
       <c r="T8" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>11.27</v>
+        <v>13.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.41</v>
+        <v>26.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>35.89</v>
+        <v>58</v>
       </c>
       <c r="AB8" t="n">
-        <v>-48.6</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>164.6</v>
+      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>26.055</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>78.2</v>
-      </c>
+        <v>411.84</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>1.26</v>
+        <v>-6.84</v>
       </c>
       <c r="AM8" t="n">
-        <v>-12.39</v>
+        <v>-15.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>-2.07</v>
+        <v>16.42</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.06</v>
+        <v>0.28</v>
       </c>
       <c r="AP8" t="n">
-        <v>25.1883</v>
+        <v>405.2238</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.7331</v>
+        <v>418.285</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
         <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>55</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
         <v>78.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="AX8" t="n">
-        <v>24.785</v>
+        <v>375.12</v>
       </c>
       <c r="AY8" t="n">
-        <v>30.11</v>
+        <v>423.74</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.44</v>
+        <v>1.63</v>
       </c>
       <c r="BA8" t="n">
-        <v>-2.54</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+        <v>-1.54</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>1546757210112</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
+      <c r="BJ8" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>78.2</v>
+      </c>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2324,10 +2322,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>63.1</v>
       </c>
       <c r="F9" t="n">
-        <v>35.7</v>
+        <v>30.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2341,7 +2339,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 64.0; priority 35.7; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 63.1; priority 30.3; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2356,12 +2354,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 12.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 14.7% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 64.0, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 12.9%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.7%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2408,22 +2406,22 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>35.67</v>
+        <v>40.93</v>
       </c>
       <c r="Z9" t="n">
-        <v>138.07</v>
+        <v>139.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>38.39</v>
+        <v>38.44</v>
       </c>
       <c r="AB9" t="n">
         <v>-44.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>61.12</v>
+        <v>62.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>37.51</v>
+        <v>38</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2432,29 +2430,29 @@
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>1578.2</v>
+        <v>1612</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>13.46</v>
+        <v>16.41</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.17</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>35.17</v>
+        <v>34.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AP9" t="n">
-        <v>1398.0824</v>
+        <v>1405.4973</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1114.1671</v>
+        <v>1118.7963</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
@@ -2467,22 +2465,22 @@
         <v>18.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>47.2</v>
+        <v>40</v>
       </c>
       <c r="AW9" t="n">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AX9" t="n">
-        <v>1394</v>
+        <v>1461.8</v>
       </c>
       <c r="AY9" t="n">
         <v>1676</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.88</v>
+        <v>14.69</v>
       </c>
       <c r="BA9" t="n">
-        <v>41.65</v>
+        <v>44.08</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -2495,7 +2493,7 @@
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>608266158080</v>
+        <v>621293273088</v>
       </c>
       <c r="BE9" t="n">
         <v>29.71</v>
@@ -2519,13 +2517,13 @@
         <v>100</v>
       </c>
       <c r="BL9" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="BM9" t="n">
         <v>18.1</v>
       </c>
       <c r="BN9" t="n">
-        <v>47.2</v>
+        <v>40</v>
       </c>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
@@ -2537,73 +2535,69 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. Rischio da controllare</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>35.4</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>81.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🟥 Riduci rischio / non aumentare</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Non aumentare esposizione: controlla peso in portafoglio, stop mentale e correlazione con posizioni simili.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 35.4; priority 27.0; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 80.6; priority 81.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 35.4, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -6.2%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 39.95 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2613,156 +2607,136 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>343.25</v>
+        <v>39.955</v>
       </c>
       <c r="T10" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+        <v>50.73</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Priorità watchlist</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>2.04</v>
+        <v>21.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.92</v>
+        <v>42.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>57.74</v>
+        <v>16.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>348.36</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>151.76</v>
-      </c>
+        <v>-19.17</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Mercati emergenti</t>
+        </is>
+      </c>
       <c r="AG10" t="n">
-        <v>379.71</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+        <v>47.74</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL10" t="n">
-        <v>-13.77</v>
+        <v>-0.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>-21.8</v>
+        <v>26.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.98</v>
+        <v>20.03</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.26</v>
+        <v>1.22</v>
       </c>
       <c r="AP10" t="n">
-        <v>404.765</v>
+        <v>46.8593</v>
       </c>
       <c r="AQ10" t="n">
-        <v>417.9647</v>
+        <v>41.3092</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT10" t="n">
-        <v>43.8</v>
+        <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>66</v>
+        <v>82.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AX10" t="n">
-        <v>375.12</v>
+        <v>45.945</v>
       </c>
       <c r="AY10" t="n">
-        <v>435.79</v>
+        <v>50.73</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-6.19</v>
+        <v>1.88</v>
       </c>
       <c r="BA10" t="n">
-        <v>-9.15</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>1426085904384</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>18.74</v>
-      </c>
+        <v>15.57</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>66</v>
-      </c>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>USA / EV</t>
-        </is>
-      </c>
+      <c r="BP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2772,20 +2746,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>80.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2799,7 +2773,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 80.7; priority 81.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 82.6; priority 81.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2819,17 +2793,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.9%.</t>
+          <t>XDEV.MI: scenario base Buy Watchlist, score 82.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.95 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 56.24 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2848,20 +2822,20 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>39.955</v>
+        <v>56.24</v>
       </c>
       <c r="T11" t="n">
-        <v>50.73</v>
+        <v>73.47</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2870,16 +2844,16 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>21.2</v>
+        <v>29.64</v>
       </c>
       <c r="Z11" t="n">
-        <v>43.55</v>
+        <v>63.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.43</v>
+        <v>13.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>-19.17</v>
+        <v>-17.8</v>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
@@ -2890,41 +2864,41 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>48.16</v>
+        <v>71.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>70.3</v>
+        <v>78.7</v>
       </c>
       <c r="AI11" t="n">
         <v>100</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AK11" t="n">
-        <v>82.8</v>
+        <v>75.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.43</v>
+        <v>0.61</v>
       </c>
       <c r="AM11" t="n">
-        <v>27.44</v>
+        <v>36.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.37</v>
+        <v>26.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="AP11" t="n">
-        <v>46.792</v>
+        <v>67.505</v>
       </c>
       <c r="AQ11" t="n">
-        <v>41.2472</v>
+        <v>56.6218</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
@@ -2934,25 +2908,25 @@
         <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AV11" t="n">
-        <v>82.8</v>
+        <v>75.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AX11" t="n">
-        <v>45.945</v>
+        <v>68.89</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.73</v>
+        <v>73.47</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.92</v>
+        <v>5.76</v>
       </c>
       <c r="BA11" t="n">
-        <v>16.76</v>
+        <v>26.08</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2988,10 +2962,10 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="F12" t="n">
-        <v>78.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3005,7 +2979,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>score 78.4; priority 78.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 78.7; priority 79.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3025,7 +2999,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>VWCE.DE: scenario base Buy Watchlist, score 78.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.4%.</t>
+          <t>VWCE.DE: scenario base Buy Watchlist, score 78.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -3076,13 +3050,13 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>14.51</v>
+        <v>15.93</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.82</v>
+        <v>26.54</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.93</v>
+        <v>12.94</v>
       </c>
       <c r="AB12" t="n">
         <v>-21.07</v>
@@ -3100,13 +3074,13 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>163.7</v>
+        <v>163.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>73.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>85.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AJ12" t="n">
         <v>67.59999999999999</v>
@@ -3115,29 +3089,29 @@
         <v>82.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.54</v>
+        <v>0.17</v>
       </c>
       <c r="AM12" t="n">
-        <v>13.54</v>
+        <v>13.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.1</v>
+        <v>17.65</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP12" t="n">
-        <v>159.8616</v>
+        <v>160.0572</v>
       </c>
       <c r="AQ12" t="n">
-        <v>148.5673</v>
+        <v>148.7023</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>85</v>
       </c>
       <c r="AT12" t="n">
-        <v>85.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AU12" t="n">
         <v>67.59999999999999</v>
@@ -3146,7 +3120,7 @@
         <v>82.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AX12" t="n">
         <v>159.24</v>
@@ -3155,10 +3129,10 @@
         <v>166.04</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.19</v>
+        <v>9.91</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -3179,7 +3153,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3194,24 +3168,24 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>77.8</v>
+        <v>78.3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 125.04. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>score 77.2; priority 77.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.6; priority 78.3; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3226,12 +3200,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
+          <t>SWDA.MI: scenario base Accumulate Carefully, score 77.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.2%.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3282,13 +3256,13 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>13.52</v>
+        <v>15.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>24.26</v>
+        <v>24.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="AB13" t="n">
         <v>-21.63</v>
@@ -3306,13 +3280,13 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>123.73</v>
+        <v>123.88</v>
       </c>
       <c r="AH13" t="n">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AI13" t="n">
-        <v>81.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="AJ13" t="n">
         <v>66.90000000000001</v>
@@ -3321,29 +3295,29 @@
         <v>82.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="AM13" t="n">
-        <v>11.52</v>
+        <v>11.42</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.8</v>
+        <v>17.41</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>121.1144</v>
+        <v>121.2584</v>
       </c>
       <c r="AQ13" t="n">
-        <v>113.4222</v>
+        <v>113.5156</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
         <v>85</v>
       </c>
       <c r="AT13" t="n">
-        <v>81.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="AU13" t="n">
         <v>66.90000000000001</v>
@@ -3352,7 +3326,7 @@
         <v>82.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AX13" t="n">
         <v>120.73</v>
@@ -3364,7 +3338,7 @@
         <v>2.16</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.09</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3385,39 +3359,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>1. Da guardare oggi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>76.8</v>
+        <v>77.2</v>
       </c>
       <c r="F14" t="n">
-        <v>77.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟢 Valuta ingresso graduale</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 63.79. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>score 76.8; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.2; priority 78.1; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3437,17 +3411,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>EXSA.DE: scenario base Accumulate Carefully, score 76.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>SXR8.DE: scenario base Accumulate Carefully, score 77.2, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 57.99 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 608.66 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3466,15 +3440,15 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>57.9933</v>
+        <v>608.66</v>
       </c>
       <c r="T14" t="n">
-        <v>63.79</v>
+        <v>703.98</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3488,16 +3462,16 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>11.23</v>
+        <v>16.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.44</v>
+        <v>24.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.88</v>
+        <v>14.16</v>
       </c>
       <c r="AB14" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -3508,69 +3482,69 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>63.33</v>
+        <v>697.76</v>
       </c>
       <c r="AH14" t="n">
-        <v>71.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>77.5</v>
+        <v>86.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="AK14" t="n">
         <v>82.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.82</v>
+        <v>-0.16</v>
       </c>
       <c r="AM14" t="n">
-        <v>10.69</v>
+        <v>11.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>15.05</v>
+        <v>18.33</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AP14" t="n">
-        <v>61.6633</v>
+        <v>683.85</v>
       </c>
       <c r="AQ14" t="n">
-        <v>58.5344</v>
+        <v>637.4372</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
         <v>85</v>
       </c>
       <c r="AT14" t="n">
-        <v>77.5</v>
+        <v>86.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>71.5</v>
+        <v>64.3</v>
       </c>
       <c r="AV14" t="n">
         <v>82.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="AX14" t="n">
-        <v>61.4745</v>
+        <v>681.24</v>
       </c>
       <c r="AY14" t="n">
-        <v>63.79</v>
+        <v>703.98</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.19</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
@@ -3596,20 +3570,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>76.7</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>77.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3618,12 +3592,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 703.98. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 63.79. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>score 76.7; priority 77.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 77.0; priority 77.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3638,22 +3612,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SXR8.DE: scenario base Accumulate Carefully, score 76.7, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.0%.</t>
+          <t>EXSA.DE: scenario base Accumulate Carefully, score 77.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 703.98 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 63.79 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 608.66 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 57.99 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3672,15 +3646,15 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>608.66</v>
+        <v>57.9933</v>
       </c>
       <c r="T15" t="n">
-        <v>703.98</v>
+        <v>63.79</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3694,16 +3668,16 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>14.69</v>
+        <v>12.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>24.65</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>14.16</v>
+        <v>12.89</v>
       </c>
       <c r="AB15" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -3714,69 +3688,69 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>696.42</v>
+        <v>63.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>70.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AI15" t="n">
-        <v>83.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AJ15" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AK15" t="n">
         <v>82.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.18</v>
+        <v>1.84</v>
       </c>
       <c r="AM15" t="n">
-        <v>11.52</v>
+        <v>10.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.73</v>
+        <v>14.77</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AP15" t="n">
-        <v>682.8828</v>
+        <v>61.6973</v>
       </c>
       <c r="AQ15" t="n">
-        <v>636.9071</v>
+        <v>58.5823</v>
       </c>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
         <v>85</v>
       </c>
       <c r="AT15" t="n">
-        <v>83.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>64.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AV15" t="n">
         <v>82.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AX15" t="n">
-        <v>681.24</v>
+        <v>61.4745</v>
       </c>
       <c r="AY15" t="n">
-        <v>703.98</v>
+        <v>63.79</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.34</v>
+        <v>8.16</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
@@ -3812,10 +3786,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>75.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="F16" t="n">
-        <v>76.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3824,12 +3798,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 75.94. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 76.14. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>score 75.1; priority 76.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 76.0; priority 77.6; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3849,12 +3823,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>IWQU.MI: scenario base Accumulate Carefully, score 75.1, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.7%.</t>
+          <t>IWQU.MI: scenario base Accumulate Carefully, score 76.0, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 3.3%.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 75.94 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 76.14 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -3881,7 +3855,7 @@
         <v>67.67</v>
       </c>
       <c r="T16" t="n">
-        <v>75.94</v>
+        <v>76.14</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
@@ -3900,13 +3874,13 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>12.1</v>
+        <v>14.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>22.25</v>
+        <v>23.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="AB16" t="n">
         <v>-20.6</v>
@@ -3924,13 +3898,13 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>75.59999999999999</v>
+        <v>76.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>66.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.3</v>
+        <v>83</v>
       </c>
       <c r="AJ16" t="n">
         <v>68.09999999999999</v>
@@ -3939,29 +3913,29 @@
         <v>82.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.68</v>
+        <v>2.59</v>
       </c>
       <c r="AM16" t="n">
-        <v>11.37</v>
+        <v>11.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>15.86</v>
+        <v>15.64</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AP16" t="n">
-        <v>73.62820000000001</v>
+        <v>73.721</v>
       </c>
       <c r="AQ16" t="n">
-        <v>69.4346</v>
+        <v>69.4943</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
         <v>85</v>
       </c>
       <c r="AT16" t="n">
-        <v>79.3</v>
+        <v>83</v>
       </c>
       <c r="AU16" t="n">
         <v>68.09999999999999</v>
@@ -3970,19 +3944,19 @@
         <v>82.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AX16" t="n">
         <v>73.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>75.94</v>
+        <v>76.14</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.68</v>
+        <v>3.28</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
@@ -4008,20 +3982,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>81.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>76.2</v>
+        <v>74.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4030,12 +4008,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 73.47. Trigger: prezzo 8.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 4.3% sotto MA50: attendere recupero.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>score 81.6; priority 76.2; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Normal risk</t>
+          <t>score 78.6; priority 74.7; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4045,27 +4023,27 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>prezzo 8.3% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
+          <t>prezzo 4.3% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 81.6, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.3%.</t>
+          <t>GOOGL: scenario base Buy Watchlist, score 78.6, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -4.3%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.24 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 295.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4080,131 +4058,153 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>56.24</v>
+        <v>295.5934</v>
       </c>
       <c r="T17" t="n">
-        <v>73.47</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
+        <v>402.3797</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>30.87</v>
+        <v>28.99</v>
       </c>
       <c r="Z17" t="n">
-        <v>66.22</v>
+        <v>104.37</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.87</v>
+        <v>29.99</v>
       </c>
       <c r="AB17" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+        <v>-29.81</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>24.3</v>
+      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>Value globale</t>
-        </is>
-      </c>
+          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
-        <v>72.83</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>65.7</v>
-      </c>
+        <v>353.65</v>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>3.28</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AM17" t="n">
-        <v>38.94</v>
+        <v>12.74</v>
       </c>
       <c r="AN17" t="n">
-        <v>27.65</v>
+        <v>44.26</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="AP17" t="n">
-        <v>67.2694</v>
+        <v>369.472</v>
       </c>
       <c r="AQ17" t="n">
-        <v>56.499</v>
+        <v>314.0734</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT17" t="n">
         <v>100</v>
       </c>
       <c r="AU17" t="n">
-        <v>69.09999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>65.7</v>
+        <v>73.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="AX17" t="n">
-        <v>68.89</v>
+        <v>337.39</v>
       </c>
       <c r="AY17" t="n">
-        <v>73.47</v>
+        <v>376.1453</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8.27</v>
+        <v>-4.28</v>
       </c>
       <c r="BA17" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="inlineStr"/>
-      <c r="BM17" t="inlineStr"/>
-      <c r="BN17" t="inlineStr"/>
+        <v>12.6</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>4315439693824</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>73.3</v>
+      </c>
       <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>USA / Internet</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4224,10 +4224,10 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>73.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>score 71.4; priority 73.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
+          <t>score 70.9; priority 72.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>RBOT.MI: scenario base Accumulate Carefully, score 71.4, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.7%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 70.9, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 6.2%.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4312,13 +4312,13 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>36.5</v>
+        <v>41.53</v>
       </c>
       <c r="Z18" t="n">
-        <v>44.5</v>
+        <v>45.64</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.67</v>
+        <v>21.68</v>
       </c>
       <c r="AB18" t="n">
         <v>-29.37</v>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>18.288</v>
+        <v>18.444</v>
       </c>
       <c r="AH18" t="n">
-        <v>52.4</v>
+        <v>52</v>
       </c>
       <c r="AI18" t="n">
         <v>100</v>
@@ -4348,25 +4348,25 @@
         <v>45.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>76</v>
+        <v>73.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>32.62</v>
+        <v>32.73</v>
       </c>
       <c r="AN18" t="n">
-        <v>19.77</v>
+        <v>19.37</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="AP18" t="n">
-        <v>17.3019</v>
+        <v>17.3626</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.8131</v>
+        <v>14.8396</v>
       </c>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
@@ -4379,10 +4379,10 @@
         <v>50.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>76</v>
+        <v>73.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AX18" t="n">
         <v>17.092</v>
@@ -4391,10 +4391,10 @@
         <v>19.164</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.7</v>
+        <v>6.23</v>
       </c>
       <c r="BA18" t="n">
-        <v>23.46</v>
+        <v>24.29</v>
       </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
@@ -4420,24 +4420,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>78.5</v>
+        <v>70.8</v>
       </c>
       <c r="F19" t="n">
-        <v>73.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4446,42 +4442,42 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 402.3797. Trigger: prezzo 8.6% sotto MA50: attendere recupero.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 64.85. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>score 78.5; priority 73.1; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 70.8; priority 72.9; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Constructive entry zone</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>Normal risk</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>prezzo 8.6% sotto MA50: attendere recupero</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>GOOGL: scenario base Buy Watchlist, score 78.5, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -8.6%.</t>
+          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.8%.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 402.38 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 64.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 295.59 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4491,158 +4487,136 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>295.5934</v>
+        <v>62.06</v>
       </c>
       <c r="T19" t="n">
-        <v>402.3797</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+        <v>64.84999999999999</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ridurre size / solo monitoraggio</t>
+          <t>Monitorare ingresso graduale</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>20.17</v>
+        <v>2.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>98.23999999999999</v>
+        <v>4.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>29.84</v>
+        <v>9.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>-29.81</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>23.18</v>
-      </c>
+        <v>-12.85</v>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Titolo forte; resta necessario controllare prezzo, trimestrali e size.</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Min volatility</t>
+        </is>
+      </c>
       <c r="AG19" t="n">
-        <v>337.39</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
+        <v>64.7</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>82.8</v>
+      </c>
       <c r="AL19" t="n">
-        <v>-13.18</v>
+        <v>1.87</v>
       </c>
       <c r="AM19" t="n">
-        <v>7.47</v>
+        <v>3.9</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.42</v>
+        <v>7.33</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.42</v>
+        <v>0.77</v>
       </c>
       <c r="AP19" t="n">
-        <v>369.1154</v>
+        <v>63.5588</v>
       </c>
       <c r="AQ19" t="n">
-        <v>313.4987</v>
+        <v>63.1877</v>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT19" t="n">
-        <v>100</v>
+        <v>57.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>40.3</v>
+        <v>78.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>66.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AX19" t="n">
-        <v>337.39</v>
+        <v>63.44</v>
       </c>
       <c r="AY19" t="n">
-        <v>380.1129</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-8.59</v>
+        <v>1.8</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>4117026308096</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>66.90000000000001</v>
-      </c>
+        <v>2.39</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>USA / Internet</t>
-        </is>
-      </c>
+      <c r="BP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4652,20 +4626,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MVOL.MI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>70.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>72.8</v>
+        <v>69.2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4674,42 +4652,42 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 64.85. Trigger: prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi.</t>
+          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>score 70.8; priority 72.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 71.4; priority 69.2; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVOL.MI: scenario base Accumulate Carefully, score 70.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 2.1%.</t>
+          <t>AAPL: scenario base Accumulate Carefully, score 71.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -3.4%.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 64.85 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 62.06 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 253.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4724,146 +4702,168 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>62.06</v>
+        <v>253.2667</v>
       </c>
       <c r="T20" t="n">
-        <v>64.84999999999999</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
+        <v>315.2</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Monitorare ingresso graduale</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>2.29</v>
+        <v>13.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.96</v>
+        <v>40.73</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.56</v>
+        <v>26.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+        <v>-33.36</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>29.32</v>
+      </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>Min volatility</t>
-        </is>
-      </c>
+          <t>Da monitorare con scenario positivo, base e negativo.</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="n">
-        <v>64.84999999999999</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>82.8</v>
-      </c>
+        <v>281.74</v>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>1.84</v>
+        <v>-9.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>3.81</v>
+        <v>3.09</v>
       </c>
       <c r="AN20" t="n">
-        <v>7.67</v>
+        <v>13.87</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="AP20" t="n">
-        <v>63.5298</v>
+        <v>291.7833</v>
       </c>
       <c r="AQ20" t="n">
-        <v>63.1763</v>
+        <v>269.3535</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AT20" t="n">
-        <v>56.5</v>
+        <v>80.7</v>
       </c>
       <c r="AU20" t="n">
-        <v>78.2</v>
+        <v>41.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>82.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AW20" t="n">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="AX20" t="n">
-        <v>63.44</v>
+        <v>275.15</v>
       </c>
       <c r="AY20" t="n">
-        <v>64.84999999999999</v>
+        <v>315.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.08</v>
+        <v>-3.44</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="inlineStr"/>
-      <c r="BF20" t="inlineStr"/>
-      <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
-      <c r="BI20" t="inlineStr"/>
-      <c r="BJ20" t="inlineStr"/>
-      <c r="BK20" t="inlineStr"/>
-      <c r="BL20" t="inlineStr"/>
-      <c r="BM20" t="inlineStr"/>
-      <c r="BN20" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>4138015391744</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>74.59999999999999</v>
+      </c>
       <c r="BO20" t="inlineStr"/>
-      <c r="BP20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4. Alert / monitoraggio</t>
+          <t>2. Rischio da controllare</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4872,24 +4872,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>71.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>69.3</v>
+        <v>51.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🟡 Metti alert / monitora</t>
+          <t>🟥 Solo size piccola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Imposta alert prezzo/news. Resistenza 60D: 315.2. Trigger: prezzo vicino a MA50: monitorare conferma.</t>
+          <t>Tieni in osservazione senza azione immediata; rivaluta dopo aggiornamento dati o news rilevanti.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>score 71.3; priority 69.3; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 70.9; priority 51.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4899,27 +4899,27 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Medium-high risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 7.1% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>AAPL: scenario base Accumulate Carefully, score 71.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.6%.</t>
+          <t>NVDA: scenario base Accumulate Carefully, score 70.9, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -7.1%.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 315.20 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 235.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 253.27 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 177.18 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4938,14 +4938,14 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>253.2667</v>
+        <v>177.1835</v>
       </c>
       <c r="T21" t="n">
-        <v>315.2</v>
+        <v>235.4656</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -4956,81 +4956,81 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>12.32</v>
+        <v>16.52</v>
       </c>
       <c r="Z21" t="n">
-        <v>41.35</v>
+        <v>25.94</v>
       </c>
       <c r="AA21" t="n">
-        <v>26.28</v>
+        <v>46.93</v>
       </c>
       <c r="AB21" t="n">
-        <v>-33.36</v>
+        <v>-36.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>34.4</v>
+        <v>29.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>29.53</v>
+        <v>15.27</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Da monitorare con scenario positivo, base e negativo.</t>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
-        <v>283.78</v>
+        <v>194.97</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-8.710000000000001</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="AM21" t="n">
-        <v>4.39</v>
+        <v>3.5</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.3</v>
+        <v>67.09</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.58</v>
+        <v>1.43</v>
       </c>
       <c r="AP21" t="n">
-        <v>291.4116</v>
+        <v>209.8549</v>
       </c>
       <c r="AQ21" t="n">
-        <v>269.0755</v>
+        <v>190.5174</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
         <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>80.2</v>
+        <v>81.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>41.8</v>
+        <v>14.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>75.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AW21" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AX21" t="n">
-        <v>275.15</v>
+        <v>192.53</v>
       </c>
       <c r="AY21" t="n">
-        <v>315.2</v>
+        <v>224.0988</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-2.62</v>
+        <v>-7.09</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.46</v>
+        <v>2.34</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -5039,46 +5039,46 @@
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4167977926656</v>
+        <v>4722368446464</v>
       </c>
       <c r="BE21" t="n">
-        <v>27.15</v>
+        <v>62.97</v>
       </c>
       <c r="BF21" t="n">
-        <v>141.47</v>
+        <v>114.29</v>
       </c>
       <c r="BG21" t="n">
-        <v>16.6</v>
+        <v>85.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>79.55</v>
+        <v>6.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="BJ21" t="n">
         <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>80.2</v>
+        <v>81.7</v>
       </c>
       <c r="BL21" t="n">
-        <v>46.1</v>
+        <v>71.7</v>
       </c>
       <c r="BM21" t="n">
-        <v>41.8</v>
+        <v>14.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>75.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>USA / Technology</t>
+          <t>USA / Semiconductors</t>
         </is>
       </c>
     </row>
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>55.2</v>
+        <v>52.6</v>
       </c>
       <c r="F22" t="n">
-        <v>56.9</v>
+        <v>54</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>score 55.2; priority 56.9; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
+          <t>score 52.6; priority 54.0; trend: Weak; entry zone: Wait for trend repair; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>prezzo 7.1% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 8.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SGLD.MI: scenario base Hold / Monitor, score 55.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.1%.</t>
+          <t>SGLD.MI: scenario base Avoid for Now, score 52.6, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.3%.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 339.65 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 338.68 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>339.65</v>
+        <v>338.68</v>
       </c>
       <c r="T22" t="n">
         <v>396.71</v>
@@ -5184,20 +5184,20 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Osservare</t>
+          <t>Evitare per ora</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>-6.06</v>
+        <v>-10.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>25.33</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>18.18</v>
+        <v>18.22</v>
       </c>
       <c r="AB22" t="n">
-        <v>-22.17</v>
+        <v>-22.39</v>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
@@ -5212,65 +5212,65 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>344.28</v>
+        <v>338.68</v>
       </c>
       <c r="AH22" t="n">
-        <v>66.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>45.7</v>
+        <v>37.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>60.4</v>
+        <v>60.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>64.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="AL22" t="n">
-        <v>-6.94</v>
+        <v>-10.21</v>
       </c>
       <c r="AM22" t="n">
-        <v>-3.59</v>
+        <v>-6.78</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.3</v>
+        <v>25.96</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AP22" t="n">
-        <v>370.4684</v>
+        <v>369.3078</v>
       </c>
       <c r="AQ22" t="n">
-        <v>366.4099</v>
+        <v>366.6128</v>
       </c>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
         <v>35</v>
       </c>
       <c r="AT22" t="n">
-        <v>45.7</v>
+        <v>37.3</v>
       </c>
       <c r="AU22" t="n">
-        <v>60.4</v>
+        <v>60.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>64.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AX22" t="n">
-        <v>339.65</v>
+        <v>338.68</v>
       </c>
       <c r="AY22" t="n">
         <v>372.59</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-7.07</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="BA22" t="n">
-        <v>-6.04</v>
+        <v>-7.62</v>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>

--- a/AlphaForge_Action_Plan.xlsx
+++ b/AlphaForge_Action_Plan.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>64.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>score 67.1; priority 66.0; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
+          <t>score 66.3; priority 64.8; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>prezzo 6.2% sotto MA50: attendere recupero</t>
+          <t>prezzo 6.8% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AMZN: scenario base Hold / Monitor, score 67.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.2%.</t>
+          <t>AMZN: scenario base Hold / Monitor, score 66.3, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.8%.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 209.77 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 212.79 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>209.77</v>
+        <v>212.79</v>
       </c>
       <c r="T2" t="n">
         <v>274.99</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>20.47</v>
+        <v>18.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.6</v>
+        <v>6.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.28</v>
+        <v>31.29</v>
       </c>
       <c r="AB2" t="n">
         <v>-30.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>32.67</v>
+        <v>31.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.3</v>
+        <v>24.12</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -888,42 +888,42 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>240.14</v>
+        <v>238.34</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-12.36</v>
+        <v>-11.93</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.75</v>
+        <v>22.49</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="AP2" t="n">
-        <v>255.9376</v>
+        <v>255.6932</v>
       </c>
       <c r="AQ2" t="n">
-        <v>232.8167</v>
+        <v>232.8586</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
         <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>83.3</v>
+        <v>79.2</v>
       </c>
       <c r="AU2" t="n">
         <v>37.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AW2" t="n">
         <v>751</v>
@@ -932,13 +932,13 @@
         <v>227.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>261.26</v>
+        <v>256.52</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-6.17</v>
+        <v>-6.79</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2583212326912</v>
+        <v>2563849584640</v>
       </c>
       <c r="BE2" t="n">
         <v>12.22</v>
@@ -970,16 +970,16 @@
         <v>78.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>83.3</v>
+        <v>79.2</v>
       </c>
       <c r="BL2" t="n">
-        <v>55.5</v>
+        <v>57.3</v>
       </c>
       <c r="BM2" t="n">
         <v>37.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
@@ -996,24 +996,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>62.2</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>54.6</v>
+        <v>63.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1027,12 +1023,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>score 62.2; priority 54.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
+          <t>score 69.0; priority 63.3; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1042,22 +1038,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>prezzo 10.0% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo 9.8% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MSFT: scenario base Hold / Monitor, score 62.2, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -10.0%.</t>
+          <t>RBOT.MI: scenario base Accumulate Carefully, score 69.0, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 9.8%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 19.16 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
+          <t>Scenario negativo: perdita area 13.44 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1067,158 +1063,136 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>352.83</v>
+        <v>13.44</v>
       </c>
       <c r="T3" t="n">
-        <v>460.52</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>19.164</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>3.53</v>
+        <v>47.51</v>
       </c>
       <c r="Z3" t="n">
-        <v>-25.32</v>
+        <v>50.16</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.4</v>
+        <v>21.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>-34.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>19.03</v>
-      </c>
+        <v>-29.37</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Robotica e automazione</t>
+        </is>
+      </c>
       <c r="AG3" t="n">
-        <v>368.57</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+        <v>19.158</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>59.4</v>
+      </c>
       <c r="AL3" t="n">
-        <v>-13.68</v>
+        <v>6.28</v>
       </c>
       <c r="AM3" t="n">
-        <v>-24.14</v>
+        <v>38.54</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.5</v>
+        <v>20.48</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>409.5063</v>
+        <v>17.4402</v>
       </c>
       <c r="AQ3" t="n">
-        <v>445.629</v>
+        <v>14.8699</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AT3" t="n">
-        <v>34.1</v>
+        <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>43.1</v>
+        <v>50.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>60.3</v>
+        <v>59.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AX3" t="n">
-        <v>352.83</v>
+        <v>17.092</v>
       </c>
       <c r="AY3" t="n">
-        <v>460.52</v>
+        <v>19.164</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-10</v>
+        <v>9.85</v>
       </c>
       <c r="BA3" t="n">
-        <v>-17.29</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>Software - Infrastructure</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>2737898258432</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>98</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>60.3</v>
-      </c>
+        <v>28.84</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>USA / Technology</t>
-        </is>
-      </c>
+      <c r="BP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1228,20 +1202,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>57.1</v>
+        <v>62.7</v>
       </c>
       <c r="F4" t="n">
-        <v>50.6</v>
+        <v>55.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1255,37 +1233,37 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>score 57.1; priority 50.6; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 62.7; priority 55.6; trend: Weak; entry zone: Wait for trend repair; risk flag: Medium-high risk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-high risk</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>prezzo 6.1% sotto MA50: attendere recupero</t>
+          <t>prezzo 8.7% sotto MA50: attendere recupero</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>INRG.MI: scenario base Hold / Monitor, score 57.1, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -6.1%.</t>
+          <t>MSFT: scenario base Hold / Monitor, score 62.7, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -8.7%.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 460.52 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 352.83 o peggioramento trend; rischio attuale: Medium-high risk.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1300,131 +1278,153 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Constructive</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8.7643</v>
+        <v>352.83</v>
       </c>
       <c r="T4" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>460.52</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>10.1</v>
+        <v>4.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>55.77</v>
+        <v>-24.18</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.59</v>
+        <v>24.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>-43.36</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+        <v>-34.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>19.26</v>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Energia pulita</t>
-        </is>
-      </c>
+          <t>Trend debole: meglio aspettare stabilizzazione tecnica.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>9.863</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>70.7</v>
-      </c>
+        <v>373.02</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-14.61</v>
+        <v>-17.15</v>
       </c>
       <c r="AM4" t="n">
-        <v>21.4</v>
+        <v>-23.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.46</v>
+        <v>4.18</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.4994</v>
+        <v>408.5292</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.9855</v>
+        <v>445.0048</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AT4" t="n">
-        <v>90.90000000000001</v>
+        <v>35.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>37</v>
+        <v>43.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>70.7</v>
+        <v>62.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.863</v>
+        <v>352.83</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.61</v>
+        <v>441.31</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-6.06</v>
+        <v>-8.69</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+        <v>-16.18</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>2770954616832</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>99</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>62.2</v>
+      </c>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>USA / Technology</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1434,24 +1434,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>64.09999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="F5" t="n">
-        <v>43.8</v>
+        <v>54.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1465,12 +1461,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>score 64.1; priority 43.8; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
+          <t>score 60.4; priority 54.8; trend: Constructive; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Wait for trend repair</t>
+          <t>Monitor / partial entry only</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1480,22 +1476,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>prezzo 7.8% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
+          <t>prezzo vicino a MA50: monitorare conferma</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>META: scenario base Hold / Monitor, score 64.1, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.8%.</t>
+          <t>INRG.MI: scenario base Hold / Monitor, score 60.4, trend Constructive. Entry zone: Monitor / partial entry only. Distanza da MA50: -2.2%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 11.61 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 8.76 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1510,153 +1506,131 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Constructive</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>542.87</v>
+        <v>8.7643</v>
       </c>
       <c r="T5" t="n">
-        <v>687.9124</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>11.61</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>7.11</v>
+        <v>16.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>-22.26</v>
+        <v>60.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>36.47</v>
+        <v>23.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>-34.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15.52</v>
-      </c>
+        <v>-43.36</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Energia pulita</t>
+        </is>
+      </c>
       <c r="AG5" t="n">
-        <v>562.6</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+        <v>10.282</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>76.40000000000001</v>
+      </c>
       <c r="AL5" t="n">
-        <v>-11.36</v>
+        <v>-9.35</v>
       </c>
       <c r="AM5" t="n">
-        <v>-15.57</v>
+        <v>27.96</v>
       </c>
       <c r="AN5" t="n">
-        <v>25.71</v>
+        <v>3.39</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.71</v>
+        <v>0.14</v>
       </c>
       <c r="AP5" t="n">
-        <v>610.1527</v>
+        <v>10.5145</v>
       </c>
       <c r="AQ5" t="n">
-        <v>647.9298</v>
+        <v>9.001799999999999</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
-        <v>45.1</v>
+        <v>100</v>
       </c>
       <c r="AU5" t="n">
-        <v>28.9</v>
+        <v>36.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>63.6</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AX5" t="n">
-        <v>542.87</v>
+        <v>9.863</v>
       </c>
       <c r="AY5" t="n">
-        <v>626.9888999999999</v>
+        <v>11.494</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-7.79</v>
+        <v>-2.21</v>
       </c>
       <c r="BA5" t="n">
-        <v>-13.17</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>Internet Content &amp; Information</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>1428116865024</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>63.6</v>
-      </c>
+        <v>14.22</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>USA / Social &amp; AI</t>
-        </is>
-      </c>
+      <c r="BP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1666,17 +1640,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>65.2</v>
+        <v>63.5</v>
       </c>
       <c r="F6" t="n">
         <v>43.4</v>
@@ -1693,12 +1671,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>score 65.2; priority 43.4; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 63.5; priority 43.4; trend: Weak; entry zone: Wait for trend repair; risk flag: High risk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monitor / partial entry only</t>
+          <t>Wait for trend repair</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1708,22 +1686,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>prezzo 10.9% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 7.3% sotto MA50: attendere recupero; vicino a supporto 60D: controllare tenuta e volumi</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SMH: scenario base Hold / Monitor, score 65.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 10.9%.</t>
+          <t>META: scenario base Hold / Monitor, score 63.5, trend Weak. Entry zone: Wait for trend repair. Distanza da MA50: -7.3%.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 687.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 392.32 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 542.87 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1738,131 +1716,153 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>392.32</v>
+        <v>542.87</v>
       </c>
       <c r="T6" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>VanEck Semiconductor ETF</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>687.9124</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>68.87</v>
+        <v>5.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>128.7</v>
+        <v>-22.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>35.81</v>
+        <v>36.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>-35.74</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+        <v>-34.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15.54</v>
+      </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Semiconduttori</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>631.98</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>55.2</v>
-      </c>
+        <v>563.29</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>5.36</v>
+        <v>-10.86</v>
       </c>
       <c r="AM6" t="n">
-        <v>73.54000000000001</v>
+        <v>-14.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>61.95</v>
+        <v>25.9</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.73</v>
+        <v>0.71</v>
       </c>
       <c r="AP6" t="n">
-        <v>569.9876</v>
+        <v>607.6603</v>
       </c>
       <c r="AQ6" t="n">
-        <v>420.9587</v>
+        <v>647.0041</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AT6" t="n">
-        <v>100</v>
+        <v>42.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>28.4</v>
+        <v>28.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>55.2</v>
+        <v>64.3</v>
       </c>
       <c r="AW6" t="n">
         <v>751</v>
       </c>
       <c r="AX6" t="n">
-        <v>569.6900000000001</v>
+        <v>542.87</v>
       </c>
       <c r="AY6" t="n">
-        <v>668.91</v>
+        <v>626.9888999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10.88</v>
+        <v>-7.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+        <v>-12.94</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>1429868380160</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>37</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>64.3</v>
+      </c>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>USA / Social &amp; AI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1872,20 +1872,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WCLD.MI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>49.2</v>
+        <v>47.7</v>
       </c>
       <c r="F7" t="n">
-        <v>39.6</v>
+        <v>41.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1899,7 +1903,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>score 49.2; priority 39.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 47.7; priority 41.6; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1914,22 +1918,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo vicino a MA50: monitorare conferma; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>WCLD.MI: scenario base High Risk, score 49.2, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 7.7%.</t>
+          <t>TSLA: scenario base High Risk, score 47.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 3.7%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1948,127 +1952,147 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>20.205</v>
+        <v>343.25</v>
       </c>
       <c r="T7" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Thematic</t>
-        </is>
-      </c>
+        <v>445.27</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>20.54</v>
+        <v>18.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>-9.470000000000001</v>
+        <v>29.96</v>
       </c>
       <c r="AA7" t="n">
-        <v>34.2</v>
+        <v>57.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>-48.6</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+        <v>-53.77</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>168.1</v>
+      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Cloud</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>27.145</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>68.09999999999999</v>
-      </c>
+        <v>420.6</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.49</v>
       </c>
       <c r="AM7" t="n">
-        <v>-10.03</v>
+        <v>-11.49</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1.69</v>
+        <v>14.65</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.05</v>
+        <v>0.25</v>
       </c>
       <c r="AP7" t="n">
-        <v>25.214</v>
+        <v>405.6234</v>
       </c>
       <c r="AQ7" t="n">
-        <v>26.7012</v>
+        <v>418.5439</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
         <v>85</v>
       </c>
       <c r="AT7" t="n">
-        <v>70.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>68.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="AX7" t="n">
-        <v>24.785</v>
+        <v>375.12</v>
       </c>
       <c r="AY7" t="n">
-        <v>29.005</v>
+        <v>423.74</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.66</v>
+        <v>3.69</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+        <v>0.49</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1579657461760</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>18.74</v>
+      </c>
       <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
+      <c r="BJ7" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>82.8</v>
+      </c>
       <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>USA / EV</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2078,24 +2102,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>43.4</v>
+        <v>48.7</v>
       </c>
       <c r="F8" t="n">
-        <v>37.1</v>
+        <v>38.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2109,7 +2129,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>score 43.4; priority 37.1; trend: Recovery; entry zone: Monitor / partial entry only; risk flag: High risk</t>
+          <t>score 48.7; priority 38.3; trend: Bullish; entry zone: Monitor / partial entry only; risk flag: High risk</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2129,17 +2149,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TSLA: scenario base High Risk, score 43.4, trend Recovery. Entry zone: Monitor / partial entry only. Distanza da MA50: 1.6%.</t>
+          <t>WCLD.MI: scenario base High Risk, score 48.7, trend Bullish. Entry zone: Monitor / partial entry only. Distanza da MA50: 8.0%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 445.27 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 30.11 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 343.25 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 20.20 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2154,151 +2174,131 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>343.25</v>
+        <v>20.205</v>
       </c>
       <c r="T8" t="n">
-        <v>445.27</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+        <v>30.11</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>13.82</v>
+        <v>18.47</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.42</v>
+        <v>-9.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>58</v>
+        <v>34.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>-53.77</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>374.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>164.6</v>
-      </c>
+        <v>-48.6</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
       <c r="AG8" t="n">
-        <v>411.84</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+        <v>27.32</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>66.90000000000001</v>
+      </c>
       <c r="AL8" t="n">
-        <v>-6.84</v>
+        <v>-9.27</v>
       </c>
       <c r="AM8" t="n">
-        <v>-15.15</v>
+        <v>-7.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>16.42</v>
+        <v>-1.59</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.28</v>
+        <v>-0.05</v>
       </c>
       <c r="AP8" t="n">
-        <v>405.2238</v>
+        <v>25.303</v>
       </c>
       <c r="AQ8" t="n">
-        <v>418.285</v>
+        <v>26.6877</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AT8" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AV8" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>78.2</v>
-      </c>
       <c r="AW8" t="n">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="AX8" t="n">
-        <v>375.12</v>
+        <v>24.785</v>
       </c>
       <c r="AY8" t="n">
-        <v>423.74</v>
+        <v>28.58</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.63</v>
+        <v>7.97</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>1546757210112</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>18.74</v>
-      </c>
+        <v>2.37</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>78.2</v>
-      </c>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>USA / EV</t>
-        </is>
-      </c>
+      <c r="BP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2308,24 +2308,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>63.1</v>
+        <v>63.3</v>
       </c>
       <c r="F9" t="n">
-        <v>30.3</v>
+        <v>33</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2339,7 +2335,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>score 63.1; priority 30.3; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
+          <t>score 63.3; priority 33.0; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2354,22 +2350,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>prezzo 14.7% sopra MA50: evitare inseguimento</t>
+          <t>prezzo 14.3% sopra MA50: evitare inseguimento</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ASML.AS: scenario base Hold / Monitor, score 63.1, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.7%.</t>
+          <t>SMH: scenario base Hold / Monitor, score 63.3, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 14.3%.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 1676.00 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 668.91 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
+          <t>Scenario negativo: perdita area 395.98 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2388,71 +2384,83 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>1111.3427</v>
+        <v>395.98</v>
       </c>
       <c r="T9" t="n">
-        <v>1676</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>ASML Holding N.V.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+        <v>668.91</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>40.93</v>
+        <v>80.92</v>
       </c>
       <c r="Z9" t="n">
-        <v>139.8</v>
+        <v>136.31</v>
       </c>
       <c r="AA9" t="n">
-        <v>38.44</v>
+        <v>35.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>-44.77</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>38</v>
-      </c>
+        <v>-35.74</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
       <c r="AG9" t="n">
-        <v>1612</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+        <v>655.89</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>41.5</v>
+      </c>
       <c r="AL9" t="n">
-        <v>16.41</v>
+        <v>9.51</v>
       </c>
       <c r="AM9" t="n">
-        <v>78.40000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>34.8</v>
+        <v>63.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.91</v>
+        <v>1.77</v>
       </c>
       <c r="AP9" t="n">
-        <v>1405.4973</v>
+        <v>573.8222</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1118.7963</v>
+        <v>422.7232</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
@@ -2462,142 +2470,112 @@
         <v>100</v>
       </c>
       <c r="AU9" t="n">
-        <v>18.1</v>
+        <v>28.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>40</v>
+        <v>41.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="AX9" t="n">
-        <v>1461.8</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>1676</v>
+        <v>668.91</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.69</v>
+        <v>14.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>44.08</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>621293273088</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>52.24</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>68</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>100</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>40</v>
-      </c>
+        <v>55.16</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>Europe / Semiconductors</t>
-        </is>
-      </c>
+      <c r="BP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. Da guardare oggi</t>
+          <t>2. Rischio da controllare</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>80.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="F10" t="n">
-        <v>81.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🟢 Valuta ingresso graduale</t>
+          <t>🟥 Riduci rischio / non aumentare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Non entrare a mercato alla cieca: valuta ingresso graduale, size piccola e conferma su trend/supporti.</t>
+          <t>Non aumentare esposizione: controlla peso in portafoglio, stop mentale e correlazione con posizioni simili.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>score 80.6; priority 81.7; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 59.8; priority 9.3; trend: Bullish; entry zone: Extended - wait pullback; risk flag: High risk</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Constructive entry zone</t>
+          <t>Extended - wait pullback</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal risk</t>
+          <t>High risk</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>prezzo vicino a MA50: monitorare conferma</t>
+          <t>prezzo 21.6% sopra MA50: evitare inseguimento; vicino a resistenza 20D: attenzione a falso breakout</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>EIMI.MI: scenario base Buy Watchlist, score 80.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 1.9%.</t>
+          <t>ASML.AS: scenario base Hold / Monitor, score 59.8, trend Bullish. Entry zone: Extended - wait pullback. Distanza da MA50: 21.6%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 1721.40 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 39.95 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 1111.34 o peggioramento trend; rischio attuale: High risk.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2607,7 +2585,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2616,83 +2594,71 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>39.955</v>
+        <v>1111.3427</v>
       </c>
       <c r="T10" t="n">
-        <v>50.73</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+        <v>1721.4</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Priorità watchlist</t>
+          <t>Ridurre size / solo monitoraggio</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>21.32</v>
+        <v>55.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>42.02</v>
+        <v>156.26</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.46</v>
+        <v>38.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>-19.17</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+        <v>-44.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>39.99</v>
+      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Mercati emergenti</t>
-        </is>
-      </c>
+          <t>Rischio elevato: volatilità/drawdown richiedono prudenza.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>47.74</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>82.8</v>
-      </c>
+        <v>1721.4</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>-0.5</v>
+        <v>23.49</v>
       </c>
       <c r="AM10" t="n">
-        <v>26.26</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.03</v>
+        <v>38.11</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.22</v>
+        <v>0.99</v>
       </c>
       <c r="AP10" t="n">
-        <v>46.8593</v>
+        <v>1415.0803</v>
       </c>
       <c r="AQ10" t="n">
-        <v>41.3092</v>
+        <v>1123.7757</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
@@ -2702,41 +2668,75 @@
         <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>64.90000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>82.8</v>
+        <v>12.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="AX10" t="n">
-        <v>45.945</v>
+        <v>1462.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>50.73</v>
+        <v>1721.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.88</v>
+        <v>21.65</v>
       </c>
       <c r="BA10" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
+        <v>53.18</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment &amp; Materials</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>663457955840</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>67</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>12.2</v>
+      </c>
       <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>Europe / Semiconductors</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>82.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="F11" t="n">
-        <v>81.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>score 82.6; priority 81.4; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
+          <t>score 80.8; priority 81.8; trend: Bullish; entry zone: Constructive entry zone; risk flag: Normal risk</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>XDEV.MI: scenario base Buy Watchlist, score 82.6, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 5.8%.</t>
+          <t>EIMI.MI: scenario base Buy Watchlist, score 80.8, trend Bullish. Entry zone: Constructive entry zone. Distanza da MA50: 4.0%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Scenario positivo: conferma sopra area 73.47 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
+          <t>Scenario positivo: conferma sopra area 50.73 con momentum stabile; valutare solo se rischio e size restano coerenti.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Scenario negativo: perdita area 56.24 o peggioramento trend; rischio attuale: Normal risk.</t>
+          <t>Scenario negativo: perdita area 39.95 o peggioramento trend; rischio attuale: Normal risk.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2822,20 +2822,20 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>56.24</v>
+        <v>39.955</v>
       </c>
       <c r="T11" t="n">
-        <v>73.47</v>
+        <v>50.73</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2844,16 +2844,16 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>29.64</v>
+        <v>23.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>63.95</v>
+        <v>45.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.93</v>
+        <v>16.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>-17.8</v>
+        <v>-19.17</v>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
@@ -2864,41 +2864,41 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Value globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>71.39</v>
+        <v>48.825</v>
       </c>
       <c r="AH11" t="n">
-        <v>78.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AI11" t="n">
         <v>100</v>
       </c>
       <c r="AJ11" t="n">
-        <v>69</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>75.7</v>
+        <v>82.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.61</v>
+        <v>-0.27</v>
       </c>
       <c r="AM11" t="n">
-        <v>36.42</v>
+        <v>29.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.3</v>
+        <v>20.68</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="AP11" t="n">
-        <v>67.505</v>
+        <v>46.9587</v>
       </c>
       <c r="AQ11" t="n">
-        <v>56.6218</v>
+        <v>41.3751</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
@@ -2908,25 +2908,25 @@
         <v>100</v>
       </c>
       <c r="AU11" t="n">
-        <v>69</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>75.7</v>
+        <v>82.8</v>
       </c>
       <c r="AW11" t="n">
         <v>756</v>
       </c>
       <c r="AX11" t="n">
-        <v>68.89</v>
+        <v>45.945</v>